--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,25 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B2" t="n">
-        <v>346.6169306487971</v>
+        <v>342.1494091330253</v>
       </c>
       <c r="C2" t="n">
-        <v>352.8597399573416</v>
+        <v>342.5877196861389</v>
       </c>
       <c r="D2" t="n">
-        <v>343.2666549867767</v>
+        <v>333.6458276900651</v>
       </c>
       <c r="E2" t="n">
-        <v>343.3153686523438</v>
+        <v>338.8668212890625</v>
       </c>
       <c r="F2" t="n">
-        <v>14016200</v>
+        <v>11035900</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>344.2562617205344</v>
+        <v>338.4869315014284</v>
       </c>
       <c r="C3" t="n">
-        <v>344.6972712574788</v>
+        <v>339.9869970175624</v>
       </c>
       <c r="D3" t="n">
-        <v>335.7003177947291</v>
+        <v>329.5450392653686</v>
       </c>
       <c r="E3" t="n">
-        <v>340.9534606933594</v>
+        <v>330.9671630859375</v>
       </c>
       <c r="F3" t="n">
-        <v>11035900</v>
+        <v>12695800</v>
       </c>
       <c r="G3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>340.5711991051483</v>
+        <v>328.9313839638723</v>
       </c>
       <c r="C4" t="n">
-        <v>342.0805014268064</v>
+        <v>334.1036568566598</v>
       </c>
       <c r="D4" t="n">
-        <v>331.5742462609258</v>
+        <v>328.9313839638723</v>
       </c>
       <c r="E4" t="n">
-        <v>333.005126953125</v>
+        <v>332.7496948242188</v>
       </c>
       <c r="F4" t="n">
-        <v>12695800</v>
+        <v>8467700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>330.9568525731296</v>
+        <v>334.6199155242764</v>
       </c>
       <c r="C5" t="n">
-        <v>336.1609748937723</v>
+        <v>335.9835980004524</v>
       </c>
       <c r="D5" t="n">
-        <v>330.9568525731296</v>
+        <v>325.4539776391221</v>
       </c>
       <c r="E5" t="n">
-        <v>334.7986755371094</v>
+        <v>326.1358337402344</v>
       </c>
       <c r="F5" t="n">
-        <v>8467700</v>
+        <v>11255600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>336.6803662104043</v>
+        <v>327.7722315420273</v>
       </c>
       <c r="C6" t="n">
-        <v>338.0524456778033</v>
+        <v>332.116544623422</v>
       </c>
       <c r="D6" t="n">
-        <v>327.4579882805058</v>
+        <v>325.1812201416126</v>
       </c>
       <c r="E6" t="n">
-        <v>328.14404296875</v>
+        <v>327.9573059082031</v>
       </c>
       <c r="F6" t="n">
-        <v>11255600</v>
+        <v>13656800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>329.7905316198508</v>
+        <v>325.7851652728215</v>
       </c>
       <c r="C7" t="n">
-        <v>334.161595373165</v>
+        <v>333.5971710589619</v>
       </c>
       <c r="D7" t="n">
-        <v>327.1835657302883</v>
+        <v>323.9734220131043</v>
       </c>
       <c r="E7" t="n">
-        <v>329.9767456054688</v>
+        <v>332.44775390625</v>
       </c>
       <c r="F7" t="n">
-        <v>13656800</v>
+        <v>8903700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>327.7911982671105</v>
+        <v>332.1555425710952</v>
       </c>
       <c r="C8" t="n">
-        <v>335.6513067387905</v>
+        <v>343.5520936054497</v>
       </c>
       <c r="D8" t="n">
-        <v>325.9682991379935</v>
+        <v>331.1425085461183</v>
       </c>
       <c r="E8" t="n">
-        <v>334.4948120117188</v>
+        <v>338.6720275878906</v>
       </c>
       <c r="F8" t="n">
-        <v>8903700</v>
+        <v>12504100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>334.2008052062361</v>
+        <v>341.1169227630601</v>
       </c>
       <c r="C9" t="n">
-        <v>345.6675310141911</v>
+        <v>345.3053823653661</v>
       </c>
       <c r="D9" t="n">
-        <v>333.1815333788629</v>
+        <v>338.8181183002055</v>
       </c>
       <c r="E9" t="n">
-        <v>340.7574157714844</v>
+        <v>342.6851501464844</v>
       </c>
       <c r="F9" t="n">
-        <v>12504100</v>
+        <v>9016300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>343.2174040946968</v>
+        <v>339.850626873286</v>
       </c>
       <c r="C10" t="n">
-        <v>347.4316547985749</v>
+        <v>341.107176659279</v>
       </c>
       <c r="D10" t="n">
-        <v>340.904444380264</v>
+        <v>334.6881040719941</v>
       </c>
       <c r="E10" t="n">
-        <v>344.7952880859375</v>
+        <v>336.5972595214844</v>
       </c>
       <c r="F10" t="n">
-        <v>9016300</v>
+        <v>8104900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>341.9432916493518</v>
+        <v>338.9057579077058</v>
       </c>
       <c r="C11" t="n">
-        <v>343.2075787683629</v>
+        <v>340.8928549002298</v>
       </c>
       <c r="D11" t="n">
-        <v>336.7489800892123</v>
+        <v>332.4477149765372</v>
       </c>
       <c r="E11" t="n">
-        <v>338.6698913574219</v>
+        <v>335.1556091308594</v>
       </c>
       <c r="F11" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>340.9926010114185</v>
+        <v>335.0582538691371</v>
       </c>
       <c r="C12" t="n">
-        <v>342.9919337348455</v>
+        <v>336.5875104266321</v>
       </c>
       <c r="D12" t="n">
-        <v>334.4947920920956</v>
+        <v>332.5938752825687</v>
       </c>
       <c r="E12" t="n">
-        <v>337.2193603515625</v>
+        <v>336.2271118164062</v>
       </c>
       <c r="F12" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>337.1213995584671</v>
+        <v>334.8342081470359</v>
       </c>
       <c r="C13" t="n">
-        <v>338.6600726249961</v>
+        <v>340.2597470322082</v>
       </c>
       <c r="D13" t="n">
-        <v>334.6418463806178</v>
+        <v>333.4510253931927</v>
       </c>
       <c r="E13" t="n">
-        <v>338.2974548339844</v>
+        <v>336.343994140625</v>
       </c>
       <c r="F13" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>336.8959869118207</v>
+        <v>334.9803326465864</v>
       </c>
       <c r="C14" t="n">
-        <v>342.3549341542898</v>
+        <v>339.6558538996071</v>
       </c>
       <c r="D14" t="n">
-        <v>335.5042870567964</v>
+        <v>332.7692198568235</v>
       </c>
       <c r="E14" t="n">
-        <v>338.4150695800781</v>
+        <v>339.2662048339844</v>
       </c>
       <c r="F14" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>337.042992446128</v>
+        <v>338.2824047650262</v>
       </c>
       <c r="C15" t="n">
-        <v>341.7473034781017</v>
+        <v>345.87033541468</v>
       </c>
       <c r="D15" t="n">
-        <v>334.8182646079004</v>
+        <v>335.7108637419195</v>
       </c>
       <c r="E15" t="n">
-        <v>341.3552551269531</v>
+        <v>344.5456237792969</v>
       </c>
       <c r="F15" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>340.3654202552976</v>
+        <v>347.9840458817623</v>
       </c>
       <c r="C16" t="n">
-        <v>348.0000745206634</v>
+        <v>358.4552243092751</v>
       </c>
       <c r="D16" t="n">
-        <v>337.7780446522378</v>
+        <v>347.3606312231566</v>
       </c>
       <c r="E16" t="n">
-        <v>346.6672058105469</v>
+        <v>350.8575439453125</v>
       </c>
       <c r="F16" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>350.126813283771</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C17" t="n">
-        <v>360.6624696666976</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D17" t="n">
-        <v>349.4995598497266</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E17" t="n">
-        <v>353.0180053710938</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F17" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>353.8314330983794</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C18" t="n">
-        <v>355.2917144647868</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D18" t="n">
-        <v>349.9895806938981</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E18" t="n">
-        <v>351.6164855957031</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F18" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>352.2437372182849</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C19" t="n">
-        <v>357.4478588776738</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D19" t="n">
-        <v>350.9206488503359</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E19" t="n">
-        <v>356.4089965820312</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F19" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>359.613786634634</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C20" t="n">
-        <v>367.1602685308417</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D20" t="n">
-        <v>358.5063128850491</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E20" t="n">
-        <v>362.544189453125</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F20" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>365.0923241938757</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="C21" t="n">
-        <v>368.7185619691624</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="D21" t="n">
-        <v>358.7807287668154</v>
+        <v>343.3669828865441</v>
       </c>
       <c r="E21" t="n">
-        <v>360.358642578125</v>
+        <v>345.3053588867188</v>
       </c>
       <c r="F21" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>362.0345124206696</v>
+        <v>345.5391725764172</v>
       </c>
       <c r="C22" t="n">
-        <v>362.0345124206696</v>
+        <v>349.8445450312873</v>
       </c>
       <c r="D22" t="n">
-        <v>345.481298369123</v>
+        <v>344.1560194689148</v>
       </c>
       <c r="E22" t="n">
-        <v>347.4316101074219</v>
+        <v>349.3575134277344</v>
       </c>
       <c r="F22" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>347.6668450586018</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C23" t="n">
-        <v>351.9987280315978</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D23" t="n">
-        <v>346.2751751256885</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E23" t="n">
-        <v>351.5086975097656</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F23" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>347.8726721794402</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C24" t="n">
-        <v>355.1054974076654</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D24" t="n">
-        <v>346.3535596478916</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E24" t="n">
-        <v>352.7533569335938</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F24" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>352.224118197926</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C25" t="n">
-        <v>356.9577994132716</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D25" t="n">
-        <v>348.7546940700243</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E25" t="n">
-        <v>353.9490051269531</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F25" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>354.6252788942206</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C26" t="n">
-        <v>354.7820922478407</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D26" t="n">
-        <v>347.3336224508748</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E26" t="n">
-        <v>349.5583801269531</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F26" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>344.0014287463771</v>
+        <v>349.2406427804422</v>
       </c>
       <c r="C27" t="n">
-        <v>351.2440942663747</v>
+        <v>356.088306176199</v>
       </c>
       <c r="D27" t="n">
-        <v>343.8348052077826</v>
+        <v>348.2373588311709</v>
       </c>
       <c r="E27" t="n">
-        <v>349.4897766113281</v>
+        <v>355.0265808105469</v>
       </c>
       <c r="F27" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>351.3911117321571</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C28" t="n">
-        <v>358.2809400014152</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D28" t="n">
-        <v>350.3816500053927</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E28" t="n">
-        <v>357.2126770019531</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F28" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>357.8595050033854</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C29" t="n">
-        <v>363.6516394702736</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D29" t="n">
-        <v>354.2920684364863</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E29" t="n">
-        <v>358.0848999023438</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F29" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>356.7029783280342</v>
+        <v>346.3573316043178</v>
       </c>
       <c r="C30" t="n">
-        <v>356.7421891409456</v>
+        <v>352.8835660308217</v>
       </c>
       <c r="D30" t="n">
-        <v>350.8618233858751</v>
+        <v>344.4676766060103</v>
       </c>
       <c r="E30" t="n">
-        <v>354.2822265625</v>
+        <v>351.1010437011719</v>
       </c>
       <c r="F30" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>348.4900782801277</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C31" t="n">
-        <v>355.0564989637384</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D31" t="n">
-        <v>346.588787450705</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E31" t="n">
-        <v>353.2630004882812</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F31" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>354.1646514889598</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C32" t="n">
-        <v>358.1339166267961</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D32" t="n">
-        <v>352.8513732909411</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E32" t="n">
-        <v>355.2721252441406</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F32" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>356.2521771853968</v>
+        <v>370.8063128551364</v>
       </c>
       <c r="C33" t="n">
-        <v>358.9179443293374</v>
+        <v>371.118020163803</v>
       </c>
       <c r="D33" t="n">
-        <v>354.194043082288</v>
+        <v>349.3282346022162</v>
       </c>
       <c r="E33" t="n">
-        <v>358.6827392578125</v>
+        <v>358.2993469238281</v>
       </c>
       <c r="F33" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>373.0896257903608</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C34" t="n">
-        <v>373.4032524981995</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D34" t="n">
-        <v>351.4792920385495</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E34" t="n">
-        <v>360.5056457519531</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F34" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>357.0166226761716</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C35" t="n">
-        <v>358.8493319750526</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D35" t="n">
-        <v>346.8239941782638</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E35" t="n">
-        <v>348.1764831542969</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F35" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>340.5908266262187</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C36" t="n">
-        <v>347.4708747692525</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D36" t="n">
-        <v>336.7490038190758</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E36" t="n">
-        <v>337.8760681152344</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F36" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>337.5232231766179</v>
+        <v>330.3340313465691</v>
       </c>
       <c r="C37" t="n">
-        <v>339.3755229195461</v>
+        <v>331.8633175824834</v>
       </c>
       <c r="D37" t="n">
-        <v>330.398160543053</v>
+        <v>318.1290216159704</v>
       </c>
       <c r="E37" t="n">
-        <v>334.7496337890625</v>
+        <v>325.1325378417969</v>
       </c>
       <c r="F37" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>332.3681048776954</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C38" t="n">
-        <v>333.9068078868114</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D38" t="n">
-        <v>320.0879412577473</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E38" t="n">
-        <v>327.1345825195312</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F38" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>321.0974041522996</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C39" t="n">
-        <v>329.7905408141606</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D39" t="n">
-        <v>320.6759850821896</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E39" t="n">
-        <v>324.2335815429688</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F39" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>319.7939098851405</v>
+        <v>320.3888776178953</v>
       </c>
       <c r="C40" t="n">
-        <v>323.6259521945154</v>
+        <v>323.7493777886428</v>
       </c>
       <c r="D40" t="n">
-        <v>317.7553960532753</v>
+        <v>313.1126243976539</v>
       </c>
       <c r="E40" t="n">
-        <v>321.2052001953125</v>
+        <v>313.2197570800781</v>
       </c>
       <c r="F40" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>322.3616713627413</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C41" t="n">
-        <v>325.7428638052234</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D41" t="n">
-        <v>315.0406146307628</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E41" t="n">
-        <v>315.1484069824219</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F41" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>313.2863092733651</v>
+        <v>311.6904703912621</v>
       </c>
       <c r="C42" t="n">
-        <v>318.0787921089143</v>
+        <v>315.8399890894766</v>
       </c>
       <c r="D42" t="n">
-        <v>307.8959736628304</v>
+        <v>308.9436347895907</v>
       </c>
       <c r="E42" t="n">
-        <v>317.7455749511719</v>
+        <v>313.2392272949219</v>
       </c>
       <c r="F42" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>313.6097058862107</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C43" t="n">
-        <v>317.7847752647608</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D43" t="n">
-        <v>310.8459566317771</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E43" t="n">
-        <v>315.1679992675781</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F43" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>316.8537128676349</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C44" t="n">
-        <v>321.3227886847148</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D44" t="n">
-        <v>313.5019209593692</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E44" t="n">
-        <v>320.9209899902344</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F44" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>321.9010364932658</v>
+        <v>329.5742822700864</v>
       </c>
       <c r="C45" t="n">
-        <v>336.3275351202159</v>
+        <v>330.2366380969722</v>
       </c>
       <c r="D45" t="n">
-        <v>320.5583278451826</v>
+        <v>322.6973986104767</v>
       </c>
       <c r="E45" t="n">
-        <v>332.2994689941406</v>
+        <v>323.8954772949219</v>
       </c>
       <c r="F45" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>331.6036653013031</v>
+        <v>318.4699396678824</v>
       </c>
       <c r="C46" t="n">
-        <v>332.2700996432553</v>
+        <v>319.6972389495053</v>
       </c>
       <c r="D46" t="n">
-        <v>324.6844366173477</v>
+        <v>312.177470693811</v>
       </c>
       <c r="E46" t="n">
-        <v>325.889892578125</v>
+        <v>313.5119323730469</v>
       </c>
       <c r="F46" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>320.4309500487702</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C47" t="n">
-        <v>321.6658065479886</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D47" t="n">
-        <v>314.0997345701073</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E47" t="n">
-        <v>315.4424133300781</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F47" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>314.2075720220705</v>
+        <v>308.7877755793916</v>
       </c>
       <c r="C48" t="n">
-        <v>321.3424151200708</v>
+        <v>309.2650570211989</v>
       </c>
       <c r="D48" t="n">
-        <v>313.06088745762</v>
+        <v>300.761474830703</v>
       </c>
       <c r="E48" t="n">
-        <v>314.129150390625</v>
+        <v>305.4467163085938</v>
       </c>
       <c r="F48" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>310.6891466030926</v>
+        <v>305.7876123248052</v>
       </c>
       <c r="C49" t="n">
-        <v>311.1693669212913</v>
+        <v>306.8298669435948</v>
       </c>
       <c r="D49" t="n">
-        <v>302.6134236399317</v>
+        <v>296.6314254151897</v>
       </c>
       <c r="E49" t="n">
-        <v>307.3275146484375</v>
+        <v>301.0731506347656</v>
       </c>
       <c r="F49" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>307.6705238330165</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C50" t="n">
-        <v>308.7191962173961</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D50" t="n">
-        <v>298.4579569753306</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E50" t="n">
-        <v>302.9270324707031</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F50" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>304.6127612455315</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C51" t="n">
-        <v>308.4742040318584</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D51" t="n">
-        <v>303.8189142172394</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E51" t="n">
-        <v>305.3282165527344</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F51" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>305.6908589139109</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C52" t="n">
-        <v>317.3829805678444</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D52" t="n">
-        <v>305.2302290041278</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E52" t="n">
-        <v>313.5901489257812</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F52" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>318.0592531062754</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C53" t="n">
-        <v>319.352941040257</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D53" t="n">
-        <v>311.2870267728116</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E53" t="n">
-        <v>312.6885070800781</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F53" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>314.7171737995267</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C54" t="n">
-        <v>321.4599980564078</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D54" t="n">
-        <v>314.5015591898327</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E54" t="n">
-        <v>319.7742919921875</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F54" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>320.07813955632</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C55" t="n">
-        <v>328.5066706952173</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D55" t="n">
-        <v>319.3921147564304</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E55" t="n">
-        <v>323.1359252929688</v>
+        <v>321.216796875</v>
       </c>
       <c r="F55" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>325.0568726515205</v>
+        <v>318.6744960548122</v>
       </c>
       <c r="C56" t="n">
-        <v>325.4390809212725</v>
+        <v>321.4992731766471</v>
       </c>
       <c r="D56" t="n">
-        <v>322.3323040363653</v>
+        <v>314.6516105859225</v>
       </c>
       <c r="E56" t="n">
-        <v>323.1947326660156</v>
+        <v>314.8269348144531</v>
       </c>
       <c r="F56" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>320.6367557882569</v>
+        <v>314.9828304691314</v>
       </c>
       <c r="C57" t="n">
-        <v>323.4789266660114</v>
+        <v>320.1746042723855</v>
       </c>
       <c r="D57" t="n">
-        <v>316.5890991303779</v>
+        <v>314.4276072787253</v>
       </c>
       <c r="E57" t="n">
-        <v>316.7655029296875</v>
+        <v>316.1224975585938</v>
       </c>
       <c r="F57" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>316.9223461399793</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C58" t="n">
-        <v>322.1460884369951</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D58" t="n">
-        <v>316.3637041471038</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E58" t="n">
-        <v>318.0690307617188</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F58" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>319.4998951185618</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C59" t="n">
-        <v>334.6026391486864</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D59" t="n">
-        <v>318.529644271779</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E59" t="n">
-        <v>332.9365234375</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F59" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>332.632709971988</v>
+        <v>326.311185594663</v>
       </c>
       <c r="C60" t="n">
-        <v>334.4556390535126</v>
+        <v>327.0027621721813</v>
       </c>
       <c r="D60" t="n">
-        <v>322.1656652751352</v>
+        <v>319.9895246756281</v>
       </c>
       <c r="E60" t="n">
-        <v>326.8405456542969</v>
+        <v>322.3272705078125</v>
       </c>
       <c r="F60" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>328.3204578992349</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C61" t="n">
-        <v>329.0162928832224</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D61" t="n">
-        <v>321.9598711365138</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E61" t="n">
-        <v>324.31201171875</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F61" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>324.3120056919803</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C62" t="n">
-        <v>324.7066598386667</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D62" t="n">
-        <v>318.5203424234218</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E62" t="n">
-        <v>319.2998046875</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F62" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G62" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>318.8459617269979</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C63" t="n">
-        <v>322.0032250879344</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D63" t="n">
-        <v>318.1750466501944</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E63" t="n">
-        <v>319.2800903320312</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F63" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>318.4414486886093</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C64" t="n">
-        <v>324.341629514822</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D64" t="n">
-        <v>315.3335056374652</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E64" t="n">
-        <v>323.9864196777344</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F64" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>325.9596900029746</v>
+        <v>330.9566402470831</v>
       </c>
       <c r="C65" t="n">
-        <v>334.7211504310009</v>
+        <v>338.291630780554</v>
       </c>
       <c r="D65" t="n">
-        <v>324.3711973012736</v>
+        <v>330.8291558641754</v>
       </c>
       <c r="E65" t="n">
-        <v>332.2348022460938</v>
+        <v>335.2124938964844</v>
       </c>
       <c r="F65" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>332.9945516695081</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C66" t="n">
-        <v>340.3747084246943</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D66" t="n">
-        <v>332.8662822838281</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E66" t="n">
-        <v>337.276611328125</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F66" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>336.4379310634787</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C67" t="n">
-        <v>340.3549345980833</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D67" t="n">
-        <v>332.5012053593197</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E67" t="n">
-        <v>336.5464782714844</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F67" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>335.875584402924</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C68" t="n">
-        <v>336.4379523174861</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D68" t="n">
-        <v>326.6109215358994</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E68" t="n">
-        <v>329.7386169433594</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F68" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>329.1564601038647</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C69" t="n">
-        <v>331.0409661792534</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D69" t="n">
-        <v>326.0682693196749</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E69" t="n">
-        <v>327.2029113769531</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F69" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>324.5389537288393</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C70" t="n">
-        <v>325.7722668994048</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D70" t="n">
-        <v>320.2371718427956</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E70" t="n">
-        <v>323.759521484375</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F70" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>323.6805434123363</v>
+        <v>316.639672337624</v>
       </c>
       <c r="C71" t="n">
-        <v>330.1332457701224</v>
+        <v>323.4058905098511</v>
       </c>
       <c r="D71" t="n">
-        <v>321.7171186569828</v>
+        <v>315.4139070917166</v>
       </c>
       <c r="E71" t="n">
-        <v>323.0491027832031</v>
+        <v>318.8558654785156</v>
       </c>
       <c r="F71" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>318.5894351738589</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C72" t="n">
-        <v>325.3973174895482</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D72" t="n">
-        <v>317.3561220691985</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E72" t="n">
-        <v>320.8192749023438</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F72" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>319.6747419864576</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C73" t="n">
-        <v>323.4240016076582</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D73" t="n">
-        <v>319.4379555165406</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E73" t="n">
-        <v>320.4640502929688</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F73" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>320.8587369294642</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C74" t="n">
-        <v>324.5981204386806</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D74" t="n">
-        <v>319.8030137263066</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E74" t="n">
-        <v>323.2069396972656</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F74" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>322.8320412014528</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C75" t="n">
-        <v>327.4594342482506</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D75" t="n">
-        <v>321.9045873641298</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E75" t="n">
-        <v>327.4002075195312</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F75" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
-        <v>326.4727780063231</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C76" t="n">
-        <v>329.787909026371</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D76" t="n">
-        <v>323.8976047048735</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E76" t="n">
-        <v>324.5487976074219</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F76" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>325.3282766160162</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C77" t="n">
-        <v>331.6625558944407</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D77" t="n">
-        <v>325.1112123040032</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E77" t="n">
-        <v>327.725830078125</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F77" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>327.8837053458195</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C78" t="n">
-        <v>328.8802018879278</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D78" t="n">
-        <v>325.4762756879338</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E78" t="n">
-        <v>325.7031860351562</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F78" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>326.4826326508298</v>
+        <v>328.9463775793847</v>
       </c>
       <c r="C79" t="n">
-        <v>335.717696654991</v>
+        <v>340.2136022879278</v>
       </c>
       <c r="D79" t="n">
-        <v>323.1280270938765</v>
+        <v>327.3773920593259</v>
       </c>
       <c r="E79" t="n">
-        <v>331.9092102050781</v>
+        <v>335.3889770507812</v>
       </c>
       <c r="F79" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>330.9719222150325</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C80" t="n">
-        <v>342.3085268229226</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D80" t="n">
-        <v>329.3932753932535</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E80" t="n">
-        <v>337.4541931152344</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F80" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>343.6996829189171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C81" t="n">
-        <v>347.9027932709801</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D81" t="n">
-        <v>340.5127911940015</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E81" t="n">
-        <v>344.3114013671875</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F81" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>344.3213032237757</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C82" t="n">
-        <v>345.4361929991165</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D82" t="n">
-        <v>333.527344316932</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E82" t="n">
-        <v>337.1384887695312</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F82" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>336.4576913463828</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C83" t="n">
-        <v>343.2556975271264</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D83" t="n">
-        <v>336.2504730653109</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E83" t="n">
-        <v>342.2197265625</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F83" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>342.6143979299363</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C84" t="n">
-        <v>344.4002329876533</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D84" t="n">
-        <v>337.9080857224443</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E84" t="n">
-        <v>339.3880615234375</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F84" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>336.8622109944222</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C85" t="n">
-        <v>338.0757717813934</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D85" t="n">
-        <v>329.4820547645052</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E85" t="n">
-        <v>335.96435546875</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F85" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>336.9411188846722</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C86" t="n">
-        <v>337.2765764147031</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D86" t="n">
-        <v>328.4065987621919</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E86" t="n">
-        <v>329.47216796875</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F86" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>330.8929641448377</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C87" t="n">
-        <v>335.5696777492312</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D87" t="n">
-        <v>329.639928884428</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E87" t="n">
-        <v>330.4884338378906</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F87" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>330.7252730384288</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C88" t="n">
-        <v>334.9185378332558</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D88" t="n">
-        <v>323.6805737302307</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E88" t="n">
-        <v>334.43505859375</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F88" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>330.3897780779105</v>
+        <v>321.0524690830655</v>
       </c>
       <c r="C89" t="n">
-        <v>331.7119162692861</v>
+        <v>333.3003373667196</v>
       </c>
       <c r="D89" t="n">
-        <v>326.0189235086448</v>
+        <v>320.1699239761241</v>
       </c>
       <c r="E89" t="n">
-        <v>326.6010437011719</v>
+        <v>331.8686218261719</v>
       </c>
       <c r="F89" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>323.0293559592084</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C90" t="n">
-        <v>335.3526407320732</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D90" t="n">
-        <v>322.1413765634589</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E90" t="n">
-        <v>333.912109375</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F90" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>334.8987575018528</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C91" t="n">
-        <v>343.4332779356386</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D91" t="n">
-        <v>334.168645798694</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E91" t="n">
-        <v>343.1076965332031</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F91" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>342.5453159613966</v>
+        <v>347.4113127291759</v>
       </c>
       <c r="C92" t="n">
-        <v>350.2116096750548</v>
+        <v>350.9317071763275</v>
       </c>
       <c r="D92" t="n">
-        <v>342.1407856401066</v>
+        <v>346.1463145255873</v>
       </c>
       <c r="E92" t="n">
-        <v>349.7380065917969</v>
+        <v>349.3529357910156</v>
       </c>
       <c r="F92" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>349.5505106781399</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C93" t="n">
-        <v>353.0925820837122</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D93" t="n">
-        <v>348.2777232015386</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E93" t="n">
-        <v>351.5040893554688</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F93" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>349.2249303389971</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C94" t="n">
-        <v>350.0537130836444</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D94" t="n">
-        <v>342.6340826093485</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E94" t="n">
-        <v>346.9457702636719</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F94" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>290.0456258453373</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C95" t="n">
-        <v>295.5018014762001</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D95" t="n">
-        <v>276.6567723884028</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E95" t="n">
-        <v>278.9260864257812</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F95" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>279.9324825435024</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C96" t="n">
-        <v>291.0027024164021</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D96" t="n">
-        <v>279.9324825435024</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E96" t="n">
-        <v>290.094970703125</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F96" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>290.4008067136846</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C97" t="n">
-        <v>291.6538720255555</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D97" t="n">
-        <v>285.3590374883647</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E97" t="n">
-        <v>288.3880615234375</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F97" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>288.200605503728</v>
+        <v>280.4746956220067</v>
       </c>
       <c r="C98" t="n">
-        <v>289.0392644171012</v>
+        <v>284.7697819219751</v>
       </c>
       <c r="D98" t="n">
-        <v>280.8993981188336</v>
+        <v>276.8072155055542</v>
       </c>
       <c r="E98" t="n">
-        <v>283.099609375</v>
+        <v>280.0530395507812</v>
       </c>
       <c r="F98" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>282.201779365365</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C99" t="n">
-        <v>286.5233135903719</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D99" t="n">
-        <v>278.5117159450099</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E99" t="n">
-        <v>281.7775268554688</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F99" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>280.899399533992</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C100" t="n">
-        <v>284.2441289542904</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D100" t="n">
-        <v>274.8808256732182</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E100" t="n">
-        <v>280.3863220214844</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F100" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>278.2453003524489</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C101" t="n">
-        <v>280.7020503139632</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D101" t="n">
-        <v>270.3915411669698</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E101" t="n">
-        <v>272.2366027832031</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F101" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>270.6283598679102</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C102" t="n">
-        <v>273.1936570552693</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D102" t="n">
-        <v>262.7351562823021</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E102" t="n">
-        <v>264.9649658203125</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F102" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>263.494873693566</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C103" t="n">
-        <v>274.1013663098342</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D103" t="n">
-        <v>262.8535569062469</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E103" t="n">
-        <v>272.9568481445312</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F103" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>270.4902353878243</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C104" t="n">
-        <v>276.4397368487514</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D104" t="n">
-        <v>269.6713287006126</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E104" t="n">
-        <v>272.0195617675781</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F104" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>273.8152476410468</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C105" t="n">
-        <v>275.7589504136547</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D105" t="n">
-        <v>269.010264317998</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E105" t="n">
-        <v>269.5726623535156</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F105" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>268.8030465161297</v>
+        <v>272.7670960064547</v>
       </c>
       <c r="C106" t="n">
-        <v>275.9562621591264</v>
+        <v>280.7590795351679</v>
       </c>
       <c r="D106" t="n">
-        <v>266.1982749187582</v>
+        <v>270.4626513270822</v>
       </c>
       <c r="E106" t="n">
-        <v>275.1866760253906</v>
+        <v>278.856689453125</v>
       </c>
       <c r="F106" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>274.4467004687212</v>
+        <v>280.092280601724</v>
       </c>
       <c r="C107" t="n">
-        <v>282.4878958393087</v>
+        <v>287.7704613201907</v>
       </c>
       <c r="D107" t="n">
-        <v>272.1280658242715</v>
+        <v>278.9939996743944</v>
       </c>
       <c r="E107" t="n">
-        <v>280.5737915039062</v>
+        <v>287.5057067871094</v>
       </c>
       <c r="F107" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>281.8169569225497</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C108" t="n">
-        <v>289.5424162609187</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D108" t="n">
-        <v>280.7119132986369</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E108" t="n">
-        <v>289.2760314941406</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F108" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>290.0752312306441</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C109" t="n">
-        <v>290.3021716729731</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D109" t="n">
-        <v>284.4907860910092</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E109" t="n">
-        <v>285.2307739257812</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F109" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>286.1286505407075</v>
+        <v>285.2503388393621</v>
       </c>
       <c r="C110" t="n">
-        <v>286.2569199258207</v>
+        <v>285.2503388393621</v>
       </c>
       <c r="D110" t="n">
-        <v>282.4681855456762</v>
+        <v>281.3278894670919</v>
       </c>
       <c r="E110" t="n">
-        <v>284.3526916503906</v>
+        <v>284.3089294433594</v>
       </c>
       <c r="F110" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>287.0067764654547</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C111" t="n">
-        <v>287.0067764654547</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D111" t="n">
-        <v>283.0601744920274</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E111" t="n">
-        <v>286.0595703125</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F111" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>285.0433100706192</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C112" t="n">
-        <v>286.9179399107358</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D112" t="n">
-        <v>281.7380250284705</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E112" t="n">
-        <v>286.1286315917969</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F112" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>284.6979833712643</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C113" t="n">
-        <v>287.8749991147026</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D113" t="n">
-        <v>277.9098533754537</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E113" t="n">
-        <v>278.5708923339844</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F113" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>278.4327740747045</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C114" t="n">
-        <v>278.6300861021672</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D114" t="n">
-        <v>268.1715851207944</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E114" t="n">
-        <v>270.2929077148438</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F114" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>273.5883087457124</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C115" t="n">
-        <v>280.9388364524249</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D115" t="n">
-        <v>273.1739023127244</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E115" t="n">
-        <v>280.4060668945312</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F115" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>283.1489568057956</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C116" t="n">
-        <v>291.3184213223429</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D116" t="n">
-        <v>281.422318519362</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E116" t="n">
-        <v>282.8332214355469</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F116" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>280.899378965855</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C117" t="n">
-        <v>290.2034849465505</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D117" t="n">
-        <v>280.0607201096653</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E117" t="n">
-        <v>289.3549499511719</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F117" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>284.3132152404683</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C118" t="n">
-        <v>291.3677603814479</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D118" t="n">
-        <v>283.6620222891216</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E118" t="n">
-        <v>290.9928283691406</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F118" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>285.1321178149137</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C119" t="n">
-        <v>289.8187076809586</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D119" t="n">
-        <v>280.5639211910132</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E119" t="n">
-        <v>285.3491821289062</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F119" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>285.1518383851878</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C120" t="n">
-        <v>290.4106717068518</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D120" t="n">
-        <v>283.839576506922</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E120" t="n">
-        <v>288.0624389648438</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F120" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>286.1779504316799</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C121" t="n">
-        <v>287.5000885291143</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D121" t="n">
-        <v>282.9121398572339</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E121" t="n">
-        <v>284.9150390625</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F121" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,25 +3589,25 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>283.5041446062434</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C122" t="n">
-        <v>287.4408703764128</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D122" t="n">
-        <v>279.2714056266989</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E122" t="n">
-        <v>282.6556396484375</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F122" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3615,25 +3615,25 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>280.3985261413432</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C123" t="n">
-        <v>283.5803655260448</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D123" t="n">
-        <v>277.0774975936055</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E123" t="n">
-        <v>283.550537109375</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F123" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G123" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>285.7479583300972</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C124" t="n">
-        <v>285.9468043127463</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D124" t="n">
-        <v>277.3161057836816</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E124" t="n">
-        <v>280.736572265625</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F124" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>280.7763694963311</v>
+        <v>281.4297838763166</v>
       </c>
       <c r="C125" t="n">
-        <v>284.5945585040109</v>
+        <v>284.177078134999</v>
       </c>
       <c r="D125" t="n">
-        <v>279.0064793259336</v>
+        <v>273.039671765164</v>
       </c>
       <c r="E125" t="n">
-        <v>283.6300659179688</v>
+        <v>273.7907104492188</v>
       </c>
       <c r="F125" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>283.1627358622739</v>
+        <v>274.7888344130931</v>
       </c>
       <c r="C126" t="n">
-        <v>285.9269470548217</v>
+        <v>279.5521380386192</v>
       </c>
       <c r="D126" t="n">
-        <v>274.7209602020642</v>
+        <v>274.5417754718342</v>
       </c>
       <c r="E126" t="n">
-        <v>275.4766235351562</v>
+        <v>278.7714233398438</v>
       </c>
       <c r="F126" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>276.4808941849521</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C127" t="n">
-        <v>281.2735286763525</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D127" t="n">
-        <v>276.2323139355343</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E127" t="n">
-        <v>280.4880065917969</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F127" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>282.3672788368328</v>
+        <v>284.41428667964</v>
       </c>
       <c r="C128" t="n">
-        <v>285.767839547621</v>
+        <v>285.5902898411239</v>
       </c>
       <c r="D128" t="n">
-        <v>279.4439727693734</v>
+        <v>281.4891167908925</v>
       </c>
       <c r="E128" t="n">
-        <v>283.8686828613281</v>
+        <v>284.18701171875</v>
       </c>
       <c r="F128" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>286.1655640520241</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C129" t="n">
-        <v>287.3488084380985</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D129" t="n">
-        <v>283.2223824666901</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E129" t="n">
-        <v>285.9368896484375</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F129" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>283.5803557381978</v>
+        <v>280.6589555118485</v>
       </c>
       <c r="C130" t="n">
-        <v>286.7621646688093</v>
+        <v>284.1671803923218</v>
       </c>
       <c r="D130" t="n">
-        <v>281.4624471949345</v>
+        <v>276.7751962176443</v>
       </c>
       <c r="E130" t="n">
-        <v>282.7152709960938</v>
+        <v>277.1408386230469</v>
       </c>
       <c r="F130" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>282.3871618979052</v>
+        <v>275.7078960775263</v>
       </c>
       <c r="C131" t="n">
-        <v>285.9169892839216</v>
+        <v>279.7695608963037</v>
       </c>
       <c r="D131" t="n">
-        <v>278.4794876796185</v>
+        <v>271.7648448878931</v>
       </c>
       <c r="E131" t="n">
-        <v>278.8473815917969</v>
+        <v>272.347900390625</v>
       </c>
       <c r="F131" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>277.4056183419098</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C132" t="n">
-        <v>281.4922936115716</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D132" t="n">
-        <v>273.4382870867091</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E132" t="n">
-        <v>274.0249328613281</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F132" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>277.5547645320462</v>
+        <v>265.7069856894997</v>
       </c>
       <c r="C133" t="n">
-        <v>279.1556066962045</v>
+        <v>270.1639393177099</v>
       </c>
       <c r="D133" t="n">
-        <v>267.5618207785692</v>
+        <v>264.44204492441</v>
       </c>
       <c r="E133" t="n">
-        <v>268.00927734375</v>
+        <v>269.0768737792969</v>
       </c>
       <c r="F133" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>267.3430655755382</v>
+        <v>271.7648799566674</v>
       </c>
       <c r="C134" t="n">
-        <v>271.8274627132414</v>
+        <v>272.8321614881822</v>
       </c>
       <c r="D134" t="n">
-        <v>266.0703359894755</v>
+        <v>263.9676840156166</v>
       </c>
       <c r="E134" t="n">
-        <v>270.7337036132812</v>
+        <v>267.3672180175781</v>
       </c>
       <c r="F134" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>273.4382596260376</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C135" t="n">
-        <v>274.5121128941823</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D135" t="n">
-        <v>265.5930528118823</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E135" t="n">
-        <v>269.0135192871094</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F135" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>268.4567257080549</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C136" t="n">
-        <v>273.0803427820733</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D136" t="n">
-        <v>265.6626860357957</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E136" t="n">
-        <v>266.5277404785156</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F136" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>265.9808641274938</v>
+        <v>257.1191907461688</v>
       </c>
       <c r="C137" t="n">
-        <v>266.1499120468286</v>
+        <v>259.2438917467647</v>
       </c>
       <c r="D137" t="n">
-        <v>254.516344356629</v>
+        <v>253.6505034942698</v>
       </c>
       <c r="E137" t="n">
-        <v>257.5490112304688</v>
+        <v>258.7102661132812</v>
       </c>
       <c r="F137" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>258.7024415515604</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C138" t="n">
-        <v>260.8402257240527</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D138" t="n">
-        <v>255.2123953265358</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E138" t="n">
-        <v>260.3033142089844</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F138" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>261.506421503485</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C139" t="n">
-        <v>270.3359967880393</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D139" t="n">
-        <v>261.1186217504552</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E139" t="n">
-        <v>269.0533142089844</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F139" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>272.6527466700565</v>
+        <v>269.0867274922702</v>
       </c>
       <c r="C140" t="n">
-        <v>273.7365528939259</v>
+        <v>275.757318970375</v>
       </c>
       <c r="D140" t="n">
-        <v>269.2223575051711</v>
+        <v>268.3356586528844</v>
       </c>
       <c r="E140" t="n">
-        <v>272.424072265625</v>
+        <v>273.9982604980469</v>
       </c>
       <c r="F140" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>270.7436786461413</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C141" t="n">
-        <v>277.4553455215711</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D141" t="n">
-        <v>269.9879849618526</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E141" t="n">
-        <v>275.6854553222656</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F141" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>276.3019282869355</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C142" t="n">
-        <v>281.6911311912249</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D142" t="n">
-        <v>275.6755011928929</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E142" t="n">
-        <v>279.7621459960938</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F142" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>307.0960565749332</v>
+        <v>308.3296014014268</v>
       </c>
       <c r="C143" t="n">
-        <v>310.6557125153819</v>
+        <v>309.2881914326393</v>
       </c>
       <c r="D143" t="n">
-        <v>299.0420501528358</v>
+        <v>301.2439367148364</v>
       </c>
       <c r="E143" t="n">
-        <v>305.982421875</v>
+        <v>302.3804321289062</v>
       </c>
       <c r="F143" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>310.2281413790238</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C144" t="n">
-        <v>311.1926339297742</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D144" t="n">
-        <v>303.0988467016243</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E144" t="n">
-        <v>304.2423400878906</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F144" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>304.0832470042582</v>
+        <v>304.3272561704691</v>
       </c>
       <c r="C145" t="n">
-        <v>306.1414986993597</v>
+        <v>306.7187701494722</v>
       </c>
       <c r="D145" t="n">
-        <v>302.4127950535677</v>
+        <v>300.6213715612747</v>
       </c>
       <c r="E145" t="n">
-        <v>305.1670532226562</v>
+        <v>300.7498168945312</v>
       </c>
       <c r="F145" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>306.2011519366599</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C146" t="n">
-        <v>308.607391668382</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D146" t="n">
-        <v>302.4724483346268</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E146" t="n">
-        <v>302.6016845703125</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F146" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>301.5278433900291</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C147" t="n">
-        <v>311.5406631473035</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D147" t="n">
-        <v>301.199730811355</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E147" t="n">
-        <v>311.2224731445312</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F147" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>310.7352487756957</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C148" t="n">
-        <v>317.8048561417646</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D148" t="n">
-        <v>310.7352487756957</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E148" t="n">
-        <v>312.4057006835938</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F148" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>314.2054174655202</v>
+        <v>311.2943017295384</v>
       </c>
       <c r="C149" t="n">
-        <v>315.9554320324556</v>
+        <v>314.8618187748353</v>
       </c>
       <c r="D149" t="n">
-        <v>309.3829548311358</v>
+        <v>309.4265214430497</v>
       </c>
       <c r="E149" t="n">
-        <v>312.2664794921875</v>
+        <v>312.6778259277344</v>
       </c>
       <c r="F149" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>313.2111061223722</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C150" t="n">
-        <v>316.8005902653832</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D150" t="n">
-        <v>311.3318249203894</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E150" t="n">
-        <v>314.6031494140625</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F150" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>318.2324307180975</v>
+        <v>320.37616900858</v>
       </c>
       <c r="C151" t="n">
-        <v>323.4227876628706</v>
+        <v>321.5719258918635</v>
       </c>
       <c r="D151" t="n">
-        <v>315.338983249174</v>
+        <v>316.35404203196</v>
       </c>
       <c r="E151" t="n">
-        <v>322.7864379882812</v>
+        <v>319.6745300292969</v>
       </c>
       <c r="F151" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>322.3489342821542</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C152" t="n">
-        <v>323.5520542213801</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D152" t="n">
-        <v>318.3020404433487</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E152" t="n">
-        <v>321.6429748535156</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F152" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>351.0052603166191</v>
+        <v>346.7521876325058</v>
       </c>
       <c r="C153" t="n">
-        <v>355.648722319699</v>
+        <v>354.3418314545246</v>
       </c>
       <c r="D153" t="n">
-        <v>343.2694442738866</v>
+        <v>344.9931290879458</v>
       </c>
       <c r="E153" t="n">
-        <v>344.0450134277344</v>
+        <v>349.3611145019531</v>
       </c>
       <c r="F153" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>348.8873678788304</v>
+        <v>350.5074994974842</v>
       </c>
       <c r="C154" t="n">
-        <v>356.5237461069854</v>
+        <v>352.6519846563255</v>
       </c>
       <c r="D154" t="n">
-        <v>347.1174776591131</v>
+        <v>346.3766807003688</v>
       </c>
       <c r="E154" t="n">
-        <v>351.5123596191406</v>
+        <v>350.388916015625</v>
       </c>
       <c r="F154" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>352.6657614176121</v>
+        <v>352.2961666917061</v>
       </c>
       <c r="C155" t="n">
-        <v>354.8234513171886</v>
+        <v>354.0651171980212</v>
       </c>
       <c r="D155" t="n">
-        <v>348.5095069624251</v>
+        <v>347.2561882957746</v>
       </c>
       <c r="E155" t="n">
-        <v>352.5464477539062</v>
+        <v>350.7446594238281</v>
       </c>
       <c r="F155" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>354.4654798371856</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C156" t="n">
-        <v>356.2453229047883</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D156" t="n">
-        <v>349.3944670661433</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E156" t="n">
-        <v>352.9044189453125</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F156" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>351.9001510435625</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C157" t="n">
-        <v>354.4654858887946</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D157" t="n">
-        <v>346.9683273478323</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E157" t="n">
-        <v>352.6757202148438</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F157" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>354.8135029963465</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C158" t="n">
-        <v>367.5308771185002</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D158" t="n">
-        <v>353.6998683282982</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E158" t="n">
-        <v>364.6871032714844</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F158" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>363.9214802466298</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C159" t="n">
-        <v>368.7339901692348</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D159" t="n">
-        <v>362.9371121823581</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E159" t="n">
-        <v>368.6345520019531</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F159" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>366.4172241064422</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C160" t="n">
-        <v>369.87744160261</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D160" t="n">
-        <v>360.9385059451532</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E160" t="n">
-        <v>368.3760375976562</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F160" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>369.8476329800702</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C161" t="n">
-        <v>370.7822971534658</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D161" t="n">
-        <v>364.9356847817637</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E161" t="n">
-        <v>366.6856994628906</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F161" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>366.4569824541582</v>
+        <v>366.1216408565838</v>
       </c>
       <c r="C162" t="n">
-        <v>368.7240330587824</v>
+        <v>367.4260893018678</v>
       </c>
       <c r="D162" t="n">
-        <v>362.5791367283888</v>
+        <v>357.5536224796683</v>
       </c>
       <c r="E162" t="n">
-        <v>368.6445007324219</v>
+        <v>359.5893859863281</v>
       </c>
       <c r="F162" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>368.3760355922912</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C163" t="n">
-        <v>369.6885161814855</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D163" t="n">
-        <v>359.7552596250864</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E163" t="n">
-        <v>361.8035583496094</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F163" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>361.0379593902868</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C164" t="n">
-        <v>366.45699060703</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D164" t="n">
-        <v>356.2154964951898</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E164" t="n">
-        <v>365.1942138671875</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F164" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>364.5578575186544</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="C165" t="n">
-        <v>367.7098380224884</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="D165" t="n">
-        <v>362.6487478916185</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="E165" t="n">
-        <v>367.6402282714844</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="F165" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>369.8774674335755</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C166" t="n">
-        <v>377.8221130371094</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D166" t="n">
-        <v>369.8774674335755</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E166" t="n">
-        <v>377.8221130371094</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F166" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>378.2894437474218</v>
+        <v>378.3460853480032</v>
       </c>
       <c r="C167" t="n">
-        <v>382.6246688242237</v>
+        <v>392.7446883171237</v>
       </c>
       <c r="D167" t="n">
-        <v>373.9343128299113</v>
+        <v>377.5159708878205</v>
       </c>
       <c r="E167" t="n">
-        <v>382.2567749023438</v>
+        <v>391.726806640625</v>
       </c>
       <c r="F167" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>380.6758011703357</v>
+        <v>391.835521582727</v>
       </c>
       <c r="C168" t="n">
-        <v>395.1630654325308</v>
+        <v>399.3955199396844</v>
       </c>
       <c r="D168" t="n">
-        <v>379.8405751710962</v>
+        <v>388.3766960454267</v>
       </c>
       <c r="E168" t="n">
-        <v>394.138916015625</v>
+        <v>396.4407043457031</v>
       </c>
       <c r="F168" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>394.2482660415264</v>
+        <v>396.2825841810375</v>
       </c>
       <c r="C169" t="n">
-        <v>401.8548154208889</v>
+        <v>397.1719904330225</v>
       </c>
       <c r="D169" t="n">
-        <v>390.7681426338459</v>
+        <v>391.3414048271592</v>
       </c>
       <c r="E169" t="n">
-        <v>398.8818054199219</v>
+        <v>394.3950500488281</v>
       </c>
       <c r="F169" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>398.7227040337817</v>
+        <v>389.6613628183419</v>
       </c>
       <c r="C170" t="n">
-        <v>399.6175868268494</v>
+        <v>392.9522049122001</v>
       </c>
       <c r="D170" t="n">
-        <v>393.7510992453305</v>
+        <v>385.6590199026367</v>
       </c>
       <c r="E170" t="n">
-        <v>396.8235473632812</v>
+        <v>389.2166748046875</v>
       </c>
       <c r="F170" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>392.0607685404387</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C171" t="n">
-        <v>395.3718745508767</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D171" t="n">
-        <v>388.0337805215488</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E171" t="n">
-        <v>391.6133422851562</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F171" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>387.7851953583757</v>
+        <v>385.4119880990537</v>
       </c>
       <c r="C172" t="n">
-        <v>389.9130568930274</v>
+        <v>390.3432754242469</v>
       </c>
       <c r="D172" t="n">
-        <v>381.3221087690695</v>
+        <v>382.9512904411622</v>
       </c>
       <c r="E172" t="n">
-        <v>388.9087829589844</v>
+        <v>384.6609191894531</v>
       </c>
       <c r="F172" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>387.7851736187118</v>
+        <v>384.9672452573303</v>
       </c>
       <c r="C173" t="n">
-        <v>392.7468254889498</v>
+        <v>388.7522052741927</v>
       </c>
       <c r="D173" t="n">
-        <v>385.3093241434657</v>
+        <v>376.2213825216763</v>
       </c>
       <c r="E173" t="n">
-        <v>387.0294799804688</v>
+        <v>378.790771484375</v>
       </c>
       <c r="F173" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>387.3377362764213</v>
+        <v>376.6364522760421</v>
       </c>
       <c r="C174" t="n">
-        <v>391.1460027273716</v>
+        <v>381.5677396470687</v>
       </c>
       <c r="D174" t="n">
-        <v>378.5380196367677</v>
+        <v>376.0632887376697</v>
       </c>
       <c r="E174" t="n">
-        <v>381.1232299804688</v>
+        <v>377.98046875</v>
       </c>
       <c r="F174" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>378.9555995605828</v>
+        <v>377.4270309363715</v>
       </c>
       <c r="C175" t="n">
-        <v>383.9172514426562</v>
+        <v>385.9456187280053</v>
       </c>
       <c r="D175" t="n">
-        <v>378.3789067550467</v>
+        <v>376.5277327371266</v>
       </c>
       <c r="E175" t="n">
-        <v>380.3078918457031</v>
+        <v>383.8999633789062</v>
       </c>
       <c r="F175" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>379.7510949944643</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C176" t="n">
-        <v>388.322137279522</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D176" t="n">
-        <v>378.846259230469</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E176" t="n">
-        <v>386.2638854980469</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F176" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>383.8078958628703</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C177" t="n">
-        <v>384.3249318452775</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D177" t="n">
-        <v>374.2723613660349</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E177" t="n">
-        <v>374.7197875976562</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F177" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>376.2808953624811</v>
+        <v>380.4312827021371</v>
       </c>
       <c r="C178" t="n">
-        <v>382.3462596379654</v>
+        <v>384.6807151570288</v>
       </c>
       <c r="D178" t="n">
-        <v>374.9485088403697</v>
+        <v>376.4783391116702</v>
       </c>
       <c r="E178" t="n">
-        <v>381.8292236328125</v>
+        <v>378.0298767089844</v>
       </c>
       <c r="F178" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>382.7737976901378</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C179" t="n">
-        <v>387.0493961299752</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D179" t="n">
-        <v>378.7965137522062</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E179" t="n">
-        <v>380.3576049804688</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F179" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>381.6005025160485</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C180" t="n">
-        <v>382.9328889810419</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D180" t="n">
-        <v>373.317822146985</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E180" t="n">
-        <v>378.1502075195312</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F180" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>373.9740550559011</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C181" t="n">
-        <v>381.172959697494</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D181" t="n">
-        <v>373.7851619834815</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E181" t="n">
-        <v>377.7027587890625</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F181" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>375.8334605430848</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C182" t="n">
-        <v>377.9215103567756</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D182" t="n">
-        <v>372.5919643898307</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E182" t="n">
-        <v>375.7738037109375</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F182" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>377.8419717237235</v>
+        <v>385.4119603627872</v>
       </c>
       <c r="C183" t="n">
-        <v>385.259597724852</v>
+        <v>396.6580885443842</v>
       </c>
       <c r="D183" t="n">
-        <v>374.6700853756592</v>
+        <v>385.2340851575979</v>
       </c>
       <c r="E183" t="n">
-        <v>374.8590087890625</v>
+        <v>391.8058471679688</v>
       </c>
       <c r="F183" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>387.7851867936407</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C184" t="n">
-        <v>399.1005645351637</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D184" t="n">
-        <v>387.606216297745</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E184" t="n">
-        <v>394.2184448242188</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F184" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>397.2710257691138</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C185" t="n">
-        <v>401.7454703246708</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D185" t="n">
-        <v>394.9443182415365</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E185" t="n">
-        <v>397.201416015625</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F185" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>394.8746856398852</v>
+        <v>405.166788512205</v>
       </c>
       <c r="C186" t="n">
-        <v>406.3889089451397</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="D186" t="n">
-        <v>392.7468242313375</v>
+        <v>402.6467992699509</v>
       </c>
       <c r="E186" t="n">
-        <v>404.2610778808594</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="F186" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>407.6616556237274</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C187" t="n">
-        <v>410.6545715332031</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D187" t="n">
-        <v>405.1261492204914</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E187" t="n">
-        <v>410.6545715332031</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F187" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>411.1517339543602</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C188" t="n">
-        <v>413.6176609610221</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D188" t="n">
-        <v>402.2525488568183</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E188" t="n">
-        <v>405.1460266113281</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F188" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>406.3889145916303</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C189" t="n">
-        <v>407.6517216421196</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D189" t="n">
-        <v>400.820711098459</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E189" t="n">
-        <v>403.2468566894531</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F189" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>406.6872501409831</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C190" t="n">
-        <v>407.5622574937536</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D190" t="n">
-        <v>402.5110897188582</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E190" t="n">
-        <v>406.2000122070312</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F190" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>406.7000122070312</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C191" t="n">
-        <v>414.1600036621094</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D191" t="n">
-        <v>399.6499938964844</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E191" t="n">
-        <v>411.0400085449219</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F191" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G191" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>410.6799926757812</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C192" t="n">
-        <v>411.75</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D192" t="n">
-        <v>406.5400085449219</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E192" t="n">
-        <v>407.6499938964844</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F192" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>409.1199951171875</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C193" t="n">
-        <v>411.1600036621094</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D193" t="n">
-        <v>398.5899963378906</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E193" t="n">
-        <v>399.5299987792969</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F193" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>402.7699890136719</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C194" t="n">
-        <v>406.2000122070312</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D194" t="n">
-        <v>399.1499938964844</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E194" t="n">
-        <v>400.9599914550781</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F194" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>402.1400146484375</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C195" t="n">
-        <v>409.4599914550781</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D195" t="n">
-        <v>402.1400146484375</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E195" t="n">
-        <v>406.6799926757812</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F195" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>409.5199890136719</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C196" t="n">
-        <v>409.8999938964844</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D196" t="n">
-        <v>402.8399963378906</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E196" t="n">
-        <v>409.25</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F196" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>410.5400085449219</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C197" t="n">
-        <v>413.4299926757812</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D197" t="n">
-        <v>400</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E197" t="n">
-        <v>405.7999877929688</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F197" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>406.6499938964844</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C198" t="n">
-        <v>417.5799865722656</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D198" t="n">
-        <v>406.6499938964844</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E198" t="n">
-        <v>415.5299987792969</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F198" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>416.1600036621094</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C199" t="n">
-        <v>427.9299926757812</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D199" t="n">
-        <v>416.1600036621094</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E199" t="n">
-        <v>427.8900146484375</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F199" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>426.5299987792969</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C200" t="n">
-        <v>426.7000122070312</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D200" t="n">
-        <v>415.8099975585938</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E200" t="n">
-        <v>419.8200073242188</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F200" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>422.7200012207031</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C201" t="n">
-        <v>422.739990234375</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D201" t="n">
-        <v>413.25</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E201" t="n">
-        <v>415.6300048828125</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F201" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>417.1099853515625</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C202" t="n">
-        <v>428.0199890136719</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D202" t="n">
-        <v>413.7300109863281</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E202" t="n">
-        <v>426.5400085449219</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F202" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>428.1300048828125</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C203" t="n">
-        <v>430.2000122070312</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D203" t="n">
-        <v>420.5400085449219</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E203" t="n">
-        <v>425.3599853515625</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F203" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>423.489990234375</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C204" t="n">
-        <v>424.4400024414062</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D204" t="n">
-        <v>415.0499877929688</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E204" t="n">
-        <v>417.989990234375</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F204" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>423.9500122070312</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C205" t="n">
-        <v>428.6000061035156</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D205" t="n">
-        <v>422.1300048828125</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E205" t="n">
-        <v>428.1900024414062</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F205" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>427.1499938964844</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C206" t="n">
-        <v>430.7699890136719</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D206" t="n">
-        <v>423.8299865722656</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E206" t="n">
-        <v>425.6000061035156</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F206" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>427.1099853515625</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C207" t="n">
-        <v>434.2999877929688</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D207" t="n">
-        <v>423.5199890136719</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E207" t="n">
-        <v>431.6799926757812</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F207" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>431.6700134277344</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C208" t="n">
-        <v>432.8599853515625</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D208" t="n">
-        <v>423.6499938964844</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E208" t="n">
-        <v>424.6199951171875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F208" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>426.4700012207031</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C209" t="n">
-        <v>431.5499877929688</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D209" t="n">
-        <v>425.5299987792969</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E209" t="n">
-        <v>429.0899963378906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F209" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>431</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C210" t="n">
-        <v>432.1499938964844</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D210" t="n">
-        <v>421.7900085449219</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E210" t="n">
-        <v>425.1900024414062</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F210" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>419.489990234375</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C211" t="n">
-        <v>424.1099853515625</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D211" t="n">
-        <v>414.3699951171875</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E211" t="n">
-        <v>418.5199890136719</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F211" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>449.3900146484375</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C212" t="n">
-        <v>461.6199951171875</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D212" t="n">
-        <v>420.3699951171875</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E212" t="n">
-        <v>423.3800048828125</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F212" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>426.7200012207031</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C213" t="n">
-        <v>437.4700012207031</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D213" t="n">
-        <v>425.1000061035156</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E213" t="n">
-        <v>426.0899963378906</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F213" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>427.25</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C214" t="n">
-        <v>431.0199890136719</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D214" t="n">
-        <v>417.3800048828125</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E214" t="n">
-        <v>421.5499877929688</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F214" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>422.4800109863281</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C215" t="n">
-        <v>437</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D215" t="n">
-        <v>420.5</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E215" t="n">
-        <v>436.3500061035156</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F215" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>434.9500122070312</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C216" t="n">
-        <v>436.3200073242188</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D216" t="n">
-        <v>429.7000122070312</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E216" t="n">
-        <v>431.3099975585938</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F216" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>428.2699890136719</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C217" t="n">
-        <v>430.489990234375</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D217" t="n">
-        <v>420.3999938964844</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E217" t="n">
-        <v>423.5599975585938</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F217" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>425.239990234375</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C218" t="n">
-        <v>429</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D218" t="n">
-        <v>418.9200134277344</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E218" t="n">
-        <v>420.739990234375</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F218" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>422.510009765625</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C219" t="n">
-        <v>422.8800048828125</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D219" t="n">
-        <v>412.5400085449219</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E219" t="n">
-        <v>417.6400146484375</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F219" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>419.9299926757812</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C220" t="n">
-        <v>430.4599914550781</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D220" t="n">
-        <v>415.1099853515625</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E220" t="n">
-        <v>428.7900085449219</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F220" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>428.260009765625</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C221" t="n">
-        <v>431.6799926757812</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D221" t="n">
-        <v>420.3500061035156</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E221" t="n">
-        <v>420.5700073242188</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F221" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>415.1900024414062</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C222" t="n">
-        <v>427.3399963378906</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D222" t="n">
-        <v>411.2900085449219</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E222" t="n">
-        <v>421.4700012207031</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F222" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>422</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C223" t="n">
-        <v>422.8099975585938</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D223" t="n">
-        <v>414.0599975585938</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E223" t="n">
-        <v>414.3999938964844</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F223" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>417.4299926757812</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C224" t="n">
-        <v>419.3399963378906</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D224" t="n">
-        <v>413.3200073242188</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E224" t="n">
-        <v>415.3599853515625</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F224" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>415.5599975585938</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C225" t="n">
-        <v>416</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D225" t="n">
-        <v>406.6700134277344</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E225" t="n">
-        <v>407.5499877929688</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F225" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>403.1900024414062</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C226" t="n">
-        <v>416.3599853515625</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D226" t="n">
-        <v>397.7999877929688</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E226" t="n">
-        <v>412.75</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F226" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>415.2699890136719</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C227" t="n">
-        <v>416.9700012207031</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D227" t="n">
-        <v>402.3999938964844</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E227" t="n">
-        <v>403.9700012207031</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F227" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>401.5899963378906</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C228" t="n">
-        <v>410.6400146484375</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D228" t="n">
-        <v>400.6600036621094</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E228" t="n">
-        <v>407.0799865722656</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F228" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>408.6000061035156</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C229" t="n">
-        <v>413.0700073242188</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D229" t="n">
-        <v>407.989990234375</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E229" t="n">
-        <v>408.739990234375</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F229" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>409</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C230" t="n">
-        <v>410.8999938964844</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D230" t="n">
-        <v>401.3200073242188</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E230" t="n">
-        <v>402.1900024414062</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F230" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>400.9800109863281</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C231" t="n">
-        <v>407.2000122070312</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D231" t="n">
-        <v>400.5</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E231" t="n">
-        <v>405.5899963378906</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F231" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>405.5899963378906</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C232" t="n">
-        <v>407.3200073242188</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D232" t="n">
-        <v>398.5899963378906</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E232" t="n">
-        <v>399.0599975585938</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F232" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>398</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C233" t="n">
-        <v>403.1799926757812</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D233" t="n">
-        <v>396.5599975585938</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E233" t="n">
-        <v>401.7300109863281</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F233" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>398.5700073242188</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C234" t="n">
-        <v>398.8999938964844</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D234" t="n">
-        <v>391.4299926757812</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E234" t="n">
-        <v>395.6199951171875</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F234" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>397.4299926757812</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C235" t="n">
-        <v>398.7900085449219</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D235" t="n">
-        <v>393.510009765625</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E235" t="n">
-        <v>393.9299926757812</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F235" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>394.5700073242188</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C236" t="n">
-        <v>396.7999877929688</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D236" t="n">
-        <v>386.3299865722656</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E236" t="n">
-        <v>388.6099853515625</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F236" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>388.25</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C237" t="n">
-        <v>392.7099914550781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D237" t="n">
-        <v>383.8299865722656</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E237" t="n">
-        <v>384.8500061035156</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F237" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>386</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C238" t="n">
-        <v>393.6600036621094</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D238" t="n">
-        <v>386</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E238" t="n">
-        <v>390.1099853515625</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F238" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>391.0400085449219</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C239" t="n">
-        <v>399.5799865722656</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D239" t="n">
-        <v>390.8599853515625</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E239" t="n">
-        <v>398.760009765625</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F239" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>397.7999877929688</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C240" t="n">
-        <v>399.0299987792969</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D240" t="n">
-        <v>395.6199951171875</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E240" t="n">
-        <v>396.5899963378906</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F240" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>396.3299865722656</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C241" t="n">
-        <v>406.25</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D241" t="n">
-        <v>396.010009765625</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E241" t="n">
-        <v>401.010009765625</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F241" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>396.8699951171875</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C242" t="n">
-        <v>399.8800048828125</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D242" t="n">
-        <v>393.7699890136719</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E242" t="n">
-        <v>395.0499877929688</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F242" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
-        <v>396.4200134277344</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C243" t="n">
-        <v>396.739990234375</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D243" t="n">
-        <v>392.6600036621094</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E243" t="n">
-        <v>392.9500122070312</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F243" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>393.5199890136719</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C244" t="n">
-        <v>394.489990234375</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D244" t="n">
-        <v>387.7099914550781</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E244" t="n">
-        <v>389.4100036621094</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F244" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>392.0799865722656</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C245" t="n">
-        <v>399.6000061035156</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D245" t="n">
-        <v>391.7799987792969</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E245" t="n">
-        <v>396.2999877929688</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F245" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>399.2699890136719</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C246" t="n">
-        <v>401.1400146484375</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D246" t="n">
-        <v>396.510009765625</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E246" t="n">
-        <v>399.6600036621094</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F246" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>400.0199890136719</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C247" t="n">
-        <v>405.1600036621094</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D247" t="n">
-        <v>395.2999877929688</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E247" t="n">
-        <v>400.9400024414062</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F247" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>397.0499877929688</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C248" t="n">
-        <v>402.2300109863281</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D248" t="n">
-        <v>395.2000122070312</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E248" t="n">
-        <v>397.1400146484375</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F248" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>392.3999938964844</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C249" t="n">
-        <v>403.8900146484375</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D249" t="n">
-        <v>390.4400024414062</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E249" t="n">
-        <v>400.8399963378906</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F249" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>405.1700134277344</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C250" t="n">
-        <v>406.5299987792969</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D250" t="n">
-        <v>378.0799865722656</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E250" t="n">
-        <v>393.0599975585938</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F250" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>396</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C251" t="n">
-        <v>399.2699890136719</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D251" t="n">
-        <v>387.6000061035156</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E251" t="n">
-        <v>388.2799987792969</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F251" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,25 +6969,25 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>390.4200134277344</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C252" t="n">
-        <v>391.7300109863281</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D252" t="n">
-        <v>375.8999938964844</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>379.0899963378906</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F252" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -10530,34 +10530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>379.09</v>
+        <v>383.55</v>
       </c>
       <c r="D2" t="n">
-        <v>388.28</v>
+        <v>376.77</v>
       </c>
       <c r="E2" t="n">
-        <v>390.42</v>
+        <v>381.44</v>
       </c>
       <c r="F2" t="n">
-        <v>391.73</v>
+        <v>386.46</v>
       </c>
       <c r="G2" t="n">
-        <v>375.9</v>
+        <v>379.2814</v>
       </c>
       <c r="H2" t="n">
-        <v>7449717</v>
+        <v>3843607</v>
       </c>
       <c r="I2" t="n">
-        <v>5312277</v>
+        <v>5298971</v>
       </c>
       <c r="J2" t="n">
-        <v>340269203456</v>
+        <v>344272470016</v>
       </c>
       <c r="K2" t="n">
-        <v>24.394466</v>
+        <v>24.681467</v>
       </c>
       <c r="L2" t="n">
-        <v>16.89698</v>
+        <v>17.01221</v>
       </c>
       <c r="M2" t="n">
         <v>15.54</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4848917</v>
+        <v>3.5258913</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>389631246336</v>
+        <v>393634512896</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:47:25</t>
+          <t>2026-09-15 14:14:31</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,25 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>342.1494091330253</v>
+        <v>328.9313839638723</v>
       </c>
       <c r="C2" t="n">
-        <v>342.5877196861389</v>
+        <v>334.1036568566598</v>
       </c>
       <c r="D2" t="n">
-        <v>333.6458276900651</v>
+        <v>328.9313839638723</v>
       </c>
       <c r="E2" t="n">
-        <v>338.8668212890625</v>
+        <v>332.7496948242188</v>
       </c>
       <c r="F2" t="n">
-        <v>11035900</v>
+        <v>8467700</v>
       </c>
       <c r="G2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>338.4869315014284</v>
+        <v>334.6198842128155</v>
       </c>
       <c r="C3" t="n">
-        <v>339.9869970175624</v>
+        <v>335.9835665613874</v>
       </c>
       <c r="D3" t="n">
-        <v>329.5450392653686</v>
+        <v>325.4539471853474</v>
       </c>
       <c r="E3" t="n">
-        <v>330.9671630859375</v>
+        <v>326.1358032226562</v>
       </c>
       <c r="F3" t="n">
-        <v>12695800</v>
+        <v>11255600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>328.9313839638723</v>
+        <v>327.7722315420273</v>
       </c>
       <c r="C4" t="n">
-        <v>334.1036568566598</v>
+        <v>332.116544623422</v>
       </c>
       <c r="D4" t="n">
-        <v>328.9313839638723</v>
+        <v>325.1812201416126</v>
       </c>
       <c r="E4" t="n">
-        <v>332.7496948242188</v>
+        <v>327.9573059082031</v>
       </c>
       <c r="F4" t="n">
-        <v>8467700</v>
+        <v>13656800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>334.6199155242764</v>
+        <v>325.7851652728215</v>
       </c>
       <c r="C5" t="n">
-        <v>335.9835980004524</v>
+        <v>333.5971710589619</v>
       </c>
       <c r="D5" t="n">
-        <v>325.4539776391221</v>
+        <v>323.9734220131043</v>
       </c>
       <c r="E5" t="n">
-        <v>326.1358337402344</v>
+        <v>332.44775390625</v>
       </c>
       <c r="F5" t="n">
-        <v>11255600</v>
+        <v>8903700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>327.7722315420273</v>
+        <v>332.1555126407144</v>
       </c>
       <c r="C6" t="n">
-        <v>332.116544623422</v>
+        <v>343.5520626481311</v>
       </c>
       <c r="D6" t="n">
-        <v>325.1812201416126</v>
+        <v>331.1424787070217</v>
       </c>
       <c r="E6" t="n">
-        <v>327.9573059082031</v>
+        <v>338.6719970703125</v>
       </c>
       <c r="F6" t="n">
-        <v>13656800</v>
+        <v>12504100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>325.7851652728215</v>
+        <v>341.1168923851393</v>
       </c>
       <c r="C7" t="n">
-        <v>333.5971710589619</v>
+        <v>345.305351614445</v>
       </c>
       <c r="D7" t="n">
-        <v>323.9734220131043</v>
+        <v>338.8180881270031</v>
       </c>
       <c r="E7" t="n">
-        <v>332.44775390625</v>
+        <v>342.6851196289062</v>
       </c>
       <c r="F7" t="n">
-        <v>8903700</v>
+        <v>9016300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>332.1555425710952</v>
+        <v>339.850626873286</v>
       </c>
       <c r="C8" t="n">
-        <v>343.5520936054497</v>
+        <v>341.107176659279</v>
       </c>
       <c r="D8" t="n">
-        <v>331.1425085461183</v>
+        <v>334.6881040719941</v>
       </c>
       <c r="E8" t="n">
-        <v>338.6720275878906</v>
+        <v>336.5972595214844</v>
       </c>
       <c r="F8" t="n">
-        <v>12504100</v>
+        <v>8104900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>341.1169227630601</v>
+        <v>338.9057579077058</v>
       </c>
       <c r="C9" t="n">
-        <v>345.3053823653661</v>
+        <v>340.8928549002298</v>
       </c>
       <c r="D9" t="n">
-        <v>338.8181183002055</v>
+        <v>332.4477149765372</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6851501464844</v>
+        <v>335.1556091308594</v>
       </c>
       <c r="F9" t="n">
-        <v>9016300</v>
+        <v>6774700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>339.850626873286</v>
+        <v>335.0582538691371</v>
       </c>
       <c r="C10" t="n">
-        <v>341.107176659279</v>
+        <v>336.5875104266321</v>
       </c>
       <c r="D10" t="n">
-        <v>334.6881040719941</v>
+        <v>332.5938752825687</v>
       </c>
       <c r="E10" t="n">
-        <v>336.5972595214844</v>
+        <v>336.2271118164062</v>
       </c>
       <c r="F10" t="n">
-        <v>8104900</v>
+        <v>6878900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>338.9057579077058</v>
+        <v>334.8342081470359</v>
       </c>
       <c r="C11" t="n">
-        <v>340.8928549002298</v>
+        <v>340.2597470322082</v>
       </c>
       <c r="D11" t="n">
-        <v>332.4477149765372</v>
+        <v>333.4510253931927</v>
       </c>
       <c r="E11" t="n">
-        <v>335.1556091308594</v>
+        <v>336.343994140625</v>
       </c>
       <c r="F11" t="n">
-        <v>6774700</v>
+        <v>7429700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>335.0582538691371</v>
+        <v>334.9803627786429</v>
       </c>
       <c r="C12" t="n">
-        <v>336.5875104266321</v>
+        <v>339.6558844522348</v>
       </c>
       <c r="D12" t="n">
-        <v>332.5938752825687</v>
+        <v>332.7692497899866</v>
       </c>
       <c r="E12" t="n">
-        <v>336.2271118164062</v>
+        <v>339.2662353515625</v>
       </c>
       <c r="F12" t="n">
-        <v>6878900</v>
+        <v>8825500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>334.8342081470359</v>
+        <v>338.2824047650262</v>
       </c>
       <c r="C13" t="n">
-        <v>340.2597470322082</v>
+        <v>345.87033541468</v>
       </c>
       <c r="D13" t="n">
-        <v>333.4510253931927</v>
+        <v>335.7108637419195</v>
       </c>
       <c r="E13" t="n">
-        <v>336.343994140625</v>
+        <v>344.5456237792969</v>
       </c>
       <c r="F13" t="n">
-        <v>7429700</v>
+        <v>8564200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>334.9803326465864</v>
+        <v>347.9840761494036</v>
       </c>
       <c r="C14" t="n">
-        <v>339.6558538996071</v>
+        <v>358.4552554876992</v>
       </c>
       <c r="D14" t="n">
-        <v>332.7692198568235</v>
+        <v>347.3606614365734</v>
       </c>
       <c r="E14" t="n">
-        <v>339.2662048339844</v>
+        <v>350.8575744628906</v>
       </c>
       <c r="F14" t="n">
-        <v>8825500</v>
+        <v>13494800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>338.2824047650262</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C15" t="n">
-        <v>345.87033541468</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D15" t="n">
-        <v>335.7108637419195</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E15" t="n">
-        <v>344.5456237792969</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F15" t="n">
-        <v>8564200</v>
+        <v>7181700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>347.9840458817623</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C16" t="n">
-        <v>358.4552243092751</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D16" t="n">
-        <v>347.3606312231566</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E16" t="n">
-        <v>350.8575439453125</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F16" t="n">
-        <v>13494800</v>
+        <v>7236200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>351.6660223866534</v>
+        <v>357.4130008055815</v>
       </c>
       <c r="C17" t="n">
-        <v>353.1173669865184</v>
+        <v>364.9132992932725</v>
       </c>
       <c r="D17" t="n">
-        <v>347.8476817099931</v>
+        <v>356.3123046396842</v>
       </c>
       <c r="E17" t="n">
-        <v>349.4646301269531</v>
+        <v>360.3254699707031</v>
       </c>
       <c r="F17" t="n">
-        <v>7181700</v>
+        <v>9438300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>350.0880452744822</v>
+        <v>362.8579709138762</v>
       </c>
       <c r="C18" t="n">
-        <v>355.2603182962649</v>
+        <v>366.4620162306247</v>
       </c>
       <c r="D18" t="n">
-        <v>348.77305405812</v>
+        <v>356.585002247802</v>
       </c>
       <c r="E18" t="n">
-        <v>354.2278137207031</v>
+        <v>358.1532592773438</v>
       </c>
       <c r="F18" t="n">
-        <v>7236200</v>
+        <v>8759800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>357.4129705346734</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="C19" t="n">
-        <v>364.9132683871306</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="D19" t="n">
-        <v>356.3122744619989</v>
+        <v>343.3670132328114</v>
       </c>
       <c r="E19" t="n">
-        <v>360.325439453125</v>
+        <v>345.3053894042969</v>
       </c>
       <c r="F19" t="n">
-        <v>9438300</v>
+        <v>13141900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>362.8580018323341</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C20" t="n">
-        <v>366.4620474561767</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D20" t="n">
-        <v>356.5850326317519</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E20" t="n">
-        <v>358.1532897949219</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F20" t="n">
-        <v>8759800</v>
+        <v>5659400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>359.8188927085395</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C21" t="n">
-        <v>359.8188927085395</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D21" t="n">
-        <v>343.3669828865441</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E21" t="n">
-        <v>345.3053588867188</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F21" t="n">
-        <v>13141900</v>
+        <v>5974800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>345.5391725764172</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C22" t="n">
-        <v>349.8445450312873</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D22" t="n">
-        <v>344.1560194689148</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E22" t="n">
-        <v>349.3575134277344</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F22" t="n">
-        <v>5659400</v>
+        <v>6579600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>345.7437279807031</v>
+        <v>352.4549874654966</v>
       </c>
       <c r="C23" t="n">
-        <v>352.9322890785681</v>
+        <v>352.6108411281484</v>
       </c>
       <c r="D23" t="n">
-        <v>344.233912258217</v>
+        <v>345.207955645442</v>
       </c>
       <c r="E23" t="n">
-        <v>350.5945434570312</v>
+        <v>347.4190979003906</v>
       </c>
       <c r="F23" t="n">
-        <v>5974800</v>
+        <v>5872100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>350.0685670322262</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C24" t="n">
-        <v>354.77327893078</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D24" t="n">
-        <v>346.6203751846734</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E24" t="n">
-        <v>351.7828979492188</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F24" t="n">
-        <v>6579600</v>
+        <v>8608400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>352.4550184254314</v>
+        <v>349.2406127602151</v>
       </c>
       <c r="C25" t="n">
-        <v>352.6108721017735</v>
+        <v>356.0882755673564</v>
       </c>
       <c r="D25" t="n">
-        <v>345.2079859687916</v>
+        <v>348.2373288971846</v>
       </c>
       <c r="E25" t="n">
-        <v>347.4191284179688</v>
+        <v>355.0265502929688</v>
       </c>
       <c r="F25" t="n">
-        <v>5872100</v>
+        <v>5996500</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>341.896162102252</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C26" t="n">
-        <v>349.0945029745603</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D26" t="n">
-        <v>341.7305582890092</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E26" t="n">
-        <v>347.3509216308594</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F26" t="n">
-        <v>8608400</v>
+        <v>6885300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>349.2406427804422</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C27" t="n">
-        <v>356.088306176199</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D27" t="n">
-        <v>348.2373588311709</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E27" t="n">
-        <v>355.0265808105469</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F27" t="n">
-        <v>5996500</v>
+        <v>7833000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>355.6694476256362</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C28" t="n">
-        <v>361.426134922211</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D28" t="n">
-        <v>352.1238433439322</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E28" t="n">
-        <v>355.8934631347656</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F28" t="n">
-        <v>6885300</v>
+        <v>5756700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>354.5200118501019</v>
+        <v>351.9971738259649</v>
       </c>
       <c r="C29" t="n">
-        <v>354.5589826989666</v>
+        <v>355.9421471732778</v>
       </c>
       <c r="D29" t="n">
-        <v>348.7146038632694</v>
+        <v>350.6919328534217</v>
       </c>
       <c r="E29" t="n">
-        <v>352.1140747070312</v>
+        <v>353.0978698730469</v>
       </c>
       <c r="F29" t="n">
-        <v>7833000</v>
+        <v>5462100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>346.3573316043178</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C30" t="n">
-        <v>352.8835660308217</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D30" t="n">
-        <v>344.4676766060103</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E30" t="n">
-        <v>351.1010437011719</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F30" t="n">
-        <v>5756700</v>
+        <v>7766400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>351.9972042484119</v>
+        <v>370.8063128551364</v>
       </c>
       <c r="C31" t="n">
-        <v>355.9421779366814</v>
+        <v>371.118020163803</v>
       </c>
       <c r="D31" t="n">
-        <v>350.6919631630593</v>
+        <v>349.3282346022162</v>
       </c>
       <c r="E31" t="n">
-        <v>353.097900390625</v>
+        <v>358.2993469238281</v>
       </c>
       <c r="F31" t="n">
-        <v>5462100</v>
+        <v>18858700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>354.0719530807468</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C32" t="n">
-        <v>356.7214060232403</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D32" t="n">
-        <v>352.0264145317695</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E32" t="n">
-        <v>356.4876403808594</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F32" t="n">
-        <v>7766400</v>
+        <v>11874900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>370.8063128551364</v>
+        <v>338.5064021770676</v>
       </c>
       <c r="C33" t="n">
-        <v>371.118020163803</v>
+        <v>345.3443442519412</v>
       </c>
       <c r="D33" t="n">
-        <v>349.3282346022162</v>
+        <v>334.6880914224008</v>
       </c>
       <c r="E33" t="n">
-        <v>358.2993469238281</v>
+        <v>335.8082580566406</v>
       </c>
       <c r="F33" t="n">
-        <v>18858700</v>
+        <v>11441900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>354.8317237421505</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C34" t="n">
-        <v>356.6532170798153</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D34" t="n">
-        <v>344.701472908826</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E34" t="n">
-        <v>346.0456848144531</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F34" t="n">
-        <v>11874900</v>
+        <v>8390800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>338.5064329398476</v>
+        <v>330.3340003407686</v>
       </c>
       <c r="C35" t="n">
-        <v>345.3443756361395</v>
+        <v>331.863286433141</v>
       </c>
       <c r="D35" t="n">
-        <v>334.6881218381804</v>
+        <v>318.128991755756</v>
       </c>
       <c r="E35" t="n">
-        <v>335.8082885742188</v>
+        <v>325.1325073242188</v>
       </c>
       <c r="F35" t="n">
-        <v>11441900</v>
+        <v>11181400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>335.4576039784424</v>
+        <v>319.1323440808776</v>
       </c>
       <c r="C36" t="n">
-        <v>337.298567772769</v>
+        <v>327.7722802636044</v>
       </c>
       <c r="D36" t="n">
-        <v>328.3761462441955</v>
+        <v>318.7135040219252</v>
       </c>
       <c r="E36" t="n">
-        <v>332.7009887695312</v>
+        <v>322.2493286132812</v>
       </c>
       <c r="F36" t="n">
-        <v>8390800</v>
+        <v>9646600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>330.3340313465691</v>
+        <v>317.8368180152801</v>
       </c>
       <c r="C37" t="n">
-        <v>331.8633175824834</v>
+        <v>321.6454087872217</v>
       </c>
       <c r="D37" t="n">
-        <v>318.1290216159704</v>
+        <v>315.8107795893674</v>
       </c>
       <c r="E37" t="n">
-        <v>325.1325378417969</v>
+        <v>319.2394714355469</v>
       </c>
       <c r="F37" t="n">
-        <v>11181400</v>
+        <v>9697100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>319.1323138584834</v>
+        <v>320.3888776178953</v>
       </c>
       <c r="C38" t="n">
-        <v>327.7722492229931</v>
+        <v>323.7493777886428</v>
       </c>
       <c r="D38" t="n">
-        <v>318.7134738391959</v>
+        <v>313.1126243976539</v>
       </c>
       <c r="E38" t="n">
-        <v>322.2492980957031</v>
+        <v>313.2197570800781</v>
       </c>
       <c r="F38" t="n">
-        <v>9646600</v>
+        <v>7922100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>317.8367876317881</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C39" t="n">
-        <v>321.6453780396488</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D39" t="n">
-        <v>315.8107493995538</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E39" t="n">
-        <v>319.2394409179688</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F39" t="n">
-        <v>9697100</v>
+        <v>9402900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>320.3888776178953</v>
+        <v>311.6904703912621</v>
       </c>
       <c r="C40" t="n">
-        <v>323.7493777886428</v>
+        <v>315.8399890894766</v>
       </c>
       <c r="D40" t="n">
-        <v>313.1126243976539</v>
+        <v>308.9436347895907</v>
       </c>
       <c r="E40" t="n">
-        <v>313.2197570800781</v>
+        <v>313.2392272949219</v>
       </c>
       <c r="F40" t="n">
-        <v>7922100</v>
+        <v>9283800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>311.3690195806419</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C41" t="n">
-        <v>316.1321727657366</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D41" t="n">
-        <v>306.011672436569</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E41" t="n">
-        <v>315.8009948730469</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F41" t="n">
-        <v>9402900</v>
+        <v>7157800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>311.6904703912621</v>
+        <v>319.9310136403228</v>
       </c>
       <c r="C42" t="n">
-        <v>315.8399890894766</v>
+        <v>334.2692226106359</v>
       </c>
       <c r="D42" t="n">
-        <v>308.9436347895907</v>
+        <v>318.5965223212373</v>
       </c>
       <c r="E42" t="n">
-        <v>313.2392272949219</v>
+        <v>330.2658081054688</v>
       </c>
       <c r="F42" t="n">
-        <v>9283800</v>
+        <v>10403300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>314.9146147475993</v>
+        <v>329.5743133227241</v>
       </c>
       <c r="C43" t="n">
-        <v>319.3563404779885</v>
+        <v>330.2366692120174</v>
       </c>
       <c r="D43" t="n">
-        <v>311.583335312832</v>
+        <v>322.6974290151713</v>
       </c>
       <c r="E43" t="n">
-        <v>318.9570007324219</v>
+        <v>323.8955078125</v>
       </c>
       <c r="F43" t="n">
-        <v>7157800</v>
+        <v>7788700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>319.931043202934</v>
+        <v>318.4699706680781</v>
       </c>
       <c r="C44" t="n">
-        <v>334.2692534981419</v>
+        <v>319.6972700691676</v>
       </c>
       <c r="D44" t="n">
-        <v>318.5965517605375</v>
+        <v>312.1775010814912</v>
       </c>
       <c r="E44" t="n">
-        <v>330.2658386230469</v>
+        <v>313.511962890625</v>
       </c>
       <c r="F44" t="n">
-        <v>10403300</v>
+        <v>8676500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>329.5742822700864</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C45" t="n">
-        <v>330.2366380969722</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D45" t="n">
-        <v>322.6973986104767</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E45" t="n">
-        <v>323.8954772949219</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F45" t="n">
-        <v>7788700</v>
+        <v>6485400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>318.4699396678824</v>
+        <v>308.7877447280039</v>
       </c>
       <c r="C46" t="n">
-        <v>319.6972389495053</v>
+        <v>309.2650261221254</v>
       </c>
       <c r="D46" t="n">
-        <v>312.177470693811</v>
+        <v>300.7614447812334</v>
       </c>
       <c r="E46" t="n">
-        <v>313.5119323730469</v>
+        <v>305.4466857910156</v>
       </c>
       <c r="F46" t="n">
-        <v>8676500</v>
+        <v>9182100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>312.2846677767845</v>
+        <v>305.7876433202538</v>
       </c>
       <c r="C47" t="n">
-        <v>319.3758466817346</v>
+        <v>306.829898044689</v>
       </c>
       <c r="D47" t="n">
-        <v>311.1450007536453</v>
+        <v>296.6314554825427</v>
       </c>
       <c r="E47" t="n">
-        <v>312.2067260742188</v>
+        <v>301.0731811523438</v>
       </c>
       <c r="F47" t="n">
-        <v>6485400</v>
+        <v>8181100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>308.7877755793916</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C48" t="n">
-        <v>309.2650570211989</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D48" t="n">
-        <v>300.761474830703</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E48" t="n">
-        <v>305.4467163085938</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F48" t="n">
-        <v>9182100</v>
+        <v>7337600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>305.7876123248052</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C49" t="n">
-        <v>306.8298669435948</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D49" t="n">
-        <v>296.6314254151897</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E49" t="n">
-        <v>301.0731506347656</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F49" t="n">
-        <v>8181100</v>
+        <v>8406300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>302.7485789287686</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C50" t="n">
-        <v>306.5863902909554</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D50" t="n">
-        <v>301.9595901197654</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E50" t="n">
-        <v>303.4596557617188</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F50" t="n">
-        <v>7337600</v>
+        <v>10773800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>303.8200433114142</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C51" t="n">
-        <v>315.4406096571707</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D51" t="n">
-        <v>303.3622324379126</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E51" t="n">
-        <v>311.6709899902344</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F51" t="n">
-        <v>8406300</v>
+        <v>6149100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>316.1127492028895</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C52" t="n">
-        <v>317.3985198428805</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D52" t="n">
-        <v>309.3819684958741</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E52" t="n">
-        <v>310.7748718261719</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F52" t="n">
-        <v>10773800</v>
+        <v>5504200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>312.7911824167217</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C53" t="n">
-        <v>319.4927422543219</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D53" t="n">
-        <v>312.576887315192</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E53" t="n">
-        <v>317.8173522949219</v>
+        <v>321.216796875</v>
       </c>
       <c r="F53" t="n">
-        <v>6149100</v>
+        <v>2464500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>318.1192834140923</v>
+        <v>318.6744960548122</v>
       </c>
       <c r="C54" t="n">
-        <v>326.4962325236318</v>
+        <v>321.4992731766471</v>
       </c>
       <c r="D54" t="n">
-        <v>317.4374570386713</v>
+        <v>314.6516105859225</v>
       </c>
       <c r="E54" t="n">
-        <v>321.1583557128906</v>
+        <v>314.8269348144531</v>
       </c>
       <c r="F54" t="n">
-        <v>5504200</v>
+        <v>6154600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>323.067540655824</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C55" t="n">
-        <v>323.4474098298547</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D55" t="n">
-        <v>320.3596462659403</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E55" t="n">
-        <v>321.216796875</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F55" t="n">
-        <v>2464500</v>
+        <v>7978100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>318.6744960548122</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C56" t="n">
-        <v>321.4992731766471</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D56" t="n">
-        <v>314.6516105859225</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E56" t="n">
-        <v>314.8269348144531</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F56" t="n">
-        <v>6154600</v>
+        <v>9770000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>314.9828304691314</v>
+        <v>330.5970491985518</v>
       </c>
       <c r="C57" t="n">
-        <v>320.1746042723855</v>
+        <v>332.4088222358486</v>
       </c>
       <c r="D57" t="n">
-        <v>314.4276072787253</v>
+        <v>320.1940611974609</v>
       </c>
       <c r="E57" t="n">
-        <v>316.1224975585938</v>
+        <v>324.84033203125</v>
       </c>
       <c r="F57" t="n">
-        <v>7978100</v>
+        <v>8061600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>317.5445892541937</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C58" t="n">
-        <v>332.5549060741021</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D58" t="n">
-        <v>316.58027624088</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E58" t="n">
-        <v>330.8989868164062</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F58" t="n">
-        <v>9770000</v>
+        <v>5906000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>330.5970181401507</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C59" t="n">
-        <v>332.4087910072381</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D59" t="n">
-        <v>320.1940311163831</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E59" t="n">
-        <v>324.8403015136719</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F59" t="n">
-        <v>8061600</v>
+        <v>4782800</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>326.311185594663</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C60" t="n">
-        <v>327.0027621721813</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D60" t="n">
-        <v>319.9895246756281</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E60" t="n">
-        <v>322.3272705078125</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F60" t="n">
-        <v>5906000</v>
+        <v>4628400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,25 +2003,25 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>322.3272606638288</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C61" t="n">
-        <v>322.7194995812246</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D61" t="n">
-        <v>316.5710415807314</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E61" t="n">
-        <v>317.3457336425781</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F61" t="n">
-        <v>4782800</v>
+        <v>5910500</v>
       </c>
       <c r="G61" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>316.894669558022</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C62" t="n">
-        <v>320.0326109139432</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D62" t="n">
-        <v>316.2278603865539</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E62" t="n">
-        <v>317.3261413574219</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F62" t="n">
-        <v>4628400</v>
+        <v>7513200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>316.4926256697473</v>
+        <v>330.9566402470831</v>
       </c>
       <c r="C63" t="n">
-        <v>322.3566981053691</v>
+        <v>338.291630780554</v>
       </c>
       <c r="D63" t="n">
-        <v>313.4037028528859</v>
+        <v>330.8291558641754</v>
       </c>
       <c r="E63" t="n">
-        <v>322.003662109375</v>
+        <v>335.2124938964844</v>
       </c>
       <c r="F63" t="n">
-        <v>5910500</v>
+        <v>7979000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>323.9648592286011</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C64" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D64" t="n">
-        <v>322.3860878949816</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E64" t="n">
-        <v>330.2015686035156</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F64" t="n">
-        <v>7513200</v>
+        <v>6447200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>330.9566402470831</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C65" t="n">
-        <v>338.291630780554</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D65" t="n">
-        <v>330.8291558641754</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E65" t="n">
-        <v>335.2124938964844</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F65" t="n">
-        <v>7979000</v>
+        <v>6334000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>334.3789640140598</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C66" t="n">
-        <v>338.2719958722702</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D66" t="n">
-        <v>330.466330684033</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E66" t="n">
-        <v>334.4868469238281</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F66" t="n">
-        <v>6447200</v>
+        <v>4685600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>333.8200517828203</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C67" t="n">
-        <v>334.3789780492049</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D67" t="n">
-        <v>324.6120879365693</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E67" t="n">
-        <v>327.7206420898438</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F67" t="n">
-        <v>6334000</v>
+        <v>6354900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>327.1420632206801</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C68" t="n">
-        <v>329.0150363516344</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D68" t="n">
-        <v>324.0727717826809</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E68" t="n">
-        <v>325.2004699707031</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F68" t="n">
-        <v>4685600</v>
+        <v>10553000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>322.5527687928765</v>
+        <v>316.639672337624</v>
       </c>
       <c r="C69" t="n">
-        <v>323.7785340619881</v>
+        <v>323.4058905098511</v>
       </c>
       <c r="D69" t="n">
-        <v>318.2773138986521</v>
+        <v>315.4139070917166</v>
       </c>
       <c r="E69" t="n">
-        <v>321.7781066894531</v>
+        <v>318.8558654785156</v>
       </c>
       <c r="F69" t="n">
-        <v>6354900</v>
+        <v>7872400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>321.6996588106788</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C70" t="n">
-        <v>328.112871433911</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D70" t="n">
-        <v>319.7482499702252</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E70" t="n">
-        <v>321.0720825195312</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F70" t="n">
-        <v>10553000</v>
+        <v>4463300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>316.639672337624</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C71" t="n">
-        <v>323.4058905098511</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D71" t="n">
-        <v>315.4139070917166</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E71" t="n">
-        <v>318.8558654785156</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F71" t="n">
-        <v>7872400</v>
+        <v>2842700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>317.7183603265456</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C72" t="n">
-        <v>321.4446748044559</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D72" t="n">
-        <v>317.4830229692616</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E72" t="n">
-        <v>318.5028381347656</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F72" t="n">
-        <v>4463300</v>
+        <v>4359300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>318.8951108888525</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C73" t="n">
-        <v>322.6116097139714</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D73" t="n">
-        <v>317.8458486148664</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E73" t="n">
-        <v>321.2289428710938</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F73" t="n">
-        <v>2842700</v>
+        <v>4346800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>320.856335890976</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C74" t="n">
-        <v>325.4554096762092</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D74" t="n">
-        <v>319.9345579941973</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E74" t="n">
-        <v>325.3965454101562</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F74" t="n">
-        <v>4359300</v>
+        <v>4432500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>324.4747973847736</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C75" t="n">
-        <v>327.7696401358382</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D75" t="n">
-        <v>321.9153838853659</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E75" t="n">
-        <v>322.5625915527344</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F75" t="n">
-        <v>4346800</v>
+        <v>4285200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>323.3373036254844</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C76" t="n">
-        <v>329.6328178168744</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D76" t="n">
-        <v>323.1215677229996</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E76" t="n">
-        <v>325.7201843261719</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F76" t="n">
-        <v>4432500</v>
+        <v>6863600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>325.8770745510859</v>
+        <v>328.9463775793847</v>
       </c>
       <c r="C77" t="n">
-        <v>326.8674725874873</v>
+        <v>340.2136022879278</v>
       </c>
       <c r="D77" t="n">
-        <v>323.484378234348</v>
+        <v>327.3773920593259</v>
       </c>
       <c r="E77" t="n">
-        <v>323.7098999023438</v>
+        <v>335.3889770507812</v>
       </c>
       <c r="F77" t="n">
-        <v>4285200</v>
+        <v>7956600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>324.4845927435845</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C78" t="n">
-        <v>333.6631391122548</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D78" t="n">
-        <v>321.1505170252981</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E78" t="n">
-        <v>329.8779602050781</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F78" t="n">
-        <v>6863600</v>
+        <v>9441900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>328.9463775793847</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C79" t="n">
-        <v>340.2136022879278</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D79" t="n">
-        <v>327.3773920593259</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E79" t="n">
-        <v>335.3889770507812</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F79" t="n">
-        <v>7956600</v>
+        <v>7461400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>341.5962793505171</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C80" t="n">
-        <v>345.7736671379334</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D80" t="n">
-        <v>338.4288910460567</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E80" t="n">
-        <v>342.2042541503906</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F80" t="n">
-        <v>9441900</v>
+        <v>5059300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>342.2140819842231</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C81" t="n">
-        <v>343.3221487155281</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D81" t="n">
-        <v>331.4861813179077</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E81" t="n">
-        <v>335.0752258300781</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F81" t="n">
-        <v>7461400</v>
+        <v>4129100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>334.3985942399352</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C82" t="n">
-        <v>341.1549971070486</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D82" t="n">
-        <v>334.1926441199842</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E82" t="n">
-        <v>340.1253662109375</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F82" t="n">
-        <v>5059300</v>
+        <v>7146400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C83" t="n">
-        <v>342.2925015847546</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D83" t="n">
-        <v>335.8400862980764</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E83" t="n">
-        <v>337.3110046386719</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F83" t="n">
-        <v>4129100</v>
+        <v>5605900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>334.8006554373331</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C84" t="n">
-        <v>336.0067893806199</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D84" t="n">
-        <v>327.465664861477</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E84" t="n">
-        <v>333.9082946777344</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F84" t="n">
-        <v>7146400</v>
+        <v>5740900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>334.8790829701986</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C85" t="n">
-        <v>335.2124875436862</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D85" t="n">
-        <v>326.3967930031341</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E85" t="n">
-        <v>327.4558410644531</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F85" t="n">
-        <v>5605900</v>
+        <v>6943500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>328.8679359740775</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C86" t="n">
-        <v>333.5160286109023</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D86" t="n">
-        <v>327.6225691502204</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E86" t="n">
-        <v>328.4658813476562</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F86" t="n">
-        <v>5740900</v>
+        <v>8039100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>328.7012542904392</v>
+        <v>321.0524690830655</v>
       </c>
       <c r="C87" t="n">
-        <v>332.8688565573256</v>
+        <v>333.3003373667196</v>
       </c>
       <c r="D87" t="n">
-        <v>321.6996681176321</v>
+        <v>320.1699239761241</v>
       </c>
       <c r="E87" t="n">
-        <v>332.3883361816406</v>
+        <v>331.8686218261719</v>
       </c>
       <c r="F87" t="n">
-        <v>6943500</v>
+        <v>7596500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>328.3678119481101</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C88" t="n">
-        <v>329.6818587310364</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D88" t="n">
-        <v>324.0237067533218</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E88" t="n">
-        <v>324.6022644042969</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F88" t="n">
-        <v>8039100</v>
+        <v>8933300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>321.0524690830655</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C89" t="n">
-        <v>333.3003373667196</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D89" t="n">
-        <v>320.1699239761241</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E89" t="n">
-        <v>331.8686218261719</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F89" t="n">
-        <v>7596500</v>
+        <v>7491400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>332.8492030913102</v>
+        <v>347.4113127291759</v>
       </c>
       <c r="C90" t="n">
-        <v>341.3314929222494</v>
+        <v>350.9317071763275</v>
       </c>
       <c r="D90" t="n">
-        <v>332.1235596151242</v>
+        <v>346.1463145255873</v>
       </c>
       <c r="E90" t="n">
-        <v>341.0079040527344</v>
+        <v>349.3529357910156</v>
       </c>
       <c r="F90" t="n">
-        <v>8933300</v>
+        <v>9082200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>340.4489540449518</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C91" t="n">
-        <v>348.0683303861261</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D91" t="n">
-        <v>340.0468994310211</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E91" t="n">
-        <v>347.5976257324219</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F91" t="n">
-        <v>7491400</v>
+        <v>10399500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>347.4113127291759</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C92" t="n">
-        <v>350.9317071763275</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D92" t="n">
-        <v>346.1463145255873</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E92" t="n">
-        <v>349.3529357910156</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F92" t="n">
-        <v>9082200</v>
+        <v>65836900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>347.0877216940886</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C93" t="n">
-        <v>347.9114324020834</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D93" t="n">
-        <v>340.537209047996</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E93" t="n">
-        <v>344.822509765625</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F93" t="n">
-        <v>10399500</v>
+        <v>23396900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>288.2705746047087</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C94" t="n">
-        <v>293.6933589672342</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D94" t="n">
-        <v>274.9636596388997</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E94" t="n">
-        <v>277.2190856933594</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F94" t="n">
-        <v>65836900</v>
+        <v>13456400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>278.2193161239855</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C95" t="n">
-        <v>289.2217870569602</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D95" t="n">
-        <v>278.2193161239855</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E95" t="n">
-        <v>288.3196105957031</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F95" t="n">
-        <v>23396900</v>
+        <v>12022200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>288.623596430627</v>
+        <v>280.4746956220067</v>
       </c>
       <c r="C96" t="n">
-        <v>289.8689931668393</v>
+        <v>284.7697819219751</v>
       </c>
       <c r="D96" t="n">
-        <v>283.6126820924317</v>
+        <v>276.8072155055542</v>
       </c>
       <c r="E96" t="n">
-        <v>286.6231689453125</v>
+        <v>280.0530395507812</v>
       </c>
       <c r="F96" t="n">
-        <v>13456400</v>
+        <v>8664200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>286.4368439245325</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C97" t="n">
-        <v>287.2703703213834</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D97" t="n">
-        <v>279.1803192669512</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E97" t="n">
-        <v>281.3670654296875</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F97" t="n">
-        <v>12022200</v>
+        <v>10809100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>280.4746956220067</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C98" t="n">
-        <v>284.7697819219751</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D98" t="n">
-        <v>276.8072155055542</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E98" t="n">
-        <v>280.0530395507812</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F98" t="n">
-        <v>8664200</v>
+        <v>12944100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>279.1803171568922</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C99" t="n">
-        <v>282.5045770944785</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D99" t="n">
-        <v>273.1985764978856</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E99" t="n">
-        <v>278.6703796386719</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F99" t="n">
-        <v>10809100</v>
+        <v>13035300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>276.5424819048067</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C100" t="n">
-        <v>278.9841969343727</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D100" t="n">
-        <v>268.7367865177365</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E100" t="n">
-        <v>270.570556640625</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F100" t="n">
-        <v>12944100</v>
+        <v>9572800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>268.9721491110363</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C101" t="n">
-        <v>271.5217470095316</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D101" t="n">
-        <v>261.127250916227</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E101" t="n">
-        <v>263.3434143066406</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F101" t="n">
-        <v>13035300</v>
+        <v>10371600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>261.882308928914</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C102" t="n">
-        <v>272.423890770905</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D102" t="n">
-        <v>261.244916942255</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E102" t="n">
-        <v>271.286376953125</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F102" t="n">
-        <v>9572800</v>
+        <v>7284700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>268.8348304873182</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C103" t="n">
-        <v>274.7479208968081</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D103" t="n">
-        <v>268.0209355231403</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E103" t="n">
-        <v>270.3547973632812</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F103" t="n">
-        <v>10371600</v>
+        <v>6333100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>272.1395338130845</v>
+        <v>272.7670960064547</v>
       </c>
       <c r="C104" t="n">
-        <v>274.0713413766361</v>
+        <v>280.7590795351679</v>
       </c>
       <c r="D104" t="n">
-        <v>267.3639563652268</v>
+        <v>270.4626513270822</v>
       </c>
       <c r="E104" t="n">
-        <v>267.9229125976562</v>
+        <v>278.856689453125</v>
       </c>
       <c r="F104" t="n">
-        <v>7284700</v>
+        <v>12336900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>267.1580010860985</v>
+        <v>280.092280601724</v>
       </c>
       <c r="C105" t="n">
-        <v>274.2674398268017</v>
+        <v>287.7704613201907</v>
       </c>
       <c r="D105" t="n">
-        <v>264.5691704078053</v>
+        <v>278.9939996743944</v>
       </c>
       <c r="E105" t="n">
-        <v>273.5025634765625</v>
+        <v>287.5057067871094</v>
       </c>
       <c r="F105" t="n">
-        <v>6333100</v>
+        <v>10281900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>272.7670960064547</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C106" t="n">
-        <v>280.7590795351679</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D106" t="n">
-        <v>270.4626513270822</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E106" t="n">
-        <v>278.856689453125</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F106" t="n">
-        <v>12336900</v>
+        <v>6091700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>280.092280601724</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C107" t="n">
-        <v>287.7704613201907</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D107" t="n">
-        <v>278.9939996743944</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E107" t="n">
-        <v>287.5057067871094</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F107" t="n">
-        <v>10281900</v>
+        <v>6632000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>288.3000088357305</v>
+        <v>285.2503388393621</v>
       </c>
       <c r="C108" t="n">
-        <v>288.5255604322975</v>
+        <v>285.2503388393621</v>
       </c>
       <c r="D108" t="n">
-        <v>282.7497397683958</v>
+        <v>281.3278894670919</v>
       </c>
       <c r="E108" t="n">
-        <v>283.4851989746094</v>
+        <v>284.3089294433594</v>
       </c>
       <c r="F108" t="n">
-        <v>6091700</v>
+        <v>4931800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>284.3775473228927</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C109" t="n">
-        <v>284.5050317012176</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D109" t="n">
-        <v>280.7394843208789</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E109" t="n">
-        <v>282.6124572753906</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F109" t="n">
-        <v>6632000</v>
+        <v>6974100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>285.2503388393621</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C110" t="n">
-        <v>285.2503388393621</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D110" t="n">
-        <v>281.3278894670919</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E110" t="n">
-        <v>284.3089294433594</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F110" t="n">
-        <v>4931800</v>
+        <v>7247500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>283.2988839747449</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C111" t="n">
-        <v>285.1620413364778</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D111" t="n">
-        <v>280.0138268252642</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E111" t="n">
-        <v>284.3775634765625</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F111" t="n">
-        <v>6974100</v>
+        <v>9684500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>282.9556520269239</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C112" t="n">
-        <v>286.1132246607002</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D112" t="n">
-        <v>276.2090649023382</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E112" t="n">
-        <v>276.8660583496094</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F112" t="n">
-        <v>7247500</v>
+        <v>11380600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>276.7288152602706</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C113" t="n">
-        <v>276.9249197733898</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D113" t="n">
-        <v>266.5304229488273</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E113" t="n">
-        <v>268.6387634277344</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F113" t="n">
-        <v>9684500</v>
+        <v>10210000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>271.9139684697379</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C114" t="n">
-        <v>279.2195114888904</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D114" t="n">
-        <v>271.5020981735627</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E114" t="n">
-        <v>278.6900024414062</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F114" t="n">
-        <v>11380600</v>
+        <v>9723300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>281.4160980059485</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C115" t="n">
-        <v>289.5355657694184</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D115" t="n">
-        <v>279.7000266676773</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E115" t="n">
-        <v>281.102294921875</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F115" t="n">
-        <v>10210000</v>
+        <v>8141400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>279.1803129234154</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C116" t="n">
-        <v>288.4274790393609</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D116" t="n">
-        <v>278.3467865455038</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E116" t="n">
-        <v>287.5841369628906</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F116" t="n">
-        <v>9723300</v>
+        <v>7051100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>282.573240677092</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C117" t="n">
-        <v>289.5846125554742</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D117" t="n">
-        <v>281.9260329754997</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E117" t="n">
-        <v>289.2119750976562</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F117" t="n">
-        <v>8141400</v>
+        <v>7796000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>283.3871388529354</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C118" t="n">
-        <v>288.0450472755065</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D118" t="n">
-        <v>278.8468991181569</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E118" t="n">
-        <v>283.6028747558594</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F118" t="n">
-        <v>7051100</v>
+        <v>5397900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>283.4067419898253</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C119" t="n">
-        <v>288.6333918574902</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D119" t="n">
-        <v>282.102511003054</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E119" t="n">
-        <v>286.2995300292969</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F119" t="n">
-        <v>7796000</v>
+        <v>6816900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,25 +3537,25 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>284.4265998459625</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C120" t="n">
-        <v>285.7406467283754</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D120" t="n">
-        <v>281.1807753649725</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E120" t="n">
-        <v>283.1714172363281</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F120" t="n">
-        <v>5397900</v>
+        <v>10348800</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>281.7691239489905</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C121" t="n">
-        <v>285.681757300537</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D121" t="n">
-        <v>277.5622889631125</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E121" t="n">
-        <v>280.9258117675781</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F121" t="n">
-        <v>6816900</v>
+        <v>6075600</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,25 +3589,25 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>278.6825254902615</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C122" t="n">
-        <v>281.8448924528684</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D122" t="n">
-        <v>275.3818211832701</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E122" t="n">
-        <v>281.8152465820312</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F122" t="n">
-        <v>10348800</v>
+        <v>6878800</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>283.9992105555065</v>
+        <v>281.4297838763166</v>
       </c>
       <c r="C123" t="n">
-        <v>284.1968396214306</v>
+        <v>284.177078134999</v>
       </c>
       <c r="D123" t="n">
-        <v>275.6189600693905</v>
+        <v>273.039671765164</v>
       </c>
       <c r="E123" t="n">
-        <v>279.0184936523438</v>
+        <v>273.7907104492188</v>
       </c>
       <c r="F123" t="n">
-        <v>6075600</v>
+        <v>10512300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>279.0580549356083</v>
+        <v>274.7888344130931</v>
       </c>
       <c r="C124" t="n">
-        <v>282.8528771272727</v>
+        <v>279.5521380386192</v>
       </c>
       <c r="D124" t="n">
-        <v>277.2989962609529</v>
+        <v>274.5417754718342</v>
       </c>
       <c r="E124" t="n">
-        <v>281.894287109375</v>
+        <v>278.7714233398438</v>
       </c>
       <c r="F124" t="n">
-        <v>6878800</v>
+        <v>4737600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>281.4297838763166</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C125" t="n">
-        <v>284.177078134999</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D125" t="n">
-        <v>273.039671765164</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E125" t="n">
-        <v>273.7907104492188</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F125" t="n">
-        <v>10512300</v>
+        <v>4854000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>274.7888344130931</v>
+        <v>284.41428667964</v>
       </c>
       <c r="C126" t="n">
-        <v>279.5521380386192</v>
+        <v>285.5902898411239</v>
       </c>
       <c r="D126" t="n">
-        <v>274.5417754718342</v>
+        <v>281.4891167908925</v>
       </c>
       <c r="E126" t="n">
-        <v>278.7714233398438</v>
+        <v>284.18701171875</v>
       </c>
       <c r="F126" t="n">
-        <v>4737600</v>
+        <v>5752000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>280.6392236042361</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C127" t="n">
-        <v>284.0189732750403</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D127" t="n">
-        <v>277.7338078332982</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E127" t="n">
-        <v>282.1314392089844</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F127" t="n">
-        <v>4854000</v>
+        <v>4544100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>284.41428667964</v>
+        <v>280.6589555118485</v>
       </c>
       <c r="C128" t="n">
-        <v>285.5902898411239</v>
+        <v>284.1671803923218</v>
       </c>
       <c r="D128" t="n">
-        <v>281.4891167908925</v>
+        <v>276.7751962176443</v>
       </c>
       <c r="E128" t="n">
-        <v>284.18701171875</v>
+        <v>277.1408386230469</v>
       </c>
       <c r="F128" t="n">
-        <v>5752000</v>
+        <v>5542100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>281.8448673992793</v>
+        <v>275.7078960775263</v>
       </c>
       <c r="C129" t="n">
-        <v>285.0072039222152</v>
+        <v>279.7695608963037</v>
       </c>
       <c r="D129" t="n">
-        <v>279.7399202812535</v>
+        <v>271.7648448878931</v>
       </c>
       <c r="E129" t="n">
-        <v>280.9850769042969</v>
+        <v>272.347900390625</v>
       </c>
       <c r="F129" t="n">
-        <v>4544100</v>
+        <v>38893000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>280.6589555118485</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C130" t="n">
-        <v>284.1671803923218</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D130" t="n">
-        <v>276.7751962176443</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E130" t="n">
-        <v>277.1408386230469</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F130" t="n">
-        <v>5542100</v>
+        <v>10424200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>275.7078960775263</v>
+        <v>265.7069856894997</v>
       </c>
       <c r="C131" t="n">
-        <v>279.7695608963037</v>
+        <v>270.1639393177099</v>
       </c>
       <c r="D131" t="n">
-        <v>271.7648448878931</v>
+        <v>264.44204492441</v>
       </c>
       <c r="E131" t="n">
-        <v>272.347900390625</v>
+        <v>269.0768737792969</v>
       </c>
       <c r="F131" t="n">
-        <v>38893000</v>
+        <v>5911700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>275.8561490740913</v>
+        <v>271.7648799566674</v>
       </c>
       <c r="C132" t="n">
-        <v>277.4471941978335</v>
+        <v>272.8321614881822</v>
       </c>
       <c r="D132" t="n">
-        <v>265.9243614270812</v>
+        <v>263.9676840156166</v>
       </c>
       <c r="E132" t="n">
-        <v>266.3690795898438</v>
+        <v>267.3672180175781</v>
       </c>
       <c r="F132" t="n">
-        <v>10424200</v>
+        <v>8121200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>265.7069856894997</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C133" t="n">
-        <v>270.1639393177099</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D133" t="n">
-        <v>264.44204492441</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E133" t="n">
-        <v>269.0768737792969</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F133" t="n">
-        <v>5911700</v>
+        <v>6218800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>271.7648799566674</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C134" t="n">
-        <v>272.8321614881822</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D134" t="n">
-        <v>263.9676840156166</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E134" t="n">
-        <v>267.3672180175781</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F134" t="n">
-        <v>8121200</v>
+        <v>10735300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>266.813786399154</v>
+        <v>257.1191907461688</v>
       </c>
       <c r="C135" t="n">
-        <v>271.4091072097051</v>
+        <v>259.2438917467647</v>
       </c>
       <c r="D135" t="n">
-        <v>264.0368460847004</v>
+        <v>253.6505034942698</v>
       </c>
       <c r="E135" t="n">
-        <v>264.8966064453125</v>
+        <v>258.7102661132812</v>
       </c>
       <c r="F135" t="n">
-        <v>6218800</v>
+        <v>7774700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>264.3530902318651</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C136" t="n">
-        <v>264.5211035963603</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D136" t="n">
-        <v>252.9587320723257</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E136" t="n">
-        <v>255.9728393554688</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F136" t="n">
-        <v>10735300</v>
+        <v>9170800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>257.1191907461688</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C137" t="n">
-        <v>259.2438917467647</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D137" t="n">
-        <v>253.6505034942698</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E137" t="n">
-        <v>258.7102661132812</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F137" t="n">
-        <v>7774700</v>
+        <v>5473400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>259.9060317076502</v>
+        <v>269.0867274922702</v>
       </c>
       <c r="C138" t="n">
-        <v>268.6815709876363</v>
+        <v>275.757318970375</v>
       </c>
       <c r="D138" t="n">
-        <v>259.5206052453565</v>
+        <v>268.3356586528844</v>
       </c>
       <c r="E138" t="n">
-        <v>267.40673828125</v>
+        <v>273.9982604980469</v>
       </c>
       <c r="F138" t="n">
-        <v>9170800</v>
+        <v>6407000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>270.9841413969268</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C139" t="n">
-        <v>272.0613148441149</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D139" t="n">
-        <v>267.5747458421163</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E139" t="n">
-        <v>270.7568664550781</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F139" t="n">
-        <v>5473400</v>
+        <v>7097000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>269.0867274922702</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C140" t="n">
-        <v>275.757318970375</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D140" t="n">
-        <v>268.3356586528844</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E140" t="n">
-        <v>273.9982604980469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F140" t="n">
-        <v>6407000</v>
+        <v>22099800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>274.6109769278597</v>
+        <v>308.3296014014268</v>
       </c>
       <c r="C141" t="n">
-        <v>279.9671982310729</v>
+        <v>309.2881914326393</v>
       </c>
       <c r="D141" t="n">
-        <v>273.9883835303555</v>
+        <v>301.2439367148364</v>
       </c>
       <c r="E141" t="n">
-        <v>278.0500183105469</v>
+        <v>302.3804321289062</v>
       </c>
       <c r="F141" t="n">
-        <v>7097000</v>
+        <v>9645000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>305.2166521040811</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C142" t="n">
-        <v>308.7545232213582</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D142" t="n">
-        <v>297.2119355877115</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E142" t="n">
-        <v>304.1098327636719</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F142" t="n">
-        <v>22099800</v>
+        <v>5742000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>308.3296014014268</v>
+        <v>304.3272561704691</v>
       </c>
       <c r="C143" t="n">
-        <v>309.2881914326393</v>
+        <v>306.7187701494722</v>
       </c>
       <c r="D143" t="n">
-        <v>301.2439367148364</v>
+        <v>300.6213715612747</v>
       </c>
       <c r="E143" t="n">
-        <v>302.3804321289062</v>
+        <v>300.7498168945312</v>
       </c>
       <c r="F143" t="n">
-        <v>9645000</v>
+        <v>5212900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>302.2222955343541</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C144" t="n">
-        <v>304.2679509863046</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D144" t="n">
-        <v>300.5620665408429</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E144" t="n">
-        <v>303.2994689941406</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F144" t="n">
-        <v>5742000</v>
+        <v>7972200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>304.3272561704691</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C145" t="n">
-        <v>306.7187701494722</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D145" t="n">
-        <v>300.6213715612747</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E145" t="n">
-        <v>300.7498168945312</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F145" t="n">
-        <v>5212900</v>
+        <v>5864500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>299.6825108634778</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C146" t="n">
-        <v>309.6340527574118</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D146" t="n">
-        <v>299.3564063143342</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E146" t="n">
-        <v>309.3178100585938</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F146" t="n">
-        <v>7972200</v>
+        <v>5041200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>308.8335760443198</v>
+        <v>311.2943017295384</v>
       </c>
       <c r="C147" t="n">
-        <v>315.8599180273897</v>
+        <v>314.8618187748353</v>
       </c>
       <c r="D147" t="n">
-        <v>308.8335760443198</v>
+        <v>309.4265214430497</v>
       </c>
       <c r="E147" t="n">
-        <v>310.4938049316406</v>
+        <v>312.6778259277344</v>
       </c>
       <c r="F147" t="n">
-        <v>5864500</v>
+        <v>5205600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>312.2825100891185</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C148" t="n">
-        <v>314.0218147327601</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D148" t="n">
-        <v>307.4895604690128</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E148" t="n">
-        <v>310.3554382324219</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F148" t="n">
-        <v>5041200</v>
+        <v>9414700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>311.2943017295384</v>
+        <v>320.37616900858</v>
       </c>
       <c r="C149" t="n">
-        <v>314.8618187748353</v>
+        <v>321.5719258918635</v>
       </c>
       <c r="D149" t="n">
-        <v>309.4265214430497</v>
+        <v>316.35404203196</v>
       </c>
       <c r="E149" t="n">
-        <v>312.6778259277344</v>
+        <v>319.6745300292969</v>
       </c>
       <c r="F149" t="n">
-        <v>5205600</v>
+        <v>9050600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>316.2848676157387</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C150" t="n">
-        <v>321.443459891993</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D150" t="n">
-        <v>313.4091278691752</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E150" t="n">
-        <v>320.8110046386719</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F150" t="n">
-        <v>9414700</v>
+        <v>26097300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>320.37616900858</v>
+        <v>346.7521876325058</v>
       </c>
       <c r="C151" t="n">
-        <v>321.5719258918635</v>
+        <v>354.3418314545246</v>
       </c>
       <c r="D151" t="n">
-        <v>316.35404203196</v>
+        <v>344.9931290879458</v>
       </c>
       <c r="E151" t="n">
-        <v>319.6745300292969</v>
+        <v>349.3611145019531</v>
       </c>
       <c r="F151" t="n">
-        <v>9050600</v>
+        <v>11807300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>348.8571343403697</v>
+        <v>350.5074994974842</v>
       </c>
       <c r="C152" t="n">
-        <v>353.472178702815</v>
+        <v>352.6519846563255</v>
       </c>
       <c r="D152" t="n">
-        <v>341.1686609140239</v>
+        <v>346.3766807003688</v>
       </c>
       <c r="E152" t="n">
-        <v>341.9394836425781</v>
+        <v>350.388916015625</v>
       </c>
       <c r="F152" t="n">
-        <v>26097300</v>
+        <v>7255800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>346.7521876325058</v>
+        <v>352.2961666917061</v>
       </c>
       <c r="C153" t="n">
-        <v>354.3418314545246</v>
+        <v>354.0651171980212</v>
       </c>
       <c r="D153" t="n">
-        <v>344.9931290879458</v>
+        <v>347.2561882957746</v>
       </c>
       <c r="E153" t="n">
-        <v>349.3611145019531</v>
+        <v>350.7446594238281</v>
       </c>
       <c r="F153" t="n">
-        <v>11807300</v>
+        <v>8554600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>350.5074994974842</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C154" t="n">
-        <v>352.6519846563255</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D154" t="n">
-        <v>346.3766807003688</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E154" t="n">
-        <v>350.388916015625</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F154" t="n">
-        <v>7255800</v>
+        <v>7256100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>352.2961666917061</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C155" t="n">
-        <v>354.0651171980212</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D155" t="n">
-        <v>347.2561882957746</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E155" t="n">
-        <v>350.7446594238281</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F155" t="n">
-        <v>8554600</v>
+        <v>10604100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>349.7465417706892</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C156" t="n">
-        <v>352.2961769099271</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D156" t="n">
-        <v>344.844900560564</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E156" t="n">
-        <v>350.5173645019531</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F156" t="n">
-        <v>7256100</v>
+        <v>9046600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>352.6420862239859</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C157" t="n">
-        <v>365.28163151709</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D157" t="n">
-        <v>351.5352668687036</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E157" t="n">
-        <v>362.4552612304688</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F157" t="n">
-        <v>10604100</v>
+        <v>6879900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>361.6943118802069</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C158" t="n">
-        <v>366.4773696532562</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D158" t="n">
-        <v>360.7159680643861</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E158" t="n">
-        <v>366.3785400390625</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F158" t="n">
-        <v>9046600</v>
+        <v>4945400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>364.1747868031508</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C159" t="n">
-        <v>367.613828109226</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D159" t="n">
-        <v>358.7295978571138</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E159" t="n">
-        <v>366.1216125488281</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F159" t="n">
-        <v>6879900</v>
+        <v>4916900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>367.5842026752116</v>
+        <v>366.1216408565838</v>
       </c>
       <c r="C160" t="n">
-        <v>368.513146797899</v>
+        <v>367.4260893018678</v>
       </c>
       <c r="D160" t="n">
-        <v>362.7023151057061</v>
+        <v>357.5536224796683</v>
       </c>
       <c r="E160" t="n">
-        <v>364.4416198730469</v>
+        <v>359.5893859863281</v>
       </c>
       <c r="F160" t="n">
-        <v>4945400</v>
+        <v>6489000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>364.214296881966</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C161" t="n">
-        <v>366.4674733296609</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D161" t="n">
-        <v>360.360183242299</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E161" t="n">
-        <v>366.388427734375</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F161" t="n">
-        <v>4916900</v>
+        <v>6695500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>366.1216408565838</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C162" t="n">
-        <v>367.4260893018678</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D162" t="n">
-        <v>357.5536224796683</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E162" t="n">
-        <v>359.5893859863281</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F162" t="n">
-        <v>6489000</v>
+        <v>5235400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>358.8284404495387</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="C163" t="n">
-        <v>364.2143076961161</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="D163" t="n">
-        <v>354.0354905816196</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="E163" t="n">
-        <v>362.9592590332031</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="F163" t="n">
-        <v>6695500</v>
+        <v>6455100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>362.3267825015715</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C164" t="n">
-        <v>365.45947304961</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D164" t="n">
-        <v>360.4293565255828</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E164" t="n">
-        <v>365.3902893066406</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F164" t="n">
-        <v>5235400</v>
+        <v>6949600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>367.6138324799484</v>
+        <v>378.3460853480032</v>
       </c>
       <c r="C165" t="n">
-        <v>375.5098571777344</v>
+        <v>392.7446883171237</v>
       </c>
       <c r="D165" t="n">
-        <v>367.6138324799484</v>
+        <v>377.5159708878205</v>
       </c>
       <c r="E165" t="n">
-        <v>375.5098571777344</v>
+        <v>391.726806640625</v>
       </c>
       <c r="F165" t="n">
-        <v>6455100</v>
+        <v>9236300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>375.9743375633532</v>
+        <v>391.835521582727</v>
       </c>
       <c r="C166" t="n">
-        <v>380.2830313516125</v>
+        <v>399.3955199396844</v>
       </c>
       <c r="D166" t="n">
-        <v>371.6458597568035</v>
+        <v>388.3766960454267</v>
       </c>
       <c r="E166" t="n">
-        <v>379.9173889160156</v>
+        <v>396.4407043457031</v>
       </c>
       <c r="F166" t="n">
-        <v>6949600</v>
+        <v>8454100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>378.3460853480032</v>
+        <v>396.2825841810375</v>
       </c>
       <c r="C167" t="n">
-        <v>392.7446883171237</v>
+        <v>397.1719904330225</v>
       </c>
       <c r="D167" t="n">
-        <v>377.5159708878205</v>
+        <v>391.3414048271592</v>
       </c>
       <c r="E167" t="n">
-        <v>391.726806640625</v>
+        <v>394.3950500488281</v>
       </c>
       <c r="F167" t="n">
-        <v>9236300</v>
+        <v>5342500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>391.835521582727</v>
+        <v>389.6613628183419</v>
       </c>
       <c r="C168" t="n">
-        <v>399.3955199396844</v>
+        <v>392.9522049122001</v>
       </c>
       <c r="D168" t="n">
-        <v>388.3766960454267</v>
+        <v>385.6590199026367</v>
       </c>
       <c r="E168" t="n">
-        <v>396.4407043457031</v>
+        <v>389.2166748046875</v>
       </c>
       <c r="F168" t="n">
-        <v>8454100</v>
+        <v>9811200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>396.2825841810375</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C169" t="n">
-        <v>397.1719904330225</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D169" t="n">
-        <v>391.3414048271592</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E169" t="n">
-        <v>394.3950500488281</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F169" t="n">
-        <v>5342500</v>
+        <v>8400700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>389.6613628183419</v>
+        <v>385.4119880990537</v>
       </c>
       <c r="C170" t="n">
-        <v>392.9522049122001</v>
+        <v>390.3432754242469</v>
       </c>
       <c r="D170" t="n">
-        <v>385.6590199026367</v>
+        <v>382.9512904411622</v>
       </c>
       <c r="E170" t="n">
-        <v>389.2166748046875</v>
+        <v>384.6609191894531</v>
       </c>
       <c r="F170" t="n">
-        <v>9811200</v>
+        <v>5016800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>385.4119752058043</v>
+        <v>384.9672452573303</v>
       </c>
       <c r="C171" t="n">
-        <v>387.5268143663777</v>
+        <v>388.7522052741927</v>
       </c>
       <c r="D171" t="n">
-        <v>378.9884422857075</v>
+        <v>376.2213825216763</v>
       </c>
       <c r="E171" t="n">
-        <v>386.5286865234375</v>
+        <v>378.790771484375</v>
       </c>
       <c r="F171" t="n">
-        <v>8400700</v>
+        <v>7783900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>385.4119880990537</v>
+        <v>376.6364522760421</v>
       </c>
       <c r="C172" t="n">
-        <v>390.3432754242469</v>
+        <v>381.5677396470687</v>
       </c>
       <c r="D172" t="n">
-        <v>382.9512904411622</v>
+        <v>376.0632887376697</v>
       </c>
       <c r="E172" t="n">
-        <v>384.6609191894531</v>
+        <v>377.98046875</v>
       </c>
       <c r="F172" t="n">
-        <v>5016800</v>
+        <v>4732500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>384.9672452573303</v>
+        <v>377.4270309363715</v>
       </c>
       <c r="C173" t="n">
-        <v>388.7522052741927</v>
+        <v>385.9456187280053</v>
       </c>
       <c r="D173" t="n">
-        <v>376.2213825216763</v>
+        <v>376.5277327371266</v>
       </c>
       <c r="E173" t="n">
-        <v>378.790771484375</v>
+        <v>383.8999633789062</v>
       </c>
       <c r="F173" t="n">
-        <v>7783900</v>
+        <v>5598600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>376.6364522760421</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C174" t="n">
-        <v>381.5677396470687</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D174" t="n">
-        <v>376.0632887376697</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E174" t="n">
-        <v>377.98046875</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F174" t="n">
-        <v>4732500</v>
+        <v>6498100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>377.4270309363715</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C175" t="n">
-        <v>385.9456187280053</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D175" t="n">
-        <v>376.5277327371266</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E175" t="n">
-        <v>383.8999633789062</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F175" t="n">
-        <v>5598600</v>
+        <v>4544000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>381.4590342432408</v>
+        <v>380.4312827021371</v>
       </c>
       <c r="C176" t="n">
-        <v>381.9729060229619</v>
+        <v>384.6807151570288</v>
       </c>
       <c r="D176" t="n">
-        <v>371.981856156588</v>
+        <v>376.4783391116702</v>
       </c>
       <c r="E176" t="n">
-        <v>372.4265441894531</v>
+        <v>378.0298767089844</v>
       </c>
       <c r="F176" t="n">
-        <v>6498100</v>
+        <v>4330800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>373.978089171931</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C177" t="n">
-        <v>380.0063339481963</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D177" t="n">
-        <v>372.6538567388769</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E177" t="n">
-        <v>379.4924621582031</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F177" t="n">
-        <v>4544000</v>
+        <v>10257900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>380.4312827021371</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C178" t="n">
-        <v>384.6807151570288</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D178" t="n">
-        <v>376.4783391116702</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E178" t="n">
-        <v>378.0298767089844</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F178" t="n">
-        <v>4330800</v>
+        <v>6623700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>379.265147571566</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C179" t="n">
-        <v>380.5893799715138</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D179" t="n">
-        <v>371.0331563353153</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E179" t="n">
-        <v>375.8359680175781</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F179" t="n">
-        <v>10257900</v>
+        <v>3874400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>371.6853813293241</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C180" t="n">
-        <v>378.8402295886877</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D180" t="n">
-        <v>371.4976442585204</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E180" t="n">
-        <v>375.3912658691406</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F180" t="n">
-        <v>6623700</v>
+        <v>6808400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>373.5333823120854</v>
+        <v>385.4119603627872</v>
       </c>
       <c r="C181" t="n">
-        <v>375.6086533861857</v>
+        <v>396.6580885443842</v>
       </c>
       <c r="D181" t="n">
-        <v>370.311723920821</v>
+        <v>385.2340851575979</v>
       </c>
       <c r="E181" t="n">
-        <v>373.4740905761719</v>
+        <v>391.8058471679688</v>
       </c>
       <c r="F181" t="n">
-        <v>3874400</v>
+        <v>12666100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>375.5296184023749</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C182" t="n">
-        <v>382.9018493087182</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D182" t="n">
-        <v>372.3771436667856</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E182" t="n">
-        <v>372.5649108886719</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F182" t="n">
-        <v>6808400</v>
+        <v>10897300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>385.4119603627872</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C183" t="n">
-        <v>396.6580885443842</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D183" t="n">
-        <v>385.2340851575979</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E183" t="n">
-        <v>391.8058471679688</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F183" t="n">
-        <v>12666100</v>
+        <v>6963200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>394.8397525939222</v>
+        <v>405.166788512205</v>
       </c>
       <c r="C184" t="n">
-        <v>399.2868138360328</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="D184" t="n">
-        <v>392.5272843670525</v>
+        <v>402.6467992699509</v>
       </c>
       <c r="E184" t="n">
-        <v>394.7705688476562</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="F184" t="n">
-        <v>10897300</v>
+        <v>8590400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>392.4580996989546</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C185" t="n">
-        <v>403.9018573320044</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D185" t="n">
-        <v>390.3432605482298</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E185" t="n">
-        <v>401.7870483398438</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F185" t="n">
-        <v>6963200</v>
+        <v>6512900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>405.166788512205</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C186" t="n">
-        <v>408.1413879394531</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D186" t="n">
-        <v>402.6467992699509</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E186" t="n">
-        <v>408.1413879394531</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F186" t="n">
-        <v>8590400</v>
+        <v>4938100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>408.6355178300448</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C187" t="n">
-        <v>411.0863535582731</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D187" t="n">
-        <v>399.7907950421236</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E187" t="n">
-        <v>402.6665649414062</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F187" t="n">
-        <v>6512900</v>
+        <v>7269600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>403.9018510073829</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C188" t="n">
-        <v>405.1569297923697</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D188" t="n">
-        <v>398.3677244184781</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E188" t="n">
-        <v>400.7790222167969</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F188" t="n">
-        <v>4938100</v>
+        <v>6777900</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>404.1983674177345</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C189" t="n">
-        <v>405.0680198185554</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D189" t="n">
-        <v>400.0477646532951</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E189" t="n">
-        <v>403.714111328125</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F189" t="n">
-        <v>7269600</v>
+        <v>4815100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>404.2110392057612</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C190" t="n">
-        <v>411.6253760831061</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D190" t="n">
-        <v>397.2041664686265</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E190" t="n">
-        <v>408.5244750976562</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F190" t="n">
-        <v>6777900</v>
+        <v>5838800</v>
       </c>
       <c r="G190" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>408.166667860176</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C191" t="n">
-        <v>409.2301268352938</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D191" t="n">
-        <v>404.0520200618331</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E191" t="n">
-        <v>405.1552124023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F191" t="n">
-        <v>4815100</v>
+        <v>11896900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>406.6162060558993</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C192" t="n">
-        <v>408.6437298747245</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D192" t="n">
-        <v>396.1506502177288</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E192" t="n">
-        <v>397.0848999023438</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F192" t="n">
-        <v>5838800</v>
+        <v>5818600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>400.3050851420949</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C193" t="n">
-        <v>403.7141170062105</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D193" t="n">
-        <v>396.7072439594676</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E193" t="n">
-        <v>398.5061645507812</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F193" t="n">
-        <v>11896900</v>
+        <v>6675900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>399.6789681783447</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C194" t="n">
-        <v>406.9541476446936</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D194" t="n">
-        <v>399.6789681783447</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E194" t="n">
-        <v>404.191162109375</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F194" t="n">
-        <v>5818600</v>
+        <v>6858800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>407.0137590655401</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C195" t="n">
-        <v>407.3914383485204</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D195" t="n">
-        <v>400.3746474166842</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E195" t="n">
-        <v>406.7454223632812</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F195" t="n">
-        <v>6675900</v>
+        <v>6014400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>408.0275405710553</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C196" t="n">
-        <v>410.8998382586385</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D196" t="n">
-        <v>397.5520359316292</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E196" t="n">
-        <v>403.3165283203125</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F196" t="n">
-        <v>6858800</v>
+        <v>10588200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>404.1613393115512</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C197" t="n">
-        <v>415.0244415980686</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D197" t="n">
-        <v>404.1613393115512</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E197" t="n">
-        <v>412.9869995117188</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F197" t="n">
-        <v>6014400</v>
+        <v>5167400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>413.6131380385679</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C198" t="n">
-        <v>425.3110956697316</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D198" t="n">
-        <v>413.6131380385679</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E198" t="n">
-        <v>425.2713623046875</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F198" t="n">
-        <v>10588200</v>
+        <v>5779800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>423.9196901108692</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C199" t="n">
-        <v>424.0886630783183</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D199" t="n">
-        <v>413.2652939172264</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E199" t="n">
-        <v>417.2507629394531</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F199" t="n">
-        <v>5167400</v>
+        <v>4985900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>420.1330016088457</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C200" t="n">
-        <v>420.1528682919667</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D200" t="n">
-        <v>410.7209557472728</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E200" t="n">
-        <v>413.0863952636719</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F200" t="n">
-        <v>5779800</v>
+        <v>3928800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>414.5573140678119</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C201" t="n">
-        <v>425.4005496015332</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D201" t="n">
-        <v>411.1980248067586</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E201" t="n">
-        <v>423.9296264648438</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F201" t="n">
-        <v>4985900</v>
+        <v>6379000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>425.5099032988985</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C202" t="n">
-        <v>427.5672424396051</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D202" t="n">
-        <v>417.9663567804552</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E202" t="n">
-        <v>422.7568359375</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F202" t="n">
-        <v>3928800</v>
+        <v>5800500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>420.8982555962246</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C203" t="n">
-        <v>421.8424537826169</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D203" t="n">
-        <v>412.5099054894139</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E203" t="n">
-        <v>415.4319152832031</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F203" t="n">
-        <v>6379000</v>
+        <v>3859200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>421.3554771585211</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C204" t="n">
-        <v>425.9770135204084</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D204" t="n">
-        <v>419.546608111588</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E204" t="n">
-        <v>425.5695190429688</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F204" t="n">
-        <v>5800500</v>
+        <v>5566000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>424.5358632950858</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C205" t="n">
-        <v>428.1337042740362</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D205" t="n">
-        <v>421.236174203027</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E205" t="n">
-        <v>422.995361328125</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F205" t="n">
-        <v>3859200</v>
+        <v>3798600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>424.4961077137118</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C206" t="n">
-        <v>431.6421079373234</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D206" t="n">
-        <v>420.9280818552513</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E206" t="n">
-        <v>429.0381469726562</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F206" t="n">
-        <v>5566000</v>
+        <v>3863800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>429.0282351931601</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C207" t="n">
-        <v>430.2109246052771</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D207" t="n">
-        <v>421.0572973965209</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E207" t="n">
-        <v>422.0213623046875</v>
+        <v>422.587890625</v>
       </c>
       <c r="F207" t="n">
-        <v>3798600</v>
+        <v>5135900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>423.8600586972866</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C208" t="n">
-        <v>428.9089563935811</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D208" t="n">
-        <v>422.9258089520534</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E208" t="n">
-        <v>426.4640197753906</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F208" t="n">
-        <v>3863800</v>
+        <v>6764800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>428.3623316954033</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C209" t="n">
-        <v>429.5052877671748</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D209" t="n">
-        <v>419.2087042833569</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E209" t="n">
-        <v>422.587890625</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F209" t="n">
-        <v>5135900</v>
+        <v>13281900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>416.9227440878186</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C210" t="n">
-        <v>421.5144651938549</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D210" t="n">
-        <v>411.8340829429332</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E210" t="n">
-        <v>415.9586791992188</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F210" t="n">
-        <v>6764800</v>
+        <v>10718100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>446.6398026289249</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C211" t="n">
-        <v>458.7949371104763</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D211" t="n">
-        <v>417.7973820738866</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E211" t="n">
-        <v>420.7889709472656</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F211" t="n">
-        <v>13281900</v>
+        <v>4818800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>424.1085101449368</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C212" t="n">
-        <v>434.7927210350189</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D212" t="n">
-        <v>422.4984292637336</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E212" t="n">
-        <v>423.4823608398438</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F212" t="n">
-        <v>10718100</v>
+        <v>6833600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>424.6352826432401</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C213" t="n">
-        <v>428.3821997886642</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D213" t="n">
-        <v>414.8256906800468</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E213" t="n">
-        <v>418.9701538085938</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F213" t="n">
-        <v>4818800</v>
+        <v>4234100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>419.8944835510819</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C214" t="n">
-        <v>434.3256119583864</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D214" t="n">
-        <v>417.926589996571</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E214" t="n">
-        <v>433.6795959472656</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F214" t="n">
-        <v>6833600</v>
+        <v>4868700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>432.2881481663885</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C215" t="n">
-        <v>433.6497590080594</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D215" t="n">
-        <v>427.0702778038668</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E215" t="n">
-        <v>428.67041015625</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F215" t="n">
-        <v>4234100</v>
+        <v>3752500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>425.6490319049457</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C216" t="n">
-        <v>427.8554470044401</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D216" t="n">
-        <v>417.8272001430648</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E216" t="n">
-        <v>420.9678649902344</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F216" t="n">
-        <v>4868700</v>
+        <v>4615700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>422.6375605105379</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C217" t="n">
-        <v>426.3745593613837</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D217" t="n">
-        <v>416.3562613820867</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E217" t="n">
-        <v>418.1651000976562</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F217" t="n">
-        <v>3752500</v>
+        <v>5917300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>419.9242977601041</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C218" t="n">
-        <v>420.2920285503067</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D218" t="n">
-        <v>410.0153117846154</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E218" t="n">
-        <v>415.0841064453125</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F218" t="n">
-        <v>4615700</v>
+        <v>5257900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>417.3600694454911</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C219" t="n">
-        <v>427.8256258440344</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D219" t="n">
-        <v>412.5695600114177</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E219" t="n">
-        <v>426.1658630371094</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F219" t="n">
-        <v>5917300</v>
+        <v>3647500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>425.6390950681477</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C220" t="n">
-        <v>429.0381479748715</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D220" t="n">
-        <v>417.7774999531414</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E220" t="n">
-        <v>417.9961547851562</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F220" t="n">
-        <v>5257900</v>
+        <v>3920900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>412.6490895753043</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C221" t="n">
-        <v>424.7247269708298</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D221" t="n">
-        <v>408.7729631722832</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E221" t="n">
-        <v>418.8906555175781</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F221" t="n">
-        <v>3647500</v>
+        <v>3209600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>419.4173861384651</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C222" t="n">
-        <v>420.2224265621711</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D222" t="n">
-        <v>411.5259760202005</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E222" t="n">
-        <v>411.8638916015625</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F222" t="n">
-        <v>3920900</v>
+        <v>5266300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>414.8753627675596</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C223" t="n">
-        <v>416.7736773978178</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D223" t="n">
-        <v>410.7905301162958</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E223" t="n">
-        <v>412.8180236816406</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F223" t="n">
-        <v>3209600</v>
+        <v>5399000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>413.0168058398714</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C224" t="n">
-        <v>413.4541155038886</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D224" t="n">
-        <v>404.1812276531693</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E224" t="n">
-        <v>405.0558166503906</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F224" t="n">
-        <v>5266300</v>
+        <v>4712400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>400.7225079776698</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C225" t="n">
-        <v>413.8118915184926</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D225" t="n">
-        <v>395.3654798398698</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E225" t="n">
-        <v>410.2239990234375</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F225" t="n">
-        <v>5399000</v>
+        <v>4095900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>412.728574598682</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C226" t="n">
-        <v>414.4181828862322</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D226" t="n">
-        <v>399.9373426764689</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E226" t="n">
-        <v>401.4977416992188</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F226" t="n">
-        <v>4712400</v>
+        <v>3182200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>399.1322922233893</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C227" t="n">
-        <v>408.1269250227407</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D227" t="n">
-        <v>398.2079910410381</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E227" t="n">
-        <v>404.5886840820312</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F227" t="n">
-        <v>4095900</v>
+        <v>3398900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>406.0993979544625</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C228" t="n">
-        <v>410.5420430290281</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D228" t="n">
-        <v>405.4931153467772</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E228" t="n">
-        <v>406.238525390625</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F228" t="n">
-        <v>3182200</v>
+        <v>3317200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>406.4969587134404</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C229" t="n">
-        <v>408.3853248271201</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D229" t="n">
-        <v>398.8639668658938</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E229" t="n">
-        <v>399.7286376953125</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F229" t="n">
-        <v>3398900</v>
+        <v>4170200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>398.5260459867315</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C230" t="n">
-        <v>404.7079813067043</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D230" t="n">
-        <v>398.0489726285335</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E230" t="n">
-        <v>403.1078186035156</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F230" t="n">
-        <v>3317200</v>
+        <v>3476400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>403.1078338152345</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C231" t="n">
-        <v>404.8272573401537</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D231" t="n">
-        <v>396.1506729824118</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E231" t="n">
-        <v>396.6177978515625</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F231" t="n">
-        <v>4170200</v>
+        <v>5295100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>395.5642702547857</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C232" t="n">
-        <v>400.7125617691589</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D232" t="n">
-        <v>394.1330805188561</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E232" t="n">
-        <v>399.2714538574219</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F232" t="n">
-        <v>3476400</v>
+        <v>3605100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>396.1308110575831</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C233" t="n">
-        <v>396.4587781552261</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D233" t="n">
-        <v>389.0344923640698</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E233" t="n">
-        <v>393.1988525390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F233" t="n">
-        <v>5295100</v>
+        <v>5268500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>394.9977452515739</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C234" t="n">
-        <v>396.3494379061722</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D234" t="n">
-        <v>391.1017523988161</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E234" t="n">
-        <v>391.5191650390625</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F234" t="n">
-        <v>3605100</v>
+        <v>4497200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>392.1552670341675</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C235" t="n">
-        <v>394.3716001815704</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D235" t="n">
-        <v>383.9656746212449</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E235" t="n">
-        <v>386.2317199707031</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F235" t="n">
-        <v>5268500</v>
+        <v>4879600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>385.8739371481429</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C236" t="n">
-        <v>390.3066337673781</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D236" t="n">
-        <v>381.4809738935195</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E236" t="n">
-        <v>382.4947509765625</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F236" t="n">
-        <v>4497200</v>
+        <v>4683900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>383.6377017073448</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C237" t="n">
-        <v>391.250826577815</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D237" t="n">
-        <v>383.6377017073448</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E237" t="n">
-        <v>387.7225341796875</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F237" t="n">
-        <v>4879600</v>
+        <v>2655000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>388.6468854751683</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C238" t="n">
-        <v>397.1345997494796</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D238" t="n">
-        <v>388.4679640045169</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E238" t="n">
-        <v>396.3196411132812</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F238" t="n">
-        <v>4683900</v>
+        <v>3557000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>395.3654892531199</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C239" t="n">
-        <v>396.5879726878088</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D239" t="n">
-        <v>393.1988379276376</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E239" t="n">
-        <v>394.1629028320312</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F239" t="n">
-        <v>2655000</v>
+        <v>3668200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>393.9044956601749</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C240" t="n">
-        <v>403.7637998223176</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D240" t="n">
-        <v>393.5864770723492</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E240" t="n">
-        <v>398.5558776855469</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F240" t="n">
-        <v>3557000</v>
+        <v>2455500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>394.4411932932572</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C241" t="n">
-        <v>397.4327821218027</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D241" t="n">
-        <v>391.360158894761</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E241" t="n">
-        <v>392.63232421875</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F241" t="n">
-        <v>3668200</v>
+        <v>5748000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>393.99396168554</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C242" t="n">
-        <v>394.3119802653936</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D242" t="n">
-        <v>390.2569628122352</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E242" t="n">
-        <v>390.5451965332031</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F242" t="n">
-        <v>2455500</v>
+        <v>3716200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>391.1116881429976</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C243" t="n">
-        <v>392.0757530584314</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D243" t="n">
-        <v>385.3372471573089</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E243" t="n">
-        <v>387.02685546875</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F243" t="n">
-        <v>5748000</v>
+        <v>3265300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>389.6804891479818</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C244" t="n">
-        <v>397.1544867752485</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D244" t="n">
-        <v>389.3823372557507</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E244" t="n">
-        <v>393.8746643066406</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F244" t="n">
-        <v>3716200</v>
+        <v>5488900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>396.8264835430965</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C245" t="n">
-        <v>398.6850647467894</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D245" t="n">
-        <v>394.083395182361</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E245" t="n">
-        <v>397.214111328125</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F245" t="n">
-        <v>3265300</v>
+        <v>5565400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>397.5719145517662</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C246" t="n">
-        <v>402.6804729256668</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D246" t="n">
-        <v>392.8807991736857</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E246" t="n">
-        <v>398.4862976074219</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F246" t="n">
-        <v>5488900</v>
+        <v>7049400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>394.6200883073414</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C247" t="n">
-        <v>399.7684103646221</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D247" t="n">
-        <v>392.7814343556134</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E247" t="n">
-        <v>394.7095642089844</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F247" t="n">
-        <v>5565400</v>
+        <v>7735200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>389.9985512542227</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C248" t="n">
-        <v>401.4182544062181</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D248" t="n">
-        <v>388.0505547204797</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E248" t="n">
-        <v>398.3869018554688</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F248" t="n">
-        <v>7049400</v>
+        <v>4339900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>402.6904143062879</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C249" t="n">
-        <v>404.0420766863295</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D249" t="n">
-        <v>375.7661756497595</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E249" t="n">
-        <v>390.6545104980469</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F249" t="n">
-        <v>7735200</v>
+        <v>7478400</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>393.5765028166354</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C250" t="n">
-        <v>396.826479685953</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D250" t="n">
-        <v>385.2279163988086</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E250" t="n">
-        <v>385.9037475585938</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F250" t="n">
-        <v>4339900</v>
+        <v>4474000</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>388.0306670998862</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C251" t="n">
-        <v>389.3326475544677</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>373.5995091898494</v>
+        <v>375.5</v>
       </c>
       <c r="E251" t="n">
-        <v>376.7699890136719</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F251" t="n">
-        <v>7478400</v>
+        <v>4391400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,25 +6969,17 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>381.4400024414062</v>
-      </c>
-      <c r="C252" t="n">
-        <v>386.4599914550781</v>
-      </c>
-      <c r="D252" t="n">
-        <v>379.2799987792969</v>
-      </c>
-      <c r="E252" t="n">
-        <v>383.5499877929688</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>4474000</v>
+        <v>4414885</v>
       </c>
       <c r="G252" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -10530,34 +10522,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>383.55</v>
+        <v>375.26</v>
       </c>
       <c r="D2" t="n">
-        <v>376.77</v>
+        <v>375.93</v>
       </c>
       <c r="E2" t="n">
-        <v>381.44</v>
+        <v>375.9</v>
       </c>
       <c r="F2" t="n">
-        <v>386.46</v>
+        <v>380.18</v>
       </c>
       <c r="G2" t="n">
-        <v>379.2814</v>
+        <v>373.63</v>
       </c>
       <c r="H2" t="n">
-        <v>3843607</v>
+        <v>4414885</v>
       </c>
       <c r="I2" t="n">
-        <v>5298971</v>
+        <v>5268283</v>
       </c>
       <c r="J2" t="n">
-        <v>344272470016</v>
+        <v>336831447040</v>
       </c>
       <c r="K2" t="n">
-        <v>24.681467</v>
+        <v>24.148006</v>
       </c>
       <c r="L2" t="n">
-        <v>17.01221</v>
+        <v>16.596376</v>
       </c>
       <c r="M2" t="n">
         <v>15.54</v>
@@ -10572,7 +10564,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10588,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.5258913</v>
+        <v>3.4496834</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10600,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>393634512896</v>
+        <v>386193457152</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10627,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:14:31</t>
+          <t>2026-09-17 08:10:19</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B2" t="n">
-        <v>328.9313839638723</v>
+        <v>334.6199155242764</v>
       </c>
       <c r="C2" t="n">
-        <v>334.1036568566598</v>
+        <v>335.9835980004524</v>
       </c>
       <c r="D2" t="n">
-        <v>328.9313839638723</v>
+        <v>325.4539776391221</v>
       </c>
       <c r="E2" t="n">
-        <v>332.7496948242188</v>
+        <v>326.1358337402344</v>
       </c>
       <c r="F2" t="n">
-        <v>8467700</v>
+        <v>11255600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B3" t="n">
-        <v>334.6198842128155</v>
+        <v>327.7722315420273</v>
       </c>
       <c r="C3" t="n">
-        <v>335.9835665613874</v>
+        <v>332.116544623422</v>
       </c>
       <c r="D3" t="n">
-        <v>325.4539471853474</v>
+        <v>325.1812201416126</v>
       </c>
       <c r="E3" t="n">
-        <v>326.1358032226562</v>
+        <v>327.9573059082031</v>
       </c>
       <c r="F3" t="n">
-        <v>11255600</v>
+        <v>13656800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B4" t="n">
-        <v>327.7722315420273</v>
+        <v>325.7851652728215</v>
       </c>
       <c r="C4" t="n">
-        <v>332.116544623422</v>
+        <v>333.5971710589619</v>
       </c>
       <c r="D4" t="n">
-        <v>325.1812201416126</v>
+        <v>323.9734220131043</v>
       </c>
       <c r="E4" t="n">
-        <v>327.9573059082031</v>
+        <v>332.44775390625</v>
       </c>
       <c r="F4" t="n">
-        <v>13656800</v>
+        <v>8903700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B5" t="n">
-        <v>325.7851652728215</v>
+        <v>332.1555126407144</v>
       </c>
       <c r="C5" t="n">
-        <v>333.5971710589619</v>
+        <v>343.5520626481311</v>
       </c>
       <c r="D5" t="n">
-        <v>323.9734220131043</v>
+        <v>331.1424787070217</v>
       </c>
       <c r="E5" t="n">
-        <v>332.44775390625</v>
+        <v>338.6719970703125</v>
       </c>
       <c r="F5" t="n">
-        <v>8903700</v>
+        <v>12504100</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B6" t="n">
-        <v>332.1555126407144</v>
+        <v>341.1169531409808</v>
       </c>
       <c r="C6" t="n">
-        <v>343.5520626481311</v>
+        <v>345.3054131162871</v>
       </c>
       <c r="D6" t="n">
-        <v>331.1424787070217</v>
+        <v>338.8181484734079</v>
       </c>
       <c r="E6" t="n">
-        <v>338.6719970703125</v>
+        <v>342.6851806640625</v>
       </c>
       <c r="F6" t="n">
-        <v>12504100</v>
+        <v>9016300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B7" t="n">
-        <v>341.1168923851393</v>
+        <v>339.850626873286</v>
       </c>
       <c r="C7" t="n">
-        <v>345.305351614445</v>
+        <v>341.107176659279</v>
       </c>
       <c r="D7" t="n">
-        <v>338.8180881270031</v>
+        <v>334.6881040719941</v>
       </c>
       <c r="E7" t="n">
-        <v>342.6851196289062</v>
+        <v>336.5972595214844</v>
       </c>
       <c r="F7" t="n">
-        <v>9016300</v>
+        <v>8104900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B8" t="n">
-        <v>339.850626873286</v>
+        <v>338.9057887667535</v>
       </c>
       <c r="C8" t="n">
-        <v>341.107176659279</v>
+        <v>340.8928859402125</v>
       </c>
       <c r="D8" t="n">
-        <v>334.6881040719941</v>
+        <v>332.4477452475481</v>
       </c>
       <c r="E8" t="n">
-        <v>336.5972595214844</v>
+        <v>335.1556396484375</v>
       </c>
       <c r="F8" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B9" t="n">
-        <v>338.9057579077058</v>
+        <v>335.0582842806241</v>
       </c>
       <c r="C9" t="n">
-        <v>340.8928549002298</v>
+        <v>336.5875409769217</v>
       </c>
       <c r="D9" t="n">
-        <v>332.4477149765372</v>
+        <v>332.593905470377</v>
       </c>
       <c r="E9" t="n">
-        <v>335.1556091308594</v>
+        <v>336.2271423339844</v>
       </c>
       <c r="F9" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B10" t="n">
-        <v>335.0582538691371</v>
+        <v>334.8341777664455</v>
       </c>
       <c r="C10" t="n">
-        <v>336.5875104266321</v>
+        <v>340.2597161593411</v>
       </c>
       <c r="D10" t="n">
-        <v>332.5938752825687</v>
+        <v>333.4509951381029</v>
       </c>
       <c r="E10" t="n">
-        <v>336.2271118164062</v>
+        <v>336.3439636230469</v>
       </c>
       <c r="F10" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>334.8342081470359</v>
+        <v>334.9803326465864</v>
       </c>
       <c r="C11" t="n">
-        <v>340.2597470322082</v>
+        <v>339.6558538996071</v>
       </c>
       <c r="D11" t="n">
-        <v>333.4510253931927</v>
+        <v>332.7692198568235</v>
       </c>
       <c r="E11" t="n">
-        <v>336.343994140625</v>
+        <v>339.2662048339844</v>
       </c>
       <c r="F11" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B12" t="n">
-        <v>334.9803627786429</v>
+        <v>338.2823748022027</v>
       </c>
       <c r="C12" t="n">
-        <v>339.6558844522348</v>
+        <v>345.8703047797677</v>
       </c>
       <c r="D12" t="n">
-        <v>332.7692497899866</v>
+        <v>335.7108340068662</v>
       </c>
       <c r="E12" t="n">
-        <v>339.2662353515625</v>
+        <v>344.5455932617188</v>
       </c>
       <c r="F12" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B13" t="n">
-        <v>338.2824047650262</v>
+        <v>347.9840458817623</v>
       </c>
       <c r="C13" t="n">
-        <v>345.87033541468</v>
+        <v>358.4552243092751</v>
       </c>
       <c r="D13" t="n">
-        <v>335.7108637419195</v>
+        <v>347.3606312231566</v>
       </c>
       <c r="E13" t="n">
-        <v>344.5456237792969</v>
+        <v>350.8575439453125</v>
       </c>
       <c r="F13" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B14" t="n">
-        <v>347.9840761494036</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C14" t="n">
-        <v>358.4552554876992</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D14" t="n">
-        <v>347.3606614365734</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E14" t="n">
-        <v>350.8575744628906</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F14" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B15" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C15" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D15" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E15" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F15" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B16" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C16" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D16" t="n">
-        <v>348.77305405812</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E16" t="n">
-        <v>354.2278137207031</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F16" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B17" t="n">
-        <v>357.4130008055815</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C17" t="n">
-        <v>364.9132992932725</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D17" t="n">
-        <v>356.3123046396842</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E17" t="n">
-        <v>360.3254699707031</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F17" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B18" t="n">
-        <v>362.8579709138762</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="C18" t="n">
-        <v>366.4620162306247</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="D18" t="n">
-        <v>356.585002247802</v>
+        <v>343.3669828865441</v>
       </c>
       <c r="E18" t="n">
-        <v>358.1532592773438</v>
+        <v>345.3053588867188</v>
       </c>
       <c r="F18" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B19" t="n">
-        <v>359.8189245088024</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C19" t="n">
-        <v>359.8189245088024</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D19" t="n">
-        <v>343.3670132328114</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E19" t="n">
-        <v>345.3053894042969</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F19" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B20" t="n">
-        <v>345.5391423923842</v>
+        <v>345.743758076041</v>
       </c>
       <c r="C20" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9323197996358</v>
       </c>
       <c r="D20" t="n">
-        <v>344.155989405705</v>
+        <v>344.2339422221326</v>
       </c>
       <c r="E20" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945739746094</v>
       </c>
       <c r="F20" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B21" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C21" t="n">
-        <v>352.9322890785681</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D21" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E21" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F21" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B22" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C22" t="n">
-        <v>354.77327893078</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D22" t="n">
-        <v>346.6203751846734</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E22" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F22" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B23" t="n">
-        <v>352.4549874654966</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C23" t="n">
-        <v>352.6108411281484</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D23" t="n">
-        <v>345.207955645442</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E23" t="n">
-        <v>347.4190979003906</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F23" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406427804422</v>
       </c>
       <c r="C24" t="n">
-        <v>349.0945029745603</v>
+        <v>356.088306176199</v>
       </c>
       <c r="D24" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373588311709</v>
       </c>
       <c r="E24" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265808105469</v>
       </c>
       <c r="F24" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>349.2406127602151</v>
+        <v>355.6694171272672</v>
       </c>
       <c r="C25" t="n">
-        <v>356.0882755673564</v>
+        <v>361.4261039302107</v>
       </c>
       <c r="D25" t="n">
-        <v>348.2373288971846</v>
+        <v>352.1238131495958</v>
       </c>
       <c r="E25" t="n">
-        <v>355.0265502929688</v>
+        <v>355.8934326171875</v>
       </c>
       <c r="F25" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5199811240022</v>
       </c>
       <c r="C26" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589519694893</v>
       </c>
       <c r="D26" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7145736403219</v>
       </c>
       <c r="E26" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140441894531</v>
       </c>
       <c r="F26" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>354.5200118501019</v>
+        <v>346.3573918148306</v>
       </c>
       <c r="C27" t="n">
-        <v>354.5589826989666</v>
+        <v>352.8836273758504</v>
       </c>
       <c r="D27" t="n">
-        <v>348.7146038632694</v>
+        <v>344.4677364880268</v>
       </c>
       <c r="E27" t="n">
-        <v>352.1140747070312</v>
+        <v>351.1011047363281</v>
       </c>
       <c r="F27" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>346.3573617095742</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C28" t="n">
-        <v>352.883596703336</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D28" t="n">
-        <v>344.4677065470185</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E28" t="n">
-        <v>351.10107421875</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F28" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B29" t="n">
-        <v>351.9971738259649</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C29" t="n">
-        <v>355.9421471732778</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D29" t="n">
-        <v>350.6919328534217</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E29" t="n">
-        <v>353.0978698730469</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F29" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B30" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063760208146</v>
       </c>
       <c r="C30" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180833825795</v>
       </c>
       <c r="D30" t="n">
-        <v>352.0264145317695</v>
+        <v>349.328294109172</v>
       </c>
       <c r="E30" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2994079589844</v>
       </c>
       <c r="F30" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B31" t="n">
-        <v>370.8063128551364</v>
+        <v>354.8317550345645</v>
       </c>
       <c r="C31" t="n">
-        <v>371.118020163803</v>
+        <v>356.6532485328659</v>
       </c>
       <c r="D31" t="n">
-        <v>349.3282346022162</v>
+        <v>344.7015033078588</v>
       </c>
       <c r="E31" t="n">
-        <v>358.2993469238281</v>
+        <v>346.0457153320312</v>
       </c>
       <c r="F31" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B32" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C32" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D32" t="n">
-        <v>344.701472908826</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E32" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F32" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B33" t="n">
-        <v>338.5064021770676</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C33" t="n">
-        <v>345.3443442519412</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D33" t="n">
-        <v>334.6880914224008</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E33" t="n">
-        <v>335.8082580566406</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F33" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B34" t="n">
-        <v>335.4576039784424</v>
+        <v>330.3340313465691</v>
       </c>
       <c r="C34" t="n">
-        <v>337.298567772769</v>
+        <v>331.8633175824834</v>
       </c>
       <c r="D34" t="n">
-        <v>328.3761462441955</v>
+        <v>318.1290216159704</v>
       </c>
       <c r="E34" t="n">
-        <v>332.7009887695312</v>
+        <v>325.1325378417969</v>
       </c>
       <c r="F34" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B35" t="n">
-        <v>330.3340003407686</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C35" t="n">
-        <v>331.863286433141</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D35" t="n">
-        <v>318.128991755756</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E35" t="n">
-        <v>325.1325073242188</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F35" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B36" t="n">
-        <v>319.1323440808776</v>
+        <v>317.8367572482962</v>
       </c>
       <c r="C36" t="n">
-        <v>327.7722802636044</v>
+        <v>321.6453472920761</v>
       </c>
       <c r="D36" t="n">
-        <v>318.7135040219252</v>
+        <v>315.8107192097402</v>
       </c>
       <c r="E36" t="n">
-        <v>322.2493286132812</v>
+        <v>319.2394104003906</v>
       </c>
       <c r="F36" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B37" t="n">
-        <v>317.8368180152801</v>
+        <v>320.3888464018165</v>
       </c>
       <c r="C37" t="n">
-        <v>321.6454087872217</v>
+        <v>323.7493462451443</v>
       </c>
       <c r="D37" t="n">
-        <v>315.8107795893674</v>
+        <v>313.1125938905139</v>
       </c>
       <c r="E37" t="n">
-        <v>319.2394714355469</v>
+        <v>313.2197265625</v>
       </c>
       <c r="F37" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B38" t="n">
-        <v>320.3888776178953</v>
+        <v>311.3690496699339</v>
       </c>
       <c r="C38" t="n">
-        <v>323.7493777886428</v>
+        <v>316.1322033153182</v>
       </c>
       <c r="D38" t="n">
-        <v>313.1126243976539</v>
+        <v>306.0117020081513</v>
       </c>
       <c r="E38" t="n">
-        <v>313.2197570800781</v>
+        <v>315.801025390625</v>
       </c>
       <c r="F38" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B39" t="n">
-        <v>311.3690195806419</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C39" t="n">
-        <v>316.1321727657366</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D39" t="n">
-        <v>306.011672436569</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E39" t="n">
-        <v>315.8009948730469</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F39" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B40" t="n">
-        <v>311.6904703912621</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C40" t="n">
-        <v>315.8399890894766</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D40" t="n">
-        <v>308.9436347895907</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E40" t="n">
-        <v>313.2392272949219</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F40" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B41" t="n">
-        <v>314.9146147475993</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C41" t="n">
-        <v>319.3563404779885</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D41" t="n">
-        <v>311.583335312832</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E41" t="n">
-        <v>318.9570007324219</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F41" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B42" t="n">
-        <v>319.9310136403228</v>
+        <v>329.5742512174487</v>
       </c>
       <c r="C42" t="n">
-        <v>334.2692226106359</v>
+        <v>330.2366069819271</v>
       </c>
       <c r="D42" t="n">
-        <v>318.5965223212373</v>
+        <v>322.6973682057821</v>
       </c>
       <c r="E42" t="n">
-        <v>330.2658081054688</v>
+        <v>323.8954467773438</v>
       </c>
       <c r="F42" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="n">
-        <v>329.5743133227241</v>
+        <v>318.4699706680781</v>
       </c>
       <c r="C43" t="n">
-        <v>330.2366692120174</v>
+        <v>319.6972700691676</v>
       </c>
       <c r="D43" t="n">
-        <v>322.6974290151713</v>
+        <v>312.1775010814912</v>
       </c>
       <c r="E43" t="n">
-        <v>323.8955078125</v>
+        <v>313.511962890625</v>
       </c>
       <c r="F43" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B44" t="n">
-        <v>318.4699706680781</v>
+        <v>312.2846372515878</v>
       </c>
       <c r="C44" t="n">
-        <v>319.6972700691676</v>
+        <v>319.3758154633895</v>
       </c>
       <c r="D44" t="n">
-        <v>312.1775010814912</v>
+        <v>311.1449703398488</v>
       </c>
       <c r="E44" t="n">
-        <v>313.511962890625</v>
+        <v>312.2066955566406</v>
       </c>
       <c r="F44" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B45" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7877755793916</v>
       </c>
       <c r="C45" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650570211989</v>
       </c>
       <c r="D45" t="n">
-        <v>311.1450007536453</v>
+        <v>300.761474830703</v>
       </c>
       <c r="E45" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4467163085938</v>
       </c>
       <c r="F45" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B46" t="n">
-        <v>308.7877447280039</v>
+        <v>305.7876433202538</v>
       </c>
       <c r="C46" t="n">
-        <v>309.2650261221254</v>
+        <v>306.829898044689</v>
       </c>
       <c r="D46" t="n">
-        <v>300.7614447812334</v>
+        <v>296.6314554825427</v>
       </c>
       <c r="E46" t="n">
-        <v>305.4466857910156</v>
+        <v>301.0731811523438</v>
       </c>
       <c r="F46" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B47" t="n">
-        <v>305.7876433202538</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C47" t="n">
-        <v>306.829898044689</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D47" t="n">
-        <v>296.6314554825427</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E47" t="n">
-        <v>301.0731811523438</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F47" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B48" t="n">
-        <v>302.7485789287686</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C48" t="n">
-        <v>306.5863902909554</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D48" t="n">
-        <v>301.9595901197654</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E48" t="n">
-        <v>303.4596557617188</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F48" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B49" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1126871193919</v>
       </c>
       <c r="C49" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3984575068617</v>
       </c>
       <c r="D49" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819077342795</v>
       </c>
       <c r="E49" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748107910156</v>
       </c>
       <c r="F49" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B50" t="n">
-        <v>316.1127492028895</v>
+        <v>312.7911523817683</v>
       </c>
       <c r="C50" t="n">
-        <v>317.3985198428805</v>
+        <v>319.4927115758689</v>
       </c>
       <c r="D50" t="n">
-        <v>309.3819684958741</v>
+        <v>312.5768573008158</v>
       </c>
       <c r="E50" t="n">
-        <v>310.7748718261719</v>
+        <v>317.8173217773438</v>
       </c>
       <c r="F50" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B51" t="n">
-        <v>312.7911824167217</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C51" t="n">
-        <v>319.4927422543219</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D51" t="n">
-        <v>312.576887315192</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E51" t="n">
-        <v>317.8173522949219</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F51" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B52" t="n">
-        <v>318.1192834140923</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C52" t="n">
-        <v>326.4962325236318</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D52" t="n">
-        <v>317.4374570386713</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E52" t="n">
-        <v>321.1583557128906</v>
+        <v>321.216796875</v>
       </c>
       <c r="F52" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
-        <v>323.067540655824</v>
+        <v>318.6744960548122</v>
       </c>
       <c r="C53" t="n">
-        <v>323.4474098298547</v>
+        <v>321.4992731766471</v>
       </c>
       <c r="D53" t="n">
-        <v>320.3596462659403</v>
+        <v>314.6516105859225</v>
       </c>
       <c r="E53" t="n">
-        <v>321.216796875</v>
+        <v>314.8269348144531</v>
       </c>
       <c r="F53" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B54" t="n">
-        <v>318.6744960548122</v>
+        <v>314.9827696540157</v>
       </c>
       <c r="C54" t="n">
-        <v>321.4992731766471</v>
+        <v>320.1745424548712</v>
       </c>
       <c r="D54" t="n">
-        <v>314.6516105859225</v>
+        <v>314.4275465708089</v>
       </c>
       <c r="E54" t="n">
-        <v>314.8269348144531</v>
+        <v>316.1224365234375</v>
       </c>
       <c r="F54" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B55" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C55" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D55" t="n">
-        <v>314.4275769247672</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E55" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F55" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B56" t="n">
-        <v>317.5445892541937</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C56" t="n">
-        <v>332.5549060741021</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D56" t="n">
-        <v>316.58027624088</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E56" t="n">
-        <v>330.8989868164062</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F56" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B57" t="n">
-        <v>330.5970491985518</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C57" t="n">
-        <v>332.4088222358486</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D57" t="n">
-        <v>320.1940611974609</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E57" t="n">
-        <v>324.84033203125</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F57" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,25 +1925,25 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B58" t="n">
-        <v>326.3111546998924</v>
+        <v>322.3272916604559</v>
       </c>
       <c r="C58" t="n">
-        <v>327.0027312119329</v>
+        <v>322.7195306155714</v>
       </c>
       <c r="D58" t="n">
-        <v>319.9894943793851</v>
+        <v>316.5710720238113</v>
       </c>
       <c r="E58" t="n">
-        <v>322.3272399902344</v>
+        <v>317.3457641601562</v>
       </c>
       <c r="F58" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B59" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894639081939</v>
       </c>
       <c r="C59" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0325801360812</v>
       </c>
       <c r="D59" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278299745985</v>
       </c>
       <c r="E59" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261108398438</v>
       </c>
       <c r="F59" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G59" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B60" t="n">
-        <v>316.894669558022</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C60" t="n">
-        <v>320.0326109139432</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D60" t="n">
-        <v>316.2278603865539</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E60" t="n">
-        <v>317.3261413574219</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F60" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B61" t="n">
-        <v>316.4926256697473</v>
+        <v>323.964889169776</v>
       </c>
       <c r="C61" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727314078914</v>
       </c>
       <c r="D61" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3861176902447</v>
       </c>
       <c r="E61" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015991210938</v>
       </c>
       <c r="F61" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B62" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566402470831</v>
       </c>
       <c r="C62" t="n">
-        <v>332.6727006619286</v>
+        <v>338.291630780554</v>
       </c>
       <c r="D62" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291558641754</v>
       </c>
       <c r="E62" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2124938964844</v>
       </c>
       <c r="F62" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B63" t="n">
-        <v>330.9566402470831</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C63" t="n">
-        <v>338.291630780554</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D63" t="n">
-        <v>330.8291558641754</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E63" t="n">
-        <v>335.2124938964844</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F63" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B64" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C64" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D64" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E64" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F64" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B65" t="n">
-        <v>333.8200517828203</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C65" t="n">
-        <v>334.3789780492049</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D65" t="n">
-        <v>324.6120879365693</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E65" t="n">
-        <v>327.7206420898438</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F65" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B66" t="n">
-        <v>327.1420632206801</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C66" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D66" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E66" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F66" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B67" t="n">
-        <v>322.5527687928765</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C67" t="n">
-        <v>323.7785340619881</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D67" t="n">
-        <v>318.2773138986521</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E67" t="n">
-        <v>321.7781066894531</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F67" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B68" t="n">
-        <v>321.6996588106788</v>
+        <v>316.6397026430911</v>
       </c>
       <c r="C68" t="n">
-        <v>328.112871433911</v>
+        <v>323.4059214629105</v>
       </c>
       <c r="D68" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139372798661</v>
       </c>
       <c r="E68" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558959960938</v>
       </c>
       <c r="F68" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B69" t="n">
-        <v>316.639672337624</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C69" t="n">
-        <v>323.4058905098511</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D69" t="n">
-        <v>315.4139070917166</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E69" t="n">
-        <v>318.8558654785156</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F69" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B70" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951411847105</v>
       </c>
       <c r="C70" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116403629064</v>
       </c>
       <c r="D70" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458788110419</v>
       </c>
       <c r="E70" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289733886719</v>
       </c>
       <c r="F70" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B71" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C71" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D71" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E71" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F71" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B72" t="n">
-        <v>320.856335890976</v>
+        <v>324.4748280832652</v>
       </c>
       <c r="C72" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696711460541</v>
       </c>
       <c r="D72" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9154143417118</v>
       </c>
       <c r="E72" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5626220703125</v>
       </c>
       <c r="F72" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B73" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3372733311646</v>
       </c>
       <c r="C73" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6327869327114</v>
       </c>
       <c r="D73" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215374488926</v>
       </c>
       <c r="E73" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201538085938</v>
       </c>
       <c r="F73" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B74" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C74" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D74" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E74" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F74" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B75" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C75" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D75" t="n">
-        <v>323.484378234348</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E75" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F75" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B76" t="n">
-        <v>324.4845927435845</v>
+        <v>328.9464075107404</v>
       </c>
       <c r="C76" t="n">
-        <v>333.6631391122548</v>
+        <v>340.2136332445062</v>
       </c>
       <c r="D76" t="n">
-        <v>321.1505170252981</v>
+        <v>327.377421847917</v>
       </c>
       <c r="E76" t="n">
-        <v>329.8779602050781</v>
+        <v>335.3890075683594</v>
       </c>
       <c r="F76" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B77" t="n">
-        <v>328.9463775793847</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C77" t="n">
-        <v>340.2136022879278</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D77" t="n">
-        <v>327.3773920593259</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E77" t="n">
-        <v>335.3889770507812</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F77" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B78" t="n">
-        <v>341.5962793505171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C78" t="n">
-        <v>345.7736671379334</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D78" t="n">
-        <v>338.4288910460567</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E78" t="n">
-        <v>342.2042541503906</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F78" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B79" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C79" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D79" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E79" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F79" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B80" t="n">
-        <v>334.3985942399352</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C80" t="n">
-        <v>341.1549971070486</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D80" t="n">
-        <v>334.1926441199842</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E80" t="n">
-        <v>340.1253662109375</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F80" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B81" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8006860364687</v>
       </c>
       <c r="C81" t="n">
-        <v>342.2925015847546</v>
+        <v>336.0068200899902</v>
       </c>
       <c r="D81" t="n">
-        <v>335.8400862980764</v>
+        <v>327.4656947902304</v>
       </c>
       <c r="E81" t="n">
-        <v>337.3110046386719</v>
+        <v>333.9083251953125</v>
       </c>
       <c r="F81" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C82" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D82" t="n">
-        <v>327.465664861477</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E82" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F82" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="n">
-        <v>334.8790829701986</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C83" t="n">
-        <v>335.2124875436862</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D83" t="n">
-        <v>326.3967930031341</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E83" t="n">
-        <v>327.4558410644531</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F83" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B84" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012241113832</v>
       </c>
       <c r="C84" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688259956294</v>
       </c>
       <c r="D84" t="n">
-        <v>327.6225691502204</v>
+        <v>321.699638581413</v>
       </c>
       <c r="E84" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883056640625</v>
       </c>
       <c r="F84" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C85" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D85" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E85" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F85" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B86" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C86" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D86" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E86" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F86" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B87" t="n">
-        <v>321.0524690830655</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C87" t="n">
-        <v>333.3003373667196</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D87" t="n">
-        <v>320.1699239761241</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E87" t="n">
-        <v>331.8686218261719</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F87" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B88" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489839349073</v>
       </c>
       <c r="C88" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683609450301</v>
       </c>
       <c r="D88" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0469292856779</v>
       </c>
       <c r="E88" t="n">
-        <v>341.0079040527344</v>
+        <v>347.59765625</v>
       </c>
       <c r="F88" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B89" t="n">
-        <v>340.4489540449518</v>
+        <v>347.4113127291759</v>
       </c>
       <c r="C89" t="n">
-        <v>348.0683303861261</v>
+        <v>350.9317071763275</v>
       </c>
       <c r="D89" t="n">
-        <v>340.0468994310211</v>
+        <v>346.1463145255873</v>
       </c>
       <c r="E89" t="n">
-        <v>347.5976257324219</v>
+        <v>349.3529357910156</v>
       </c>
       <c r="F89" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B90" t="n">
-        <v>347.4113127291759</v>
+        <v>347.0876909760341</v>
       </c>
       <c r="C90" t="n">
-        <v>350.9317071763275</v>
+        <v>347.9114016111286</v>
       </c>
       <c r="D90" t="n">
-        <v>346.1463145255873</v>
+        <v>340.5371789096768</v>
       </c>
       <c r="E90" t="n">
-        <v>349.3529357910156</v>
+        <v>344.8224792480469</v>
       </c>
       <c r="F90" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B91" t="n">
-        <v>347.0877216940886</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C91" t="n">
-        <v>347.9114324020834</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D91" t="n">
-        <v>340.537209047996</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E91" t="n">
-        <v>344.822509765625</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F91" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B92" t="n">
-        <v>288.2705746047087</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C92" t="n">
-        <v>293.6933589672342</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D92" t="n">
-        <v>274.9636596388997</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E92" t="n">
-        <v>277.2190856933594</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F92" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B93" t="n">
-        <v>278.2193161239855</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C93" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D93" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E93" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F93" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="n">
-        <v>288.623596430627</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C94" t="n">
-        <v>289.8689931668393</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D94" t="n">
-        <v>283.6126820924317</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E94" t="n">
-        <v>286.6231689453125</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F94" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4747261855329</v>
       </c>
       <c r="C95" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7698129535399</v>
       </c>
       <c r="D95" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072456694325</v>
       </c>
       <c r="E95" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530700683594</v>
       </c>
       <c r="F95" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>280.4746956220067</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C96" t="n">
-        <v>284.7697819219751</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D96" t="n">
-        <v>276.8072155055542</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E96" t="n">
-        <v>280.0530395507812</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F96" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424507136568</v>
       </c>
       <c r="C97" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841654678224</v>
       </c>
       <c r="D97" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367562069888</v>
       </c>
       <c r="E97" t="n">
-        <v>278.6703796386719</v>
+        <v>270.5705261230469</v>
       </c>
       <c r="F97" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>276.5424819048067</v>
+        <v>268.9721802809009</v>
       </c>
       <c r="C98" t="n">
-        <v>278.9841969343727</v>
+        <v>271.5217784748567</v>
       </c>
       <c r="D98" t="n">
-        <v>268.7367865177365</v>
+        <v>261.1272811769848</v>
       </c>
       <c r="E98" t="n">
-        <v>270.570556640625</v>
+        <v>263.3434448242188</v>
       </c>
       <c r="F98" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>268.9721491110363</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C99" t="n">
-        <v>271.5217470095316</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D99" t="n">
-        <v>261.127250916227</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E99" t="n">
-        <v>263.3434143066406</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F99" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B100" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C100" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D100" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E100" t="n">
-        <v>271.286376953125</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F100" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" t="n">
-        <v>268.8348304873182</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C101" t="n">
-        <v>274.7479208968081</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D101" t="n">
-        <v>268.0209355231403</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E101" t="n">
-        <v>270.3547973632812</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F101" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B102" t="n">
-        <v>272.1395338130845</v>
+        <v>267.1580308957466</v>
       </c>
       <c r="C102" t="n">
-        <v>274.0713413766361</v>
+        <v>274.2674704297252</v>
       </c>
       <c r="D102" t="n">
-        <v>267.3639563652268</v>
+        <v>264.5691999285901</v>
       </c>
       <c r="E102" t="n">
-        <v>267.9229125976562</v>
+        <v>273.5025939941406</v>
       </c>
       <c r="F102" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B103" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7671258575986</v>
       </c>
       <c r="C103" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7591102609402</v>
       </c>
       <c r="D103" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626809260317</v>
       </c>
       <c r="E103" t="n">
-        <v>273.5025634765625</v>
+        <v>278.8567199707031</v>
       </c>
       <c r="F103" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B104" t="n">
-        <v>272.7670960064547</v>
+        <v>280.0922508710514</v>
       </c>
       <c r="C104" t="n">
-        <v>280.7590795351679</v>
+        <v>287.7704307745099</v>
       </c>
       <c r="D104" t="n">
-        <v>270.4626513270822</v>
+        <v>278.9939700602999</v>
       </c>
       <c r="E104" t="n">
-        <v>278.856689453125</v>
+        <v>287.5056762695312</v>
       </c>
       <c r="F104" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B105" t="n">
-        <v>280.092280601724</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C105" t="n">
-        <v>287.7704613201907</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D105" t="n">
-        <v>278.9939996743944</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E105" t="n">
-        <v>287.5057067871094</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F105" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B106" t="n">
-        <v>288.3000088357305</v>
+        <v>284.377578031072</v>
       </c>
       <c r="C106" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050624231632</v>
       </c>
       <c r="D106" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7395146362062</v>
       </c>
       <c r="E106" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124877929688</v>
       </c>
       <c r="F106" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B107" t="n">
-        <v>284.3775473228927</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C107" t="n">
-        <v>284.5050317012176</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D107" t="n">
-        <v>280.7394843208789</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E107" t="n">
-        <v>282.6124572753906</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F107" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B108" t="n">
-        <v>285.2503388393621</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C108" t="n">
-        <v>285.2503388393621</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D108" t="n">
-        <v>281.3278894670919</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E108" t="n">
-        <v>284.3089294433594</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F108" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B109" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C109" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D109" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E109" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F109" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B110" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7287838236561</v>
       </c>
       <c r="C110" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9248883144977</v>
       </c>
       <c r="D110" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5303926707583</v>
       </c>
       <c r="E110" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387329101562</v>
       </c>
       <c r="F110" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B111" t="n">
-        <v>276.7288152602706</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C111" t="n">
-        <v>276.9249197733898</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D111" t="n">
-        <v>266.5304229488273</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E111" t="n">
-        <v>268.6387634277344</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F111" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B112" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C112" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D112" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E112" t="n">
-        <v>278.6900024414062</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F112" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B113" t="n">
-        <v>281.4160980059485</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C113" t="n">
-        <v>289.5355657694184</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D113" t="n">
-        <v>279.7000266676773</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E113" t="n">
-        <v>281.102294921875</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F113" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B114" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C114" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D114" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E114" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F114" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B115" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C115" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D115" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E115" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F115" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B116" t="n">
-        <v>283.3871388529354</v>
+        <v>283.406772199052</v>
       </c>
       <c r="C116" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6334226238421</v>
       </c>
       <c r="D116" t="n">
-        <v>278.8468991181569</v>
+        <v>282.1025410732585</v>
       </c>
       <c r="E116" t="n">
-        <v>283.6028747558594</v>
+        <v>286.299560546875</v>
       </c>
       <c r="F116" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B117" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265691931125</v>
       </c>
       <c r="C117" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406159339096</v>
       </c>
       <c r="D117" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807450619272</v>
       </c>
       <c r="E117" t="n">
-        <v>286.2995300292969</v>
+        <v>283.17138671875</v>
       </c>
       <c r="F117" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B118" t="n">
-        <v>284.4265998459625</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C118" t="n">
-        <v>285.7406467283754</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D118" t="n">
-        <v>281.1807753649725</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E118" t="n">
-        <v>283.1714172363281</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F118" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,25 +3511,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B119" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C119" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D119" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E119" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F119" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3537,25 +3537,25 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B120" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C120" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D120" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E120" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F120" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G120" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B121" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C121" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D121" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E121" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F121" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B122" t="n">
-        <v>279.0580549356083</v>
+        <v>281.42981524537</v>
       </c>
       <c r="C122" t="n">
-        <v>282.8528771272727</v>
+        <v>284.1771098102745</v>
       </c>
       <c r="D122" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039702199029</v>
       </c>
       <c r="E122" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907409667969</v>
       </c>
       <c r="F122" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B123" t="n">
-        <v>281.4297838763166</v>
+        <v>274.7888644946905</v>
       </c>
       <c r="C123" t="n">
-        <v>284.177078134999</v>
+        <v>279.5521686416635</v>
       </c>
       <c r="D123" t="n">
-        <v>273.039671765164</v>
+        <v>274.5418055263856</v>
       </c>
       <c r="E123" t="n">
-        <v>273.7907104492188</v>
+        <v>278.7714538574219</v>
       </c>
       <c r="F123" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B124" t="n">
-        <v>274.7888344130931</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C124" t="n">
-        <v>279.5521380386192</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D124" t="n">
-        <v>274.5417754718342</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E124" t="n">
-        <v>278.7714233398438</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F124" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B125" t="n">
-        <v>280.6392236042361</v>
+        <v>284.4142561376558</v>
       </c>
       <c r="C125" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902591728541</v>
       </c>
       <c r="D125" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4890865630293</v>
       </c>
       <c r="E125" t="n">
-        <v>282.1314392089844</v>
+        <v>284.1869812011719</v>
       </c>
       <c r="F125" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B126" t="n">
-        <v>284.41428667964</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C126" t="n">
-        <v>285.5902898411239</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D126" t="n">
-        <v>281.4891167908925</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E126" t="n">
-        <v>284.18701171875</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F126" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B127" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589864168267</v>
       </c>
       <c r="C127" t="n">
-        <v>285.0072039222152</v>
+        <v>284.167211683611</v>
       </c>
       <c r="D127" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7752266949594</v>
       </c>
       <c r="E127" t="n">
-        <v>280.9850769042969</v>
+        <v>277.140869140625</v>
       </c>
       <c r="F127" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B128" t="n">
-        <v>280.6589555118485</v>
+        <v>275.7079269716043</v>
       </c>
       <c r="C128" t="n">
-        <v>284.1671803923218</v>
+        <v>279.769592245506</v>
       </c>
       <c r="D128" t="n">
-        <v>276.7751962176443</v>
+        <v>271.7648753401377</v>
       </c>
       <c r="E128" t="n">
-        <v>277.1408386230469</v>
+        <v>272.3479309082031</v>
       </c>
       <c r="F128" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B129" t="n">
-        <v>275.7078960775263</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C129" t="n">
-        <v>279.7695608963037</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D129" t="n">
-        <v>271.7648448878931</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E129" t="n">
-        <v>272.347900390625</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F129" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B130" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069555541203</v>
       </c>
       <c r="C130" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639086768414</v>
       </c>
       <c r="D130" t="n">
-        <v>265.9243614270812</v>
+        <v>264.4420149324948</v>
       </c>
       <c r="E130" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768432617188</v>
       </c>
       <c r="F130" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B131" t="n">
-        <v>265.7069856894997</v>
+        <v>271.7648489371355</v>
       </c>
       <c r="C131" t="n">
-        <v>270.1639393177099</v>
+        <v>272.8321303468297</v>
       </c>
       <c r="D131" t="n">
-        <v>264.44204492441</v>
+        <v>263.9676538860649</v>
       </c>
       <c r="E131" t="n">
-        <v>269.0768737792969</v>
+        <v>267.3671875</v>
       </c>
       <c r="F131" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B132" t="n">
-        <v>271.7648799566674</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C132" t="n">
-        <v>272.8321614881822</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D132" t="n">
-        <v>263.9676840156166</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E132" t="n">
-        <v>267.3672180175781</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F132" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B133" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C133" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D133" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E133" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F133" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B134" t="n">
-        <v>264.3530902318651</v>
+        <v>257.119221076063</v>
       </c>
       <c r="C134" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2439223272896</v>
       </c>
       <c r="D134" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505334149961</v>
       </c>
       <c r="E134" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102966308594</v>
       </c>
       <c r="F134" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" t="n">
-        <v>257.1191907461688</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C135" t="n">
-        <v>259.2438917467647</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D135" t="n">
-        <v>253.6505034942698</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E135" t="n">
-        <v>258.7102661132812</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F135" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C136" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D136" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E136" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F136" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B137" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867574628081</v>
       </c>
       <c r="C137" t="n">
-        <v>272.0613148441149</v>
+        <v>275.7573496838748</v>
       </c>
       <c r="D137" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356885397691</v>
       </c>
       <c r="E137" t="n">
-        <v>270.7568664550781</v>
+        <v>273.998291015625</v>
       </c>
       <c r="F137" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B138" t="n">
-        <v>269.0867274922702</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C138" t="n">
-        <v>275.757318970375</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D138" t="n">
-        <v>268.3356586528844</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E138" t="n">
-        <v>273.9982604980469</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F138" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B139" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C139" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D139" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E139" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F139" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B140" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3295702834321</v>
       </c>
       <c r="C140" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881602178994</v>
       </c>
       <c r="D140" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439063119584</v>
       </c>
       <c r="E140" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804016113281</v>
       </c>
       <c r="F140" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B141" t="n">
-        <v>308.3296014014268</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C141" t="n">
-        <v>309.2881914326393</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D141" t="n">
-        <v>301.2439367148364</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E141" t="n">
-        <v>302.3804321289062</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F141" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B142" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272252898824</v>
       </c>
       <c r="C142" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187390262146</v>
       </c>
       <c r="D142" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213410567302</v>
       </c>
       <c r="E142" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7497863769531</v>
       </c>
       <c r="F142" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B143" t="n">
-        <v>304.3272561704691</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C143" t="n">
-        <v>306.7187701494722</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D143" t="n">
-        <v>300.6213715612747</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E143" t="n">
-        <v>300.7498168945312</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F143" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B144" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C144" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D144" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E144" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F144" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C145" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D145" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E145" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F145" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B146" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2942713469933</v>
       </c>
       <c r="C146" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8617880440979</v>
       </c>
       <c r="D146" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4264912428012</v>
       </c>
       <c r="E146" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6777954101562</v>
       </c>
       <c r="F146" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B147" t="n">
-        <v>311.2943017295384</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C147" t="n">
-        <v>314.8618187748353</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D147" t="n">
-        <v>309.4265214430497</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E147" t="n">
-        <v>312.6778259277344</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F147" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="n">
-        <v>316.2848676157387</v>
+        <v>320.3761995931397</v>
       </c>
       <c r="C148" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719565905757</v>
       </c>
       <c r="D148" t="n">
-        <v>313.4091278691752</v>
+        <v>316.3540722325493</v>
       </c>
       <c r="E148" t="n">
-        <v>320.8110046386719</v>
+        <v>319.674560546875</v>
       </c>
       <c r="F148" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B149" t="n">
-        <v>320.37616900858</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C149" t="n">
-        <v>321.5719258918635</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D149" t="n">
-        <v>316.35404203196</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E149" t="n">
-        <v>319.6745300292969</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F149" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B150" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7522179221875</v>
       </c>
       <c r="C150" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418624071809</v>
       </c>
       <c r="D150" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931592239693</v>
       </c>
       <c r="E150" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611450195312</v>
       </c>
       <c r="F150" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B151" t="n">
-        <v>346.7521876325058</v>
+        <v>350.5074689695779</v>
       </c>
       <c r="C151" t="n">
-        <v>354.3418314545246</v>
+        <v>352.6519539416425</v>
       </c>
       <c r="D151" t="n">
-        <v>344.9931290879458</v>
+        <v>346.3766505322415</v>
       </c>
       <c r="E151" t="n">
-        <v>349.3611145019531</v>
+        <v>350.3888854980469</v>
       </c>
       <c r="F151" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B152" t="n">
-        <v>350.5074994974842</v>
+        <v>352.2961973442777</v>
       </c>
       <c r="C152" t="n">
-        <v>352.6519846563255</v>
+        <v>354.0651480045056</v>
       </c>
       <c r="D152" t="n">
-        <v>346.3766807003688</v>
+        <v>347.256218509828</v>
       </c>
       <c r="E152" t="n">
-        <v>350.388916015625</v>
+        <v>350.7446899414062</v>
       </c>
       <c r="F152" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B153" t="n">
-        <v>352.2961666917061</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C153" t="n">
-        <v>354.0651171980212</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D153" t="n">
-        <v>347.2561882957746</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E153" t="n">
-        <v>350.7446594238281</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F153" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C154" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D154" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E154" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F154" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B155" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C155" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D155" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E155" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F155" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C156" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D156" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E156" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F156" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C157" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D157" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E157" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F157" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C158" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D158" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E158" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F158" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B159" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216097846273</v>
       </c>
       <c r="C159" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260581192055</v>
       </c>
       <c r="D159" t="n">
-        <v>360.360183242299</v>
+        <v>357.553592134861</v>
       </c>
       <c r="E159" t="n">
-        <v>366.388427734375</v>
+        <v>359.58935546875</v>
       </c>
       <c r="F159" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B160" t="n">
-        <v>366.1216408565838</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C160" t="n">
-        <v>367.4260893018678</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D160" t="n">
-        <v>357.5536224796683</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E160" t="n">
-        <v>359.5893859863281</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F160" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B161" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C161" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D161" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E161" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F161" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B162" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="C162" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="D162" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="E162" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="F162" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B163" t="n">
-        <v>367.6138324799484</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C163" t="n">
-        <v>375.5098571777344</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D163" t="n">
-        <v>367.6138324799484</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E163" t="n">
-        <v>375.5098571777344</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F163" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B164" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3461148231528</v>
       </c>
       <c r="C164" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7447189140002</v>
       </c>
       <c r="D164" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5160002982997</v>
       </c>
       <c r="E164" t="n">
-        <v>379.9173889160156</v>
+        <v>391.7268371582031</v>
       </c>
       <c r="F164" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="n">
-        <v>378.3460853480032</v>
+        <v>391.8354914196509</v>
       </c>
       <c r="C165" t="n">
-        <v>392.7446883171237</v>
+        <v>399.3954891946478</v>
       </c>
       <c r="D165" t="n">
-        <v>377.5159708878205</v>
+        <v>388.3766661486073</v>
       </c>
       <c r="E165" t="n">
-        <v>391.726806640625</v>
+        <v>396.440673828125</v>
       </c>
       <c r="F165" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B166" t="n">
-        <v>391.835521582727</v>
+        <v>396.2825535174053</v>
       </c>
       <c r="C166" t="n">
-        <v>399.3955199396844</v>
+        <v>397.1719597005697</v>
       </c>
       <c r="D166" t="n">
-        <v>388.3766960454267</v>
+        <v>391.3413745458666</v>
       </c>
       <c r="E166" t="n">
-        <v>396.4407043457031</v>
+        <v>394.39501953125</v>
       </c>
       <c r="F166" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" t="n">
-        <v>396.2825841810375</v>
+        <v>389.661393370787</v>
       </c>
       <c r="C167" t="n">
-        <v>397.1719904330225</v>
+        <v>392.9522357226725</v>
       </c>
       <c r="D167" t="n">
-        <v>391.3414048271592</v>
+        <v>385.6590501412673</v>
       </c>
       <c r="E167" t="n">
-        <v>394.3950500488281</v>
+        <v>389.2167053222656</v>
       </c>
       <c r="F167" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B168" t="n">
-        <v>389.6613628183419</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C168" t="n">
-        <v>392.9522049122001</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D168" t="n">
-        <v>385.6590199026367</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E168" t="n">
-        <v>389.2166748046875</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F168" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B169" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119575218886</v>
       </c>
       <c r="C169" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432444558516</v>
       </c>
       <c r="D169" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512600592197</v>
       </c>
       <c r="E169" t="n">
-        <v>386.5286865234375</v>
+        <v>384.660888671875</v>
       </c>
       <c r="F169" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B170" t="n">
-        <v>385.4119880990537</v>
+        <v>384.9672762725209</v>
       </c>
       <c r="C170" t="n">
-        <v>390.3432754242469</v>
+        <v>388.7522365943216</v>
       </c>
       <c r="D170" t="n">
-        <v>382.9512904411622</v>
+        <v>376.2214128322495</v>
       </c>
       <c r="E170" t="n">
-        <v>384.6609191894531</v>
+        <v>378.7908020019531</v>
       </c>
       <c r="F170" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B171" t="n">
-        <v>384.9672452573303</v>
+        <v>376.6364218669779</v>
       </c>
       <c r="C171" t="n">
-        <v>388.7522052741927</v>
+        <v>381.5677088398597</v>
       </c>
       <c r="D171" t="n">
-        <v>376.2213825216763</v>
+        <v>376.0632583748818</v>
       </c>
       <c r="E171" t="n">
-        <v>378.790771484375</v>
+        <v>377.9804382324219</v>
       </c>
       <c r="F171" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B172" t="n">
-        <v>376.6364522760421</v>
+        <v>377.4270609393932</v>
       </c>
       <c r="C172" t="n">
-        <v>381.5677396470687</v>
+        <v>385.9456494081999</v>
       </c>
       <c r="D172" t="n">
-        <v>376.0632887376697</v>
+        <v>376.5277626686598</v>
       </c>
       <c r="E172" t="n">
-        <v>377.98046875</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F172" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="n">
-        <v>377.4270309363715</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C173" t="n">
-        <v>385.9456187280053</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D173" t="n">
-        <v>376.5277327371266</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E173" t="n">
-        <v>383.8999633789062</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F173" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C174" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D174" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E174" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F174" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312519906984</v>
       </c>
       <c r="C175" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6806841025421</v>
       </c>
       <c r="D175" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783087193446</v>
       </c>
       <c r="E175" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298461914062</v>
       </c>
       <c r="F175" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="n">
-        <v>380.4312827021371</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C176" t="n">
-        <v>384.6807151570288</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D176" t="n">
-        <v>376.4783391116702</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E176" t="n">
-        <v>378.0298767089844</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F176" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C177" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D177" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E177" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F177" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C178" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D178" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E178" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F178" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C179" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D179" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E179" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F179" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119903823484</v>
       </c>
       <c r="C180" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6581194399012</v>
       </c>
       <c r="D180" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2341151633045</v>
       </c>
       <c r="E180" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058776855469</v>
       </c>
       <c r="F180" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="n">
-        <v>385.4119603627872</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C181" t="n">
-        <v>396.6580885443842</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D181" t="n">
-        <v>385.2340851575979</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E181" t="n">
-        <v>391.8058471679688</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F181" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B182" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C182" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D182" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E182" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F182" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B183" t="n">
-        <v>392.4580996989546</v>
+        <v>405.1668188073661</v>
       </c>
       <c r="C183" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="D183" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6468293766872</v>
       </c>
       <c r="E183" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="F183" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B184" t="n">
-        <v>405.166788512205</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C184" t="n">
-        <v>408.1413879394531</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D184" t="n">
-        <v>402.6467992699509</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E184" t="n">
-        <v>408.1413879394531</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F184" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B185" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C185" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D185" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E185" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F185" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B186" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C186" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D186" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E186" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F186" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B187" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C187" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D187" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E187" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F187" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B188" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C188" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D188" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E188" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F188" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G188" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B189" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C189" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D189" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E189" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F189" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B190" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C190" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D190" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E190" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F190" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B191" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C191" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D191" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E191" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F191" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B192" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C192" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D192" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E192" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F192" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B193" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C193" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D193" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E193" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F193" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B194" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C194" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D194" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E194" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F194" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B195" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C195" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D195" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E195" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F195" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B196" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C196" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D196" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E196" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F196" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C197" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D197" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E197" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F197" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B198" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C198" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D198" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E198" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F198" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B199" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C199" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D199" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E199" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F199" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B200" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C200" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D200" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E200" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F200" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B201" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C201" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D201" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E201" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F201" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B202" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C202" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D202" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E202" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F202" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B203" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C203" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D203" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E203" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F203" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B204" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C204" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D204" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E204" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F204" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B205" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C205" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D205" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E205" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F205" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C206" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D206" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E206" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F206" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C207" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D207" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E207" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F207" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C208" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D208" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E208" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F208" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B209" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C209" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D209" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E209" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F209" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B210" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C210" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D210" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E210" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F210" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B211" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C211" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D211" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E211" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F211" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B212" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C212" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D212" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E212" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F212" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B213" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C213" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D213" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E213" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F213" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B214" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C214" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D214" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E214" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F214" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B215" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C215" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D215" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E215" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F215" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B216" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C216" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D216" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E216" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F216" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B217" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C217" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D217" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E217" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F217" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B218" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C218" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D218" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E218" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F218" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B219" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C219" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D219" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E219" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F219" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B220" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C220" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D220" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E220" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F220" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B221" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C221" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D221" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E221" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F221" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B222" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C222" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D222" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E222" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F222" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B223" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C223" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D223" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E223" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F223" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B224" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C224" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D224" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E224" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F224" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B225" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C225" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D225" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E225" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F225" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B226" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C226" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D226" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E226" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F226" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B227" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C227" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D227" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E227" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F227" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B228" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C228" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D228" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E228" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F228" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C229" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D229" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E229" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F229" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B230" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C230" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D230" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E230" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F230" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B231" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C231" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D231" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E231" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F231" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B232" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C232" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D232" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E232" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F232" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B233" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C233" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D233" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E233" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F233" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C234" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D234" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E234" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F234" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B235" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C235" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D235" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E235" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F235" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B236" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C236" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D236" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E236" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F236" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B237" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C237" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D237" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E237" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F237" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B238" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C238" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D238" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E238" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F238" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B239" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C239" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D239" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E239" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F239" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B240" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C240" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D240" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E240" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F240" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B241" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C241" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D241" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E241" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F241" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B242" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C242" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D242" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E242" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F242" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B243" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C243" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D243" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E243" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F243" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C244" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D244" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E244" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F244" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B245" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C245" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D245" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E245" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F245" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B246" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C246" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D246" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E246" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F246" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B247" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C247" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D247" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E247" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F247" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B248" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C248" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D248" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E248" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F248" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B249" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C249" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D249" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E249" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F249" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,25 +6917,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B250" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C250" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D250" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E250" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F250" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G250" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B251" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C251" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D251" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E251" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F251" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46282</v>
+      </c>
+      <c r="B252" t="n">
+        <v>376.4500122070312</v>
+      </c>
+      <c r="C252" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="D252" t="n">
+        <v>374.2000122070312</v>
+      </c>
+      <c r="E252" t="n">
+        <v>375.2099914550781</v>
+      </c>
       <c r="F252" t="n">
-        <v>4414885</v>
+        <v>4833700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10522,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="D2" t="n">
         <v>375.26</v>
       </c>
-      <c r="D2" t="n">
-        <v>375.93</v>
-      </c>
       <c r="E2" t="n">
-        <v>375.9</v>
+        <v>376.45</v>
       </c>
       <c r="F2" t="n">
-        <v>380.18</v>
+        <v>380.45</v>
       </c>
       <c r="G2" t="n">
-        <v>373.63</v>
+        <v>374.2</v>
       </c>
       <c r="H2" t="n">
-        <v>4414885</v>
+        <v>4712779</v>
       </c>
       <c r="I2" t="n">
-        <v>5268283</v>
+        <v>5136275</v>
       </c>
       <c r="J2" t="n">
-        <v>336831447040</v>
+        <v>336786554880</v>
       </c>
       <c r="K2" t="n">
-        <v>24.148006</v>
+        <v>24.098267</v>
       </c>
       <c r="L2" t="n">
-        <v>16.596376</v>
+        <v>16.594164</v>
       </c>
       <c r="M2" t="n">
-        <v>15.54</v>
+        <v>15.57</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10588,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4496834</v>
+        <v>3.4492238</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10600,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>386193457152</v>
+        <v>386148564992</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10627,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:10:19</t>
+          <t>2026-09-18 13:15:51</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B2" t="n">
-        <v>334.6199155242764</v>
+        <v>327.7722315420273</v>
       </c>
       <c r="C2" t="n">
-        <v>335.9835980004524</v>
+        <v>332.116544623422</v>
       </c>
       <c r="D2" t="n">
-        <v>325.4539776391221</v>
+        <v>325.1812201416126</v>
       </c>
       <c r="E2" t="n">
-        <v>326.1358337402344</v>
+        <v>327.9573059082031</v>
       </c>
       <c r="F2" t="n">
-        <v>11255600</v>
+        <v>13656800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>327.7722315420273</v>
+        <v>325.7851652728215</v>
       </c>
       <c r="C3" t="n">
-        <v>332.116544623422</v>
+        <v>333.5971710589619</v>
       </c>
       <c r="D3" t="n">
-        <v>325.1812201416126</v>
+        <v>323.9734220131043</v>
       </c>
       <c r="E3" t="n">
-        <v>327.9573059082031</v>
+        <v>332.44775390625</v>
       </c>
       <c r="F3" t="n">
-        <v>13656800</v>
+        <v>8903700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>325.7851652728215</v>
+        <v>332.1555425710952</v>
       </c>
       <c r="C4" t="n">
-        <v>333.5971710589619</v>
+        <v>343.5520936054497</v>
       </c>
       <c r="D4" t="n">
-        <v>323.9734220131043</v>
+        <v>331.1425085461183</v>
       </c>
       <c r="E4" t="n">
-        <v>332.44775390625</v>
+        <v>338.6720275878906</v>
       </c>
       <c r="F4" t="n">
-        <v>8903700</v>
+        <v>12504100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>332.1555126407144</v>
+        <v>341.1169227630601</v>
       </c>
       <c r="C5" t="n">
-        <v>343.5520626481311</v>
+        <v>345.3053823653661</v>
       </c>
       <c r="D5" t="n">
-        <v>331.1424787070217</v>
+        <v>338.8181183002055</v>
       </c>
       <c r="E5" t="n">
-        <v>338.6719970703125</v>
+        <v>342.6851501464844</v>
       </c>
       <c r="F5" t="n">
-        <v>12504100</v>
+        <v>9016300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>341.1169531409808</v>
+        <v>339.8505960607415</v>
       </c>
       <c r="C6" t="n">
-        <v>345.3054131162871</v>
+        <v>341.1071457328094</v>
       </c>
       <c r="D6" t="n">
-        <v>338.8181484734079</v>
+        <v>334.6880737275095</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6851806640625</v>
+        <v>336.5972290039062</v>
       </c>
       <c r="F6" t="n">
-        <v>9016300</v>
+        <v>8104900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>339.850626873286</v>
+        <v>338.9057887667535</v>
       </c>
       <c r="C7" t="n">
-        <v>341.107176659279</v>
+        <v>340.8928859402125</v>
       </c>
       <c r="D7" t="n">
-        <v>334.6881040719941</v>
+        <v>332.4477452475481</v>
       </c>
       <c r="E7" t="n">
-        <v>336.5972595214844</v>
+        <v>335.1556396484375</v>
       </c>
       <c r="F7" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>338.9057887667535</v>
+        <v>335.0582842806241</v>
       </c>
       <c r="C8" t="n">
-        <v>340.8928859402125</v>
+        <v>336.5875409769217</v>
       </c>
       <c r="D8" t="n">
-        <v>332.4477452475481</v>
+        <v>332.593905470377</v>
       </c>
       <c r="E8" t="n">
-        <v>335.1556396484375</v>
+        <v>336.2271423339844</v>
       </c>
       <c r="F8" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>335.0582842806241</v>
+        <v>334.8342081470359</v>
       </c>
       <c r="C9" t="n">
-        <v>336.5875409769217</v>
+        <v>340.2597470322082</v>
       </c>
       <c r="D9" t="n">
-        <v>332.593905470377</v>
+        <v>333.4510253931927</v>
       </c>
       <c r="E9" t="n">
-        <v>336.2271423339844</v>
+        <v>336.343994140625</v>
       </c>
       <c r="F9" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>334.8341777664455</v>
+        <v>334.9803025145298</v>
       </c>
       <c r="C10" t="n">
-        <v>340.2597161593411</v>
+        <v>339.6558233469793</v>
       </c>
       <c r="D10" t="n">
-        <v>333.4509951381029</v>
+        <v>332.7691899236603</v>
       </c>
       <c r="E10" t="n">
-        <v>336.3439636230469</v>
+        <v>339.2661743164062</v>
       </c>
       <c r="F10" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>334.9803326465864</v>
+        <v>338.2824347278496</v>
       </c>
       <c r="C11" t="n">
-        <v>339.6558538996071</v>
+        <v>345.8703660495923</v>
       </c>
       <c r="D11" t="n">
-        <v>332.7692198568235</v>
+        <v>335.7108934769728</v>
       </c>
       <c r="E11" t="n">
-        <v>339.2662048339844</v>
+        <v>344.545654296875</v>
       </c>
       <c r="F11" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>338.2823748022027</v>
+        <v>347.9840458817623</v>
       </c>
       <c r="C12" t="n">
-        <v>345.8703047797677</v>
+        <v>358.4552243092751</v>
       </c>
       <c r="D12" t="n">
-        <v>335.7108340068662</v>
+        <v>347.3606312231566</v>
       </c>
       <c r="E12" t="n">
-        <v>344.5455932617188</v>
+        <v>350.8575439453125</v>
       </c>
       <c r="F12" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>347.9840458817623</v>
+        <v>351.6659916768351</v>
       </c>
       <c r="C13" t="n">
-        <v>358.4552243092751</v>
+        <v>353.117336149959</v>
       </c>
       <c r="D13" t="n">
-        <v>347.3606312231566</v>
+        <v>347.8476513336176</v>
       </c>
       <c r="E13" t="n">
-        <v>350.8575439453125</v>
+        <v>349.464599609375</v>
       </c>
       <c r="F13" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C14" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D14" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E14" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F14" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C15" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D15" t="n">
-        <v>348.77305405812</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E15" t="n">
-        <v>354.2278137207031</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F15" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>357.4129705346734</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C16" t="n">
-        <v>364.9132683871306</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D16" t="n">
-        <v>356.3122744619989</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E16" t="n">
-        <v>360.325439453125</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F16" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>362.8580018323341</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="C17" t="n">
-        <v>366.4620474561767</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="D17" t="n">
-        <v>356.5850326317519</v>
+        <v>343.3670132328114</v>
       </c>
       <c r="E17" t="n">
-        <v>358.1532897949219</v>
+        <v>345.3053894042969</v>
       </c>
       <c r="F17" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>359.8188927085395</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C18" t="n">
-        <v>359.8188927085395</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D18" t="n">
-        <v>343.3669828865441</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E18" t="n">
-        <v>345.3053588867188</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F18" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>345.5391423923842</v>
+        <v>345.743758076041</v>
       </c>
       <c r="C19" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9323197996358</v>
       </c>
       <c r="D19" t="n">
-        <v>344.155989405705</v>
+        <v>344.2339422221326</v>
       </c>
       <c r="E19" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945739746094</v>
       </c>
       <c r="F19" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>345.743758076041</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C20" t="n">
-        <v>352.9323197996358</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D20" t="n">
-        <v>344.2339422221326</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E20" t="n">
-        <v>350.5945739746094</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F20" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4550493853661</v>
       </c>
       <c r="C21" t="n">
-        <v>354.77327893078</v>
+        <v>352.6109030753987</v>
       </c>
       <c r="D21" t="n">
-        <v>346.6203751846734</v>
+        <v>345.2080162921412</v>
       </c>
       <c r="E21" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4191589355469</v>
       </c>
       <c r="F21" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>352.4550184254314</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C22" t="n">
-        <v>352.6108721017735</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D22" t="n">
-        <v>345.2079859687916</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E22" t="n">
-        <v>347.4191284179688</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F22" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406427804422</v>
       </c>
       <c r="C23" t="n">
-        <v>349.0945029745603</v>
+        <v>356.088306176199</v>
       </c>
       <c r="D23" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373588311709</v>
       </c>
       <c r="E23" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265808105469</v>
       </c>
       <c r="F23" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>349.2406427804422</v>
+        <v>355.6694171272672</v>
       </c>
       <c r="C24" t="n">
-        <v>356.088306176199</v>
+        <v>361.4261039302107</v>
       </c>
       <c r="D24" t="n">
-        <v>348.2373588311709</v>
+        <v>352.1238131495958</v>
       </c>
       <c r="E24" t="n">
-        <v>355.0265808105469</v>
+        <v>355.8934326171875</v>
       </c>
       <c r="F24" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>355.6694171272672</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C25" t="n">
-        <v>361.4261039302107</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D25" t="n">
-        <v>352.1238131495958</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E25" t="n">
-        <v>355.8934326171875</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F25" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>354.5199811240022</v>
+        <v>346.3573918148306</v>
       </c>
       <c r="C26" t="n">
-        <v>354.5589519694893</v>
+        <v>352.8836273758504</v>
       </c>
       <c r="D26" t="n">
-        <v>348.7145736403219</v>
+        <v>344.4677364880268</v>
       </c>
       <c r="E26" t="n">
-        <v>352.1140441894531</v>
+        <v>351.1011047363281</v>
       </c>
       <c r="F26" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>346.3573918148306</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C27" t="n">
-        <v>352.8836273758504</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D27" t="n">
-        <v>344.4677364880268</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E27" t="n">
-        <v>351.1011047363281</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F27" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>351.9972042484119</v>
+        <v>354.071983391527</v>
       </c>
       <c r="C28" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7214365608302</v>
       </c>
       <c r="D28" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0264446674387</v>
       </c>
       <c r="E28" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876708984375</v>
       </c>
       <c r="F28" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063760208146</v>
       </c>
       <c r="C29" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180833825795</v>
       </c>
       <c r="D29" t="n">
-        <v>352.0264145317695</v>
+        <v>349.328294109172</v>
       </c>
       <c r="E29" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2994079589844</v>
       </c>
       <c r="F29" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>370.8063760208146</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C30" t="n">
-        <v>371.1180833825795</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D30" t="n">
-        <v>349.328294109172</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E30" t="n">
-        <v>358.2994079589844</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F30" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>354.8317550345645</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C31" t="n">
-        <v>356.6532485328659</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D31" t="n">
-        <v>344.7015033078588</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E31" t="n">
-        <v>346.0457153320312</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F31" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>338.5064329398476</v>
+        <v>335.4576347488759</v>
       </c>
       <c r="C32" t="n">
-        <v>345.3443756361395</v>
+        <v>337.298598712068</v>
       </c>
       <c r="D32" t="n">
-        <v>334.6881218381804</v>
+        <v>328.3761763650699</v>
       </c>
       <c r="E32" t="n">
-        <v>335.8082885742188</v>
+        <v>332.7010192871094</v>
       </c>
       <c r="F32" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>335.4576039784424</v>
+        <v>330.3340313465691</v>
       </c>
       <c r="C33" t="n">
-        <v>337.298567772769</v>
+        <v>331.8633175824834</v>
       </c>
       <c r="D33" t="n">
-        <v>328.3761462441955</v>
+        <v>318.1290216159704</v>
       </c>
       <c r="E33" t="n">
-        <v>332.7009887695312</v>
+        <v>325.1325378417969</v>
       </c>
       <c r="F33" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>330.3340313465691</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C34" t="n">
-        <v>331.8633175824834</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D34" t="n">
-        <v>318.1290216159704</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E34" t="n">
-        <v>325.1325378417969</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F34" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>319.1323138584834</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C35" t="n">
-        <v>327.7722492229931</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D35" t="n">
-        <v>318.7134738391959</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E35" t="n">
-        <v>322.2492980957031</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F35" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>317.8367572482962</v>
+        <v>320.388908833974</v>
       </c>
       <c r="C36" t="n">
-        <v>321.6453472920761</v>
+        <v>323.7494093321413</v>
       </c>
       <c r="D36" t="n">
-        <v>315.8107192097402</v>
+        <v>313.1126549047939</v>
       </c>
       <c r="E36" t="n">
-        <v>319.2394104003906</v>
+        <v>313.2197875976562</v>
       </c>
       <c r="F36" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>320.3888464018165</v>
+        <v>311.3690496699339</v>
       </c>
       <c r="C37" t="n">
-        <v>323.7493462451443</v>
+        <v>316.1322033153182</v>
       </c>
       <c r="D37" t="n">
-        <v>313.1125938905139</v>
+        <v>306.0117020081513</v>
       </c>
       <c r="E37" t="n">
-        <v>313.2197265625</v>
+        <v>315.801025390625</v>
       </c>
       <c r="F37" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>311.3690496699339</v>
+        <v>311.6904703912621</v>
       </c>
       <c r="C38" t="n">
-        <v>316.1322033153182</v>
+        <v>315.8399890894766</v>
       </c>
       <c r="D38" t="n">
-        <v>306.0117020081513</v>
+        <v>308.9436347895907</v>
       </c>
       <c r="E38" t="n">
-        <v>315.801025390625</v>
+        <v>313.2392272949219</v>
       </c>
       <c r="F38" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>311.6904400245728</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C39" t="n">
-        <v>315.8399583185172</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D39" t="n">
-        <v>308.9436046905141</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E39" t="n">
-        <v>313.2391967773438</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F39" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>314.9146147475993</v>
+        <v>319.9310727655453</v>
       </c>
       <c r="C40" t="n">
-        <v>319.3563404779885</v>
+        <v>334.2692843856479</v>
       </c>
       <c r="D40" t="n">
-        <v>311.583335312832</v>
+        <v>318.5965811998377</v>
       </c>
       <c r="E40" t="n">
-        <v>318.9570007324219</v>
+        <v>330.265869140625</v>
       </c>
       <c r="F40" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>319.931043202934</v>
+        <v>329.5742822700864</v>
       </c>
       <c r="C41" t="n">
-        <v>334.2692534981419</v>
+        <v>330.2366380969722</v>
       </c>
       <c r="D41" t="n">
-        <v>318.5965517605375</v>
+        <v>322.6973986104767</v>
       </c>
       <c r="E41" t="n">
-        <v>330.2658386230469</v>
+        <v>323.8954772949219</v>
       </c>
       <c r="F41" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>329.5742512174487</v>
+        <v>318.4699396678824</v>
       </c>
       <c r="C42" t="n">
-        <v>330.2366069819271</v>
+        <v>319.6972389495053</v>
       </c>
       <c r="D42" t="n">
-        <v>322.6973682057821</v>
+        <v>312.177470693811</v>
       </c>
       <c r="E42" t="n">
-        <v>323.8954467773438</v>
+        <v>313.5119323730469</v>
       </c>
       <c r="F42" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>318.4699706680781</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C43" t="n">
-        <v>319.6972700691676</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D43" t="n">
-        <v>312.1775010814912</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E43" t="n">
-        <v>313.511962890625</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F43" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>312.2846372515878</v>
+        <v>308.7877755793916</v>
       </c>
       <c r="C44" t="n">
-        <v>319.3758154633895</v>
+        <v>309.2650570211989</v>
       </c>
       <c r="D44" t="n">
-        <v>311.1449703398488</v>
+        <v>300.761474830703</v>
       </c>
       <c r="E44" t="n">
-        <v>312.2066955566406</v>
+        <v>305.4467163085938</v>
       </c>
       <c r="F44" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>308.7877755793916</v>
+        <v>305.7876743157023</v>
       </c>
       <c r="C45" t="n">
-        <v>309.2650570211989</v>
+        <v>306.8299291457832</v>
       </c>
       <c r="D45" t="n">
-        <v>300.761474830703</v>
+        <v>296.6314855498956</v>
       </c>
       <c r="E45" t="n">
-        <v>305.4467163085938</v>
+        <v>301.0732116699219</v>
       </c>
       <c r="F45" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>305.7876433202538</v>
+        <v>302.7485484827002</v>
       </c>
       <c r="C46" t="n">
-        <v>306.829898044689</v>
+        <v>306.5863594589355</v>
       </c>
       <c r="D46" t="n">
-        <v>296.6314554825427</v>
+        <v>301.9595597530421</v>
       </c>
       <c r="E46" t="n">
-        <v>301.0731811523438</v>
+        <v>303.4596252441406</v>
       </c>
       <c r="F46" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>302.7485789287686</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C47" t="n">
-        <v>306.5863902909554</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D47" t="n">
-        <v>301.9595901197654</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E47" t="n">
-        <v>303.4596557617188</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F47" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C48" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D48" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E48" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F48" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>316.1126871193919</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C49" t="n">
-        <v>317.3984575068617</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D49" t="n">
-        <v>309.3819077342795</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E49" t="n">
-        <v>310.7748107910156</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F49" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>312.7911523817683</v>
+        <v>318.1192531852973</v>
       </c>
       <c r="C50" t="n">
-        <v>319.4927115758689</v>
+        <v>326.4962014988301</v>
       </c>
       <c r="D50" t="n">
-        <v>312.5768573008158</v>
+        <v>317.4374268746658</v>
       </c>
       <c r="E50" t="n">
-        <v>317.8173217773438</v>
+        <v>321.1583251953125</v>
       </c>
       <c r="F50" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>318.1192834140923</v>
+        <v>323.0675713492342</v>
       </c>
       <c r="C51" t="n">
-        <v>326.4962325236318</v>
+        <v>323.4474405593548</v>
       </c>
       <c r="D51" t="n">
-        <v>317.4374570386713</v>
+        <v>320.3596767020838</v>
       </c>
       <c r="E51" t="n">
-        <v>321.1583557128906</v>
+        <v>321.2168273925781</v>
       </c>
       <c r="F51" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>323.067540655824</v>
+        <v>318.6745269453515</v>
       </c>
       <c r="C52" t="n">
-        <v>323.4474098298547</v>
+        <v>321.4993043410047</v>
       </c>
       <c r="D52" t="n">
-        <v>320.3596462659403</v>
+        <v>314.6516410865056</v>
       </c>
       <c r="E52" t="n">
-        <v>321.216796875</v>
+        <v>314.8269653320312</v>
       </c>
       <c r="F52" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>318.6744960548122</v>
+        <v>314.9827696540157</v>
       </c>
       <c r="C53" t="n">
-        <v>321.4992731766471</v>
+        <v>320.1745424548712</v>
       </c>
       <c r="D53" t="n">
-        <v>314.6516105859225</v>
+        <v>314.4275465708089</v>
       </c>
       <c r="E53" t="n">
-        <v>314.8269348144531</v>
+        <v>316.1224365234375</v>
       </c>
       <c r="F53" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>314.9827696540157</v>
+        <v>317.5446185401456</v>
       </c>
       <c r="C54" t="n">
-        <v>320.1745424548712</v>
+        <v>332.5549367443995</v>
       </c>
       <c r="D54" t="n">
-        <v>314.4275465708089</v>
+        <v>316.5803054378969</v>
       </c>
       <c r="E54" t="n">
-        <v>316.1224365234375</v>
+        <v>330.8990173339844</v>
       </c>
       <c r="F54" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>317.5445892541937</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C55" t="n">
-        <v>332.5549060741021</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D55" t="n">
-        <v>316.58027624088</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E55" t="n">
-        <v>330.8989868164062</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F55" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>330.5970181401507</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C56" t="n">
-        <v>332.4087910072381</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D56" t="n">
-        <v>320.1940311163831</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E56" t="n">
-        <v>324.8403015136719</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F56" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>326.3111546998924</v>
+        <v>322.3272916604559</v>
       </c>
       <c r="C57" t="n">
-        <v>327.0027312119329</v>
+        <v>322.7195306155714</v>
       </c>
       <c r="D57" t="n">
-        <v>319.9894943793851</v>
+        <v>316.5710720238113</v>
       </c>
       <c r="E57" t="n">
-        <v>322.3272399902344</v>
+        <v>317.3457641601562</v>
       </c>
       <c r="F57" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,25 +1925,25 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>322.3272916604559</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C58" t="n">
-        <v>322.7195306155714</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D58" t="n">
-        <v>316.5710720238113</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E58" t="n">
-        <v>317.3457641601562</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F58" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G58" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>316.894639081939</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C59" t="n">
-        <v>320.0325801360812</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D59" t="n">
-        <v>316.2278299745985</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E59" t="n">
-        <v>317.3261108398438</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F59" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>316.4926256697473</v>
+        <v>323.964889169776</v>
       </c>
       <c r="C60" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727314078914</v>
       </c>
       <c r="D60" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3861176902447</v>
       </c>
       <c r="E60" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015991210938</v>
       </c>
       <c r="F60" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>323.964889169776</v>
+        <v>330.9566402470831</v>
       </c>
       <c r="C61" t="n">
-        <v>332.6727314078914</v>
+        <v>338.291630780554</v>
       </c>
       <c r="D61" t="n">
-        <v>322.3861176902447</v>
+        <v>330.8291558641754</v>
       </c>
       <c r="E61" t="n">
-        <v>330.2015991210938</v>
+        <v>335.2124938964844</v>
       </c>
       <c r="F61" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>330.9566402470831</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C62" t="n">
-        <v>338.291630780554</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D62" t="n">
-        <v>330.8291558641754</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E62" t="n">
-        <v>335.2124938964844</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F62" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C63" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D63" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E63" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F63" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>333.8200517828203</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C64" t="n">
-        <v>334.3789780492049</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D64" t="n">
-        <v>324.6120879365693</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E64" t="n">
-        <v>327.7206420898438</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F64" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>327.1420632206801</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C65" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D65" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E65" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F65" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>322.5527687928765</v>
+        <v>321.6996282334502</v>
       </c>
       <c r="C66" t="n">
-        <v>323.7785340619881</v>
+        <v>328.112840247113</v>
       </c>
       <c r="D66" t="n">
-        <v>318.2773138986521</v>
+        <v>319.7482195784761</v>
       </c>
       <c r="E66" t="n">
-        <v>321.7781066894531</v>
+        <v>321.0720520019531</v>
       </c>
       <c r="F66" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>321.6996588106788</v>
+        <v>316.6397026430911</v>
       </c>
       <c r="C67" t="n">
-        <v>328.112871433911</v>
+        <v>323.4059214629105</v>
       </c>
       <c r="D67" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139372798661</v>
       </c>
       <c r="E67" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558959960938</v>
       </c>
       <c r="F67" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>316.6397026430911</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C68" t="n">
-        <v>323.4059214629105</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D68" t="n">
-        <v>315.4139372798661</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E68" t="n">
-        <v>318.8558959960938</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F68" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C69" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D69" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E69" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F69" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>318.8951411847105</v>
+        <v>320.8563659827469</v>
       </c>
       <c r="C70" t="n">
-        <v>322.6116403629064</v>
+        <v>325.455440199308</v>
       </c>
       <c r="D70" t="n">
-        <v>317.8458788110419</v>
+        <v>319.9345879995185</v>
       </c>
       <c r="E70" t="n">
-        <v>321.2289733886719</v>
+        <v>325.3965759277344</v>
       </c>
       <c r="F70" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>320.856335890976</v>
+        <v>324.4748280832652</v>
       </c>
       <c r="C71" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696711460541</v>
       </c>
       <c r="D71" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9154143417118</v>
       </c>
       <c r="E71" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5626220703125</v>
       </c>
       <c r="F71" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
-        <v>324.4748280832652</v>
+        <v>323.3372733311646</v>
       </c>
       <c r="C72" t="n">
-        <v>327.7696711460541</v>
+        <v>329.6327869327114</v>
       </c>
       <c r="D72" t="n">
-        <v>321.9154143417118</v>
+        <v>323.1215374488926</v>
       </c>
       <c r="E72" t="n">
-        <v>322.5626220703125</v>
+        <v>325.7201538085938</v>
       </c>
       <c r="F72" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>323.3372733311646</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C73" t="n">
-        <v>329.6327869327114</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D73" t="n">
-        <v>323.1215374488926</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E73" t="n">
-        <v>325.7201538085938</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F73" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845627249562</v>
       </c>
       <c r="C74" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631082445032</v>
       </c>
       <c r="D74" t="n">
-        <v>323.484378234348</v>
+        <v>321.1504873151108</v>
       </c>
       <c r="E74" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779296875</v>
       </c>
       <c r="F74" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>324.4845927435845</v>
+        <v>328.9464075107404</v>
       </c>
       <c r="C75" t="n">
-        <v>333.6631391122548</v>
+        <v>340.2136332445062</v>
       </c>
       <c r="D75" t="n">
-        <v>321.1505170252981</v>
+        <v>327.377421847917</v>
       </c>
       <c r="E75" t="n">
-        <v>329.8779602050781</v>
+        <v>335.3890075683594</v>
       </c>
       <c r="F75" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>328.9464075107404</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C76" t="n">
-        <v>340.2136332445062</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D76" t="n">
-        <v>327.377421847917</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E76" t="n">
-        <v>335.3890075683594</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F76" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>341.5962793505171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C77" t="n">
-        <v>345.7736671379334</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D77" t="n">
-        <v>338.4288910460567</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E77" t="n">
-        <v>342.2042541503906</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F77" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3986242436816</v>
       </c>
       <c r="C78" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1550277170099</v>
       </c>
       <c r="D78" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926741052517</v>
       </c>
       <c r="E78" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253967285156</v>
       </c>
       <c r="F78" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>334.3985942399352</v>
+        <v>340.5176266555306</v>
       </c>
       <c r="C79" t="n">
-        <v>341.1549971070486</v>
+        <v>342.2925325530242</v>
       </c>
       <c r="D79" t="n">
-        <v>334.1926441199842</v>
+        <v>335.840116682576</v>
       </c>
       <c r="E79" t="n">
-        <v>340.1253662109375</v>
+        <v>337.31103515625</v>
       </c>
       <c r="F79" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C80" t="n">
-        <v>342.2925015847546</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D80" t="n">
-        <v>335.8400862980764</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E80" t="n">
-        <v>337.3110046386719</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F80" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>334.8006860364687</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C81" t="n">
-        <v>336.0068200899902</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D81" t="n">
-        <v>327.4656947902304</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E81" t="n">
-        <v>333.9083251953125</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F81" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>334.8790829701986</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C82" t="n">
-        <v>335.2124875436862</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D82" t="n">
-        <v>326.3967930031341</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E82" t="n">
-        <v>327.4558410644531</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F82" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C83" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D83" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E83" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F83" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>328.7012241113832</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C84" t="n">
-        <v>332.8688259956294</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D84" t="n">
-        <v>321.699638581413</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E84" t="n">
-        <v>332.3883056640625</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F84" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524690830655</v>
       </c>
       <c r="C85" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003373667196</v>
       </c>
       <c r="D85" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1699239761241</v>
       </c>
       <c r="E85" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8686218261719</v>
       </c>
       <c r="F85" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C86" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D86" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E86" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F86" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C87" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D87" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E87" t="n">
-        <v>341.0079040527344</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F87" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>340.4489839349073</v>
+        <v>347.4113127291759</v>
       </c>
       <c r="C88" t="n">
-        <v>348.0683609450301</v>
+        <v>350.9317071763275</v>
       </c>
       <c r="D88" t="n">
-        <v>340.0469292856779</v>
+        <v>346.1463145255873</v>
       </c>
       <c r="E88" t="n">
-        <v>347.59765625</v>
+        <v>349.3529357910156</v>
       </c>
       <c r="F88" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>347.4113127291759</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C89" t="n">
-        <v>350.9317071763275</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D89" t="n">
-        <v>346.1463145255873</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E89" t="n">
-        <v>349.3529357910156</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F89" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>347.0876909760341</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C90" t="n">
-        <v>347.9114016111286</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D90" t="n">
-        <v>340.5371789096768</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E90" t="n">
-        <v>344.8224792480469</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F90" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>288.2705746047087</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C91" t="n">
-        <v>293.6933589672342</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D91" t="n">
-        <v>274.9636596388997</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E91" t="n">
-        <v>277.2190856933594</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F91" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>278.2193161239855</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C92" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D92" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E92" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F92" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>288.623596430627</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C93" t="n">
-        <v>289.8689931668393</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D93" t="n">
-        <v>283.6126820924317</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E93" t="n">
-        <v>286.6231689453125</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F93" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4747261855329</v>
       </c>
       <c r="C94" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7698129535399</v>
       </c>
       <c r="D94" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072456694325</v>
       </c>
       <c r="E94" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530700683594</v>
       </c>
       <c r="F94" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>280.4747261855329</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C95" t="n">
-        <v>284.7698129535399</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D95" t="n">
-        <v>276.8072456694325</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E95" t="n">
-        <v>280.0530700683594</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F95" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C96" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D96" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E96" t="n">
-        <v>278.6703796386719</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F96" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>276.5424507136568</v>
+        <v>268.9721802809009</v>
       </c>
       <c r="C97" t="n">
-        <v>278.9841654678224</v>
+        <v>271.5217784748567</v>
       </c>
       <c r="D97" t="n">
-        <v>268.7367562069888</v>
+        <v>261.1272811769848</v>
       </c>
       <c r="E97" t="n">
-        <v>270.5705261230469</v>
+        <v>263.3434448242188</v>
       </c>
       <c r="F97" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>268.9721802809009</v>
+        <v>261.8822794692194</v>
       </c>
       <c r="C98" t="n">
-        <v>271.5217784748567</v>
+        <v>272.4238601253656</v>
       </c>
       <c r="D98" t="n">
-        <v>261.1272811769848</v>
+        <v>261.2448875542619</v>
       </c>
       <c r="E98" t="n">
-        <v>263.3434448242188</v>
+        <v>271.2863464355469</v>
       </c>
       <c r="F98" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348608333229</v>
       </c>
       <c r="C99" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479519102809</v>
       </c>
       <c r="D99" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209657772727</v>
       </c>
       <c r="E99" t="n">
-        <v>271.286376953125</v>
+        <v>270.3548278808594</v>
       </c>
       <c r="F99" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>268.8348304873182</v>
+        <v>272.139502815215</v>
       </c>
       <c r="C100" t="n">
-        <v>274.7479208968081</v>
+        <v>274.0713101587253</v>
       </c>
       <c r="D100" t="n">
-        <v>268.0209355231403</v>
+        <v>267.3639259113162</v>
       </c>
       <c r="E100" t="n">
-        <v>270.3547973632812</v>
+        <v>267.9228820800781</v>
       </c>
       <c r="F100" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>272.1395338130845</v>
+        <v>267.1580308957466</v>
       </c>
       <c r="C101" t="n">
-        <v>274.0713413766361</v>
+        <v>274.2674704297252</v>
       </c>
       <c r="D101" t="n">
-        <v>267.3639563652268</v>
+        <v>264.5691999285901</v>
       </c>
       <c r="E101" t="n">
-        <v>267.9229125976562</v>
+        <v>273.5025939941406</v>
       </c>
       <c r="F101" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>267.1580308957466</v>
+        <v>272.7671258575986</v>
       </c>
       <c r="C102" t="n">
-        <v>274.2674704297252</v>
+        <v>280.7591102609402</v>
       </c>
       <c r="D102" t="n">
-        <v>264.5691999285901</v>
+        <v>270.4626809260317</v>
       </c>
       <c r="E102" t="n">
-        <v>273.5025939941406</v>
+        <v>278.8567199707031</v>
       </c>
       <c r="F102" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>272.7671258575986</v>
+        <v>280.0922508710514</v>
       </c>
       <c r="C103" t="n">
-        <v>280.7591102609402</v>
+        <v>287.7704307745099</v>
       </c>
       <c r="D103" t="n">
-        <v>270.4626809260317</v>
+        <v>278.9939700602999</v>
       </c>
       <c r="E103" t="n">
-        <v>278.8567199707031</v>
+        <v>287.5056762695312</v>
       </c>
       <c r="F103" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>280.0922508710514</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C104" t="n">
-        <v>287.7704307745099</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D104" t="n">
-        <v>278.9939700602999</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E104" t="n">
-        <v>287.5056762695312</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F104" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>288.3000088357305</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C105" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D105" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E105" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F105" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>284.377578031072</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C106" t="n">
-        <v>284.5050624231632</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D106" t="n">
-        <v>280.7395146362062</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E106" t="n">
-        <v>282.6124877929688</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F106" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>285.2503082207336</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C107" t="n">
-        <v>285.2503082207336</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D107" t="n">
-        <v>281.3278592694971</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E107" t="n">
-        <v>284.3088989257812</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F107" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C108" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D108" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E108" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F108" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C109" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D109" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E109" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F109" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>276.7287838236561</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C110" t="n">
-        <v>276.9248883144977</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D110" t="n">
-        <v>266.5303926707583</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E110" t="n">
-        <v>268.6387329101562</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F110" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C111" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D111" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E111" t="n">
-        <v>278.6900024414062</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F111" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>281.4160980059485</v>
+        <v>279.1802832976262</v>
       </c>
       <c r="C112" t="n">
-        <v>289.5355657694184</v>
+        <v>288.4274484322898</v>
       </c>
       <c r="D112" t="n">
-        <v>279.7000266676773</v>
+        <v>278.346757008166</v>
       </c>
       <c r="E112" t="n">
-        <v>281.102294921875</v>
+        <v>287.5841064453125</v>
       </c>
       <c r="F112" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C113" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D113" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E113" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F113" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C114" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D114" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E114" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F114" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>283.3871388529354</v>
+        <v>283.406772199052</v>
       </c>
       <c r="C115" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6334226238421</v>
       </c>
       <c r="D115" t="n">
-        <v>278.8468991181569</v>
+        <v>282.1025410732585</v>
       </c>
       <c r="E115" t="n">
-        <v>283.6028747558594</v>
+        <v>286.299560546875</v>
       </c>
       <c r="F115" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>283.406772199052</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C116" t="n">
-        <v>288.6334226238421</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D116" t="n">
-        <v>282.1025410732585</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E116" t="n">
-        <v>286.299560546875</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F116" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>284.4265691931125</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C117" t="n">
-        <v>285.7406159339096</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D117" t="n">
-        <v>281.1807450619272</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E117" t="n">
-        <v>283.17138671875</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F117" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,25 +3485,25 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C118" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D118" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E118" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F118" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3511,25 +3511,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C119" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D119" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E119" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F119" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G119" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C120" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D120" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E120" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F120" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>279.0580549356083</v>
+        <v>281.42981524537</v>
       </c>
       <c r="C121" t="n">
-        <v>282.8528771272727</v>
+        <v>284.1771098102745</v>
       </c>
       <c r="D121" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039702199029</v>
       </c>
       <c r="E121" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907409667969</v>
       </c>
       <c r="F121" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>281.42981524537</v>
+        <v>274.7888644946905</v>
       </c>
       <c r="C122" t="n">
-        <v>284.1771098102745</v>
+        <v>279.5521686416635</v>
       </c>
       <c r="D122" t="n">
-        <v>273.039702199029</v>
+        <v>274.5418055263856</v>
       </c>
       <c r="E122" t="n">
-        <v>273.7907409667969</v>
+        <v>278.7714538574219</v>
       </c>
       <c r="F122" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>274.7888644946905</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C123" t="n">
-        <v>279.5521686416635</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D123" t="n">
-        <v>274.5418055263856</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E123" t="n">
-        <v>278.7714538574219</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F123" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>280.6392236042361</v>
+        <v>284.4142561376558</v>
       </c>
       <c r="C124" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902591728541</v>
       </c>
       <c r="D124" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4890865630293</v>
       </c>
       <c r="E124" t="n">
-        <v>282.1314392089844</v>
+        <v>284.1869812011719</v>
       </c>
       <c r="F124" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>284.4142561376558</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C125" t="n">
-        <v>285.5902591728541</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D125" t="n">
-        <v>281.4890865630293</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E125" t="n">
-        <v>284.1869812011719</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F125" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589864168267</v>
       </c>
       <c r="C126" t="n">
-        <v>285.0072039222152</v>
+        <v>284.167211683611</v>
       </c>
       <c r="D126" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7752266949594</v>
       </c>
       <c r="E126" t="n">
-        <v>280.9850769042969</v>
+        <v>277.140869140625</v>
       </c>
       <c r="F126" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>280.6589864168267</v>
+        <v>275.7079269716043</v>
       </c>
       <c r="C127" t="n">
-        <v>284.167211683611</v>
+        <v>279.769592245506</v>
       </c>
       <c r="D127" t="n">
-        <v>276.7752266949594</v>
+        <v>271.7648753401377</v>
       </c>
       <c r="E127" t="n">
-        <v>277.140869140625</v>
+        <v>272.3479309082031</v>
       </c>
       <c r="F127" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>275.7079269716043</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C128" t="n">
-        <v>279.769592245506</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D128" t="n">
-        <v>271.7648753401377</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E128" t="n">
-        <v>272.3479309082031</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F128" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069555541203</v>
       </c>
       <c r="C129" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639086768414</v>
       </c>
       <c r="D129" t="n">
-        <v>265.9243614270812</v>
+        <v>264.4420149324948</v>
       </c>
       <c r="E129" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768432617188</v>
       </c>
       <c r="F129" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>265.7069555541203</v>
+        <v>271.7648489371355</v>
       </c>
       <c r="C130" t="n">
-        <v>270.1639086768414</v>
+        <v>272.8321303468297</v>
       </c>
       <c r="D130" t="n">
-        <v>264.4420149324948</v>
+        <v>263.9676538860649</v>
       </c>
       <c r="E130" t="n">
-        <v>269.0768432617188</v>
+        <v>267.3671875</v>
       </c>
       <c r="F130" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>271.7648489371355</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C131" t="n">
-        <v>272.8321303468297</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D131" t="n">
-        <v>263.9676538860649</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E131" t="n">
-        <v>267.3671875</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F131" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C132" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D132" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E132" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F132" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>264.3530902318651</v>
+        <v>257.119221076063</v>
       </c>
       <c r="C133" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2439223272896</v>
       </c>
       <c r="D133" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505334149961</v>
       </c>
       <c r="E133" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102966308594</v>
       </c>
       <c r="F133" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>257.119221076063</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C134" t="n">
-        <v>259.2439223272896</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D134" t="n">
-        <v>253.6505334149961</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E134" t="n">
-        <v>258.7102966308594</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F134" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C135" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D135" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E135" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F135" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867574628081</v>
       </c>
       <c r="C136" t="n">
-        <v>272.0613148441149</v>
+        <v>275.7573496838748</v>
       </c>
       <c r="D136" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356885397691</v>
       </c>
       <c r="E136" t="n">
-        <v>270.7568664550781</v>
+        <v>273.998291015625</v>
       </c>
       <c r="F136" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>269.0867574628081</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C137" t="n">
-        <v>275.7573496838748</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D137" t="n">
-        <v>268.3356885397691</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E137" t="n">
-        <v>273.998291015625</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F137" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C138" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D138" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E138" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F138" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3295702834321</v>
       </c>
       <c r="C139" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881602178994</v>
       </c>
       <c r="D139" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439063119584</v>
       </c>
       <c r="E139" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804016113281</v>
       </c>
       <c r="F139" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>308.3295702834321</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C140" t="n">
-        <v>309.2881602178994</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D140" t="n">
-        <v>301.2439063119584</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E140" t="n">
-        <v>302.3804016113281</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F140" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272252898824</v>
       </c>
       <c r="C141" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187390262146</v>
       </c>
       <c r="D141" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213410567302</v>
       </c>
       <c r="E141" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7497863769531</v>
       </c>
       <c r="F141" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>304.3272252898824</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C142" t="n">
-        <v>306.7187390262146</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D142" t="n">
-        <v>300.6213410567302</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E142" t="n">
-        <v>300.7497863769531</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F142" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C143" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D143" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E143" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F143" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C144" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D144" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E144" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F144" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2942713469933</v>
       </c>
       <c r="C145" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8617880440979</v>
       </c>
       <c r="D145" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4264912428012</v>
       </c>
       <c r="E145" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6777954101562</v>
       </c>
       <c r="F145" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>311.2942713469933</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C146" t="n">
-        <v>314.8617880440979</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D146" t="n">
-        <v>309.4264912428012</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E146" t="n">
-        <v>312.6777954101562</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F146" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>316.2848676157387</v>
+        <v>320.3761995931397</v>
       </c>
       <c r="C147" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719565905757</v>
       </c>
       <c r="D147" t="n">
-        <v>313.4091278691752</v>
+        <v>316.3540722325493</v>
       </c>
       <c r="E147" t="n">
-        <v>320.8110046386719</v>
+        <v>319.674560546875</v>
       </c>
       <c r="F147" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>320.3761995931397</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C148" t="n">
-        <v>321.5719565905757</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D148" t="n">
-        <v>316.3540722325493</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E148" t="n">
-        <v>319.674560546875</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F148" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7522179221875</v>
       </c>
       <c r="C149" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418624071809</v>
       </c>
       <c r="D149" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931592239693</v>
       </c>
       <c r="E149" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611450195312</v>
       </c>
       <c r="F149" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>346.7522179221875</v>
+        <v>350.5074689695779</v>
       </c>
       <c r="C150" t="n">
-        <v>354.3418624071809</v>
+        <v>352.6519539416425</v>
       </c>
       <c r="D150" t="n">
-        <v>344.9931592239693</v>
+        <v>346.3766505322415</v>
       </c>
       <c r="E150" t="n">
-        <v>349.3611450195312</v>
+        <v>350.3888854980469</v>
       </c>
       <c r="F150" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>350.5074689695779</v>
+        <v>352.2961973442777</v>
       </c>
       <c r="C151" t="n">
-        <v>352.6519539416425</v>
+        <v>354.0651480045056</v>
       </c>
       <c r="D151" t="n">
-        <v>346.3766505322415</v>
+        <v>347.256218509828</v>
       </c>
       <c r="E151" t="n">
-        <v>350.3888854980469</v>
+        <v>350.7446899414062</v>
       </c>
       <c r="F151" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>352.2961973442777</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C152" t="n">
-        <v>354.0651480045056</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D152" t="n">
-        <v>347.256218509828</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E152" t="n">
-        <v>350.7446899414062</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F152" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C153" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D153" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E153" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F153" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C154" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D154" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E154" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F154" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C155" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D155" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E155" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F155" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C156" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D156" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E156" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F156" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C157" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D157" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E157" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F157" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216097846273</v>
       </c>
       <c r="C158" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260581192055</v>
       </c>
       <c r="D158" t="n">
-        <v>360.360183242299</v>
+        <v>357.553592134861</v>
       </c>
       <c r="E158" t="n">
-        <v>366.388427734375</v>
+        <v>359.58935546875</v>
       </c>
       <c r="F158" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>366.1216097846273</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C159" t="n">
-        <v>367.4260581192055</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D159" t="n">
-        <v>357.553592134861</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E159" t="n">
-        <v>359.58935546875</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F159" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C160" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D160" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E160" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F160" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="C161" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="D161" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="E161" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="F161" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>367.6138623558188</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C162" t="n">
-        <v>375.5098876953125</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D162" t="n">
-        <v>367.6138623558188</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E162" t="n">
-        <v>375.5098876953125</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F162" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3461148231528</v>
       </c>
       <c r="C163" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7447189140002</v>
       </c>
       <c r="D163" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5160002982997</v>
       </c>
       <c r="E163" t="n">
-        <v>379.9173889160156</v>
+        <v>391.7268371582031</v>
       </c>
       <c r="F163" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>378.3461148231528</v>
+        <v>391.8354914196509</v>
       </c>
       <c r="C164" t="n">
-        <v>392.7447189140002</v>
+        <v>399.3954891946478</v>
       </c>
       <c r="D164" t="n">
-        <v>377.5160002982997</v>
+        <v>388.3766661486073</v>
       </c>
       <c r="E164" t="n">
-        <v>391.7268371582031</v>
+        <v>396.440673828125</v>
       </c>
       <c r="F164" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>391.8354914196509</v>
+        <v>396.2825535174053</v>
       </c>
       <c r="C165" t="n">
-        <v>399.3954891946478</v>
+        <v>397.1719597005697</v>
       </c>
       <c r="D165" t="n">
-        <v>388.3766661486073</v>
+        <v>391.3413745458666</v>
       </c>
       <c r="E165" t="n">
-        <v>396.440673828125</v>
+        <v>394.39501953125</v>
       </c>
       <c r="F165" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>396.2825535174053</v>
+        <v>389.661393370787</v>
       </c>
       <c r="C166" t="n">
-        <v>397.1719597005697</v>
+        <v>392.9522357226725</v>
       </c>
       <c r="D166" t="n">
-        <v>391.3413745458666</v>
+        <v>385.6590501412673</v>
       </c>
       <c r="E166" t="n">
-        <v>394.39501953125</v>
+        <v>389.2167053222656</v>
       </c>
       <c r="F166" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>389.661393370787</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C167" t="n">
-        <v>392.9522357226725</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D167" t="n">
-        <v>385.6590501412673</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E167" t="n">
-        <v>389.2167053222656</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F167" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119575218886</v>
       </c>
       <c r="C168" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432444558516</v>
       </c>
       <c r="D168" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512600592197</v>
       </c>
       <c r="E168" t="n">
-        <v>386.5286865234375</v>
+        <v>384.660888671875</v>
       </c>
       <c r="F168" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>385.4119575218886</v>
+        <v>384.9672762725209</v>
       </c>
       <c r="C169" t="n">
-        <v>390.3432444558516</v>
+        <v>388.7522365943216</v>
       </c>
       <c r="D169" t="n">
-        <v>382.9512600592197</v>
+        <v>376.2214128322495</v>
       </c>
       <c r="E169" t="n">
-        <v>384.660888671875</v>
+        <v>378.7908020019531</v>
       </c>
       <c r="F169" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>384.9672762725209</v>
+        <v>376.6364218669779</v>
       </c>
       <c r="C170" t="n">
-        <v>388.7522365943216</v>
+        <v>381.5677088398597</v>
       </c>
       <c r="D170" t="n">
-        <v>376.2214128322495</v>
+        <v>376.0632583748818</v>
       </c>
       <c r="E170" t="n">
-        <v>378.7908020019531</v>
+        <v>377.9804382324219</v>
       </c>
       <c r="F170" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>376.6364218669779</v>
+        <v>377.4270609393932</v>
       </c>
       <c r="C171" t="n">
-        <v>381.5677088398597</v>
+        <v>385.9456494081999</v>
       </c>
       <c r="D171" t="n">
-        <v>376.0632583748818</v>
+        <v>376.5277626686598</v>
       </c>
       <c r="E171" t="n">
-        <v>377.9804382324219</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F171" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>377.4270609393932</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C172" t="n">
-        <v>385.9456494081999</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D172" t="n">
-        <v>376.5277626686598</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E172" t="n">
-        <v>383.8999938964844</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F172" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C173" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D173" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E173" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F173" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312519906984</v>
       </c>
       <c r="C174" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6806841025421</v>
       </c>
       <c r="D174" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783087193446</v>
       </c>
       <c r="E174" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298461914062</v>
       </c>
       <c r="F174" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>380.4312519906984</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C175" t="n">
-        <v>384.6806841025421</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D175" t="n">
-        <v>376.4783087193446</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E175" t="n">
-        <v>378.0298461914062</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F175" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C176" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D176" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E176" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F176" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C177" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D177" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E177" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F177" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C178" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D178" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E178" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F178" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119903823484</v>
       </c>
       <c r="C179" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6581194399012</v>
       </c>
       <c r="D179" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2341151633045</v>
       </c>
       <c r="E179" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058776855469</v>
       </c>
       <c r="F179" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>385.4119903823484</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C180" t="n">
-        <v>396.6581194399012</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D180" t="n">
-        <v>385.2341151633045</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E180" t="n">
-        <v>391.8058776855469</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F180" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C181" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D181" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E181" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F181" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>392.4580996989546</v>
+        <v>405.1668188073661</v>
       </c>
       <c r="C182" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="D182" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6468293766872</v>
       </c>
       <c r="E182" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="F182" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>405.1668188073661</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C183" t="n">
-        <v>408.1414184570312</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D183" t="n">
-        <v>402.6468293766872</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E183" t="n">
-        <v>408.1414184570312</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F183" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C184" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D184" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E184" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F184" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C185" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D185" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E185" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F185" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C186" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D186" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E186" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F186" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C187" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D187" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E187" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F187" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G187" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C188" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D188" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E188" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F188" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C189" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D189" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E189" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F189" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C190" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D190" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E190" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F190" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C191" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D191" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E191" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F191" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C192" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D192" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E192" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F192" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C193" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D193" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E193" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F193" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C194" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D194" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E194" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F194" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C195" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D195" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E195" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F195" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C196" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D196" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E196" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F196" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C197" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D197" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E197" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F197" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C198" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D198" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E198" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F198" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C199" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D199" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E199" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F199" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C200" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D200" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E200" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F200" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C201" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D201" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E201" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F201" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C202" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D202" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E202" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F202" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C203" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D203" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E203" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F203" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C204" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D204" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E204" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F204" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C205" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D205" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E205" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F205" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C206" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D206" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E206" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F206" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C207" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D207" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E207" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F207" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C208" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D208" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E208" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F208" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C209" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D209" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E209" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F209" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C210" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D210" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E210" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F210" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C211" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D211" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E211" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F211" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C212" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D212" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E212" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F212" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C213" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D213" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E213" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F213" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C214" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D214" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E214" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F214" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C215" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D215" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E215" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F215" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C216" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D216" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E216" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F216" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C217" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D217" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E217" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F217" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C218" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D218" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E218" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F218" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C219" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D219" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E219" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F219" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C220" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D220" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E220" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F220" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C221" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D221" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E221" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F221" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C222" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D222" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E222" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F222" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C223" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D223" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E223" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F223" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C224" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D224" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E224" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F224" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C225" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D225" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E225" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F225" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C226" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D226" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E226" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F226" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C227" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D227" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E227" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F227" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C228" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D228" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E228" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F228" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C229" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D229" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E229" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F229" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C230" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D230" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E230" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F230" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C231" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D231" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E231" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F231" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C232" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D232" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E232" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F232" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C233" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D233" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E233" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F233" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C234" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D234" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E234" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F234" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C235" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D235" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E235" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F235" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C236" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D236" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E236" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F236" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C237" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D237" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E237" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F237" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C238" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D238" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E238" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F238" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C239" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D239" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E239" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F239" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C240" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D240" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E240" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F240" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C241" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D241" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E241" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F241" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C242" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D242" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E242" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F242" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C243" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D243" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E243" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F243" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C244" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D244" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E244" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F244" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C245" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D245" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E245" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F245" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C246" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D246" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E246" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F246" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C247" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D247" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E247" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F247" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C248" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D248" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F248" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C249" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D249" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E249" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F249" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G249" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E250" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F250" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C251" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D251" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E251" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F251" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C252" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D252" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E252" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F252" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="D2" t="n">
         <v>375.21</v>
       </c>
-      <c r="D2" t="n">
-        <v>375.26</v>
-      </c>
       <c r="E2" t="n">
-        <v>376.45</v>
+        <v>375.29</v>
       </c>
       <c r="F2" t="n">
-        <v>380.45</v>
+        <v>378.49</v>
       </c>
       <c r="G2" t="n">
-        <v>374.2</v>
+        <v>372.42</v>
       </c>
       <c r="H2" t="n">
-        <v>4712779</v>
+        <v>8563301</v>
       </c>
       <c r="I2" t="n">
-        <v>5136275</v>
+        <v>5186552</v>
       </c>
       <c r="J2" t="n">
-        <v>336786554880</v>
+        <v>338303483904</v>
       </c>
       <c r="K2" t="n">
-        <v>24.098267</v>
+        <v>24.098465</v>
       </c>
       <c r="L2" t="n">
-        <v>16.594164</v>
+        <v>16.668907</v>
       </c>
       <c r="M2" t="n">
-        <v>15.57</v>
+        <v>15.64</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4492238</v>
+        <v>3.4647596</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>386148564992</v>
+        <v>387665494016</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:15:51</t>
+          <t>2026-09-19 15:21:36</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>327.7722315420273</v>
+        <v>339.850626873286</v>
       </c>
       <c r="C2" t="n">
-        <v>332.116544623422</v>
+        <v>341.107176659279</v>
       </c>
       <c r="D2" t="n">
-        <v>325.1812201416126</v>
+        <v>334.6881040719941</v>
       </c>
       <c r="E2" t="n">
-        <v>327.9573059082031</v>
+        <v>336.5972595214844</v>
       </c>
       <c r="F2" t="n">
-        <v>13656800</v>
+        <v>8104900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>325.7851652728215</v>
+        <v>338.9057887667535</v>
       </c>
       <c r="C3" t="n">
-        <v>333.5971710589619</v>
+        <v>340.8928859402125</v>
       </c>
       <c r="D3" t="n">
-        <v>323.9734220131043</v>
+        <v>332.4477452475481</v>
       </c>
       <c r="E3" t="n">
-        <v>332.44775390625</v>
+        <v>335.1556396484375</v>
       </c>
       <c r="F3" t="n">
-        <v>8903700</v>
+        <v>6774700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>332.1555425710952</v>
+        <v>335.0582538691371</v>
       </c>
       <c r="C4" t="n">
-        <v>343.5520936054497</v>
+        <v>336.5875104266321</v>
       </c>
       <c r="D4" t="n">
-        <v>331.1425085461183</v>
+        <v>332.5938752825687</v>
       </c>
       <c r="E4" t="n">
-        <v>338.6720275878906</v>
+        <v>336.2271118164062</v>
       </c>
       <c r="F4" t="n">
-        <v>12504100</v>
+        <v>6878900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>341.1169227630601</v>
+        <v>334.8342385276262</v>
       </c>
       <c r="C5" t="n">
-        <v>345.3053823653661</v>
+        <v>340.2597779050752</v>
       </c>
       <c r="D5" t="n">
-        <v>338.8181183002055</v>
+        <v>333.4510556482824</v>
       </c>
       <c r="E5" t="n">
-        <v>342.6851501464844</v>
+        <v>336.3440246582031</v>
       </c>
       <c r="F5" t="n">
-        <v>9016300</v>
+        <v>7429700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>339.8505960607415</v>
+        <v>334.9803025145298</v>
       </c>
       <c r="C6" t="n">
-        <v>341.1071457328094</v>
+        <v>339.6558233469793</v>
       </c>
       <c r="D6" t="n">
-        <v>334.6880737275095</v>
+        <v>332.7691899236603</v>
       </c>
       <c r="E6" t="n">
-        <v>336.5972290039062</v>
+        <v>339.2661743164062</v>
       </c>
       <c r="F6" t="n">
-        <v>8104900</v>
+        <v>8825500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>338.9057887667535</v>
+        <v>338.2823748022027</v>
       </c>
       <c r="C7" t="n">
-        <v>340.8928859402125</v>
+        <v>345.8703047797677</v>
       </c>
       <c r="D7" t="n">
-        <v>332.4477452475481</v>
+        <v>335.7108340068662</v>
       </c>
       <c r="E7" t="n">
-        <v>335.1556396484375</v>
+        <v>344.5455932617188</v>
       </c>
       <c r="F7" t="n">
-        <v>6774700</v>
+        <v>8564200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>335.0582842806241</v>
+        <v>347.9840761494036</v>
       </c>
       <c r="C8" t="n">
-        <v>336.5875409769217</v>
+        <v>358.4552554876992</v>
       </c>
       <c r="D8" t="n">
-        <v>332.593905470377</v>
+        <v>347.3606614365734</v>
       </c>
       <c r="E8" t="n">
-        <v>336.2271423339844</v>
+        <v>350.8575744628906</v>
       </c>
       <c r="F8" t="n">
-        <v>6878900</v>
+        <v>13494800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>334.8342081470359</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C9" t="n">
-        <v>340.2597470322082</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D9" t="n">
-        <v>333.4510253931927</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E9" t="n">
-        <v>336.343994140625</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F9" t="n">
-        <v>7429700</v>
+        <v>7181700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>334.9803025145298</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C10" t="n">
-        <v>339.6558233469793</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D10" t="n">
-        <v>332.7691899236603</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E10" t="n">
-        <v>339.2661743164062</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F10" t="n">
-        <v>8825500</v>
+        <v>7236200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>338.2824347278496</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C11" t="n">
-        <v>345.8703660495923</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D11" t="n">
-        <v>335.7108934769728</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E11" t="n">
-        <v>344.545654296875</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F11" t="n">
-        <v>8564200</v>
+        <v>9438300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>347.9840458817623</v>
+        <v>362.8580327507921</v>
       </c>
       <c r="C12" t="n">
-        <v>358.4552243092751</v>
+        <v>366.4620786817287</v>
       </c>
       <c r="D12" t="n">
-        <v>347.3606312231566</v>
+        <v>356.5850630157017</v>
       </c>
       <c r="E12" t="n">
-        <v>350.8575439453125</v>
+        <v>358.1533203125</v>
       </c>
       <c r="F12" t="n">
-        <v>13494800</v>
+        <v>8759800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>351.6659916768351</v>
+        <v>359.8189563090651</v>
       </c>
       <c r="C13" t="n">
-        <v>353.117336149959</v>
+        <v>359.8189563090651</v>
       </c>
       <c r="D13" t="n">
-        <v>347.8476513336176</v>
+        <v>343.3670435790787</v>
       </c>
       <c r="E13" t="n">
-        <v>349.464599609375</v>
+        <v>345.305419921875</v>
       </c>
       <c r="F13" t="n">
-        <v>7181700</v>
+        <v>13141900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>350.0880452744822</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C14" t="n">
-        <v>355.2603182962649</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D14" t="n">
-        <v>348.77305405812</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E14" t="n">
-        <v>354.2278137207031</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F14" t="n">
-        <v>7236200</v>
+        <v>5659400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>357.4129705346734</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C15" t="n">
-        <v>364.9132683871306</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D15" t="n">
-        <v>356.3122744619989</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E15" t="n">
-        <v>360.325439453125</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F15" t="n">
-        <v>9438300</v>
+        <v>5974800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>362.8580018323341</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C16" t="n">
-        <v>366.4620474561767</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D16" t="n">
-        <v>356.5850326317519</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E16" t="n">
-        <v>358.1532897949219</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F16" t="n">
-        <v>8759800</v>
+        <v>6579600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>359.8189245088024</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C17" t="n">
-        <v>359.8189245088024</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D17" t="n">
-        <v>343.3670132328114</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E17" t="n">
-        <v>345.3053894042969</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F17" t="n">
-        <v>13141900</v>
+        <v>5872100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>345.5391423923842</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C18" t="n">
-        <v>349.8445144711653</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D18" t="n">
-        <v>344.155989405705</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E18" t="n">
-        <v>349.3574829101562</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F18" t="n">
-        <v>5659400</v>
+        <v>8608400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>345.743758076041</v>
+        <v>349.2406127602151</v>
       </c>
       <c r="C19" t="n">
-        <v>352.9323197996358</v>
+        <v>356.0882755673564</v>
       </c>
       <c r="D19" t="n">
-        <v>344.2339422221326</v>
+        <v>348.2373288971846</v>
       </c>
       <c r="E19" t="n">
-        <v>350.5945739746094</v>
+        <v>355.0265502929688</v>
       </c>
       <c r="F19" t="n">
-        <v>5974800</v>
+        <v>5996500</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>350.0685670322262</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C20" t="n">
-        <v>354.77327893078</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D20" t="n">
-        <v>346.6203751846734</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E20" t="n">
-        <v>351.7828979492188</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F20" t="n">
-        <v>6579600</v>
+        <v>6885300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>352.4550493853661</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C21" t="n">
-        <v>352.6109030753987</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D21" t="n">
-        <v>345.2080162921412</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E21" t="n">
-        <v>347.4191589355469</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F21" t="n">
-        <v>5872100</v>
+        <v>7833000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>341.896162102252</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C22" t="n">
-        <v>349.0945029745603</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D22" t="n">
-        <v>341.7305582890092</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E22" t="n">
-        <v>347.3509216308594</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F22" t="n">
-        <v>8608400</v>
+        <v>5756700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>349.2406427804422</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C23" t="n">
-        <v>356.088306176199</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D23" t="n">
-        <v>348.2373588311709</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E23" t="n">
-        <v>355.0265808105469</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F23" t="n">
-        <v>5996500</v>
+        <v>5462100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>355.6694171272672</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C24" t="n">
-        <v>361.4261039302107</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D24" t="n">
-        <v>352.1238131495958</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E24" t="n">
-        <v>355.8934326171875</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F24" t="n">
-        <v>6885300</v>
+        <v>7766400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>354.5200118501019</v>
+        <v>370.8063128551364</v>
       </c>
       <c r="C25" t="n">
-        <v>354.5589826989666</v>
+        <v>371.118020163803</v>
       </c>
       <c r="D25" t="n">
-        <v>348.7146038632694</v>
+        <v>349.3282346022162</v>
       </c>
       <c r="E25" t="n">
-        <v>352.1140747070312</v>
+        <v>358.2993469238281</v>
       </c>
       <c r="F25" t="n">
-        <v>7833000</v>
+        <v>18858700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>346.3573918148306</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C26" t="n">
-        <v>352.8836273758504</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D26" t="n">
-        <v>344.4677364880268</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E26" t="n">
-        <v>351.1011047363281</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F26" t="n">
-        <v>5756700</v>
+        <v>11874900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>351.9972042484119</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C27" t="n">
-        <v>355.9421779366814</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D27" t="n">
-        <v>350.6919631630593</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E27" t="n">
-        <v>353.097900390625</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F27" t="n">
-        <v>5462100</v>
+        <v>11441900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>354.071983391527</v>
+        <v>335.4576347488759</v>
       </c>
       <c r="C28" t="n">
-        <v>356.7214365608302</v>
+        <v>337.298598712068</v>
       </c>
       <c r="D28" t="n">
-        <v>352.0264446674387</v>
+        <v>328.3761763650699</v>
       </c>
       <c r="E28" t="n">
-        <v>356.4876708984375</v>
+        <v>332.7010192871094</v>
       </c>
       <c r="F28" t="n">
-        <v>7766400</v>
+        <v>8390800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>370.8063760208146</v>
+        <v>330.3340623523696</v>
       </c>
       <c r="C29" t="n">
-        <v>371.1180833825795</v>
+        <v>331.8633487318257</v>
       </c>
       <c r="D29" t="n">
-        <v>349.328294109172</v>
+        <v>318.1290514761847</v>
       </c>
       <c r="E29" t="n">
-        <v>358.2994079589844</v>
+        <v>325.132568359375</v>
       </c>
       <c r="F29" t="n">
-        <v>18858700</v>
+        <v>11181400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>354.8317237421505</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C30" t="n">
-        <v>356.6532170798153</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D30" t="n">
-        <v>344.701472908826</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E30" t="n">
-        <v>346.0456848144531</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F30" t="n">
-        <v>11874900</v>
+        <v>9646600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>338.5064329398476</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C31" t="n">
-        <v>345.3443756361395</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D31" t="n">
-        <v>334.6881218381804</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E31" t="n">
-        <v>335.8082885742188</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F31" t="n">
-        <v>11441900</v>
+        <v>9697100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>335.4576347488759</v>
+        <v>320.3888464018165</v>
       </c>
       <c r="C32" t="n">
-        <v>337.298598712068</v>
+        <v>323.7493462451443</v>
       </c>
       <c r="D32" t="n">
-        <v>328.3761763650699</v>
+        <v>313.1125938905139</v>
       </c>
       <c r="E32" t="n">
-        <v>332.7010192871094</v>
+        <v>313.2197265625</v>
       </c>
       <c r="F32" t="n">
-        <v>8390800</v>
+        <v>7922100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>330.3340313465691</v>
+        <v>311.3690496699339</v>
       </c>
       <c r="C33" t="n">
-        <v>331.8633175824834</v>
+        <v>316.1322033153182</v>
       </c>
       <c r="D33" t="n">
-        <v>318.1290216159704</v>
+        <v>306.0117020081513</v>
       </c>
       <c r="E33" t="n">
-        <v>325.1325378417969</v>
+        <v>315.801025390625</v>
       </c>
       <c r="F33" t="n">
-        <v>11181400</v>
+        <v>9402900</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>319.1323138584834</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C34" t="n">
-        <v>327.7722492229931</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D34" t="n">
-        <v>318.7134738391959</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E34" t="n">
-        <v>322.2492980957031</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F34" t="n">
-        <v>9646600</v>
+        <v>9283800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>317.8367876317881</v>
+        <v>314.9145846167937</v>
       </c>
       <c r="C35" t="n">
-        <v>321.6453780396488</v>
+        <v>319.3563099222018</v>
       </c>
       <c r="D35" t="n">
-        <v>315.8107493995538</v>
+        <v>311.5833055007609</v>
       </c>
       <c r="E35" t="n">
-        <v>319.2394409179688</v>
+        <v>318.9569702148438</v>
       </c>
       <c r="F35" t="n">
-        <v>9697100</v>
+        <v>7157800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>320.388908833974</v>
+        <v>319.9310727655453</v>
       </c>
       <c r="C36" t="n">
-        <v>323.7494093321413</v>
+        <v>334.2692843856479</v>
       </c>
       <c r="D36" t="n">
-        <v>313.1126549047939</v>
+        <v>318.5965811998377</v>
       </c>
       <c r="E36" t="n">
-        <v>313.2197875976562</v>
+        <v>330.265869140625</v>
       </c>
       <c r="F36" t="n">
-        <v>7922100</v>
+        <v>10403300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>311.3690496699339</v>
+        <v>329.5742512174487</v>
       </c>
       <c r="C37" t="n">
-        <v>316.1322033153182</v>
+        <v>330.2366069819271</v>
       </c>
       <c r="D37" t="n">
-        <v>306.0117020081513</v>
+        <v>322.6973682057821</v>
       </c>
       <c r="E37" t="n">
-        <v>315.801025390625</v>
+        <v>323.8954467773438</v>
       </c>
       <c r="F37" t="n">
-        <v>9402900</v>
+        <v>7788700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>311.6904703912621</v>
+        <v>318.4699396678824</v>
       </c>
       <c r="C38" t="n">
-        <v>315.8399890894766</v>
+        <v>319.6972389495053</v>
       </c>
       <c r="D38" t="n">
-        <v>308.9436347895907</v>
+        <v>312.177470693811</v>
       </c>
       <c r="E38" t="n">
-        <v>313.2392272949219</v>
+        <v>313.5119323730469</v>
       </c>
       <c r="F38" t="n">
-        <v>9283800</v>
+        <v>8676500</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>314.9146147475993</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C39" t="n">
-        <v>319.3563404779885</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D39" t="n">
-        <v>311.583335312832</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E39" t="n">
-        <v>318.9570007324219</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F39" t="n">
-        <v>7157800</v>
+        <v>6485400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>319.9310727655453</v>
+        <v>308.7878064307793</v>
       </c>
       <c r="C40" t="n">
-        <v>334.2692843856479</v>
+        <v>309.2650879202724</v>
       </c>
       <c r="D40" t="n">
-        <v>318.5965811998377</v>
+        <v>300.7615048801725</v>
       </c>
       <c r="E40" t="n">
-        <v>330.265869140625</v>
+        <v>305.4467468261719</v>
       </c>
       <c r="F40" t="n">
-        <v>10403300</v>
+        <v>9182100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>329.5742822700864</v>
+        <v>305.7876433202538</v>
       </c>
       <c r="C41" t="n">
-        <v>330.2366380969722</v>
+        <v>306.829898044689</v>
       </c>
       <c r="D41" t="n">
-        <v>322.6973986104767</v>
+        <v>296.6314554825427</v>
       </c>
       <c r="E41" t="n">
-        <v>323.8954772949219</v>
+        <v>301.0731811523438</v>
       </c>
       <c r="F41" t="n">
-        <v>7788700</v>
+        <v>8181100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>318.4699396678824</v>
+        <v>302.7486093748369</v>
       </c>
       <c r="C42" t="n">
-        <v>319.6972389495053</v>
+        <v>306.5864211229751</v>
       </c>
       <c r="D42" t="n">
-        <v>312.177470693811</v>
+        <v>301.9596204864886</v>
       </c>
       <c r="E42" t="n">
-        <v>313.5119323730469</v>
+        <v>303.4596862792969</v>
       </c>
       <c r="F42" t="n">
-        <v>8676500</v>
+        <v>7337600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>312.2846677767845</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C43" t="n">
-        <v>319.3758466817346</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D43" t="n">
-        <v>311.1450007536453</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E43" t="n">
-        <v>312.2067260742188</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F43" t="n">
-        <v>6485400</v>
+        <v>8406300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>308.7877755793916</v>
+        <v>316.1127181611407</v>
       </c>
       <c r="C44" t="n">
-        <v>309.2650570211989</v>
+        <v>317.3984886748711</v>
       </c>
       <c r="D44" t="n">
-        <v>300.761474830703</v>
+        <v>309.3819381150768</v>
       </c>
       <c r="E44" t="n">
-        <v>305.4467163085938</v>
+        <v>310.7748413085938</v>
       </c>
       <c r="F44" t="n">
-        <v>9182100</v>
+        <v>10773800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>305.7876743157023</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C45" t="n">
-        <v>306.8299291457832</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D45" t="n">
-        <v>296.6314855498956</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E45" t="n">
-        <v>301.0732116699219</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F45" t="n">
-        <v>8181100</v>
+        <v>6149100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>302.7485484827002</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C46" t="n">
-        <v>306.5863594589355</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D46" t="n">
-        <v>301.9595597530421</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E46" t="n">
-        <v>303.4596252441406</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F46" t="n">
-        <v>7337600</v>
+        <v>5504200</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>303.8200433114142</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C47" t="n">
-        <v>315.4406096571707</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D47" t="n">
-        <v>303.3622324379126</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E47" t="n">
-        <v>311.6709899902344</v>
+        <v>321.216796875</v>
       </c>
       <c r="F47" t="n">
-        <v>8406300</v>
+        <v>2464500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>316.1127492028895</v>
+        <v>318.6744651642728</v>
       </c>
       <c r="C48" t="n">
-        <v>317.3985198428805</v>
+        <v>321.4992420122895</v>
       </c>
       <c r="D48" t="n">
-        <v>309.3819684958741</v>
+        <v>314.6515800853393</v>
       </c>
       <c r="E48" t="n">
-        <v>310.7748718261719</v>
+        <v>314.826904296875</v>
       </c>
       <c r="F48" t="n">
-        <v>10773800</v>
+        <v>6154600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>312.7911824167217</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C49" t="n">
-        <v>319.4927422543219</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D49" t="n">
-        <v>312.576887315192</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E49" t="n">
-        <v>317.8173522949219</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F49" t="n">
-        <v>6149100</v>
+        <v>7978100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>318.1192531852973</v>
+        <v>317.5446185401456</v>
       </c>
       <c r="C50" t="n">
-        <v>326.4962014988301</v>
+        <v>332.5549367443995</v>
       </c>
       <c r="D50" t="n">
-        <v>317.4374268746658</v>
+        <v>316.5803054378969</v>
       </c>
       <c r="E50" t="n">
-        <v>321.1583251953125</v>
+        <v>330.8990173339844</v>
       </c>
       <c r="F50" t="n">
-        <v>5504200</v>
+        <v>9770000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>323.0675713492342</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C51" t="n">
-        <v>323.4474405593548</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D51" t="n">
-        <v>320.3596767020838</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E51" t="n">
-        <v>321.2168273925781</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F51" t="n">
-        <v>2464500</v>
+        <v>8061600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>318.6745269453515</v>
+        <v>326.311185594663</v>
       </c>
       <c r="C52" t="n">
-        <v>321.4993043410047</v>
+        <v>327.0027621721813</v>
       </c>
       <c r="D52" t="n">
-        <v>314.6516410865056</v>
+        <v>319.9895246756281</v>
       </c>
       <c r="E52" t="n">
-        <v>314.8269653320312</v>
+        <v>322.3272705078125</v>
       </c>
       <c r="F52" t="n">
-        <v>6154600</v>
+        <v>5906000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>314.9827696540157</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C53" t="n">
-        <v>320.1745424548712</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D53" t="n">
-        <v>314.4275465708089</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E53" t="n">
-        <v>316.1224365234375</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F53" t="n">
-        <v>7978100</v>
+        <v>4782800</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>317.5446185401456</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C54" t="n">
-        <v>332.5549367443995</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D54" t="n">
-        <v>316.5803054378969</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E54" t="n">
-        <v>330.8990173339844</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F54" t="n">
-        <v>9770000</v>
+        <v>4628400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>330.5970181401507</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C55" t="n">
-        <v>332.4087910072381</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D55" t="n">
-        <v>320.1940311163831</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E55" t="n">
-        <v>324.8403015136719</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F55" t="n">
-        <v>8061600</v>
+        <v>5910500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>326.3111546998924</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C56" t="n">
-        <v>327.0027312119329</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D56" t="n">
-        <v>319.9894943793851</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E56" t="n">
-        <v>322.3272399902344</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F56" t="n">
-        <v>5906000</v>
+        <v>7513200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>322.3272916604559</v>
+        <v>330.9566101169558</v>
       </c>
       <c r="C57" t="n">
-        <v>322.7195306155714</v>
+        <v>338.2915999826528</v>
       </c>
       <c r="D57" t="n">
-        <v>316.5710720238113</v>
+        <v>330.8291257456542</v>
       </c>
       <c r="E57" t="n">
-        <v>317.3457641601562</v>
+        <v>335.2124633789062</v>
       </c>
       <c r="F57" t="n">
-        <v>4782800</v>
+        <v>7979000</v>
       </c>
       <c r="G57" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>316.894669558022</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C58" t="n">
-        <v>320.0326109139432</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D58" t="n">
-        <v>316.2278603865539</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E58" t="n">
-        <v>317.3261413574219</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F58" t="n">
-        <v>4628400</v>
+        <v>6447200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>316.4926256697473</v>
+        <v>333.8200206972608</v>
       </c>
       <c r="C59" t="n">
-        <v>322.3566981053691</v>
+        <v>334.3789469115978</v>
       </c>
       <c r="D59" t="n">
-        <v>313.4037028528859</v>
+        <v>324.6120577084619</v>
       </c>
       <c r="E59" t="n">
-        <v>322.003662109375</v>
+        <v>327.7206115722656</v>
       </c>
       <c r="F59" t="n">
-        <v>5910500</v>
+        <v>6334000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>323.964889169776</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C60" t="n">
-        <v>332.6727314078914</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D60" t="n">
-        <v>322.3861176902447</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E60" t="n">
-        <v>330.2015991210938</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F60" t="n">
-        <v>7513200</v>
+        <v>4685600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>330.9566402470831</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C61" t="n">
-        <v>338.291630780554</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D61" t="n">
-        <v>330.8291558641754</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E61" t="n">
-        <v>335.2124938964844</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F61" t="n">
-        <v>7979000</v>
+        <v>6354900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>334.3789640140598</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C62" t="n">
-        <v>338.2719958722702</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D62" t="n">
-        <v>330.466330684033</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E62" t="n">
-        <v>334.4868469238281</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F62" t="n">
-        <v>6447200</v>
+        <v>10553000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>333.8200517828203</v>
+        <v>316.639672337624</v>
       </c>
       <c r="C63" t="n">
-        <v>334.3789780492049</v>
+        <v>323.4058905098511</v>
       </c>
       <c r="D63" t="n">
-        <v>324.6120879365693</v>
+        <v>315.4139070917166</v>
       </c>
       <c r="E63" t="n">
-        <v>327.7206420898438</v>
+        <v>318.8558654785156</v>
       </c>
       <c r="F63" t="n">
-        <v>6334000</v>
+        <v>7872400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>327.1420632206801</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C64" t="n">
-        <v>329.0150363516344</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D64" t="n">
-        <v>324.0727717826809</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E64" t="n">
-        <v>325.2004699707031</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F64" t="n">
-        <v>4685600</v>
+        <v>4463300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>322.5527687928765</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C65" t="n">
-        <v>323.7785340619881</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D65" t="n">
-        <v>318.2773138986521</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E65" t="n">
-        <v>321.7781066894531</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F65" t="n">
-        <v>6354900</v>
+        <v>2842700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>321.6996282334502</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C66" t="n">
-        <v>328.112840247113</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D66" t="n">
-        <v>319.7482195784761</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E66" t="n">
-        <v>321.0720520019531</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F66" t="n">
-        <v>10553000</v>
+        <v>4359300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>316.6397026430911</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C67" t="n">
-        <v>323.4059214629105</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D67" t="n">
-        <v>315.4139372798661</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E67" t="n">
-        <v>318.8558959960938</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F67" t="n">
-        <v>7872400</v>
+        <v>4346800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>317.7183603265456</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C68" t="n">
-        <v>321.4446748044559</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D68" t="n">
-        <v>317.4830229692616</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E68" t="n">
-        <v>318.5028381347656</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F68" t="n">
-        <v>4463300</v>
+        <v>4432500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>318.8951108888525</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C69" t="n">
-        <v>322.6116097139714</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D69" t="n">
-        <v>317.8458486148664</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E69" t="n">
-        <v>321.2289428710938</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F69" t="n">
-        <v>2842700</v>
+        <v>4285200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>320.8563659827469</v>
+        <v>324.4845627249562</v>
       </c>
       <c r="C70" t="n">
-        <v>325.455440199308</v>
+        <v>333.6631082445032</v>
       </c>
       <c r="D70" t="n">
-        <v>319.9345879995185</v>
+        <v>321.1504873151108</v>
       </c>
       <c r="E70" t="n">
-        <v>325.3965759277344</v>
+        <v>329.8779296875</v>
       </c>
       <c r="F70" t="n">
-        <v>4359300</v>
+        <v>6863600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>324.4748280832652</v>
+        <v>328.9463775793847</v>
       </c>
       <c r="C71" t="n">
-        <v>327.7696711460541</v>
+        <v>340.2136022879278</v>
       </c>
       <c r="D71" t="n">
-        <v>321.9154143417118</v>
+        <v>327.3773920593259</v>
       </c>
       <c r="E71" t="n">
-        <v>322.5626220703125</v>
+        <v>335.3889770507812</v>
       </c>
       <c r="F71" t="n">
-        <v>4346800</v>
+        <v>7956600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>323.3372733311646</v>
+        <v>341.5963098138764</v>
       </c>
       <c r="C72" t="n">
-        <v>329.6327869327114</v>
+        <v>345.7736979738297</v>
       </c>
       <c r="D72" t="n">
-        <v>323.1215374488926</v>
+        <v>338.4289212269501</v>
       </c>
       <c r="E72" t="n">
-        <v>325.7201538085938</v>
+        <v>342.2042846679688</v>
       </c>
       <c r="F72" t="n">
-        <v>4432500</v>
+        <v>9441900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>325.8770745510859</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C73" t="n">
-        <v>326.8674725874873</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D73" t="n">
-        <v>323.484378234348</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E73" t="n">
-        <v>323.7098999023438</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F73" t="n">
-        <v>4285200</v>
+        <v>7461400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>324.4845627249562</v>
+        <v>334.3986242436816</v>
       </c>
       <c r="C74" t="n">
-        <v>333.6631082445032</v>
+        <v>341.1550277170099</v>
       </c>
       <c r="D74" t="n">
-        <v>321.1504873151108</v>
+        <v>334.1926741052517</v>
       </c>
       <c r="E74" t="n">
-        <v>329.8779296875</v>
+        <v>340.1253967285156</v>
       </c>
       <c r="F74" t="n">
-        <v>6863600</v>
+        <v>5059300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>328.9464075107404</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C75" t="n">
-        <v>340.2136332445062</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D75" t="n">
-        <v>327.377421847917</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E75" t="n">
-        <v>335.3890075683594</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F75" t="n">
-        <v>7956600</v>
+        <v>4129100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>341.5962793505171</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C76" t="n">
-        <v>345.7736671379334</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D76" t="n">
-        <v>338.4288910460567</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E76" t="n">
-        <v>342.2042541503906</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F76" t="n">
-        <v>9441900</v>
+        <v>7146400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>342.2140819842231</v>
+        <v>334.8791141795932</v>
       </c>
       <c r="C77" t="n">
-        <v>343.3221487155281</v>
+        <v>335.2125187841528</v>
       </c>
       <c r="D77" t="n">
-        <v>331.4861813179077</v>
+        <v>326.3968234220132</v>
       </c>
       <c r="E77" t="n">
-        <v>335.0752258300781</v>
+        <v>327.4558715820312</v>
       </c>
       <c r="F77" t="n">
-        <v>7461400</v>
+        <v>5605900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>334.3986242436816</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C78" t="n">
-        <v>341.1550277170099</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D78" t="n">
-        <v>334.1926741052517</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E78" t="n">
-        <v>340.1253967285156</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F78" t="n">
-        <v>5059300</v>
+        <v>5740900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>340.5176266555306</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C79" t="n">
-        <v>342.2925325530242</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D79" t="n">
-        <v>335.840116682576</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E79" t="n">
-        <v>337.31103515625</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F79" t="n">
-        <v>4129100</v>
+        <v>6943500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>334.8006554373331</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C80" t="n">
-        <v>336.0067893806199</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D80" t="n">
-        <v>327.465664861477</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E80" t="n">
-        <v>333.9082946777344</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F80" t="n">
-        <v>7146400</v>
+        <v>8039100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>334.8790829701986</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C81" t="n">
-        <v>335.2124875436862</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D81" t="n">
-        <v>326.3967930031341</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E81" t="n">
-        <v>327.4558410644531</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F81" t="n">
-        <v>5605900</v>
+        <v>7596500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>328.8679359740775</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C82" t="n">
-        <v>333.5160286109023</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D82" t="n">
-        <v>327.6225691502204</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E82" t="n">
-        <v>328.4658813476562</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F82" t="n">
-        <v>5740900</v>
+        <v>8933300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>328.7012542904392</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C83" t="n">
-        <v>332.8688565573256</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D83" t="n">
-        <v>321.6996681176321</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E83" t="n">
-        <v>332.3883361816406</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F83" t="n">
-        <v>6943500</v>
+        <v>7491400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>328.3678119481101</v>
+        <v>347.4113430771444</v>
       </c>
       <c r="C84" t="n">
-        <v>329.6818587310364</v>
+        <v>350.9317378318185</v>
       </c>
       <c r="D84" t="n">
-        <v>324.0237067533218</v>
+        <v>346.1463447630524</v>
       </c>
       <c r="E84" t="n">
-        <v>324.6022644042969</v>
+        <v>349.3529663085938</v>
       </c>
       <c r="F84" t="n">
-        <v>8039100</v>
+        <v>9082200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>321.0524690830655</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C85" t="n">
-        <v>333.3003373667196</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D85" t="n">
-        <v>320.1699239761241</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E85" t="n">
-        <v>331.8686218261719</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F85" t="n">
-        <v>7596500</v>
+        <v>10399500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>332.8492030913102</v>
+        <v>288.2706063388866</v>
       </c>
       <c r="C86" t="n">
-        <v>341.3314929222494</v>
+        <v>293.6933912983777</v>
       </c>
       <c r="D86" t="n">
-        <v>332.1235596151242</v>
+        <v>274.96368990819</v>
       </c>
       <c r="E86" t="n">
-        <v>341.0079040527344</v>
+        <v>277.2191162109375</v>
       </c>
       <c r="F86" t="n">
-        <v>8933300</v>
+        <v>65836900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>340.4489540449518</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C87" t="n">
-        <v>348.0683303861261</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D87" t="n">
-        <v>340.0468994310211</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E87" t="n">
-        <v>347.5976257324219</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F87" t="n">
-        <v>7491400</v>
+        <v>23396900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>347.4113127291759</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C88" t="n">
-        <v>350.9317071763275</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D88" t="n">
-        <v>346.1463145255873</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E88" t="n">
-        <v>349.3529357910156</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F88" t="n">
-        <v>9082200</v>
+        <v>13456400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>347.0877216940886</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C89" t="n">
-        <v>347.9114324020834</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D89" t="n">
-        <v>340.537209047996</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E89" t="n">
-        <v>344.822509765625</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F89" t="n">
-        <v>10399500</v>
+        <v>12022200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>288.2705746047087</v>
+        <v>280.4746956220067</v>
       </c>
       <c r="C90" t="n">
-        <v>293.6933589672342</v>
+        <v>284.7697819219751</v>
       </c>
       <c r="D90" t="n">
-        <v>274.9636596388997</v>
+        <v>276.8072155055542</v>
       </c>
       <c r="E90" t="n">
-        <v>277.2190856933594</v>
+        <v>280.0530395507812</v>
       </c>
       <c r="F90" t="n">
-        <v>65836900</v>
+        <v>8664200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>278.2193161239855</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C91" t="n">
-        <v>289.2217870569602</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D91" t="n">
-        <v>278.2193161239855</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E91" t="n">
-        <v>288.3196105957031</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F91" t="n">
-        <v>23396900</v>
+        <v>10809100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>288.623596430627</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C92" t="n">
-        <v>289.8689931668393</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D92" t="n">
-        <v>283.6126820924317</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E92" t="n">
-        <v>286.6231689453125</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F92" t="n">
-        <v>13456400</v>
+        <v>12944100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>286.4368439245325</v>
+        <v>268.9721802809009</v>
       </c>
       <c r="C93" t="n">
-        <v>287.2703703213834</v>
+        <v>271.5217784748567</v>
       </c>
       <c r="D93" t="n">
-        <v>279.1803192669512</v>
+        <v>261.1272811769848</v>
       </c>
       <c r="E93" t="n">
-        <v>281.3670654296875</v>
+        <v>263.3434448242188</v>
       </c>
       <c r="F93" t="n">
-        <v>12022200</v>
+        <v>13035300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>280.4747261855329</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C94" t="n">
-        <v>284.7698129535399</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D94" t="n">
-        <v>276.8072456694325</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E94" t="n">
-        <v>280.0530700683594</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F94" t="n">
-        <v>8664200</v>
+        <v>9572800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>279.1803171568922</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C95" t="n">
-        <v>282.5045770944785</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D95" t="n">
-        <v>273.1985764978856</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E95" t="n">
-        <v>278.6703796386719</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F95" t="n">
-        <v>10809100</v>
+        <v>10371600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>276.5424819048067</v>
+        <v>272.139502815215</v>
       </c>
       <c r="C96" t="n">
-        <v>278.9841969343727</v>
+        <v>274.0713101587253</v>
       </c>
       <c r="D96" t="n">
-        <v>268.7367865177365</v>
+        <v>267.3639259113162</v>
       </c>
       <c r="E96" t="n">
-        <v>270.570556640625</v>
+        <v>267.9228820800781</v>
       </c>
       <c r="F96" t="n">
-        <v>12944100</v>
+        <v>7284700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>268.9721802809009</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C97" t="n">
-        <v>271.5217784748567</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D97" t="n">
-        <v>261.1272811769848</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E97" t="n">
-        <v>263.3434448242188</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F97" t="n">
-        <v>13035300</v>
+        <v>6333100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>261.8822794692194</v>
+        <v>272.7670960064547</v>
       </c>
       <c r="C98" t="n">
-        <v>272.4238601253656</v>
+        <v>280.7590795351679</v>
       </c>
       <c r="D98" t="n">
-        <v>261.2448875542619</v>
+        <v>270.4626513270822</v>
       </c>
       <c r="E98" t="n">
-        <v>271.2863464355469</v>
+        <v>278.856689453125</v>
       </c>
       <c r="F98" t="n">
-        <v>9572800</v>
+        <v>12336900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>268.8348608333229</v>
+        <v>280.0923103323967</v>
       </c>
       <c r="C99" t="n">
-        <v>274.7479519102809</v>
+        <v>287.7704918658715</v>
       </c>
       <c r="D99" t="n">
-        <v>268.0209657772727</v>
+        <v>278.994029288489</v>
       </c>
       <c r="E99" t="n">
-        <v>270.3548278808594</v>
+        <v>287.5057373046875</v>
       </c>
       <c r="F99" t="n">
-        <v>10371600</v>
+        <v>10281900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>272.139502815215</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C100" t="n">
-        <v>274.0713101587253</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D100" t="n">
-        <v>267.3639259113162</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E100" t="n">
-        <v>267.9228820800781</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F100" t="n">
-        <v>7284700</v>
+        <v>6091700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>267.1580308957466</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C101" t="n">
-        <v>274.2674704297252</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D101" t="n">
-        <v>264.5691999285901</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E101" t="n">
-        <v>273.5025939941406</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F101" t="n">
-        <v>6333100</v>
+        <v>6632000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>272.7671258575986</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C102" t="n">
-        <v>280.7591102609402</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D102" t="n">
-        <v>270.4626809260317</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E102" t="n">
-        <v>278.8567199707031</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F102" t="n">
-        <v>12336900</v>
+        <v>4931800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>280.0922508710514</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C103" t="n">
-        <v>287.7704307745099</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D103" t="n">
-        <v>278.9939700602999</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E103" t="n">
-        <v>287.5056762695312</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F103" t="n">
-        <v>10281900</v>
+        <v>6974100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>288.3000088357305</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C104" t="n">
-        <v>288.5255604322975</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D104" t="n">
-        <v>282.7497397683958</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E104" t="n">
-        <v>283.4851989746094</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F104" t="n">
-        <v>6091700</v>
+        <v>7247500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>284.3775473228927</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C105" t="n">
-        <v>284.5050317012176</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D105" t="n">
-        <v>280.7394843208789</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E105" t="n">
-        <v>282.6124572753906</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F105" t="n">
-        <v>6632000</v>
+        <v>9684500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>285.2503082207336</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C106" t="n">
-        <v>285.2503082207336</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D106" t="n">
-        <v>281.3278592694971</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E106" t="n">
-        <v>284.3088989257812</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F106" t="n">
-        <v>4931800</v>
+        <v>11380600</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>283.2988839747449</v>
+        <v>281.4161285575944</v>
       </c>
       <c r="C107" t="n">
-        <v>285.1620413364778</v>
+        <v>289.5355972025459</v>
       </c>
       <c r="D107" t="n">
-        <v>280.0138268252642</v>
+        <v>279.7000570330196</v>
       </c>
       <c r="E107" t="n">
-        <v>284.3775634765625</v>
+        <v>281.1023254394531</v>
       </c>
       <c r="F107" t="n">
-        <v>6974100</v>
+        <v>10210000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>282.9556520269239</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C108" t="n">
-        <v>286.1132246607002</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D108" t="n">
-        <v>276.2090649023382</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E108" t="n">
-        <v>276.8660583496094</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F108" t="n">
-        <v>7247500</v>
+        <v>9723300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>276.7288152602706</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C109" t="n">
-        <v>276.9249197733898</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D109" t="n">
-        <v>266.5304229488273</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E109" t="n">
-        <v>268.6387634277344</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F109" t="n">
-        <v>9684500</v>
+        <v>8141400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>271.9139684697379</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C110" t="n">
-        <v>279.2195114888904</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D110" t="n">
-        <v>271.5020981735627</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E110" t="n">
-        <v>278.6900024414062</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F110" t="n">
-        <v>11380600</v>
+        <v>7051100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>281.4160980059485</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C111" t="n">
-        <v>289.5355657694184</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D111" t="n">
-        <v>279.7000266676773</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E111" t="n">
-        <v>281.102294921875</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F111" t="n">
-        <v>10210000</v>
+        <v>7796000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>279.1802832976262</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C112" t="n">
-        <v>288.4274484322898</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D112" t="n">
-        <v>278.346757008166</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E112" t="n">
-        <v>287.5841064453125</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F112" t="n">
-        <v>9723300</v>
+        <v>5397900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>282.573240677092</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C113" t="n">
-        <v>289.5846125554742</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D113" t="n">
-        <v>281.9260329754997</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E113" t="n">
-        <v>289.2119750976562</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F113" t="n">
-        <v>8141400</v>
+        <v>6816900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>283.3871388529354</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C114" t="n">
-        <v>288.0450472755065</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D114" t="n">
-        <v>278.8468991181569</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E114" t="n">
-        <v>283.6028747558594</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F114" t="n">
-        <v>7051100</v>
+        <v>10348800</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>283.406772199052</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C115" t="n">
-        <v>288.6334226238421</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D115" t="n">
-        <v>282.1025410732585</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E115" t="n">
-        <v>286.299560546875</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F115" t="n">
-        <v>7796000</v>
+        <v>6075600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>284.4265998459625</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C116" t="n">
-        <v>285.7406467283754</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D116" t="n">
-        <v>281.1807753649725</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E116" t="n">
-        <v>283.1714172363281</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F116" t="n">
-        <v>5397900</v>
+        <v>6878800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>281.7691239489905</v>
+        <v>281.4297838763166</v>
       </c>
       <c r="C117" t="n">
-        <v>285.681757300537</v>
+        <v>284.177078134999</v>
       </c>
       <c r="D117" t="n">
-        <v>277.5622889631125</v>
+        <v>273.039671765164</v>
       </c>
       <c r="E117" t="n">
-        <v>280.9258117675781</v>
+        <v>273.7907104492188</v>
       </c>
       <c r="F117" t="n">
-        <v>6816900</v>
+        <v>10512300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,25 +3485,25 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>278.6825254902615</v>
+        <v>274.7888344130931</v>
       </c>
       <c r="C118" t="n">
-        <v>281.8448924528684</v>
+        <v>279.5521380386192</v>
       </c>
       <c r="D118" t="n">
-        <v>275.3818211832701</v>
+        <v>274.5417754718342</v>
       </c>
       <c r="E118" t="n">
-        <v>281.8152465820312</v>
+        <v>278.7714233398438</v>
       </c>
       <c r="F118" t="n">
-        <v>10348800</v>
+        <v>4737600</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>283.9992105555065</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C119" t="n">
-        <v>284.1968396214306</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D119" t="n">
-        <v>275.6189600693905</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E119" t="n">
-        <v>279.0184936523438</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F119" t="n">
-        <v>6075600</v>
+        <v>4854000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>279.0580549356083</v>
+        <v>284.41428667964</v>
       </c>
       <c r="C120" t="n">
-        <v>282.8528771272727</v>
+        <v>285.5902898411239</v>
       </c>
       <c r="D120" t="n">
-        <v>277.2989962609529</v>
+        <v>281.4891167908925</v>
       </c>
       <c r="E120" t="n">
-        <v>281.894287109375</v>
+        <v>284.18701171875</v>
       </c>
       <c r="F120" t="n">
-        <v>6878800</v>
+        <v>5752000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>281.42981524537</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C121" t="n">
-        <v>284.1771098102745</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D121" t="n">
-        <v>273.039702199029</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E121" t="n">
-        <v>273.7907409667969</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F121" t="n">
-        <v>10512300</v>
+        <v>4544100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>274.7888644946905</v>
+        <v>280.6589555118485</v>
       </c>
       <c r="C122" t="n">
-        <v>279.5521686416635</v>
+        <v>284.1671803923218</v>
       </c>
       <c r="D122" t="n">
-        <v>274.5418055263856</v>
+        <v>276.7751962176443</v>
       </c>
       <c r="E122" t="n">
-        <v>278.7714538574219</v>
+        <v>277.1408386230469</v>
       </c>
       <c r="F122" t="n">
-        <v>4737600</v>
+        <v>5542100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>280.6392236042361</v>
+        <v>275.7078960775263</v>
       </c>
       <c r="C123" t="n">
-        <v>284.0189732750403</v>
+        <v>279.7695608963037</v>
       </c>
       <c r="D123" t="n">
-        <v>277.7338078332982</v>
+        <v>271.7648448878931</v>
       </c>
       <c r="E123" t="n">
-        <v>282.1314392089844</v>
+        <v>272.347900390625</v>
       </c>
       <c r="F123" t="n">
-        <v>4854000</v>
+        <v>38893000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>284.4142561376558</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C124" t="n">
-        <v>285.5902591728541</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D124" t="n">
-        <v>281.4890865630293</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E124" t="n">
-        <v>284.1869812011719</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F124" t="n">
-        <v>5752000</v>
+        <v>10424200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>281.8448673992793</v>
+        <v>265.7069856894997</v>
       </c>
       <c r="C125" t="n">
-        <v>285.0072039222152</v>
+        <v>270.1639393177099</v>
       </c>
       <c r="D125" t="n">
-        <v>279.7399202812535</v>
+        <v>264.44204492441</v>
       </c>
       <c r="E125" t="n">
-        <v>280.9850769042969</v>
+        <v>269.0768737792969</v>
       </c>
       <c r="F125" t="n">
-        <v>4544100</v>
+        <v>5911700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>280.6589864168267</v>
+        <v>271.7648799566674</v>
       </c>
       <c r="C126" t="n">
-        <v>284.167211683611</v>
+        <v>272.8321614881822</v>
       </c>
       <c r="D126" t="n">
-        <v>276.7752266949594</v>
+        <v>263.9676840156166</v>
       </c>
       <c r="E126" t="n">
-        <v>277.140869140625</v>
+        <v>267.3672180175781</v>
       </c>
       <c r="F126" t="n">
-        <v>5542100</v>
+        <v>8121200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>275.7079269716043</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C127" t="n">
-        <v>279.769592245506</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D127" t="n">
-        <v>271.7648753401377</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E127" t="n">
-        <v>272.3479309082031</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F127" t="n">
-        <v>38893000</v>
+        <v>6218800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>275.8561490740913</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C128" t="n">
-        <v>277.4471941978335</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D128" t="n">
-        <v>265.9243614270812</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E128" t="n">
-        <v>266.3690795898438</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F128" t="n">
-        <v>10424200</v>
+        <v>10735300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>265.7069555541203</v>
+        <v>257.1191907461688</v>
       </c>
       <c r="C129" t="n">
-        <v>270.1639086768414</v>
+        <v>259.2438917467647</v>
       </c>
       <c r="D129" t="n">
-        <v>264.4420149324948</v>
+        <v>253.6505034942698</v>
       </c>
       <c r="E129" t="n">
-        <v>269.0768432617188</v>
+        <v>258.7102661132812</v>
       </c>
       <c r="F129" t="n">
-        <v>5911700</v>
+        <v>7774700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>271.7648489371355</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C130" t="n">
-        <v>272.8321303468297</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D130" t="n">
-        <v>263.9676538860649</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E130" t="n">
-        <v>267.3671875</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F130" t="n">
-        <v>8121200</v>
+        <v>9170800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>266.813786399154</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C131" t="n">
-        <v>271.4091072097051</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D131" t="n">
-        <v>264.0368460847004</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E131" t="n">
-        <v>264.8966064453125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F131" t="n">
-        <v>6218800</v>
+        <v>5473400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>264.3530902318651</v>
+        <v>269.0867274922702</v>
       </c>
       <c r="C132" t="n">
-        <v>264.5211035963603</v>
+        <v>275.757318970375</v>
       </c>
       <c r="D132" t="n">
-        <v>252.9587320723257</v>
+        <v>268.3356586528844</v>
       </c>
       <c r="E132" t="n">
-        <v>255.9728393554688</v>
+        <v>273.9982604980469</v>
       </c>
       <c r="F132" t="n">
-        <v>10735300</v>
+        <v>6407000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>257.119221076063</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C133" t="n">
-        <v>259.2439223272896</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D133" t="n">
-        <v>253.6505334149961</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E133" t="n">
-        <v>258.7102966308594</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F133" t="n">
-        <v>7774700</v>
+        <v>7097000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>259.9060317076502</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C134" t="n">
-        <v>268.6815709876363</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D134" t="n">
-        <v>259.5206052453565</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E134" t="n">
-        <v>267.40673828125</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F134" t="n">
-        <v>9170800</v>
+        <v>22099800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>270.9841413969268</v>
+        <v>308.3296014014268</v>
       </c>
       <c r="C135" t="n">
-        <v>272.0613148441149</v>
+        <v>309.2881914326393</v>
       </c>
       <c r="D135" t="n">
-        <v>267.5747458421163</v>
+        <v>301.2439367148364</v>
       </c>
       <c r="E135" t="n">
-        <v>270.7568664550781</v>
+        <v>302.3804321289062</v>
       </c>
       <c r="F135" t="n">
-        <v>5473400</v>
+        <v>9645000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>269.0867574628081</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C136" t="n">
-        <v>275.7573496838748</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D136" t="n">
-        <v>268.3356885397691</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E136" t="n">
-        <v>273.998291015625</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F136" t="n">
-        <v>6407000</v>
+        <v>5742000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>274.6109769278597</v>
+        <v>304.3272561704691</v>
       </c>
       <c r="C137" t="n">
-        <v>279.9671982310729</v>
+        <v>306.7187701494722</v>
       </c>
       <c r="D137" t="n">
-        <v>273.9883835303555</v>
+        <v>300.6213715612747</v>
       </c>
       <c r="E137" t="n">
-        <v>278.0500183105469</v>
+        <v>300.7498168945312</v>
       </c>
       <c r="F137" t="n">
-        <v>7097000</v>
+        <v>5212900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>305.2166521040811</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C138" t="n">
-        <v>308.7545232213582</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D138" t="n">
-        <v>297.2119355877115</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E138" t="n">
-        <v>304.1098327636719</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F138" t="n">
-        <v>22099800</v>
+        <v>7972200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>308.3295702834321</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C139" t="n">
-        <v>309.2881602178994</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D139" t="n">
-        <v>301.2439063119584</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E139" t="n">
-        <v>302.3804016113281</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F139" t="n">
-        <v>9645000</v>
+        <v>5864500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>302.2222955343541</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C140" t="n">
-        <v>304.2679509863046</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D140" t="n">
-        <v>300.5620665408429</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E140" t="n">
-        <v>303.2994689941406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F140" t="n">
-        <v>5742000</v>
+        <v>5041200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>304.3272252898824</v>
+        <v>311.2943017295384</v>
       </c>
       <c r="C141" t="n">
-        <v>306.7187390262146</v>
+        <v>314.8618187748353</v>
       </c>
       <c r="D141" t="n">
-        <v>300.6213410567302</v>
+        <v>309.4265214430497</v>
       </c>
       <c r="E141" t="n">
-        <v>300.7497863769531</v>
+        <v>312.6778259277344</v>
       </c>
       <c r="F141" t="n">
-        <v>5212900</v>
+        <v>5205600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>299.6825108634778</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C142" t="n">
-        <v>309.6340527574118</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D142" t="n">
-        <v>299.3564063143342</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E142" t="n">
-        <v>309.3178100585938</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F142" t="n">
-        <v>7972200</v>
+        <v>9414700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>308.8335760443198</v>
+        <v>320.37616900858</v>
       </c>
       <c r="C143" t="n">
-        <v>315.8599180273897</v>
+        <v>321.5719258918635</v>
       </c>
       <c r="D143" t="n">
-        <v>308.8335760443198</v>
+        <v>316.35404203196</v>
       </c>
       <c r="E143" t="n">
-        <v>310.4938049316406</v>
+        <v>319.6745300292969</v>
       </c>
       <c r="F143" t="n">
-        <v>5864500</v>
+        <v>9050600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>312.2825100891185</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C144" t="n">
-        <v>314.0218147327601</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D144" t="n">
-        <v>307.4895604690128</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E144" t="n">
-        <v>310.3554382324219</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F144" t="n">
-        <v>5041200</v>
+        <v>26097300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>311.2942713469933</v>
+        <v>346.7521876325058</v>
       </c>
       <c r="C145" t="n">
-        <v>314.8617880440979</v>
+        <v>354.3418314545246</v>
       </c>
       <c r="D145" t="n">
-        <v>309.4264912428012</v>
+        <v>344.9931290879458</v>
       </c>
       <c r="E145" t="n">
-        <v>312.6777954101562</v>
+        <v>349.3611145019531</v>
       </c>
       <c r="F145" t="n">
-        <v>5205600</v>
+        <v>11807300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>316.2848676157387</v>
+        <v>350.5074994974842</v>
       </c>
       <c r="C146" t="n">
-        <v>321.443459891993</v>
+        <v>352.6519846563255</v>
       </c>
       <c r="D146" t="n">
-        <v>313.4091278691752</v>
+        <v>346.3766807003688</v>
       </c>
       <c r="E146" t="n">
-        <v>320.8110046386719</v>
+        <v>350.388916015625</v>
       </c>
       <c r="F146" t="n">
-        <v>9414700</v>
+        <v>7255800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>320.3761995931397</v>
+        <v>352.2961666917061</v>
       </c>
       <c r="C147" t="n">
-        <v>321.5719565905757</v>
+        <v>354.0651171980212</v>
       </c>
       <c r="D147" t="n">
-        <v>316.3540722325493</v>
+        <v>347.2561882957746</v>
       </c>
       <c r="E147" t="n">
-        <v>319.674560546875</v>
+        <v>350.7446594238281</v>
       </c>
       <c r="F147" t="n">
-        <v>9050600</v>
+        <v>8554600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>348.8571343403697</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C148" t="n">
-        <v>353.472178702815</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D148" t="n">
-        <v>341.1686609140239</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E148" t="n">
-        <v>341.9394836425781</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F148" t="n">
-        <v>26097300</v>
+        <v>7256100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>346.7522179221875</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C149" t="n">
-        <v>354.3418624071809</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D149" t="n">
-        <v>344.9931592239693</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E149" t="n">
-        <v>349.3611450195312</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F149" t="n">
-        <v>11807300</v>
+        <v>10604100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>350.5074689695779</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C150" t="n">
-        <v>352.6519539416425</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D150" t="n">
-        <v>346.3766505322415</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E150" t="n">
-        <v>350.3888854980469</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F150" t="n">
-        <v>7255800</v>
+        <v>9046600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>352.2961973442777</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C151" t="n">
-        <v>354.0651480045056</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D151" t="n">
-        <v>347.256218509828</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E151" t="n">
-        <v>350.7446899414062</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F151" t="n">
-        <v>8554600</v>
+        <v>6879900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>349.7465417706892</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C152" t="n">
-        <v>352.2961769099271</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D152" t="n">
-        <v>344.844900560564</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E152" t="n">
-        <v>350.5173645019531</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F152" t="n">
-        <v>7256100</v>
+        <v>4945400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>352.6420862239859</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C153" t="n">
-        <v>365.28163151709</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D153" t="n">
-        <v>351.5352668687036</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E153" t="n">
-        <v>362.4552612304688</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F153" t="n">
-        <v>10604100</v>
+        <v>4916900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>361.6943118802069</v>
+        <v>366.1216408565838</v>
       </c>
       <c r="C154" t="n">
-        <v>366.4773696532562</v>
+        <v>367.4260893018678</v>
       </c>
       <c r="D154" t="n">
-        <v>360.7159680643861</v>
+        <v>357.5536224796683</v>
       </c>
       <c r="E154" t="n">
-        <v>366.3785400390625</v>
+        <v>359.5893859863281</v>
       </c>
       <c r="F154" t="n">
-        <v>9046600</v>
+        <v>6489000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>364.1747868031508</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C155" t="n">
-        <v>367.613828109226</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D155" t="n">
-        <v>358.7295978571138</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E155" t="n">
-        <v>366.1216125488281</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F155" t="n">
-        <v>6879900</v>
+        <v>6695500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>367.5842026752116</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C156" t="n">
-        <v>368.513146797899</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D156" t="n">
-        <v>362.7023151057061</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E156" t="n">
-        <v>364.4416198730469</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F156" t="n">
-        <v>4945400</v>
+        <v>5235400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>364.214296881966</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="C157" t="n">
-        <v>366.4674733296609</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="D157" t="n">
-        <v>360.360183242299</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="E157" t="n">
-        <v>366.388427734375</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="F157" t="n">
-        <v>4916900</v>
+        <v>6455100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>366.1216097846273</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C158" t="n">
-        <v>367.4260581192055</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D158" t="n">
-        <v>357.553592134861</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E158" t="n">
-        <v>359.58935546875</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F158" t="n">
-        <v>6489000</v>
+        <v>6949600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>358.8284404495387</v>
+        <v>378.3460853480032</v>
       </c>
       <c r="C159" t="n">
-        <v>364.2143076961161</v>
+        <v>392.7446883171237</v>
       </c>
       <c r="D159" t="n">
-        <v>354.0354905816196</v>
+        <v>377.5159708878205</v>
       </c>
       <c r="E159" t="n">
-        <v>362.9592590332031</v>
+        <v>391.726806640625</v>
       </c>
       <c r="F159" t="n">
-        <v>6695500</v>
+        <v>9236300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>362.3267825015715</v>
+        <v>391.835521582727</v>
       </c>
       <c r="C160" t="n">
-        <v>365.45947304961</v>
+        <v>399.3955199396844</v>
       </c>
       <c r="D160" t="n">
-        <v>360.4293565255828</v>
+        <v>388.3766960454267</v>
       </c>
       <c r="E160" t="n">
-        <v>365.3902893066406</v>
+        <v>396.4407043457031</v>
       </c>
       <c r="F160" t="n">
-        <v>5235400</v>
+        <v>8454100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>367.6138623558188</v>
+        <v>396.2825841810375</v>
       </c>
       <c r="C161" t="n">
-        <v>375.5098876953125</v>
+        <v>397.1719904330225</v>
       </c>
       <c r="D161" t="n">
-        <v>367.6138623558188</v>
+        <v>391.3414048271592</v>
       </c>
       <c r="E161" t="n">
-        <v>375.5098876953125</v>
+        <v>394.3950500488281</v>
       </c>
       <c r="F161" t="n">
-        <v>6455100</v>
+        <v>5342500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>375.9743375633532</v>
+        <v>389.6613628183419</v>
       </c>
       <c r="C162" t="n">
-        <v>380.2830313516125</v>
+        <v>392.9522049122001</v>
       </c>
       <c r="D162" t="n">
-        <v>371.6458597568035</v>
+        <v>385.6590199026367</v>
       </c>
       <c r="E162" t="n">
-        <v>379.9173889160156</v>
+        <v>389.2166748046875</v>
       </c>
       <c r="F162" t="n">
-        <v>6949600</v>
+        <v>9811200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>378.3461148231528</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C163" t="n">
-        <v>392.7447189140002</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D163" t="n">
-        <v>377.5160002982997</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E163" t="n">
-        <v>391.7268371582031</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F163" t="n">
-        <v>9236300</v>
+        <v>8400700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>391.8354914196509</v>
+        <v>385.4119880990537</v>
       </c>
       <c r="C164" t="n">
-        <v>399.3954891946478</v>
+        <v>390.3432754242469</v>
       </c>
       <c r="D164" t="n">
-        <v>388.3766661486073</v>
+        <v>382.9512904411622</v>
       </c>
       <c r="E164" t="n">
-        <v>396.440673828125</v>
+        <v>384.6609191894531</v>
       </c>
       <c r="F164" t="n">
-        <v>8454100</v>
+        <v>5016800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>396.2825535174053</v>
+        <v>384.9672452573303</v>
       </c>
       <c r="C165" t="n">
-        <v>397.1719597005697</v>
+        <v>388.7522052741927</v>
       </c>
       <c r="D165" t="n">
-        <v>391.3413745458666</v>
+        <v>376.2213825216763</v>
       </c>
       <c r="E165" t="n">
-        <v>394.39501953125</v>
+        <v>378.790771484375</v>
       </c>
       <c r="F165" t="n">
-        <v>5342500</v>
+        <v>7783900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>389.661393370787</v>
+        <v>376.6364522760421</v>
       </c>
       <c r="C166" t="n">
-        <v>392.9522357226725</v>
+        <v>381.5677396470687</v>
       </c>
       <c r="D166" t="n">
-        <v>385.6590501412673</v>
+        <v>376.0632887376697</v>
       </c>
       <c r="E166" t="n">
-        <v>389.2167053222656</v>
+        <v>377.98046875</v>
       </c>
       <c r="F166" t="n">
-        <v>9811200</v>
+        <v>4732500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>385.4119752058043</v>
+        <v>377.4270309363715</v>
       </c>
       <c r="C167" t="n">
-        <v>387.5268143663777</v>
+        <v>385.9456187280053</v>
       </c>
       <c r="D167" t="n">
-        <v>378.9884422857075</v>
+        <v>376.5277327371266</v>
       </c>
       <c r="E167" t="n">
-        <v>386.5286865234375</v>
+        <v>383.8999633789062</v>
       </c>
       <c r="F167" t="n">
-        <v>8400700</v>
+        <v>5598600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>385.4119575218886</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C168" t="n">
-        <v>390.3432444558516</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D168" t="n">
-        <v>382.9512600592197</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E168" t="n">
-        <v>384.660888671875</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F168" t="n">
-        <v>5016800</v>
+        <v>6498100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>384.9672762725209</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C169" t="n">
-        <v>388.7522365943216</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D169" t="n">
-        <v>376.2214128322495</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E169" t="n">
-        <v>378.7908020019531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F169" t="n">
-        <v>7783900</v>
+        <v>4544000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>376.6364218669779</v>
+        <v>380.4312827021371</v>
       </c>
       <c r="C170" t="n">
-        <v>381.5677088398597</v>
+        <v>384.6807151570288</v>
       </c>
       <c r="D170" t="n">
-        <v>376.0632583748818</v>
+        <v>376.4783391116702</v>
       </c>
       <c r="E170" t="n">
-        <v>377.9804382324219</v>
+        <v>378.0298767089844</v>
       </c>
       <c r="F170" t="n">
-        <v>4732500</v>
+        <v>4330800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>377.4270609393932</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C171" t="n">
-        <v>385.9456494081999</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D171" t="n">
-        <v>376.5277626686598</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E171" t="n">
-        <v>383.8999938964844</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F171" t="n">
-        <v>5598600</v>
+        <v>10257900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>381.4590342432408</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C172" t="n">
-        <v>381.9729060229619</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D172" t="n">
-        <v>371.981856156588</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E172" t="n">
-        <v>372.4265441894531</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F172" t="n">
-        <v>6498100</v>
+        <v>6623700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>373.978089171931</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C173" t="n">
-        <v>380.0063339481963</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D173" t="n">
-        <v>372.6538567388769</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E173" t="n">
-        <v>379.4924621582031</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F173" t="n">
-        <v>4544000</v>
+        <v>3874400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>380.4312519906984</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C174" t="n">
-        <v>384.6806841025421</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D174" t="n">
-        <v>376.4783087193446</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E174" t="n">
-        <v>378.0298461914062</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F174" t="n">
-        <v>4330800</v>
+        <v>6808400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>379.265147571566</v>
+        <v>385.4119603627872</v>
       </c>
       <c r="C175" t="n">
-        <v>380.5893799715138</v>
+        <v>396.6580885443842</v>
       </c>
       <c r="D175" t="n">
-        <v>371.0331563353153</v>
+        <v>385.2340851575979</v>
       </c>
       <c r="E175" t="n">
-        <v>375.8359680175781</v>
+        <v>391.8058471679688</v>
       </c>
       <c r="F175" t="n">
-        <v>10257900</v>
+        <v>12666100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>371.6853813293241</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C176" t="n">
-        <v>378.8402295886877</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D176" t="n">
-        <v>371.4976442585204</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E176" t="n">
-        <v>375.3912658691406</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F176" t="n">
-        <v>6623700</v>
+        <v>10897300</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>373.5333823120854</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C177" t="n">
-        <v>375.6086533861857</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D177" t="n">
-        <v>370.311723920821</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E177" t="n">
-        <v>373.4740905761719</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F177" t="n">
-        <v>3874400</v>
+        <v>6963200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>375.5296184023749</v>
+        <v>405.166788512205</v>
       </c>
       <c r="C178" t="n">
-        <v>382.9018493087182</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="D178" t="n">
-        <v>372.3771436667856</v>
+        <v>402.6467992699509</v>
       </c>
       <c r="E178" t="n">
-        <v>372.5649108886719</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="F178" t="n">
-        <v>6808400</v>
+        <v>8590400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>385.4119903823484</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C179" t="n">
-        <v>396.6581194399012</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D179" t="n">
-        <v>385.2341151633045</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E179" t="n">
-        <v>391.8058776855469</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F179" t="n">
-        <v>12666100</v>
+        <v>6512900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>394.8397525939222</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C180" t="n">
-        <v>399.2868138360328</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D180" t="n">
-        <v>392.5272843670525</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E180" t="n">
-        <v>394.7705688476562</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F180" t="n">
-        <v>10897300</v>
+        <v>4938100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>392.4580996989546</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C181" t="n">
-        <v>403.9018573320044</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D181" t="n">
-        <v>390.3432605482298</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E181" t="n">
-        <v>401.7870483398438</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F181" t="n">
-        <v>6963200</v>
+        <v>7269600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,25 +5149,25 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>405.1668188073661</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C182" t="n">
-        <v>408.1414184570312</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D182" t="n">
-        <v>402.6468293766872</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E182" t="n">
-        <v>408.1414184570312</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F182" t="n">
-        <v>8590400</v>
+        <v>6777900</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>408.6355178300448</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C183" t="n">
-        <v>411.0863535582731</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D183" t="n">
-        <v>399.7907950421236</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E183" t="n">
-        <v>402.6665649414062</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F183" t="n">
-        <v>6512900</v>
+        <v>4815100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>403.9018510073829</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C184" t="n">
-        <v>405.1569297923697</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D184" t="n">
-        <v>398.3677244184781</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E184" t="n">
-        <v>400.7790222167969</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F184" t="n">
-        <v>4938100</v>
+        <v>5838800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>404.1983674177345</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C185" t="n">
-        <v>405.0680198185554</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D185" t="n">
-        <v>400.0477646532951</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E185" t="n">
-        <v>403.714111328125</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F185" t="n">
-        <v>7269600</v>
+        <v>11896900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>404.2110392057612</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C186" t="n">
-        <v>411.6253760831061</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D186" t="n">
-        <v>397.2041664686265</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E186" t="n">
-        <v>408.5244750976562</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F186" t="n">
-        <v>6777900</v>
+        <v>5818600</v>
       </c>
       <c r="G186" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>408.166667860176</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C187" t="n">
-        <v>409.2301268352938</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D187" t="n">
-        <v>404.0520200618331</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E187" t="n">
-        <v>405.1552124023438</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F187" t="n">
-        <v>4815100</v>
+        <v>6675900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>406.6162060558993</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C188" t="n">
-        <v>408.6437298747245</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D188" t="n">
-        <v>396.1506502177288</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E188" t="n">
-        <v>397.0848999023438</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F188" t="n">
-        <v>5838800</v>
+        <v>6858800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>400.3050851420949</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C189" t="n">
-        <v>403.7141170062105</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D189" t="n">
-        <v>396.7072439594676</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E189" t="n">
-        <v>398.5061645507812</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F189" t="n">
-        <v>11896900</v>
+        <v>6014400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>399.6789681783447</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C190" t="n">
-        <v>406.9541476446936</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D190" t="n">
-        <v>399.6789681783447</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E190" t="n">
-        <v>404.191162109375</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F190" t="n">
-        <v>5818600</v>
+        <v>10588200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>407.0137590655401</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C191" t="n">
-        <v>407.3914383485204</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D191" t="n">
-        <v>400.3746474166842</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E191" t="n">
-        <v>406.7454223632812</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F191" t="n">
-        <v>6675900</v>
+        <v>5167400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>408.0275405710553</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C192" t="n">
-        <v>410.8998382586385</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D192" t="n">
-        <v>397.5520359316292</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E192" t="n">
-        <v>403.3165283203125</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F192" t="n">
-        <v>6858800</v>
+        <v>5779800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>404.1613393115512</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C193" t="n">
-        <v>415.0244415980686</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D193" t="n">
-        <v>404.1613393115512</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E193" t="n">
-        <v>412.9869995117188</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F193" t="n">
-        <v>6014400</v>
+        <v>4985900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>413.6131380385679</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C194" t="n">
-        <v>425.3110956697316</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D194" t="n">
-        <v>413.6131380385679</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E194" t="n">
-        <v>425.2713623046875</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F194" t="n">
-        <v>10588200</v>
+        <v>3928800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>423.9196901108692</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C195" t="n">
-        <v>424.0886630783183</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D195" t="n">
-        <v>413.2652939172264</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E195" t="n">
-        <v>417.2507629394531</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F195" t="n">
-        <v>5167400</v>
+        <v>6379000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>420.1330016088457</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C196" t="n">
-        <v>420.1528682919667</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D196" t="n">
-        <v>410.7209557472728</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E196" t="n">
-        <v>413.0863952636719</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F196" t="n">
-        <v>5779800</v>
+        <v>5800500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>414.5573140678119</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C197" t="n">
-        <v>425.4005496015332</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D197" t="n">
-        <v>411.1980248067586</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E197" t="n">
-        <v>423.9296264648438</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F197" t="n">
-        <v>4985900</v>
+        <v>3859200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>425.5099032988985</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C198" t="n">
-        <v>427.5672424396051</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D198" t="n">
-        <v>417.9663567804552</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E198" t="n">
-        <v>422.7568359375</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F198" t="n">
-        <v>3928800</v>
+        <v>5566000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>420.8982555962246</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C199" t="n">
-        <v>421.8424537826169</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D199" t="n">
-        <v>412.5099054894139</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E199" t="n">
-        <v>415.4319152832031</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F199" t="n">
-        <v>6379000</v>
+        <v>3798600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>421.3554771585211</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C200" t="n">
-        <v>425.9770135204084</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D200" t="n">
-        <v>419.546608111588</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E200" t="n">
-        <v>425.5695190429688</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F200" t="n">
-        <v>5800500</v>
+        <v>3863800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>424.5358632950858</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C201" t="n">
-        <v>428.1337042740362</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D201" t="n">
-        <v>421.236174203027</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E201" t="n">
-        <v>422.995361328125</v>
+        <v>422.587890625</v>
       </c>
       <c r="F201" t="n">
-        <v>3859200</v>
+        <v>5135900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>424.4961077137118</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C202" t="n">
-        <v>431.6421079373234</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D202" t="n">
-        <v>420.9280818552513</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E202" t="n">
-        <v>429.0381469726562</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F202" t="n">
-        <v>5566000</v>
+        <v>6764800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>429.0282351931601</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C203" t="n">
-        <v>430.2109246052771</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D203" t="n">
-        <v>421.0572973965209</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E203" t="n">
-        <v>422.0213623046875</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F203" t="n">
-        <v>3798600</v>
+        <v>13281900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>423.8600586972866</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C204" t="n">
-        <v>428.9089563935811</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D204" t="n">
-        <v>422.9258089520534</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E204" t="n">
-        <v>426.4640197753906</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F204" t="n">
-        <v>3863800</v>
+        <v>10718100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>428.3623316954033</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C205" t="n">
-        <v>429.5052877671748</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D205" t="n">
-        <v>419.2087042833569</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E205" t="n">
-        <v>422.587890625</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F205" t="n">
-        <v>5135900</v>
+        <v>4818800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>416.9227440878186</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C206" t="n">
-        <v>421.5144651938549</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D206" t="n">
-        <v>411.8340829429332</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E206" t="n">
-        <v>415.9586791992188</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F206" t="n">
-        <v>6764800</v>
+        <v>6833600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>446.6398026289249</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C207" t="n">
-        <v>458.7949371104763</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D207" t="n">
-        <v>417.7973820738866</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E207" t="n">
-        <v>420.7889709472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F207" t="n">
-        <v>13281900</v>
+        <v>4234100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>424.1085101449368</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C208" t="n">
-        <v>434.7927210350189</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D208" t="n">
-        <v>422.4984292637336</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E208" t="n">
-        <v>423.4823608398438</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F208" t="n">
-        <v>10718100</v>
+        <v>4868700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>424.6352826432401</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C209" t="n">
-        <v>428.3821997886642</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D209" t="n">
-        <v>414.8256906800468</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E209" t="n">
-        <v>418.9701538085938</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F209" t="n">
-        <v>4818800</v>
+        <v>3752500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>419.8944835510819</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C210" t="n">
-        <v>434.3256119583864</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D210" t="n">
-        <v>417.926589996571</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E210" t="n">
-        <v>433.6795959472656</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F210" t="n">
-        <v>6833600</v>
+        <v>4615700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>432.2881481663885</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C211" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D211" t="n">
-        <v>427.0702778038668</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E211" t="n">
-        <v>428.67041015625</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F211" t="n">
-        <v>4234100</v>
+        <v>5917300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>425.6490319049457</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C212" t="n">
-        <v>427.8554470044401</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D212" t="n">
-        <v>417.8272001430648</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E212" t="n">
-        <v>420.9678649902344</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F212" t="n">
-        <v>4868700</v>
+        <v>5257900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>422.6375605105379</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C213" t="n">
-        <v>426.3745593613837</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D213" t="n">
-        <v>416.3562613820867</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E213" t="n">
-        <v>418.1651000976562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F213" t="n">
-        <v>3752500</v>
+        <v>3647500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>419.9242977601041</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C214" t="n">
-        <v>420.2920285503067</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D214" t="n">
-        <v>410.0153117846154</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E214" t="n">
-        <v>415.0841064453125</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F214" t="n">
-        <v>4615700</v>
+        <v>3920900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>417.3600694454911</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C215" t="n">
-        <v>427.8256258440344</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D215" t="n">
-        <v>412.5695600114177</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E215" t="n">
-        <v>426.1658630371094</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F215" t="n">
-        <v>5917300</v>
+        <v>3209600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>425.6390950681477</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C216" t="n">
-        <v>429.0381479748715</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D216" t="n">
-        <v>417.7774999531414</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E216" t="n">
-        <v>417.9961547851562</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F216" t="n">
-        <v>5257900</v>
+        <v>5266300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>412.6490895753043</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C217" t="n">
-        <v>424.7247269708298</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D217" t="n">
-        <v>408.7729631722832</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E217" t="n">
-        <v>418.8906555175781</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F217" t="n">
-        <v>3647500</v>
+        <v>5399000</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>419.4173861384651</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C218" t="n">
-        <v>420.2224265621711</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D218" t="n">
-        <v>411.5259760202005</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E218" t="n">
-        <v>411.8638916015625</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F218" t="n">
-        <v>3920900</v>
+        <v>4712400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>414.8753627675596</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C219" t="n">
-        <v>416.7736773978178</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D219" t="n">
-        <v>410.7905301162958</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E219" t="n">
-        <v>412.8180236816406</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F219" t="n">
-        <v>3209600</v>
+        <v>4095900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>413.0168058398714</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C220" t="n">
-        <v>413.4541155038886</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D220" t="n">
-        <v>404.1812276531693</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E220" t="n">
-        <v>405.0558166503906</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F220" t="n">
-        <v>5266300</v>
+        <v>3182200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>400.7225079776698</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C221" t="n">
-        <v>413.8118915184926</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D221" t="n">
-        <v>395.3654798398698</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E221" t="n">
-        <v>410.2239990234375</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F221" t="n">
-        <v>5399000</v>
+        <v>3398900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>412.728574598682</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C222" t="n">
-        <v>414.4181828862322</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D222" t="n">
-        <v>399.9373426764689</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E222" t="n">
-        <v>401.4977416992188</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F222" t="n">
-        <v>4712400</v>
+        <v>3317200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>399.1322922233893</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C223" t="n">
-        <v>408.1269250227407</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D223" t="n">
-        <v>398.2079910410381</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E223" t="n">
-        <v>404.5886840820312</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F223" t="n">
-        <v>4095900</v>
+        <v>4170200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>406.0993979544625</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C224" t="n">
-        <v>410.5420430290281</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D224" t="n">
-        <v>405.4931153467772</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E224" t="n">
-        <v>406.238525390625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F224" t="n">
-        <v>3182200</v>
+        <v>3476400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>406.4969587134404</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C225" t="n">
-        <v>408.3853248271201</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D225" t="n">
-        <v>398.8639668658938</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E225" t="n">
-        <v>399.7286376953125</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F225" t="n">
-        <v>3398900</v>
+        <v>5295100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>398.5260459867315</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C226" t="n">
-        <v>404.7079813067043</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D226" t="n">
-        <v>398.0489726285335</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E226" t="n">
-        <v>403.1078186035156</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F226" t="n">
-        <v>3317200</v>
+        <v>3605100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>403.1078338152345</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C227" t="n">
-        <v>404.8272573401537</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D227" t="n">
-        <v>396.1506729824118</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E227" t="n">
-        <v>396.6177978515625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F227" t="n">
-        <v>4170200</v>
+        <v>5268500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>395.5642702547857</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C228" t="n">
-        <v>400.7125617691589</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D228" t="n">
-        <v>394.1330805188561</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E228" t="n">
-        <v>399.2714538574219</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F228" t="n">
-        <v>3476400</v>
+        <v>4497200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>396.1308110575831</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C229" t="n">
-        <v>396.4587781552261</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D229" t="n">
-        <v>389.0344923640698</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E229" t="n">
-        <v>393.1988525390625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F229" t="n">
-        <v>5295100</v>
+        <v>4879600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>394.9977452515739</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C230" t="n">
-        <v>396.3494379061722</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D230" t="n">
-        <v>391.1017523988161</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E230" t="n">
-        <v>391.5191650390625</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F230" t="n">
-        <v>3605100</v>
+        <v>4683900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>392.1552670341675</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C231" t="n">
-        <v>394.3716001815704</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D231" t="n">
-        <v>383.9656746212449</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E231" t="n">
-        <v>386.2317199707031</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F231" t="n">
-        <v>5268500</v>
+        <v>2655000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>385.8739371481429</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C232" t="n">
-        <v>390.3066337673781</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D232" t="n">
-        <v>381.4809738935195</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E232" t="n">
-        <v>382.4947509765625</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F232" t="n">
-        <v>4497200</v>
+        <v>3557000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>383.6377017073448</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C233" t="n">
-        <v>391.250826577815</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D233" t="n">
-        <v>383.6377017073448</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E233" t="n">
-        <v>387.7225341796875</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F233" t="n">
-        <v>4879600</v>
+        <v>3668200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>388.6468854751683</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C234" t="n">
-        <v>397.1345997494796</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D234" t="n">
-        <v>388.4679640045169</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E234" t="n">
-        <v>396.3196411132812</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F234" t="n">
-        <v>4683900</v>
+        <v>2455500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>395.3654892531199</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C235" t="n">
-        <v>396.5879726878088</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D235" t="n">
-        <v>393.1988379276376</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E235" t="n">
-        <v>394.1629028320312</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F235" t="n">
-        <v>2655000</v>
+        <v>5748000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>393.9044956601749</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C236" t="n">
-        <v>403.7637998223176</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D236" t="n">
-        <v>393.5864770723492</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E236" t="n">
-        <v>398.5558776855469</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F236" t="n">
-        <v>3557000</v>
+        <v>3716200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>394.4411932932572</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C237" t="n">
-        <v>397.4327821218027</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D237" t="n">
-        <v>391.360158894761</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E237" t="n">
-        <v>392.63232421875</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F237" t="n">
-        <v>3668200</v>
+        <v>3265300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>393.99396168554</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C238" t="n">
-        <v>394.3119802653936</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D238" t="n">
-        <v>390.2569628122352</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E238" t="n">
-        <v>390.5451965332031</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F238" t="n">
-        <v>2455500</v>
+        <v>5488900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>391.1116881429976</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C239" t="n">
-        <v>392.0757530584314</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D239" t="n">
-        <v>385.3372471573089</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E239" t="n">
-        <v>387.02685546875</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F239" t="n">
-        <v>5748000</v>
+        <v>5565400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>389.6804891479818</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C240" t="n">
-        <v>397.1544867752485</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D240" t="n">
-        <v>389.3823372557507</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E240" t="n">
-        <v>393.8746643066406</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F240" t="n">
-        <v>3716200</v>
+        <v>7049400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>396.8264835430965</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C241" t="n">
-        <v>398.6850647467894</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D241" t="n">
-        <v>394.083395182361</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E241" t="n">
-        <v>397.214111328125</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F241" t="n">
-        <v>3265300</v>
+        <v>7735200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>397.5719145517662</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C242" t="n">
-        <v>402.6804729256668</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D242" t="n">
-        <v>392.8807991736857</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E242" t="n">
-        <v>398.4862976074219</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F242" t="n">
-        <v>5488900</v>
+        <v>4339900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>394.6200883073414</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C243" t="n">
-        <v>399.7684103646221</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D243" t="n">
-        <v>392.7814343556134</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E243" t="n">
-        <v>394.7095642089844</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F243" t="n">
-        <v>5565400</v>
+        <v>7478400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,25 +6761,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>389.9985512542227</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C244" t="n">
-        <v>401.4182544062181</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D244" t="n">
-        <v>388.0505547204797</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E244" t="n">
-        <v>398.3869018554688</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F244" t="n">
-        <v>7049400</v>
+        <v>4474000</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>402.6904143062879</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C245" t="n">
-        <v>404.0420766863295</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D245" t="n">
-        <v>375.7661756497595</v>
+        <v>375.5</v>
       </c>
       <c r="E245" t="n">
-        <v>390.6545104980469</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F245" t="n">
-        <v>7735200</v>
+        <v>4391400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>393.5765028166354</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C246" t="n">
-        <v>396.826479685953</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D246" t="n">
-        <v>385.2279163988086</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E246" t="n">
-        <v>385.9037475585938</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F246" t="n">
-        <v>4339900</v>
+        <v>4414900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>388.0306670998862</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C247" t="n">
-        <v>389.3326475544677</v>
+        <v>380.5</v>
       </c>
       <c r="D247" t="n">
-        <v>373.5995091898494</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E247" t="n">
-        <v>376.7699890136719</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F247" t="n">
-        <v>7478400</v>
+        <v>4833700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>381.4400024414062</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C248" t="n">
-        <v>386.4599914550781</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D248" t="n">
-        <v>379.2799987792969</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E248" t="n">
-        <v>383.5499877929688</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F248" t="n">
-        <v>4474000</v>
+        <v>8606300</v>
       </c>
       <c r="G248" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>383.5499877929688</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C249" t="n">
-        <v>383.7999877929688</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D249" t="n">
-        <v>375.5</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E249" t="n">
-        <v>375.9299926757812</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F249" t="n">
-        <v>4391400</v>
+        <v>5712300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>375.8999938964844</v>
+        <v>370.8900146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>380.2200012207031</v>
+        <v>372.6099853515625</v>
       </c>
       <c r="D250" t="n">
-        <v>373.6300048828125</v>
+        <v>366</v>
       </c>
       <c r="E250" t="n">
-        <v>375.260009765625</v>
+        <v>371.2900085449219</v>
       </c>
       <c r="F250" t="n">
-        <v>4414900</v>
+        <v>3859300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,53 +6943,27 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>376.4500122070312</v>
+        <v>371.9200134277344</v>
       </c>
       <c r="C251" t="n">
-        <v>380.5</v>
+        <v>375.2799987792969</v>
       </c>
       <c r="D251" t="n">
-        <v>374.2000122070312</v>
+        <v>368.5</v>
       </c>
       <c r="E251" t="n">
-        <v>375.2099914550781</v>
+        <v>375.010009765625</v>
       </c>
       <c r="F251" t="n">
-        <v>4833700</v>
+        <v>4651000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B252" t="n">
-        <v>375.2900085449219</v>
-      </c>
-      <c r="C252" t="n">
-        <v>378.489990234375</v>
-      </c>
-      <c r="D252" t="n">
-        <v>372.4200134277344</v>
-      </c>
-      <c r="E252" t="n">
-        <v>376.8999938964844</v>
-      </c>
-      <c r="F252" t="n">
-        <v>8606300</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10530,37 +10504,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>376.9</v>
+        <v>375.01</v>
       </c>
       <c r="D2" t="n">
-        <v>375.21</v>
+        <v>371.29</v>
       </c>
       <c r="E2" t="n">
-        <v>375.29</v>
+        <v>371.92</v>
       </c>
       <c r="F2" t="n">
-        <v>378.49</v>
+        <v>375.28</v>
       </c>
       <c r="G2" t="n">
-        <v>372.42</v>
+        <v>368.501</v>
       </c>
       <c r="H2" t="n">
-        <v>8563301</v>
+        <v>4641711</v>
       </c>
       <c r="I2" t="n">
-        <v>5186552</v>
+        <v>5080995</v>
       </c>
       <c r="J2" t="n">
-        <v>338303483904</v>
+        <v>336607051776</v>
       </c>
       <c r="K2" t="n">
-        <v>24.098465</v>
+        <v>23.870783</v>
       </c>
       <c r="L2" t="n">
-        <v>16.668907</v>
+        <v>16.585886</v>
       </c>
       <c r="M2" t="n">
-        <v>15.64</v>
+        <v>15.71</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10572,7 +10546,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10570,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4647596</v>
+        <v>3.4473853</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10582,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>387665494016</v>
+        <v>385969029120</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10609,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:36</t>
+          <t>2026-09-25 14:29:23</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>339.850626873286</v>
+        <v>338.9057579077058</v>
       </c>
       <c r="C2" t="n">
-        <v>341.107176659279</v>
+        <v>340.8928549002298</v>
       </c>
       <c r="D2" t="n">
-        <v>334.6881040719941</v>
+        <v>332.4477149765372</v>
       </c>
       <c r="E2" t="n">
-        <v>336.5972595214844</v>
+        <v>335.1556091308594</v>
       </c>
       <c r="F2" t="n">
-        <v>8104900</v>
+        <v>6774700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>338.9057887667535</v>
+        <v>335.0582538691371</v>
       </c>
       <c r="C3" t="n">
-        <v>340.8928859402125</v>
+        <v>336.5875104266321</v>
       </c>
       <c r="D3" t="n">
-        <v>332.4477452475481</v>
+        <v>332.5938752825687</v>
       </c>
       <c r="E3" t="n">
-        <v>335.1556396484375</v>
+        <v>336.2271118164062</v>
       </c>
       <c r="F3" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>335.0582538691371</v>
+        <v>334.8342081470359</v>
       </c>
       <c r="C4" t="n">
-        <v>336.5875104266321</v>
+        <v>340.2597470322082</v>
       </c>
       <c r="D4" t="n">
-        <v>332.5938752825687</v>
+        <v>333.4510253931927</v>
       </c>
       <c r="E4" t="n">
-        <v>336.2271118164062</v>
+        <v>336.343994140625</v>
       </c>
       <c r="F4" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>334.8342385276262</v>
+        <v>334.9803326465864</v>
       </c>
       <c r="C5" t="n">
-        <v>340.2597779050752</v>
+        <v>339.6558538996071</v>
       </c>
       <c r="D5" t="n">
-        <v>333.4510556482824</v>
+        <v>332.7692198568235</v>
       </c>
       <c r="E5" t="n">
-        <v>336.3440246582031</v>
+        <v>339.2662048339844</v>
       </c>
       <c r="F5" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>334.9803025145298</v>
+        <v>338.2824047650262</v>
       </c>
       <c r="C6" t="n">
-        <v>339.6558233469793</v>
+        <v>345.87033541468</v>
       </c>
       <c r="D6" t="n">
-        <v>332.7691899236603</v>
+        <v>335.7108637419195</v>
       </c>
       <c r="E6" t="n">
-        <v>339.2661743164062</v>
+        <v>344.5456237792969</v>
       </c>
       <c r="F6" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>338.2823748022027</v>
+        <v>347.9840761494036</v>
       </c>
       <c r="C7" t="n">
-        <v>345.8703047797677</v>
+        <v>358.4552554876992</v>
       </c>
       <c r="D7" t="n">
-        <v>335.7108340068662</v>
+        <v>347.3606614365734</v>
       </c>
       <c r="E7" t="n">
-        <v>344.5455932617188</v>
+        <v>350.8575744628906</v>
       </c>
       <c r="F7" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>347.9840761494036</v>
+        <v>351.6660530964717</v>
       </c>
       <c r="C8" t="n">
-        <v>358.4552554876992</v>
+        <v>353.1173978230779</v>
       </c>
       <c r="D8" t="n">
-        <v>347.3606614365734</v>
+        <v>347.8477120863685</v>
       </c>
       <c r="E8" t="n">
-        <v>350.8575744628906</v>
+        <v>349.4646606445312</v>
       </c>
       <c r="F8" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C9" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D9" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E9" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F9" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4130008055815</v>
       </c>
       <c r="C10" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132992932725</v>
       </c>
       <c r="D10" t="n">
-        <v>348.77305405812</v>
+        <v>356.3123046396842</v>
       </c>
       <c r="E10" t="n">
-        <v>354.2278137207031</v>
+        <v>360.3254699707031</v>
       </c>
       <c r="F10" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>357.4129705346734</v>
+        <v>362.8579709138762</v>
       </c>
       <c r="C11" t="n">
-        <v>364.9132683871306</v>
+        <v>366.4620162306247</v>
       </c>
       <c r="D11" t="n">
-        <v>356.3122744619989</v>
+        <v>356.585002247802</v>
       </c>
       <c r="E11" t="n">
-        <v>360.325439453125</v>
+        <v>358.1532592773438</v>
       </c>
       <c r="F11" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>362.8580327507921</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="C12" t="n">
-        <v>366.4620786817287</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="D12" t="n">
-        <v>356.5850630157017</v>
+        <v>343.3670132328114</v>
       </c>
       <c r="E12" t="n">
-        <v>358.1533203125</v>
+        <v>345.3053894042969</v>
       </c>
       <c r="F12" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>359.8189563090651</v>
+        <v>345.5391725764172</v>
       </c>
       <c r="C13" t="n">
-        <v>359.8189563090651</v>
+        <v>349.8445450312873</v>
       </c>
       <c r="D13" t="n">
-        <v>343.3670435790787</v>
+        <v>344.1560194689148</v>
       </c>
       <c r="E13" t="n">
-        <v>345.305419921875</v>
+        <v>349.3575134277344</v>
       </c>
       <c r="F13" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>345.5391423923842</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C14" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D14" t="n">
-        <v>344.155989405705</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E14" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F14" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C15" t="n">
-        <v>352.9322890785681</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D15" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E15" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F15" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4549874654966</v>
       </c>
       <c r="C16" t="n">
-        <v>354.77327893078</v>
+        <v>352.6108411281484</v>
       </c>
       <c r="D16" t="n">
-        <v>346.6203751846734</v>
+        <v>345.207955645442</v>
       </c>
       <c r="E16" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4190979003906</v>
       </c>
       <c r="F16" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>352.4550184254314</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C17" t="n">
-        <v>352.6108721017735</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D17" t="n">
-        <v>345.2079859687916</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E17" t="n">
-        <v>347.4191284179688</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F17" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406127602151</v>
       </c>
       <c r="C18" t="n">
-        <v>349.0945029745603</v>
+        <v>356.0882755673564</v>
       </c>
       <c r="D18" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373288971846</v>
       </c>
       <c r="E18" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265502929688</v>
       </c>
       <c r="F18" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>349.2406127602151</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C19" t="n">
-        <v>356.0882755673564</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D19" t="n">
-        <v>348.2373288971846</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E19" t="n">
-        <v>355.0265502929688</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F19" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C20" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D20" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E20" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F20" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>354.5200118501019</v>
+        <v>346.3573316043178</v>
       </c>
       <c r="C21" t="n">
-        <v>354.5589826989666</v>
+        <v>352.8835660308217</v>
       </c>
       <c r="D21" t="n">
-        <v>348.7146038632694</v>
+        <v>344.4676766060103</v>
       </c>
       <c r="E21" t="n">
-        <v>352.1140747070312</v>
+        <v>351.1010437011719</v>
       </c>
       <c r="F21" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>346.3573617095742</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C22" t="n">
-        <v>352.883596703336</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D22" t="n">
-        <v>344.4677065470185</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E22" t="n">
-        <v>351.10107421875</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F22" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>351.9972042484119</v>
+        <v>354.0719227699667</v>
       </c>
       <c r="C23" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7213754856504</v>
       </c>
       <c r="D23" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0263843961002</v>
       </c>
       <c r="E23" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876098632812</v>
       </c>
       <c r="F23" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063444379755</v>
       </c>
       <c r="C24" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180517731913</v>
       </c>
       <c r="D24" t="n">
-        <v>352.0264145317695</v>
+        <v>349.3282643556941</v>
       </c>
       <c r="E24" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2993774414062</v>
       </c>
       <c r="F24" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>370.8063128551364</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C25" t="n">
-        <v>371.118020163803</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D25" t="n">
-        <v>349.3282346022162</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E25" t="n">
-        <v>358.2993469238281</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F25" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064021770676</v>
       </c>
       <c r="C26" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443442519412</v>
       </c>
       <c r="D26" t="n">
-        <v>344.701472908826</v>
+        <v>334.6880914224008</v>
       </c>
       <c r="E26" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082580566406</v>
       </c>
       <c r="F26" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>338.5064329398476</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C27" t="n">
-        <v>345.3443756361395</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D27" t="n">
-        <v>334.6881218381804</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E27" t="n">
-        <v>335.8082885742188</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F27" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>335.4576347488759</v>
+        <v>330.3340003407686</v>
       </c>
       <c r="C28" t="n">
-        <v>337.298598712068</v>
+        <v>331.863286433141</v>
       </c>
       <c r="D28" t="n">
-        <v>328.3761763650699</v>
+        <v>318.128991755756</v>
       </c>
       <c r="E28" t="n">
-        <v>332.7010192871094</v>
+        <v>325.1325073242188</v>
       </c>
       <c r="F28" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>330.3340623523696</v>
+        <v>319.1323440808776</v>
       </c>
       <c r="C29" t="n">
-        <v>331.8633487318257</v>
+        <v>327.7722802636044</v>
       </c>
       <c r="D29" t="n">
-        <v>318.1290514761847</v>
+        <v>318.7135040219252</v>
       </c>
       <c r="E29" t="n">
-        <v>325.132568359375</v>
+        <v>322.2493286132812</v>
       </c>
       <c r="F29" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>319.1323138584834</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C30" t="n">
-        <v>327.7722492229931</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D30" t="n">
-        <v>318.7134738391959</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E30" t="n">
-        <v>322.2492980957031</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F30" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>317.8367876317881</v>
+        <v>320.3888776178953</v>
       </c>
       <c r="C31" t="n">
-        <v>321.6453780396488</v>
+        <v>323.7493777886428</v>
       </c>
       <c r="D31" t="n">
-        <v>315.8107493995538</v>
+        <v>313.1126243976539</v>
       </c>
       <c r="E31" t="n">
-        <v>319.2394409179688</v>
+        <v>313.2197570800781</v>
       </c>
       <c r="F31" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>320.3888464018165</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C32" t="n">
-        <v>323.7493462451443</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D32" t="n">
-        <v>313.1125938905139</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E32" t="n">
-        <v>313.2197265625</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F32" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>311.3690496699339</v>
+        <v>311.6904703912621</v>
       </c>
       <c r="C33" t="n">
-        <v>316.1322033153182</v>
+        <v>315.8399890894766</v>
       </c>
       <c r="D33" t="n">
-        <v>306.0117020081513</v>
+        <v>308.9436347895907</v>
       </c>
       <c r="E33" t="n">
-        <v>315.801025390625</v>
+        <v>313.2392272949219</v>
       </c>
       <c r="F33" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>311.6904400245728</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C34" t="n">
-        <v>315.8399583185172</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D34" t="n">
-        <v>308.9436046905141</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E34" t="n">
-        <v>313.2391967773438</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F34" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>314.9145846167937</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C35" t="n">
-        <v>319.3563099222018</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D35" t="n">
-        <v>311.5833055007609</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E35" t="n">
-        <v>318.9569702148438</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F35" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>319.9310727655453</v>
+        <v>329.5743133227241</v>
       </c>
       <c r="C36" t="n">
-        <v>334.2692843856479</v>
+        <v>330.2366692120174</v>
       </c>
       <c r="D36" t="n">
-        <v>318.5965811998377</v>
+        <v>322.6974290151713</v>
       </c>
       <c r="E36" t="n">
-        <v>330.265869140625</v>
+        <v>323.8955078125</v>
       </c>
       <c r="F36" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>329.5742512174487</v>
+        <v>318.4699706680781</v>
       </c>
       <c r="C37" t="n">
-        <v>330.2366069819271</v>
+        <v>319.6972700691676</v>
       </c>
       <c r="D37" t="n">
-        <v>322.6973682057821</v>
+        <v>312.1775010814912</v>
       </c>
       <c r="E37" t="n">
-        <v>323.8954467773438</v>
+        <v>313.511962890625</v>
       </c>
       <c r="F37" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>318.4699396678824</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C38" t="n">
-        <v>319.6972389495053</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D38" t="n">
-        <v>312.177470693811</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E38" t="n">
-        <v>313.5119323730469</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F38" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7877447280039</v>
       </c>
       <c r="C39" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650261221254</v>
       </c>
       <c r="D39" t="n">
-        <v>311.1450007536453</v>
+        <v>300.7614447812334</v>
       </c>
       <c r="E39" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4466857910156</v>
       </c>
       <c r="F39" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>308.7878064307793</v>
+        <v>305.7876123248052</v>
       </c>
       <c r="C40" t="n">
-        <v>309.2650879202724</v>
+        <v>306.8298669435948</v>
       </c>
       <c r="D40" t="n">
-        <v>300.7615048801725</v>
+        <v>296.6314254151897</v>
       </c>
       <c r="E40" t="n">
-        <v>305.4467468261719</v>
+        <v>301.0731506347656</v>
       </c>
       <c r="F40" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>305.7876433202538</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C41" t="n">
-        <v>306.829898044689</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D41" t="n">
-        <v>296.6314554825427</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E41" t="n">
-        <v>301.0731811523438</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F41" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>302.7486093748369</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C42" t="n">
-        <v>306.5864211229751</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D42" t="n">
-        <v>301.9596204864886</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E42" t="n">
-        <v>303.4596862792969</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F42" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C43" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D43" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E43" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F43" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>316.1127181611407</v>
+        <v>312.7911523817683</v>
       </c>
       <c r="C44" t="n">
-        <v>317.3984886748711</v>
+        <v>319.4927115758689</v>
       </c>
       <c r="D44" t="n">
-        <v>309.3819381150768</v>
+        <v>312.5768573008158</v>
       </c>
       <c r="E44" t="n">
-        <v>310.7748413085938</v>
+        <v>317.8173217773438</v>
       </c>
       <c r="F44" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>312.7911824167217</v>
+        <v>318.1193136428872</v>
       </c>
       <c r="C45" t="n">
-        <v>319.4927422543219</v>
+        <v>326.4962635484334</v>
       </c>
       <c r="D45" t="n">
-        <v>312.576887315192</v>
+        <v>317.4374872026767</v>
       </c>
       <c r="E45" t="n">
-        <v>317.8173522949219</v>
+        <v>321.1583862304688</v>
       </c>
       <c r="F45" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>318.1192834140923</v>
+        <v>323.0675713492342</v>
       </c>
       <c r="C46" t="n">
-        <v>326.4962325236318</v>
+        <v>323.4474405593548</v>
       </c>
       <c r="D46" t="n">
-        <v>317.4374570386713</v>
+        <v>320.3596767020838</v>
       </c>
       <c r="E46" t="n">
-        <v>321.1583557128906</v>
+        <v>321.2168273925781</v>
       </c>
       <c r="F46" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>323.067540655824</v>
+        <v>318.6745269453515</v>
       </c>
       <c r="C47" t="n">
-        <v>323.4474098298547</v>
+        <v>321.4993043410047</v>
       </c>
       <c r="D47" t="n">
-        <v>320.3596462659403</v>
+        <v>314.6516410865056</v>
       </c>
       <c r="E47" t="n">
-        <v>321.216796875</v>
+        <v>314.8269653320312</v>
       </c>
       <c r="F47" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>318.6744651642728</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C48" t="n">
-        <v>321.4992420122895</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D48" t="n">
-        <v>314.6515800853393</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E48" t="n">
-        <v>314.826904296875</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F48" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C49" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D49" t="n">
-        <v>314.4275769247672</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E49" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F49" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>317.5446185401456</v>
+        <v>330.5970491985518</v>
       </c>
       <c r="C50" t="n">
-        <v>332.5549367443995</v>
+        <v>332.4088222358486</v>
       </c>
       <c r="D50" t="n">
-        <v>316.5803054378969</v>
+        <v>320.1940611974609</v>
       </c>
       <c r="E50" t="n">
-        <v>330.8990173339844</v>
+        <v>324.84033203125</v>
       </c>
       <c r="F50" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>330.5970181401507</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C51" t="n">
-        <v>332.4087910072381</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D51" t="n">
-        <v>320.1940311163831</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E51" t="n">
-        <v>324.8403015136719</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F51" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,25 +1769,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>326.311185594663</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C52" t="n">
-        <v>327.0027621721813</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D52" t="n">
-        <v>319.9895246756281</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E52" t="n">
-        <v>322.3272705078125</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F52" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894639081939</v>
       </c>
       <c r="C53" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0325801360812</v>
       </c>
       <c r="D53" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278299745985</v>
       </c>
       <c r="E53" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261108398438</v>
       </c>
       <c r="F53" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G53" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>316.894669558022</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C54" t="n">
-        <v>320.0326109139432</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D54" t="n">
-        <v>316.2278603865539</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E54" t="n">
-        <v>317.3261413574219</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F54" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C55" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D55" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E55" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F55" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566703772105</v>
       </c>
       <c r="C56" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2916615784552</v>
       </c>
       <c r="D56" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291859826966</v>
       </c>
       <c r="E56" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2125244140625</v>
       </c>
       <c r="F56" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>330.9566101169558</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C57" t="n">
-        <v>338.2915999826528</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D57" t="n">
-        <v>330.8291257456542</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E57" t="n">
-        <v>335.2124633789062</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F57" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C58" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D58" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E58" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F58" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>333.8200206972608</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C59" t="n">
-        <v>334.3789469115978</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D59" t="n">
-        <v>324.6120577084619</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E59" t="n">
-        <v>327.7206115722656</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F59" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>327.1420632206801</v>
+        <v>322.552799383924</v>
       </c>
       <c r="C60" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785647692876</v>
       </c>
       <c r="D60" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773440842135</v>
       </c>
       <c r="E60" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781372070312</v>
       </c>
       <c r="F60" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>322.5527687928765</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C61" t="n">
-        <v>323.7785340619881</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D61" t="n">
-        <v>318.2773138986521</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E61" t="n">
-        <v>321.7781066894531</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F61" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>321.6996588106788</v>
+        <v>316.6397026430911</v>
       </c>
       <c r="C62" t="n">
-        <v>328.112871433911</v>
+        <v>323.4059214629105</v>
       </c>
       <c r="D62" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139372798661</v>
       </c>
       <c r="E62" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558959960938</v>
       </c>
       <c r="F62" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>316.639672337624</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C63" t="n">
-        <v>323.4058905098511</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D63" t="n">
-        <v>315.4139070917166</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E63" t="n">
-        <v>318.8558654785156</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F63" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C64" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D64" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E64" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F64" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C65" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D65" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E65" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F65" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C66" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D66" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E66" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F66" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C67" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D67" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E67" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F67" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C68" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D68" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E68" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F68" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C69" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D69" t="n">
-        <v>323.484378234348</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E69" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F69" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>324.4845627249562</v>
+        <v>328.9464075107404</v>
       </c>
       <c r="C70" t="n">
-        <v>333.6631082445032</v>
+        <v>340.2136332445062</v>
       </c>
       <c r="D70" t="n">
-        <v>321.1504873151108</v>
+        <v>327.377421847917</v>
       </c>
       <c r="E70" t="n">
-        <v>329.8779296875</v>
+        <v>335.3890075683594</v>
       </c>
       <c r="F70" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>328.9463775793847</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C71" t="n">
-        <v>340.2136022879278</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D71" t="n">
-        <v>327.3773920593259</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E71" t="n">
-        <v>335.3889770507812</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F71" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>341.5963098138764</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C72" t="n">
-        <v>345.7736979738297</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D72" t="n">
-        <v>338.4289212269501</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E72" t="n">
-        <v>342.2042846679688</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F72" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C73" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D73" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E73" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F73" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>334.3986242436816</v>
+        <v>340.5176266555306</v>
       </c>
       <c r="C74" t="n">
-        <v>341.1550277170099</v>
+        <v>342.2925325530242</v>
       </c>
       <c r="D74" t="n">
-        <v>334.1926741052517</v>
+        <v>335.840116682576</v>
       </c>
       <c r="E74" t="n">
-        <v>340.1253967285156</v>
+        <v>337.31103515625</v>
       </c>
       <c r="F74" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C75" t="n">
-        <v>342.2925015847546</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D75" t="n">
-        <v>335.8400862980764</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E75" t="n">
-        <v>337.3110046386719</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F75" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C76" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D76" t="n">
-        <v>327.465664861477</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E76" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F76" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>334.8791141795932</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C77" t="n">
-        <v>335.2125187841528</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D77" t="n">
-        <v>326.3968234220132</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E77" t="n">
-        <v>327.4558715820312</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F77" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C78" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D78" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E78" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F78" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C79" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D79" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E79" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F79" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C80" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D80" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E80" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F80" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C81" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D81" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E81" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F81" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489839349073</v>
       </c>
       <c r="C82" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683609450301</v>
       </c>
       <c r="D82" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0469292856779</v>
       </c>
       <c r="E82" t="n">
-        <v>341.0079040527344</v>
+        <v>347.59765625</v>
       </c>
       <c r="F82" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>340.4489540449518</v>
+        <v>347.4112823812074</v>
       </c>
       <c r="C83" t="n">
-        <v>348.0683303861261</v>
+        <v>350.9316765208364</v>
       </c>
       <c r="D83" t="n">
-        <v>340.0468994310211</v>
+        <v>346.1462842881223</v>
       </c>
       <c r="E83" t="n">
-        <v>347.5976257324219</v>
+        <v>349.3529052734375</v>
       </c>
       <c r="F83" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>347.4113430771444</v>
+        <v>347.0876909760341</v>
       </c>
       <c r="C84" t="n">
-        <v>350.9317378318185</v>
+        <v>347.9114016111286</v>
       </c>
       <c r="D84" t="n">
-        <v>346.1463447630524</v>
+        <v>340.5371789096768</v>
       </c>
       <c r="E84" t="n">
-        <v>349.3529663085938</v>
+        <v>344.8224792480469</v>
       </c>
       <c r="F84" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>347.0877216940886</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C85" t="n">
-        <v>347.9114324020834</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D85" t="n">
-        <v>340.537209047996</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E85" t="n">
-        <v>344.822509765625</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F85" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>288.2706063388866</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C86" t="n">
-        <v>293.6933912983777</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D86" t="n">
-        <v>274.96368990819</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E86" t="n">
-        <v>277.2191162109375</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F86" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>278.2193161239855</v>
+        <v>288.6235657000577</v>
       </c>
       <c r="C87" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689623036692</v>
       </c>
       <c r="D87" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126518953886</v>
       </c>
       <c r="E87" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231384277344</v>
       </c>
       <c r="F87" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>288.623596430627</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C88" t="n">
-        <v>289.8689931668393</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D88" t="n">
-        <v>283.6126820924317</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E88" t="n">
-        <v>286.6231689453125</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F88" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4747261855329</v>
       </c>
       <c r="C89" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7698129535399</v>
       </c>
       <c r="D89" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072456694325</v>
       </c>
       <c r="E89" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530700683594</v>
       </c>
       <c r="F89" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>280.4746956220067</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C90" t="n">
-        <v>284.7697819219751</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D90" t="n">
-        <v>276.8072155055542</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E90" t="n">
-        <v>280.0530395507812</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F90" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424507136568</v>
       </c>
       <c r="C91" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841654678224</v>
       </c>
       <c r="D91" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367562069888</v>
       </c>
       <c r="E91" t="n">
-        <v>278.6703796386719</v>
+        <v>270.5705261230469</v>
       </c>
       <c r="F91" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>276.5424819048067</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C92" t="n">
-        <v>278.9841969343727</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D92" t="n">
-        <v>268.7367865177365</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E92" t="n">
-        <v>270.570556640625</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F92" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>268.9721802809009</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C93" t="n">
-        <v>271.5217784748567</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D93" t="n">
-        <v>261.1272811769848</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E93" t="n">
-        <v>263.3434448242188</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F93" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348608333229</v>
       </c>
       <c r="C94" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479519102809</v>
       </c>
       <c r="D94" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209657772727</v>
       </c>
       <c r="E94" t="n">
-        <v>271.286376953125</v>
+        <v>270.3548278808594</v>
       </c>
       <c r="F94" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>268.8348304873182</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C95" t="n">
-        <v>274.7479208968081</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D95" t="n">
-        <v>268.0209355231403</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E95" t="n">
-        <v>270.3547973632812</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F95" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>272.139502815215</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C96" t="n">
-        <v>274.0713101587253</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D96" t="n">
-        <v>267.3639259113162</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E96" t="n">
-        <v>267.9228820800781</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F96" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7671258575986</v>
       </c>
       <c r="C97" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7591102609402</v>
       </c>
       <c r="D97" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626809260317</v>
       </c>
       <c r="E97" t="n">
-        <v>273.5025634765625</v>
+        <v>278.8567199707031</v>
       </c>
       <c r="F97" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>272.7670960064547</v>
+        <v>280.0922508710514</v>
       </c>
       <c r="C98" t="n">
-        <v>280.7590795351679</v>
+        <v>287.7704307745099</v>
       </c>
       <c r="D98" t="n">
-        <v>270.4626513270822</v>
+        <v>278.9939700602999</v>
       </c>
       <c r="E98" t="n">
-        <v>278.856689453125</v>
+        <v>287.5056762695312</v>
       </c>
       <c r="F98" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>280.0923103323967</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C99" t="n">
-        <v>287.7704918658715</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D99" t="n">
-        <v>278.994029288489</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E99" t="n">
-        <v>287.5057373046875</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F99" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>288.3000088357305</v>
+        <v>284.377578031072</v>
       </c>
       <c r="C100" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050624231632</v>
       </c>
       <c r="D100" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7395146362062</v>
       </c>
       <c r="E100" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124877929688</v>
       </c>
       <c r="F100" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>284.3775473228927</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C101" t="n">
-        <v>284.5050317012176</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D101" t="n">
-        <v>280.7394843208789</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E101" t="n">
-        <v>282.6124572753906</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F101" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>285.2503082207336</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C102" t="n">
-        <v>285.2503082207336</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D102" t="n">
-        <v>281.3278592694971</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E102" t="n">
-        <v>284.3088989257812</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F102" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C103" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D103" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E103" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F103" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7287838236561</v>
       </c>
       <c r="C104" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9248883144977</v>
       </c>
       <c r="D104" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5303926707583</v>
       </c>
       <c r="E104" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387329101562</v>
       </c>
       <c r="F104" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>276.7288152602706</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C105" t="n">
-        <v>276.9249197733898</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D105" t="n">
-        <v>266.5304229488273</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E105" t="n">
-        <v>268.6387634277344</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F105" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C106" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D106" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E106" t="n">
-        <v>278.6900024414062</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F106" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>281.4161285575944</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C107" t="n">
-        <v>289.5355972025459</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D107" t="n">
-        <v>279.7000570330196</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E107" t="n">
-        <v>281.1023254394531</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F107" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C108" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D108" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E108" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F108" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C109" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D109" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E109" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F109" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>283.3871388529354</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C110" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D110" t="n">
-        <v>278.8468991181569</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E110" t="n">
-        <v>283.6028747558594</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F110" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265691931125</v>
       </c>
       <c r="C111" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406159339096</v>
       </c>
       <c r="D111" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807450619272</v>
       </c>
       <c r="E111" t="n">
-        <v>286.2995300292969</v>
+        <v>283.17138671875</v>
       </c>
       <c r="F111" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>284.4265998459625</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C112" t="n">
-        <v>285.7406467283754</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D112" t="n">
-        <v>281.1807753649725</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E112" t="n">
-        <v>283.1714172363281</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F112" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C113" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D113" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E113" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F113" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C114" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D114" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E114" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F114" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G114" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C115" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D115" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E115" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F115" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>279.0580549356083</v>
+        <v>281.42981524537</v>
       </c>
       <c r="C116" t="n">
-        <v>282.8528771272727</v>
+        <v>284.1771098102745</v>
       </c>
       <c r="D116" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039702199029</v>
       </c>
       <c r="E116" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907409667969</v>
       </c>
       <c r="F116" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>281.4297838763166</v>
+        <v>274.7888644946905</v>
       </c>
       <c r="C117" t="n">
-        <v>284.177078134999</v>
+        <v>279.5521686416635</v>
       </c>
       <c r="D117" t="n">
-        <v>273.039671765164</v>
+        <v>274.5418055263856</v>
       </c>
       <c r="E117" t="n">
-        <v>273.7907104492188</v>
+        <v>278.7714538574219</v>
       </c>
       <c r="F117" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>274.7888344130931</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C118" t="n">
-        <v>279.5521380386192</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D118" t="n">
-        <v>274.5417754718342</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E118" t="n">
-        <v>278.7714233398438</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F118" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>280.6392236042361</v>
+        <v>284.4142561376558</v>
       </c>
       <c r="C119" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902591728541</v>
       </c>
       <c r="D119" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4890865630293</v>
       </c>
       <c r="E119" t="n">
-        <v>282.1314392089844</v>
+        <v>284.1869812011719</v>
       </c>
       <c r="F119" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>284.41428667964</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C120" t="n">
-        <v>285.5902898411239</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D120" t="n">
-        <v>281.4891167908925</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E120" t="n">
-        <v>284.18701171875</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F120" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589864168267</v>
       </c>
       <c r="C121" t="n">
-        <v>285.0072039222152</v>
+        <v>284.167211683611</v>
       </c>
       <c r="D121" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7752266949594</v>
       </c>
       <c r="E121" t="n">
-        <v>280.9850769042969</v>
+        <v>277.140869140625</v>
       </c>
       <c r="F121" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>280.6589555118485</v>
+        <v>275.7079269716043</v>
       </c>
       <c r="C122" t="n">
-        <v>284.1671803923218</v>
+        <v>279.769592245506</v>
       </c>
       <c r="D122" t="n">
-        <v>276.7751962176443</v>
+        <v>271.7648753401377</v>
       </c>
       <c r="E122" t="n">
-        <v>277.1408386230469</v>
+        <v>272.3479309082031</v>
       </c>
       <c r="F122" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>275.7078960775263</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C123" t="n">
-        <v>279.7695608963037</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D123" t="n">
-        <v>271.7648448878931</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E123" t="n">
-        <v>272.347900390625</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F123" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069555541203</v>
       </c>
       <c r="C124" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639086768414</v>
       </c>
       <c r="D124" t="n">
-        <v>265.9243614270812</v>
+        <v>264.4420149324948</v>
       </c>
       <c r="E124" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768432617188</v>
       </c>
       <c r="F124" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>265.7069856894997</v>
+        <v>271.7648489371355</v>
       </c>
       <c r="C125" t="n">
-        <v>270.1639393177099</v>
+        <v>272.8321303468297</v>
       </c>
       <c r="D125" t="n">
-        <v>264.44204492441</v>
+        <v>263.9676538860649</v>
       </c>
       <c r="E125" t="n">
-        <v>269.0768737792969</v>
+        <v>267.3671875</v>
       </c>
       <c r="F125" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>271.7648799566674</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C126" t="n">
-        <v>272.8321614881822</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D126" t="n">
-        <v>263.9676840156166</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E126" t="n">
-        <v>267.3672180175781</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F126" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C127" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D127" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E127" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F127" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>264.3530902318651</v>
+        <v>257.119221076063</v>
       </c>
       <c r="C128" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2439223272896</v>
       </c>
       <c r="D128" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505334149961</v>
       </c>
       <c r="E128" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102966308594</v>
       </c>
       <c r="F128" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>257.1191907461688</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C129" t="n">
-        <v>259.2438917467647</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D129" t="n">
-        <v>253.6505034942698</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E129" t="n">
-        <v>258.7102661132812</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F129" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C130" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D130" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E130" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F130" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867574628081</v>
       </c>
       <c r="C131" t="n">
-        <v>272.0613148441149</v>
+        <v>275.7573496838748</v>
       </c>
       <c r="D131" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356885397691</v>
       </c>
       <c r="E131" t="n">
-        <v>270.7568664550781</v>
+        <v>273.998291015625</v>
       </c>
       <c r="F131" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>269.0867274922702</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C132" t="n">
-        <v>275.757318970375</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D132" t="n">
-        <v>268.3356586528844</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E132" t="n">
-        <v>273.9982604980469</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F132" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C133" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D133" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E133" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F133" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3295702834321</v>
       </c>
       <c r="C134" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881602178994</v>
       </c>
       <c r="D134" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439063119584</v>
       </c>
       <c r="E134" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804016113281</v>
       </c>
       <c r="F134" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>308.3296014014268</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C135" t="n">
-        <v>309.2881914326393</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D135" t="n">
-        <v>301.2439367148364</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E135" t="n">
-        <v>302.3804321289062</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F135" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272252898824</v>
       </c>
       <c r="C136" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187390262146</v>
       </c>
       <c r="D136" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213410567302</v>
       </c>
       <c r="E136" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7497863769531</v>
       </c>
       <c r="F136" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>304.3272561704691</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C137" t="n">
-        <v>306.7187701494722</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D137" t="n">
-        <v>300.6213715612747</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E137" t="n">
-        <v>300.7498168945312</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F137" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C138" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D138" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E138" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F138" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C139" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D139" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E139" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F139" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2942713469933</v>
       </c>
       <c r="C140" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8617880440979</v>
       </c>
       <c r="D140" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4264912428012</v>
       </c>
       <c r="E140" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6777954101562</v>
       </c>
       <c r="F140" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>311.2943017295384</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C141" t="n">
-        <v>314.8618187748353</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D141" t="n">
-        <v>309.4265214430497</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E141" t="n">
-        <v>312.6778259277344</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F141" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>316.2848676157387</v>
+        <v>320.3761995931397</v>
       </c>
       <c r="C142" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719565905757</v>
       </c>
       <c r="D142" t="n">
-        <v>313.4091278691752</v>
+        <v>316.3540722325493</v>
       </c>
       <c r="E142" t="n">
-        <v>320.8110046386719</v>
+        <v>319.674560546875</v>
       </c>
       <c r="F142" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>320.37616900858</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C143" t="n">
-        <v>321.5719258918635</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D143" t="n">
-        <v>316.35404203196</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E143" t="n">
-        <v>319.6745300292969</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F143" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7522179221875</v>
       </c>
       <c r="C144" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418624071809</v>
       </c>
       <c r="D144" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931592239693</v>
       </c>
       <c r="E144" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611450195312</v>
       </c>
       <c r="F144" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>346.7521876325058</v>
+        <v>350.5074689695779</v>
       </c>
       <c r="C145" t="n">
-        <v>354.3418314545246</v>
+        <v>352.6519539416425</v>
       </c>
       <c r="D145" t="n">
-        <v>344.9931290879458</v>
+        <v>346.3766505322415</v>
       </c>
       <c r="E145" t="n">
-        <v>349.3611145019531</v>
+        <v>350.3888854980469</v>
       </c>
       <c r="F145" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>350.5074994974842</v>
+        <v>352.2961973442777</v>
       </c>
       <c r="C146" t="n">
-        <v>352.6519846563255</v>
+        <v>354.0651480045056</v>
       </c>
       <c r="D146" t="n">
-        <v>346.3766807003688</v>
+        <v>347.256218509828</v>
       </c>
       <c r="E146" t="n">
-        <v>350.388916015625</v>
+        <v>350.7446899414062</v>
       </c>
       <c r="F146" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>352.2961666917061</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C147" t="n">
-        <v>354.0651171980212</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D147" t="n">
-        <v>347.2561882957746</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E147" t="n">
-        <v>350.7446594238281</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F147" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C148" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D148" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E148" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F148" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C149" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D149" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E149" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F149" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C150" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D150" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E150" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F150" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C151" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D151" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E151" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F151" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C152" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D152" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E152" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F152" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216097846273</v>
       </c>
       <c r="C153" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260581192055</v>
       </c>
       <c r="D153" t="n">
-        <v>360.360183242299</v>
+        <v>357.553592134861</v>
       </c>
       <c r="E153" t="n">
-        <v>366.388427734375</v>
+        <v>359.58935546875</v>
       </c>
       <c r="F153" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>366.1216408565838</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C154" t="n">
-        <v>367.4260893018678</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D154" t="n">
-        <v>357.5536224796683</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E154" t="n">
-        <v>359.5893859863281</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F154" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C155" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D155" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E155" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F155" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="C156" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="D156" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="E156" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="F156" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>367.6138324799484</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C157" t="n">
-        <v>375.5098571777344</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D157" t="n">
-        <v>367.6138324799484</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E157" t="n">
-        <v>375.5098571777344</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F157" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3461148231528</v>
       </c>
       <c r="C158" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7447189140002</v>
       </c>
       <c r="D158" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5160002982997</v>
       </c>
       <c r="E158" t="n">
-        <v>379.9173889160156</v>
+        <v>391.7268371582031</v>
       </c>
       <c r="F158" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>378.3460853480032</v>
+        <v>391.8354914196509</v>
       </c>
       <c r="C159" t="n">
-        <v>392.7446883171237</v>
+        <v>399.3954891946478</v>
       </c>
       <c r="D159" t="n">
-        <v>377.5159708878205</v>
+        <v>388.3766661486073</v>
       </c>
       <c r="E159" t="n">
-        <v>391.726806640625</v>
+        <v>396.440673828125</v>
       </c>
       <c r="F159" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>391.835521582727</v>
+        <v>396.2825535174053</v>
       </c>
       <c r="C160" t="n">
-        <v>399.3955199396844</v>
+        <v>397.1719597005697</v>
       </c>
       <c r="D160" t="n">
-        <v>388.3766960454267</v>
+        <v>391.3413745458666</v>
       </c>
       <c r="E160" t="n">
-        <v>396.4407043457031</v>
+        <v>394.39501953125</v>
       </c>
       <c r="F160" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>396.2825841810375</v>
+        <v>389.661393370787</v>
       </c>
       <c r="C161" t="n">
-        <v>397.1719904330225</v>
+        <v>392.9522357226725</v>
       </c>
       <c r="D161" t="n">
-        <v>391.3414048271592</v>
+        <v>385.6590501412673</v>
       </c>
       <c r="E161" t="n">
-        <v>394.3950500488281</v>
+        <v>389.2167053222656</v>
       </c>
       <c r="F161" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>389.6613628183419</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C162" t="n">
-        <v>392.9522049122001</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D162" t="n">
-        <v>385.6590199026367</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E162" t="n">
-        <v>389.2166748046875</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F162" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119575218886</v>
       </c>
       <c r="C163" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432444558516</v>
       </c>
       <c r="D163" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512600592197</v>
       </c>
       <c r="E163" t="n">
-        <v>386.5286865234375</v>
+        <v>384.660888671875</v>
       </c>
       <c r="F163" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>385.4119880990537</v>
+        <v>384.9672762725209</v>
       </c>
       <c r="C164" t="n">
-        <v>390.3432754242469</v>
+        <v>388.7522365943216</v>
       </c>
       <c r="D164" t="n">
-        <v>382.9512904411622</v>
+        <v>376.2214128322495</v>
       </c>
       <c r="E164" t="n">
-        <v>384.6609191894531</v>
+        <v>378.7908020019531</v>
       </c>
       <c r="F164" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>384.9672452573303</v>
+        <v>376.6364218669779</v>
       </c>
       <c r="C165" t="n">
-        <v>388.7522052741927</v>
+        <v>381.5677088398597</v>
       </c>
       <c r="D165" t="n">
-        <v>376.2213825216763</v>
+        <v>376.0632583748818</v>
       </c>
       <c r="E165" t="n">
-        <v>378.790771484375</v>
+        <v>377.9804382324219</v>
       </c>
       <c r="F165" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>376.6364522760421</v>
+        <v>377.4270609393932</v>
       </c>
       <c r="C166" t="n">
-        <v>381.5677396470687</v>
+        <v>385.9456494081999</v>
       </c>
       <c r="D166" t="n">
-        <v>376.0632887376697</v>
+        <v>376.5277626686598</v>
       </c>
       <c r="E166" t="n">
-        <v>377.98046875</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F166" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>377.4270309363715</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C167" t="n">
-        <v>385.9456187280053</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D167" t="n">
-        <v>376.5277327371266</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E167" t="n">
-        <v>383.8999633789062</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F167" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C168" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D168" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E168" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F168" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312519906984</v>
       </c>
       <c r="C169" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6806841025421</v>
       </c>
       <c r="D169" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783087193446</v>
       </c>
       <c r="E169" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298461914062</v>
       </c>
       <c r="F169" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>380.4312827021371</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C170" t="n">
-        <v>384.6807151570288</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D170" t="n">
-        <v>376.4783391116702</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E170" t="n">
-        <v>378.0298767089844</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F170" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C171" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D171" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E171" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F171" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C172" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D172" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E172" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F172" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C173" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D173" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E173" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F173" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119903823484</v>
       </c>
       <c r="C174" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6581194399012</v>
       </c>
       <c r="D174" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2341151633045</v>
       </c>
       <c r="E174" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058776855469</v>
       </c>
       <c r="F174" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>385.4119603627872</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C175" t="n">
-        <v>396.6580885443842</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D175" t="n">
-        <v>385.2340851575979</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E175" t="n">
-        <v>391.8058471679688</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F175" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C176" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D176" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E176" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F176" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>392.4580996989546</v>
+        <v>405.1668188073661</v>
       </c>
       <c r="C177" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="D177" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6468293766872</v>
       </c>
       <c r="E177" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="F177" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>405.166788512205</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C178" t="n">
-        <v>408.1413879394531</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D178" t="n">
-        <v>402.6467992699509</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E178" t="n">
-        <v>408.1413879394531</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F178" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C179" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D179" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E179" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F179" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C180" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D180" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E180" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F180" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,25 +5123,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C181" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D181" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E181" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F181" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5149,25 +5149,25 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C182" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D182" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E182" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F182" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G182" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C183" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D183" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E183" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F183" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C184" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D184" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E184" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F184" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C185" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D185" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E185" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F185" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C186" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D186" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E186" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F186" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C187" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D187" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E187" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F187" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C188" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D188" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E188" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F188" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C189" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D189" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E189" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F189" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C190" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D190" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E190" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F190" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C191" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D191" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E191" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F191" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C192" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D192" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E192" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F192" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C193" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D193" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E193" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F193" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C194" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D194" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E194" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F194" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C195" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D195" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E195" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F195" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C196" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D196" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E196" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F196" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C197" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D197" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E197" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F197" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C198" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D198" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E198" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F198" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C199" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D199" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E199" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F199" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C200" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D200" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E200" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F200" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C201" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D201" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E201" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F201" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C202" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D202" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E202" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F202" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C203" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D203" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E203" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F203" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C204" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D204" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E204" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F204" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C205" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D205" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E205" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F205" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C206" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D206" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E206" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F206" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C207" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D207" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E207" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F207" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C208" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D208" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E208" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F208" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C209" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D209" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E209" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F209" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C210" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D210" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E210" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F210" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C211" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D211" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E211" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F211" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C212" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D212" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E212" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F212" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C213" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D213" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E213" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F213" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C214" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D214" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E214" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F214" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C215" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D215" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E215" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F215" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C216" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D216" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E216" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F216" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C217" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D217" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E217" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F217" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C218" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D218" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E218" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F218" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C219" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D219" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E219" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F219" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C220" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D220" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E220" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F220" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C221" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D221" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E221" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F221" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C222" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D222" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E222" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F222" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C223" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D223" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E223" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F223" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C224" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D224" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E224" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F224" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C225" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D225" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E225" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F225" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C226" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D226" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E226" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F226" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C227" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D227" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E227" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F227" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C228" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D228" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E228" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F228" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C229" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D229" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E229" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F229" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C230" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D230" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E230" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F230" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C231" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D231" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E231" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F231" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C232" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D232" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E232" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F232" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C233" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D233" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E233" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F233" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C234" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D234" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E234" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F234" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C235" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D235" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E235" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F235" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C236" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D236" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E236" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F236" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C237" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D237" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E237" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F237" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C238" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D238" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E238" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F238" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C239" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D239" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E239" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F239" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C240" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D240" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E240" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F240" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C241" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D241" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E241" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F241" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C242" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D242" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E242" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F242" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C243" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D243" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F243" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,25 +6761,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C244" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D244" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E244" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F244" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G244" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C245" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D245" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E245" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F245" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C246" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D246" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E246" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F246" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C247" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D247" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E247" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F247" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>375.2900085449219</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C248" t="n">
-        <v>378.489990234375</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D248" t="n">
-        <v>372.4200134277344</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E248" t="n">
-        <v>376.8999938964844</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F248" t="n">
-        <v>8606300</v>
+        <v>5712300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>377.8699951171875</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="C249" t="n">
-        <v>378.9500122070312</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="D249" t="n">
-        <v>373.8200073242188</v>
+        <v>372.4100036621094</v>
       </c>
       <c r="E249" t="n">
-        <v>377.5599975585938</v>
+        <v>372.9500122070312</v>
       </c>
       <c r="F249" t="n">
-        <v>5712300</v>
+        <v>4495000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6964,6 +6964,32 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B252" t="n">
+        <v>375.9500122070312</v>
+      </c>
+      <c r="C252" t="n">
+        <v>379.1700134277344</v>
+      </c>
+      <c r="D252" t="n">
+        <v>371.1700134277344</v>
+      </c>
+      <c r="E252" t="n">
+        <v>376.5899963378906</v>
+      </c>
+      <c r="F252" t="n">
+        <v>4077400</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10504,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>376.59</v>
+      </c>
+      <c r="D2" t="n">
         <v>375.01</v>
       </c>
-      <c r="D2" t="n">
-        <v>371.29</v>
-      </c>
       <c r="E2" t="n">
-        <v>371.92</v>
+        <v>375.95</v>
       </c>
       <c r="F2" t="n">
-        <v>375.28</v>
+        <v>379.17</v>
       </c>
       <c r="G2" t="n">
-        <v>368.501</v>
+        <v>371.27</v>
       </c>
       <c r="H2" t="n">
-        <v>4641711</v>
+        <v>4073729</v>
       </c>
       <c r="I2" t="n">
-        <v>5080995</v>
+        <v>4992169</v>
       </c>
       <c r="J2" t="n">
-        <v>336607051776</v>
+        <v>338025218048</v>
       </c>
       <c r="K2" t="n">
-        <v>23.870783</v>
+        <v>24.202442</v>
       </c>
       <c r="L2" t="n">
-        <v>16.585886</v>
+        <v>16.655766</v>
       </c>
       <c r="M2" t="n">
-        <v>15.71</v>
+        <v>15.56</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10546,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10570,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4473853</v>
+        <v>3.4619098</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10582,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>385969029120</v>
+        <v>387387228160</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10609,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:29:23</t>
+          <t>2026-09-26 14:49:56</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>338.9057579077058</v>
+        <v>335.0582538691371</v>
       </c>
       <c r="C2" t="n">
-        <v>340.8928549002298</v>
+        <v>336.5875104266321</v>
       </c>
       <c r="D2" t="n">
-        <v>332.4477149765372</v>
+        <v>332.5938752825687</v>
       </c>
       <c r="E2" t="n">
-        <v>335.1556091308594</v>
+        <v>336.2271118164062</v>
       </c>
       <c r="F2" t="n">
-        <v>6774700</v>
+        <v>6878900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>335.0582538691371</v>
+        <v>334.8342385276262</v>
       </c>
       <c r="C3" t="n">
-        <v>336.5875104266321</v>
+        <v>340.2597779050752</v>
       </c>
       <c r="D3" t="n">
-        <v>332.5938752825687</v>
+        <v>333.4510556482824</v>
       </c>
       <c r="E3" t="n">
-        <v>336.2271118164062</v>
+        <v>336.3440246582031</v>
       </c>
       <c r="F3" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>334.8342081470359</v>
+        <v>334.9803025145298</v>
       </c>
       <c r="C4" t="n">
-        <v>340.2597470322082</v>
+        <v>339.6558233469793</v>
       </c>
       <c r="D4" t="n">
-        <v>333.4510253931927</v>
+        <v>332.7691899236603</v>
       </c>
       <c r="E4" t="n">
-        <v>336.343994140625</v>
+        <v>339.2661743164062</v>
       </c>
       <c r="F4" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>334.9803326465864</v>
+        <v>338.2823748022027</v>
       </c>
       <c r="C5" t="n">
-        <v>339.6558538996071</v>
+        <v>345.8703047797677</v>
       </c>
       <c r="D5" t="n">
-        <v>332.7692198568235</v>
+        <v>335.7108340068662</v>
       </c>
       <c r="E5" t="n">
-        <v>339.2662048339844</v>
+        <v>344.5455932617188</v>
       </c>
       <c r="F5" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>338.2824047650262</v>
+        <v>347.9840761494036</v>
       </c>
       <c r="C6" t="n">
-        <v>345.87033541468</v>
+        <v>358.4552554876992</v>
       </c>
       <c r="D6" t="n">
-        <v>335.7108637419195</v>
+        <v>347.3606614365734</v>
       </c>
       <c r="E6" t="n">
-        <v>344.5456237792969</v>
+        <v>350.8575744628906</v>
       </c>
       <c r="F6" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>347.9840761494036</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C7" t="n">
-        <v>358.4552554876992</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D7" t="n">
-        <v>347.3606614365734</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E7" t="n">
-        <v>350.8575744628906</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F7" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>351.6660530964717</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C8" t="n">
-        <v>353.1173978230779</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D8" t="n">
-        <v>347.8477120863685</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E8" t="n">
-        <v>349.4646606445312</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F8" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C9" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D9" t="n">
-        <v>348.77305405812</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E9" t="n">
-        <v>354.2278137207031</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F9" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>357.4130008055815</v>
+        <v>362.8580327507921</v>
       </c>
       <c r="C10" t="n">
-        <v>364.9132992932725</v>
+        <v>366.4620786817287</v>
       </c>
       <c r="D10" t="n">
-        <v>356.3123046396842</v>
+        <v>356.5850630157017</v>
       </c>
       <c r="E10" t="n">
-        <v>360.3254699707031</v>
+        <v>358.1533203125</v>
       </c>
       <c r="F10" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>362.8579709138762</v>
+        <v>359.8189563090651</v>
       </c>
       <c r="C11" t="n">
-        <v>366.4620162306247</v>
+        <v>359.8189563090651</v>
       </c>
       <c r="D11" t="n">
-        <v>356.585002247802</v>
+        <v>343.3670435790787</v>
       </c>
       <c r="E11" t="n">
-        <v>358.1532592773438</v>
+        <v>345.305419921875</v>
       </c>
       <c r="F11" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>359.8189245088024</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C12" t="n">
-        <v>359.8189245088024</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D12" t="n">
-        <v>343.3670132328114</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E12" t="n">
-        <v>345.3053894042969</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F12" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>345.5391725764172</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C13" t="n">
-        <v>349.8445450312873</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D13" t="n">
-        <v>344.1560194689148</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E13" t="n">
-        <v>349.3575134277344</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F13" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C14" t="n">
-        <v>352.9322890785681</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D14" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E14" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F14" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C15" t="n">
-        <v>354.77327893078</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D15" t="n">
-        <v>346.6203751846734</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E15" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F15" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>352.4549874654966</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C16" t="n">
-        <v>352.6108411281484</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D16" t="n">
-        <v>345.207955645442</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E16" t="n">
-        <v>347.4190979003906</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F16" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406127602151</v>
       </c>
       <c r="C17" t="n">
-        <v>349.0945029745603</v>
+        <v>356.0882755673564</v>
       </c>
       <c r="D17" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373288971846</v>
       </c>
       <c r="E17" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265502929688</v>
       </c>
       <c r="F17" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>349.2406127602151</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C18" t="n">
-        <v>356.0882755673564</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D18" t="n">
-        <v>348.2373288971846</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E18" t="n">
-        <v>355.0265502929688</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F18" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C19" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D19" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E19" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F19" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>354.5200118501019</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C20" t="n">
-        <v>354.5589826989666</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D20" t="n">
-        <v>348.7146038632694</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E20" t="n">
-        <v>352.1140747070312</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F20" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>346.3573316043178</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C21" t="n">
-        <v>352.8835660308217</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D21" t="n">
-        <v>344.4676766060103</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E21" t="n">
-        <v>351.1010437011719</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F21" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>351.9972042484119</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C22" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D22" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E22" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F22" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>354.0719227699667</v>
+        <v>370.8063128551364</v>
       </c>
       <c r="C23" t="n">
-        <v>356.7213754856504</v>
+        <v>371.118020163803</v>
       </c>
       <c r="D23" t="n">
-        <v>352.0263843961002</v>
+        <v>349.3282346022162</v>
       </c>
       <c r="E23" t="n">
-        <v>356.4876098632812</v>
+        <v>358.2993469238281</v>
       </c>
       <c r="F23" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>370.8063444379755</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C24" t="n">
-        <v>371.1180517731913</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D24" t="n">
-        <v>349.3282643556941</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E24" t="n">
-        <v>358.2993774414062</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F24" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C25" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D25" t="n">
-        <v>344.701472908826</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E25" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F25" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>338.5064021770676</v>
+        <v>335.4576347488759</v>
       </c>
       <c r="C26" t="n">
-        <v>345.3443442519412</v>
+        <v>337.298598712068</v>
       </c>
       <c r="D26" t="n">
-        <v>334.6880914224008</v>
+        <v>328.3761763650699</v>
       </c>
       <c r="E26" t="n">
-        <v>335.8082580566406</v>
+        <v>332.7010192871094</v>
       </c>
       <c r="F26" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>335.4576039784424</v>
+        <v>330.3340623523696</v>
       </c>
       <c r="C27" t="n">
-        <v>337.298567772769</v>
+        <v>331.8633487318257</v>
       </c>
       <c r="D27" t="n">
-        <v>328.3761462441955</v>
+        <v>318.1290514761847</v>
       </c>
       <c r="E27" t="n">
-        <v>332.7009887695312</v>
+        <v>325.132568359375</v>
       </c>
       <c r="F27" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>330.3340003407686</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C28" t="n">
-        <v>331.863286433141</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D28" t="n">
-        <v>318.128991755756</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E28" t="n">
-        <v>325.1325073242188</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F28" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>319.1323440808776</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C29" t="n">
-        <v>327.7722802636044</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D29" t="n">
-        <v>318.7135040219252</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E29" t="n">
-        <v>322.2493286132812</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F29" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>317.8367876317881</v>
+        <v>320.3888464018165</v>
       </c>
       <c r="C30" t="n">
-        <v>321.6453780396488</v>
+        <v>323.7493462451443</v>
       </c>
       <c r="D30" t="n">
-        <v>315.8107493995538</v>
+        <v>313.1125938905139</v>
       </c>
       <c r="E30" t="n">
-        <v>319.2394409179688</v>
+        <v>313.2197265625</v>
       </c>
       <c r="F30" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>320.3888776178953</v>
+        <v>311.3690496699339</v>
       </c>
       <c r="C31" t="n">
-        <v>323.7493777886428</v>
+        <v>316.1322033153182</v>
       </c>
       <c r="D31" t="n">
-        <v>313.1126243976539</v>
+        <v>306.0117020081513</v>
       </c>
       <c r="E31" t="n">
-        <v>313.2197570800781</v>
+        <v>315.801025390625</v>
       </c>
       <c r="F31" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>311.3690195806419</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C32" t="n">
-        <v>316.1321727657366</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D32" t="n">
-        <v>306.011672436569</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E32" t="n">
-        <v>315.8009948730469</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F32" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>311.6904703912621</v>
+        <v>314.9145846167937</v>
       </c>
       <c r="C33" t="n">
-        <v>315.8399890894766</v>
+        <v>319.3563099222018</v>
       </c>
       <c r="D33" t="n">
-        <v>308.9436347895907</v>
+        <v>311.5833055007609</v>
       </c>
       <c r="E33" t="n">
-        <v>313.2392272949219</v>
+        <v>318.9569702148438</v>
       </c>
       <c r="F33" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>314.9146147475993</v>
+        <v>319.9310727655453</v>
       </c>
       <c r="C34" t="n">
-        <v>319.3563404779885</v>
+        <v>334.2692843856479</v>
       </c>
       <c r="D34" t="n">
-        <v>311.583335312832</v>
+        <v>318.5965811998377</v>
       </c>
       <c r="E34" t="n">
-        <v>318.9570007324219</v>
+        <v>330.265869140625</v>
       </c>
       <c r="F34" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>319.931043202934</v>
+        <v>329.5742512174487</v>
       </c>
       <c r="C35" t="n">
-        <v>334.2692534981419</v>
+        <v>330.2366069819271</v>
       </c>
       <c r="D35" t="n">
-        <v>318.5965517605375</v>
+        <v>322.6973682057821</v>
       </c>
       <c r="E35" t="n">
-        <v>330.2658386230469</v>
+        <v>323.8954467773438</v>
       </c>
       <c r="F35" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>329.5743133227241</v>
+        <v>318.4699396678824</v>
       </c>
       <c r="C36" t="n">
-        <v>330.2366692120174</v>
+        <v>319.6972389495053</v>
       </c>
       <c r="D36" t="n">
-        <v>322.6974290151713</v>
+        <v>312.177470693811</v>
       </c>
       <c r="E36" t="n">
-        <v>323.8955078125</v>
+        <v>313.5119323730469</v>
       </c>
       <c r="F36" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>318.4699706680781</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C37" t="n">
-        <v>319.6972700691676</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D37" t="n">
-        <v>312.1775010814912</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E37" t="n">
-        <v>313.511962890625</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F37" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7878064307793</v>
       </c>
       <c r="C38" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650879202724</v>
       </c>
       <c r="D38" t="n">
-        <v>311.1450007536453</v>
+        <v>300.7615048801725</v>
       </c>
       <c r="E38" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4467468261719</v>
       </c>
       <c r="F38" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>308.7877447280039</v>
+        <v>305.7876433202538</v>
       </c>
       <c r="C39" t="n">
-        <v>309.2650261221254</v>
+        <v>306.829898044689</v>
       </c>
       <c r="D39" t="n">
-        <v>300.7614447812334</v>
+        <v>296.6314554825427</v>
       </c>
       <c r="E39" t="n">
-        <v>305.4466857910156</v>
+        <v>301.0731811523438</v>
       </c>
       <c r="F39" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>305.7876123248052</v>
+        <v>302.7486093748369</v>
       </c>
       <c r="C40" t="n">
-        <v>306.8298669435948</v>
+        <v>306.5864211229751</v>
       </c>
       <c r="D40" t="n">
-        <v>296.6314254151897</v>
+        <v>301.9596204864886</v>
       </c>
       <c r="E40" t="n">
-        <v>301.0731506347656</v>
+        <v>303.4596862792969</v>
       </c>
       <c r="F40" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>302.7485789287686</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C41" t="n">
-        <v>306.5863902909554</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D41" t="n">
-        <v>301.9595901197654</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E41" t="n">
-        <v>303.4596557617188</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F41" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127181611407</v>
       </c>
       <c r="C42" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3984886748711</v>
       </c>
       <c r="D42" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819381150768</v>
       </c>
       <c r="E42" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748413085938</v>
       </c>
       <c r="F42" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>316.1127492028895</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C43" t="n">
-        <v>317.3985198428805</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D43" t="n">
-        <v>309.3819684958741</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E43" t="n">
-        <v>310.7748718261719</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F43" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>312.7911523817683</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C44" t="n">
-        <v>319.4927115758689</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D44" t="n">
-        <v>312.5768573008158</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E44" t="n">
-        <v>317.8173217773438</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F44" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>318.1193136428872</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C45" t="n">
-        <v>326.4962635484334</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D45" t="n">
-        <v>317.4374872026767</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E45" t="n">
-        <v>321.1583862304688</v>
+        <v>321.216796875</v>
       </c>
       <c r="F45" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>323.0675713492342</v>
+        <v>318.6744651642728</v>
       </c>
       <c r="C46" t="n">
-        <v>323.4474405593548</v>
+        <v>321.4992420122895</v>
       </c>
       <c r="D46" t="n">
-        <v>320.3596767020838</v>
+        <v>314.6515800853393</v>
       </c>
       <c r="E46" t="n">
-        <v>321.2168273925781</v>
+        <v>314.826904296875</v>
       </c>
       <c r="F46" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>318.6745269453515</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C47" t="n">
-        <v>321.4993043410047</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D47" t="n">
-        <v>314.6516410865056</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E47" t="n">
-        <v>314.8269653320312</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F47" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5446185401456</v>
       </c>
       <c r="C48" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549367443995</v>
       </c>
       <c r="D48" t="n">
-        <v>314.4275769247672</v>
+        <v>316.5803054378969</v>
       </c>
       <c r="E48" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8990173339844</v>
       </c>
       <c r="F48" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>317.5445892541937</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C49" t="n">
-        <v>332.5549060741021</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D49" t="n">
-        <v>316.58027624088</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E49" t="n">
-        <v>330.8989868164062</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F49" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>330.5970491985518</v>
+        <v>326.311185594663</v>
       </c>
       <c r="C50" t="n">
-        <v>332.4088222358486</v>
+        <v>327.0027621721813</v>
       </c>
       <c r="D50" t="n">
-        <v>320.1940611974609</v>
+        <v>319.9895246756281</v>
       </c>
       <c r="E50" t="n">
-        <v>324.84033203125</v>
+        <v>322.3272705078125</v>
       </c>
       <c r="F50" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>326.3111546998924</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C51" t="n">
-        <v>327.0027312119329</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D51" t="n">
-        <v>319.9894943793851</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E51" t="n">
-        <v>322.3272399902344</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F51" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1769,25 +1769,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C52" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D52" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E52" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F52" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G52" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>316.894639081939</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C53" t="n">
-        <v>320.0325801360812</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D53" t="n">
-        <v>316.2278299745985</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E53" t="n">
-        <v>317.3261108398438</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F53" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C54" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D54" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E54" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F54" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566101169558</v>
       </c>
       <c r="C55" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2915999826528</v>
       </c>
       <c r="D55" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291257456542</v>
       </c>
       <c r="E55" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2124633789062</v>
       </c>
       <c r="F55" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>330.9566703772105</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C56" t="n">
-        <v>338.2916615784552</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D56" t="n">
-        <v>330.8291859826966</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E56" t="n">
-        <v>335.2125244140625</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F56" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200206972608</v>
       </c>
       <c r="C57" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789469115978</v>
       </c>
       <c r="D57" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120577084619</v>
       </c>
       <c r="E57" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206115722656</v>
       </c>
       <c r="F57" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>333.8200517828203</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C58" t="n">
-        <v>334.3789780492049</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D58" t="n">
-        <v>324.6120879365693</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E58" t="n">
-        <v>327.7206420898438</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F58" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>327.1420632206801</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C59" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D59" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E59" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F59" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>322.552799383924</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C60" t="n">
-        <v>323.7785647692876</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D60" t="n">
-        <v>318.2773440842135</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E60" t="n">
-        <v>321.7781372070312</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F60" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>321.6996588106788</v>
+        <v>316.639672337624</v>
       </c>
       <c r="C61" t="n">
-        <v>328.112871433911</v>
+        <v>323.4058905098511</v>
       </c>
       <c r="D61" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139070917166</v>
       </c>
       <c r="E61" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558654785156</v>
       </c>
       <c r="F61" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>316.6397026430911</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C62" t="n">
-        <v>323.4059214629105</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D62" t="n">
-        <v>315.4139372798661</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E62" t="n">
-        <v>318.8558959960938</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F62" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C63" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D63" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E63" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F63" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C64" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D64" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E64" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F64" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C65" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D65" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E65" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F65" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C66" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D66" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E66" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F66" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C67" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D67" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E67" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F67" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845627249562</v>
       </c>
       <c r="C68" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631082445032</v>
       </c>
       <c r="D68" t="n">
-        <v>323.484378234348</v>
+        <v>321.1504873151108</v>
       </c>
       <c r="E68" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779296875</v>
       </c>
       <c r="F68" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>324.4845927435845</v>
+        <v>328.9463775793847</v>
       </c>
       <c r="C69" t="n">
-        <v>333.6631391122548</v>
+        <v>340.2136022879278</v>
       </c>
       <c r="D69" t="n">
-        <v>321.1505170252981</v>
+        <v>327.3773920593259</v>
       </c>
       <c r="E69" t="n">
-        <v>329.8779602050781</v>
+        <v>335.3889770507812</v>
       </c>
       <c r="F69" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>328.9464075107404</v>
+        <v>341.5963098138764</v>
       </c>
       <c r="C70" t="n">
-        <v>340.2136332445062</v>
+        <v>345.7736979738297</v>
       </c>
       <c r="D70" t="n">
-        <v>327.377421847917</v>
+        <v>338.4289212269501</v>
       </c>
       <c r="E70" t="n">
-        <v>335.3890075683594</v>
+        <v>342.2042846679688</v>
       </c>
       <c r="F70" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>341.5962793505171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C71" t="n">
-        <v>345.7736671379334</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D71" t="n">
-        <v>338.4288910460567</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E71" t="n">
-        <v>342.2042541503906</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F71" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3986242436816</v>
       </c>
       <c r="C72" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1550277170099</v>
       </c>
       <c r="D72" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926741052517</v>
       </c>
       <c r="E72" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253967285156</v>
       </c>
       <c r="F72" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>334.3985942399352</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C73" t="n">
-        <v>341.1549971070486</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D73" t="n">
-        <v>334.1926441199842</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E73" t="n">
-        <v>340.1253662109375</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F73" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>340.5176266555306</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C74" t="n">
-        <v>342.2925325530242</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D74" t="n">
-        <v>335.840116682576</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E74" t="n">
-        <v>337.31103515625</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F74" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8791141795932</v>
       </c>
       <c r="C75" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2125187841528</v>
       </c>
       <c r="D75" t="n">
-        <v>327.465664861477</v>
+        <v>326.3968234220132</v>
       </c>
       <c r="E75" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558715820312</v>
       </c>
       <c r="F75" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>334.8790829701986</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C76" t="n">
-        <v>335.2124875436862</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D76" t="n">
-        <v>326.3967930031341</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E76" t="n">
-        <v>327.4558410644531</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F76" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C77" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D77" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E77" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F77" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C78" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D78" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E78" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F78" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C79" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D79" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E79" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F79" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C80" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D80" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E80" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F80" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C81" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D81" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E81" t="n">
-        <v>341.0079040527344</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F81" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>340.4489839349073</v>
+        <v>347.4113430771444</v>
       </c>
       <c r="C82" t="n">
-        <v>348.0683609450301</v>
+        <v>350.9317378318185</v>
       </c>
       <c r="D82" t="n">
-        <v>340.0469292856779</v>
+        <v>346.1463447630524</v>
       </c>
       <c r="E82" t="n">
-        <v>347.59765625</v>
+        <v>349.3529663085938</v>
       </c>
       <c r="F82" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>347.4112823812074</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C83" t="n">
-        <v>350.9316765208364</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D83" t="n">
-        <v>346.1462842881223</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E83" t="n">
-        <v>349.3529052734375</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F83" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>347.0876909760341</v>
+        <v>288.2706063388866</v>
       </c>
       <c r="C84" t="n">
-        <v>347.9114016111286</v>
+        <v>293.6933912983777</v>
       </c>
       <c r="D84" t="n">
-        <v>340.5371789096768</v>
+        <v>274.96368990819</v>
       </c>
       <c r="E84" t="n">
-        <v>344.8224792480469</v>
+        <v>277.2191162109375</v>
       </c>
       <c r="F84" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>288.2705746047087</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C85" t="n">
-        <v>293.6933589672342</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D85" t="n">
-        <v>274.9636596388997</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E85" t="n">
-        <v>277.2190856933594</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F85" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>278.2193161239855</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C86" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D86" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E86" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F86" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>288.6235657000577</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C87" t="n">
-        <v>289.8689623036692</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D87" t="n">
-        <v>283.6126518953886</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E87" t="n">
-        <v>286.6231384277344</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F87" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4746956220067</v>
       </c>
       <c r="C88" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7697819219751</v>
       </c>
       <c r="D88" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072155055542</v>
       </c>
       <c r="E88" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530395507812</v>
       </c>
       <c r="F88" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>280.4747261855329</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C89" t="n">
-        <v>284.7698129535399</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D89" t="n">
-        <v>276.8072456694325</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E89" t="n">
-        <v>280.0530700683594</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F89" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C90" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D90" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E90" t="n">
-        <v>278.6703796386719</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F90" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>276.5424507136568</v>
+        <v>268.9721802809009</v>
       </c>
       <c r="C91" t="n">
-        <v>278.9841654678224</v>
+        <v>271.5217784748567</v>
       </c>
       <c r="D91" t="n">
-        <v>268.7367562069888</v>
+        <v>261.1272811769848</v>
       </c>
       <c r="E91" t="n">
-        <v>270.5705261230469</v>
+        <v>263.3434448242188</v>
       </c>
       <c r="F91" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>268.9721491110363</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C92" t="n">
-        <v>271.5217470095316</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D92" t="n">
-        <v>261.127250916227</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E92" t="n">
-        <v>263.3434143066406</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F92" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C93" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D93" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E93" t="n">
-        <v>271.286376953125</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F93" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>268.8348608333229</v>
+        <v>272.139502815215</v>
       </c>
       <c r="C94" t="n">
-        <v>274.7479519102809</v>
+        <v>274.0713101587253</v>
       </c>
       <c r="D94" t="n">
-        <v>268.0209657772727</v>
+        <v>267.3639259113162</v>
       </c>
       <c r="E94" t="n">
-        <v>270.3548278808594</v>
+        <v>267.9228820800781</v>
       </c>
       <c r="F94" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>272.1395338130845</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C95" t="n">
-        <v>274.0713413766361</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D95" t="n">
-        <v>267.3639563652268</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E95" t="n">
-        <v>267.9229125976562</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F95" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7670960064547</v>
       </c>
       <c r="C96" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7590795351679</v>
       </c>
       <c r="D96" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626513270822</v>
       </c>
       <c r="E96" t="n">
-        <v>273.5025634765625</v>
+        <v>278.856689453125</v>
       </c>
       <c r="F96" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>272.7671258575986</v>
+        <v>280.0923103323967</v>
       </c>
       <c r="C97" t="n">
-        <v>280.7591102609402</v>
+        <v>287.7704918658715</v>
       </c>
       <c r="D97" t="n">
-        <v>270.4626809260317</v>
+        <v>278.994029288489</v>
       </c>
       <c r="E97" t="n">
-        <v>278.8567199707031</v>
+        <v>287.5057373046875</v>
       </c>
       <c r="F97" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>280.0922508710514</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C98" t="n">
-        <v>287.7704307745099</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D98" t="n">
-        <v>278.9939700602999</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E98" t="n">
-        <v>287.5056762695312</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F98" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>288.3000088357305</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C99" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D99" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E99" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F99" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>284.377578031072</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C100" t="n">
-        <v>284.5050624231632</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D100" t="n">
-        <v>280.7395146362062</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E100" t="n">
-        <v>282.6124877929688</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F100" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>285.2503082207336</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C101" t="n">
-        <v>285.2503082207336</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D101" t="n">
-        <v>281.3278592694971</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E101" t="n">
-        <v>284.3088989257812</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F101" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C102" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D102" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E102" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F102" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C103" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D103" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E103" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F103" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>276.7287838236561</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C104" t="n">
-        <v>276.9248883144977</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D104" t="n">
-        <v>266.5303926707583</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E104" t="n">
-        <v>268.6387329101562</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F104" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4161285575944</v>
       </c>
       <c r="C105" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355972025459</v>
       </c>
       <c r="D105" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000570330196</v>
       </c>
       <c r="E105" t="n">
-        <v>278.6900024414062</v>
+        <v>281.1023254394531</v>
       </c>
       <c r="F105" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>281.4160980059485</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C106" t="n">
-        <v>289.5355657694184</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D106" t="n">
-        <v>279.7000266676773</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E106" t="n">
-        <v>281.102294921875</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F106" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C107" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D107" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E107" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F107" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C108" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D108" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E108" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F108" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>283.3871388529354</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C109" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D109" t="n">
-        <v>278.8468991181569</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E109" t="n">
-        <v>283.6028747558594</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F109" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C110" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D110" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E110" t="n">
-        <v>286.2995300292969</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F110" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>284.4265691931125</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C111" t="n">
-        <v>285.7406159339096</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D111" t="n">
-        <v>281.1807450619272</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E111" t="n">
-        <v>283.17138671875</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F111" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C112" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D112" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E112" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F112" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C113" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D113" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E113" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F113" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G113" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C114" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D114" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E114" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F114" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>279.0580549356083</v>
+        <v>281.4297838763166</v>
       </c>
       <c r="C115" t="n">
-        <v>282.8528771272727</v>
+        <v>284.177078134999</v>
       </c>
       <c r="D115" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039671765164</v>
       </c>
       <c r="E115" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907104492188</v>
       </c>
       <c r="F115" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>281.42981524537</v>
+        <v>274.7888344130931</v>
       </c>
       <c r="C116" t="n">
-        <v>284.1771098102745</v>
+        <v>279.5521380386192</v>
       </c>
       <c r="D116" t="n">
-        <v>273.039702199029</v>
+        <v>274.5417754718342</v>
       </c>
       <c r="E116" t="n">
-        <v>273.7907409667969</v>
+        <v>278.7714233398438</v>
       </c>
       <c r="F116" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>274.7888644946905</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C117" t="n">
-        <v>279.5521686416635</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D117" t="n">
-        <v>274.5418055263856</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E117" t="n">
-        <v>278.7714538574219</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F117" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>280.6392236042361</v>
+        <v>284.41428667964</v>
       </c>
       <c r="C118" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902898411239</v>
       </c>
       <c r="D118" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4891167908925</v>
       </c>
       <c r="E118" t="n">
-        <v>282.1314392089844</v>
+        <v>284.18701171875</v>
       </c>
       <c r="F118" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>284.4142561376558</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C119" t="n">
-        <v>285.5902591728541</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D119" t="n">
-        <v>281.4890865630293</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E119" t="n">
-        <v>284.1869812011719</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F119" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589555118485</v>
       </c>
       <c r="C120" t="n">
-        <v>285.0072039222152</v>
+        <v>284.1671803923218</v>
       </c>
       <c r="D120" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7751962176443</v>
       </c>
       <c r="E120" t="n">
-        <v>280.9850769042969</v>
+        <v>277.1408386230469</v>
       </c>
       <c r="F120" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>280.6589864168267</v>
+        <v>275.7078960775263</v>
       </c>
       <c r="C121" t="n">
-        <v>284.167211683611</v>
+        <v>279.7695608963037</v>
       </c>
       <c r="D121" t="n">
-        <v>276.7752266949594</v>
+        <v>271.7648448878931</v>
       </c>
       <c r="E121" t="n">
-        <v>277.140869140625</v>
+        <v>272.347900390625</v>
       </c>
       <c r="F121" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>275.7079269716043</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C122" t="n">
-        <v>279.769592245506</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D122" t="n">
-        <v>271.7648753401377</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E122" t="n">
-        <v>272.3479309082031</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F122" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069856894997</v>
       </c>
       <c r="C123" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639393177099</v>
       </c>
       <c r="D123" t="n">
-        <v>265.9243614270812</v>
+        <v>264.44204492441</v>
       </c>
       <c r="E123" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768737792969</v>
       </c>
       <c r="F123" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>265.7069555541203</v>
+        <v>271.7648799566674</v>
       </c>
       <c r="C124" t="n">
-        <v>270.1639086768414</v>
+        <v>272.8321614881822</v>
       </c>
       <c r="D124" t="n">
-        <v>264.4420149324948</v>
+        <v>263.9676840156166</v>
       </c>
       <c r="E124" t="n">
-        <v>269.0768432617188</v>
+        <v>267.3672180175781</v>
       </c>
       <c r="F124" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>271.7648489371355</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C125" t="n">
-        <v>272.8321303468297</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D125" t="n">
-        <v>263.9676538860649</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E125" t="n">
-        <v>267.3671875</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F125" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C126" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D126" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E126" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F126" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>264.3530902318651</v>
+        <v>257.1191907461688</v>
       </c>
       <c r="C127" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2438917467647</v>
       </c>
       <c r="D127" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505034942698</v>
       </c>
       <c r="E127" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102661132812</v>
       </c>
       <c r="F127" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>257.119221076063</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C128" t="n">
-        <v>259.2439223272896</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D128" t="n">
-        <v>253.6505334149961</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E128" t="n">
-        <v>258.7102966308594</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F128" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C129" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D129" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E129" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F129" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867274922702</v>
       </c>
       <c r="C130" t="n">
-        <v>272.0613148441149</v>
+        <v>275.757318970375</v>
       </c>
       <c r="D130" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356586528844</v>
       </c>
       <c r="E130" t="n">
-        <v>270.7568664550781</v>
+        <v>273.9982604980469</v>
       </c>
       <c r="F130" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>269.0867574628081</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C131" t="n">
-        <v>275.7573496838748</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D131" t="n">
-        <v>268.3356885397691</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E131" t="n">
-        <v>273.998291015625</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F131" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C132" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D132" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E132" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F132" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3296014014268</v>
       </c>
       <c r="C133" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881914326393</v>
       </c>
       <c r="D133" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439367148364</v>
       </c>
       <c r="E133" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804321289062</v>
       </c>
       <c r="F133" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>308.3295702834321</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C134" t="n">
-        <v>309.2881602178994</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D134" t="n">
-        <v>301.2439063119584</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E134" t="n">
-        <v>302.3804016113281</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F134" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272561704691</v>
       </c>
       <c r="C135" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187701494722</v>
       </c>
       <c r="D135" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213715612747</v>
       </c>
       <c r="E135" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7498168945312</v>
       </c>
       <c r="F135" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>304.3272252898824</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C136" t="n">
-        <v>306.7187390262146</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D136" t="n">
-        <v>300.6213410567302</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E136" t="n">
-        <v>300.7497863769531</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F136" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C137" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D137" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E137" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F137" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C138" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D138" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E138" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F138" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2943017295384</v>
       </c>
       <c r="C139" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8618187748353</v>
       </c>
       <c r="D139" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4265214430497</v>
       </c>
       <c r="E139" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6778259277344</v>
       </c>
       <c r="F139" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>311.2942713469933</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C140" t="n">
-        <v>314.8617880440979</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D140" t="n">
-        <v>309.4264912428012</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E140" t="n">
-        <v>312.6777954101562</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F140" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>316.2848676157387</v>
+        <v>320.37616900858</v>
       </c>
       <c r="C141" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719258918635</v>
       </c>
       <c r="D141" t="n">
-        <v>313.4091278691752</v>
+        <v>316.35404203196</v>
       </c>
       <c r="E141" t="n">
-        <v>320.8110046386719</v>
+        <v>319.6745300292969</v>
       </c>
       <c r="F141" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>320.3761995931397</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C142" t="n">
-        <v>321.5719565905757</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D142" t="n">
-        <v>316.3540722325493</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E142" t="n">
-        <v>319.674560546875</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F142" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7521876325058</v>
       </c>
       <c r="C143" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418314545246</v>
       </c>
       <c r="D143" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931290879458</v>
       </c>
       <c r="E143" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611145019531</v>
       </c>
       <c r="F143" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>346.7522179221875</v>
+        <v>350.5074994974842</v>
       </c>
       <c r="C144" t="n">
-        <v>354.3418624071809</v>
+        <v>352.6519846563255</v>
       </c>
       <c r="D144" t="n">
-        <v>344.9931592239693</v>
+        <v>346.3766807003688</v>
       </c>
       <c r="E144" t="n">
-        <v>349.3611450195312</v>
+        <v>350.388916015625</v>
       </c>
       <c r="F144" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>350.5074689695779</v>
+        <v>352.2961666917061</v>
       </c>
       <c r="C145" t="n">
-        <v>352.6519539416425</v>
+        <v>354.0651171980212</v>
       </c>
       <c r="D145" t="n">
-        <v>346.3766505322415</v>
+        <v>347.2561882957746</v>
       </c>
       <c r="E145" t="n">
-        <v>350.3888854980469</v>
+        <v>350.7446594238281</v>
       </c>
       <c r="F145" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>352.2961973442777</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C146" t="n">
-        <v>354.0651480045056</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D146" t="n">
-        <v>347.256218509828</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E146" t="n">
-        <v>350.7446899414062</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F146" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C147" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D147" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E147" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F147" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C148" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D148" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E148" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F148" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C149" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D149" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E149" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F149" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C150" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D150" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E150" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F150" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C151" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D151" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E151" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F151" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216408565838</v>
       </c>
       <c r="C152" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260893018678</v>
       </c>
       <c r="D152" t="n">
-        <v>360.360183242299</v>
+        <v>357.5536224796683</v>
       </c>
       <c r="E152" t="n">
-        <v>366.388427734375</v>
+        <v>359.5893859863281</v>
       </c>
       <c r="F152" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>366.1216097846273</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C153" t="n">
-        <v>367.4260581192055</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D153" t="n">
-        <v>357.553592134861</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E153" t="n">
-        <v>359.58935546875</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F153" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C154" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D154" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E154" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F154" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="C155" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="D155" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="E155" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="F155" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>367.6138623558188</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C156" t="n">
-        <v>375.5098876953125</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D156" t="n">
-        <v>367.6138623558188</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E156" t="n">
-        <v>375.5098876953125</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F156" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3460853480032</v>
       </c>
       <c r="C157" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7446883171237</v>
       </c>
       <c r="D157" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5159708878205</v>
       </c>
       <c r="E157" t="n">
-        <v>379.9173889160156</v>
+        <v>391.726806640625</v>
       </c>
       <c r="F157" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>378.3461148231528</v>
+        <v>391.835521582727</v>
       </c>
       <c r="C158" t="n">
-        <v>392.7447189140002</v>
+        <v>399.3955199396844</v>
       </c>
       <c r="D158" t="n">
-        <v>377.5160002982997</v>
+        <v>388.3766960454267</v>
       </c>
       <c r="E158" t="n">
-        <v>391.7268371582031</v>
+        <v>396.4407043457031</v>
       </c>
       <c r="F158" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>391.8354914196509</v>
+        <v>396.2825841810375</v>
       </c>
       <c r="C159" t="n">
-        <v>399.3954891946478</v>
+        <v>397.1719904330225</v>
       </c>
       <c r="D159" t="n">
-        <v>388.3766661486073</v>
+        <v>391.3414048271592</v>
       </c>
       <c r="E159" t="n">
-        <v>396.440673828125</v>
+        <v>394.3950500488281</v>
       </c>
       <c r="F159" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>396.2825535174053</v>
+        <v>389.6613628183419</v>
       </c>
       <c r="C160" t="n">
-        <v>397.1719597005697</v>
+        <v>392.9522049122001</v>
       </c>
       <c r="D160" t="n">
-        <v>391.3413745458666</v>
+        <v>385.6590199026367</v>
       </c>
       <c r="E160" t="n">
-        <v>394.39501953125</v>
+        <v>389.2166748046875</v>
       </c>
       <c r="F160" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>389.661393370787</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C161" t="n">
-        <v>392.9522357226725</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D161" t="n">
-        <v>385.6590501412673</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E161" t="n">
-        <v>389.2167053222656</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F161" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119880990537</v>
       </c>
       <c r="C162" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432754242469</v>
       </c>
       <c r="D162" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512904411622</v>
       </c>
       <c r="E162" t="n">
-        <v>386.5286865234375</v>
+        <v>384.6609191894531</v>
       </c>
       <c r="F162" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>385.4119575218886</v>
+        <v>384.9672452573303</v>
       </c>
       <c r="C163" t="n">
-        <v>390.3432444558516</v>
+        <v>388.7522052741927</v>
       </c>
       <c r="D163" t="n">
-        <v>382.9512600592197</v>
+        <v>376.2213825216763</v>
       </c>
       <c r="E163" t="n">
-        <v>384.660888671875</v>
+        <v>378.790771484375</v>
       </c>
       <c r="F163" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>384.9672762725209</v>
+        <v>376.6364522760421</v>
       </c>
       <c r="C164" t="n">
-        <v>388.7522365943216</v>
+        <v>381.5677396470687</v>
       </c>
       <c r="D164" t="n">
-        <v>376.2214128322495</v>
+        <v>376.0632887376697</v>
       </c>
       <c r="E164" t="n">
-        <v>378.7908020019531</v>
+        <v>377.98046875</v>
       </c>
       <c r="F164" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>376.6364218669779</v>
+        <v>377.4270309363715</v>
       </c>
       <c r="C165" t="n">
-        <v>381.5677088398597</v>
+        <v>385.9456187280053</v>
       </c>
       <c r="D165" t="n">
-        <v>376.0632583748818</v>
+        <v>376.5277327371266</v>
       </c>
       <c r="E165" t="n">
-        <v>377.9804382324219</v>
+        <v>383.8999633789062</v>
       </c>
       <c r="F165" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>377.4270609393932</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C166" t="n">
-        <v>385.9456494081999</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D166" t="n">
-        <v>376.5277626686598</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E166" t="n">
-        <v>383.8999938964844</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F166" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C167" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D167" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E167" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F167" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312827021371</v>
       </c>
       <c r="C168" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6807151570288</v>
       </c>
       <c r="D168" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783391116702</v>
       </c>
       <c r="E168" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298767089844</v>
       </c>
       <c r="F168" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>380.4312519906984</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C169" t="n">
-        <v>384.6806841025421</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D169" t="n">
-        <v>376.4783087193446</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E169" t="n">
-        <v>378.0298461914062</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F169" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C170" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D170" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E170" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F170" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C171" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D171" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E171" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F171" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C172" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D172" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E172" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F172" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119603627872</v>
       </c>
       <c r="C173" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6580885443842</v>
       </c>
       <c r="D173" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2340851575979</v>
       </c>
       <c r="E173" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058471679688</v>
       </c>
       <c r="F173" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>385.4119903823484</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C174" t="n">
-        <v>396.6581194399012</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D174" t="n">
-        <v>385.2341151633045</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E174" t="n">
-        <v>391.8058776855469</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F174" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C175" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D175" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E175" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F175" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>392.4580996989546</v>
+        <v>405.166788512205</v>
       </c>
       <c r="C176" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="D176" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6467992699509</v>
       </c>
       <c r="E176" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="F176" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>405.1668188073661</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C177" t="n">
-        <v>408.1414184570312</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D177" t="n">
-        <v>402.6468293766872</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E177" t="n">
-        <v>408.1414184570312</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F177" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C178" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D178" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E178" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F178" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C179" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D179" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E179" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F179" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C180" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D180" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E180" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F180" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,25 +5123,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C181" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D181" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E181" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F181" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G181" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C182" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D182" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E182" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F182" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C183" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D183" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E183" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F183" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C184" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D184" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E184" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F184" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C185" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D185" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E185" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F185" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C186" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D186" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E186" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F186" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C187" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D187" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E187" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F187" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C188" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D188" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E188" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F188" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C189" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D189" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E189" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F189" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C190" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D190" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E190" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F190" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C191" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D191" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E191" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F191" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C192" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D192" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E192" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F192" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C193" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D193" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E193" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F193" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C194" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D194" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E194" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F194" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C195" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D195" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E195" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F195" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C196" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D196" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E196" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F196" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C197" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D197" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E197" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F197" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C198" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D198" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E198" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F198" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C199" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D199" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E199" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F199" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C200" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D200" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E200" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F200" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C201" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D201" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E201" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F201" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C202" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D202" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E202" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F202" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C203" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D203" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E203" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F203" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C204" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D204" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E204" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F204" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C205" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D205" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E205" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F205" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C206" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D206" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E206" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F206" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C207" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D207" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E207" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F207" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C208" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D208" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E208" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F208" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C209" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D209" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E209" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F209" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C210" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D210" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E210" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F210" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C211" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D211" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E211" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F211" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C212" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D212" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E212" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F212" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C213" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D213" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E213" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F213" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C214" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D214" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E214" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F214" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C215" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D215" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E215" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F215" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C216" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D216" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E216" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F216" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C217" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D217" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E217" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F217" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C218" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D218" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E218" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F218" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C219" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D219" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E219" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F219" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C220" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D220" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E220" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F220" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C221" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D221" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E221" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F221" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C222" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D222" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E222" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F222" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C223" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D223" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E223" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F223" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C224" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D224" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E224" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F224" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C225" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D225" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E225" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F225" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C226" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D226" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E226" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F226" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C227" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D227" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E227" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F227" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C228" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D228" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E228" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F228" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C229" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D229" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E229" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F229" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C230" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D230" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E230" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F230" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C231" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D231" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E231" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F231" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C232" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D232" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E232" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F232" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C233" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D233" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E233" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F233" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C234" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D234" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E234" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F234" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C235" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D235" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E235" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F235" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C236" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D236" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E236" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F236" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C237" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D237" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E237" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F237" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C238" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D238" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E238" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F238" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C239" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D239" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E239" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F239" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C240" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D240" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E240" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F240" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C241" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D241" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E241" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F241" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C242" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D242" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E242" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F242" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C243" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D243" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E243" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F243" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G243" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C244" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D244" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E244" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F244" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C245" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D245" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E245" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F245" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C246" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D246" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E246" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F246" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>375.2900085449219</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C247" t="n">
-        <v>378.489990234375</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D247" t="n">
-        <v>372.4200134277344</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E247" t="n">
-        <v>376.8999938964844</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F247" t="n">
-        <v>8606300</v>
+        <v>5712300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>377.8699951171875</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="C248" t="n">
-        <v>378.9500122070312</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="D248" t="n">
-        <v>373.8200073242188</v>
+        <v>372.4100036621094</v>
       </c>
       <c r="E248" t="n">
-        <v>377.5599975585938</v>
+        <v>372.9500122070312</v>
       </c>
       <c r="F248" t="n">
-        <v>5712300</v>
+        <v>4495000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>381.3900146484375</v>
+        <v>370.8900146484375</v>
       </c>
       <c r="C249" t="n">
-        <v>381.3900146484375</v>
+        <v>372.6099853515625</v>
       </c>
       <c r="D249" t="n">
-        <v>372.4100036621094</v>
+        <v>366</v>
       </c>
       <c r="E249" t="n">
-        <v>372.9500122070312</v>
+        <v>371.2900085449219</v>
       </c>
       <c r="F249" t="n">
-        <v>4495000</v>
+        <v>3859300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>370.8900146484375</v>
+        <v>371.9200134277344</v>
       </c>
       <c r="C250" t="n">
-        <v>372.6099853515625</v>
+        <v>375.2799987792969</v>
       </c>
       <c r="D250" t="n">
-        <v>366</v>
+        <v>368.5</v>
       </c>
       <c r="E250" t="n">
-        <v>371.2900085449219</v>
+        <v>375.010009765625</v>
       </c>
       <c r="F250" t="n">
-        <v>3859300</v>
+        <v>4651000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>371.9200134277344</v>
+        <v>375.9500122070312</v>
       </c>
       <c r="C251" t="n">
-        <v>375.2799987792969</v>
+        <v>379.1700134277344</v>
       </c>
       <c r="D251" t="n">
-        <v>368.5</v>
+        <v>371.1700134277344</v>
       </c>
       <c r="E251" t="n">
-        <v>375.010009765625</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="F251" t="n">
-        <v>4651000</v>
+        <v>4077400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>375.9500122070312</v>
+        <v>376.3599853515625</v>
       </c>
       <c r="C252" t="n">
-        <v>379.1700134277344</v>
+        <v>380.9800109863281</v>
       </c>
       <c r="D252" t="n">
-        <v>371.1700134277344</v>
+        <v>374.5599975585938</v>
       </c>
       <c r="E252" t="n">
-        <v>376.5899963378906</v>
+        <v>377.8299865722656</v>
       </c>
       <c r="F252" t="n">
-        <v>4077400</v>
+        <v>4614700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="D2" t="n">
         <v>376.59</v>
       </c>
-      <c r="D2" t="n">
-        <v>375.01</v>
-      </c>
       <c r="E2" t="n">
-        <v>375.95</v>
+        <v>376.36</v>
       </c>
       <c r="F2" t="n">
-        <v>379.17</v>
+        <v>380.98</v>
       </c>
       <c r="G2" t="n">
-        <v>371.27</v>
+        <v>374.56</v>
       </c>
       <c r="H2" t="n">
-        <v>4073729</v>
+        <v>4494798</v>
       </c>
       <c r="I2" t="n">
-        <v>4992169</v>
+        <v>4968876</v>
       </c>
       <c r="J2" t="n">
-        <v>338025218048</v>
+        <v>339138248704</v>
       </c>
       <c r="K2" t="n">
-        <v>24.202442</v>
+        <v>24.21987</v>
       </c>
       <c r="L2" t="n">
-        <v>16.655766</v>
+        <v>16.710608</v>
       </c>
       <c r="M2" t="n">
-        <v>15.56</v>
+        <v>15.6</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10572,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4619098</v>
+        <v>3.4733088</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>387387228160</v>
+        <v>388500258816</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:56</t>
+          <t>2026-09-29 13:24:52</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>335.0582538691371</v>
+        <v>334.8342081470359</v>
       </c>
       <c r="C2" t="n">
-        <v>336.5875104266321</v>
+        <v>340.2597470322082</v>
       </c>
       <c r="D2" t="n">
-        <v>332.5938752825687</v>
+        <v>333.4510253931927</v>
       </c>
       <c r="E2" t="n">
-        <v>336.2271118164062</v>
+        <v>336.343994140625</v>
       </c>
       <c r="F2" t="n">
-        <v>6878900</v>
+        <v>7429700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>334.8342385276262</v>
+        <v>334.9803326465864</v>
       </c>
       <c r="C3" t="n">
-        <v>340.2597779050752</v>
+        <v>339.6558538996071</v>
       </c>
       <c r="D3" t="n">
-        <v>333.4510556482824</v>
+        <v>332.7692198568235</v>
       </c>
       <c r="E3" t="n">
-        <v>336.3440246582031</v>
+        <v>339.2662048339844</v>
       </c>
       <c r="F3" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>334.9803025145298</v>
+        <v>338.2824047650262</v>
       </c>
       <c r="C4" t="n">
-        <v>339.6558233469793</v>
+        <v>345.87033541468</v>
       </c>
       <c r="D4" t="n">
-        <v>332.7691899236603</v>
+        <v>335.7108637419195</v>
       </c>
       <c r="E4" t="n">
-        <v>339.2661743164062</v>
+        <v>344.5456237792969</v>
       </c>
       <c r="F4" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>338.2823748022027</v>
+        <v>347.9840761494036</v>
       </c>
       <c r="C5" t="n">
-        <v>345.8703047797677</v>
+        <v>358.4552554876992</v>
       </c>
       <c r="D5" t="n">
-        <v>335.7108340068662</v>
+        <v>347.3606614365734</v>
       </c>
       <c r="E5" t="n">
-        <v>344.5455932617188</v>
+        <v>350.8575744628906</v>
       </c>
       <c r="F5" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>347.9840761494036</v>
+        <v>351.6660530964717</v>
       </c>
       <c r="C6" t="n">
-        <v>358.4552554876992</v>
+        <v>353.1173978230779</v>
       </c>
       <c r="D6" t="n">
-        <v>347.3606614365734</v>
+        <v>347.8477120863685</v>
       </c>
       <c r="E6" t="n">
-        <v>350.8575744628906</v>
+        <v>349.4646606445312</v>
       </c>
       <c r="F6" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C7" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D7" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E7" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F7" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4130008055815</v>
       </c>
       <c r="C8" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132992932725</v>
       </c>
       <c r="D8" t="n">
-        <v>348.77305405812</v>
+        <v>356.3123046396842</v>
       </c>
       <c r="E8" t="n">
-        <v>354.2278137207031</v>
+        <v>360.3254699707031</v>
       </c>
       <c r="F8" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>357.4129705346734</v>
+        <v>362.8579709138762</v>
       </c>
       <c r="C9" t="n">
-        <v>364.9132683871306</v>
+        <v>366.4620162306247</v>
       </c>
       <c r="D9" t="n">
-        <v>356.3122744619989</v>
+        <v>356.585002247802</v>
       </c>
       <c r="E9" t="n">
-        <v>360.325439453125</v>
+        <v>358.1532592773438</v>
       </c>
       <c r="F9" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>362.8580327507921</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="C10" t="n">
-        <v>366.4620786817287</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="D10" t="n">
-        <v>356.5850630157017</v>
+        <v>343.3670132328114</v>
       </c>
       <c r="E10" t="n">
-        <v>358.1533203125</v>
+        <v>345.3053894042969</v>
       </c>
       <c r="F10" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>359.8189563090651</v>
+        <v>345.5391725764172</v>
       </c>
       <c r="C11" t="n">
-        <v>359.8189563090651</v>
+        <v>349.8445450312873</v>
       </c>
       <c r="D11" t="n">
-        <v>343.3670435790787</v>
+        <v>344.1560194689148</v>
       </c>
       <c r="E11" t="n">
-        <v>345.305419921875</v>
+        <v>349.3575134277344</v>
       </c>
       <c r="F11" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>345.5391423923842</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C12" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D12" t="n">
-        <v>344.155989405705</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E12" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F12" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C13" t="n">
-        <v>352.9322890785681</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D13" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E13" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F13" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4549874654966</v>
       </c>
       <c r="C14" t="n">
-        <v>354.77327893078</v>
+        <v>352.6108411281484</v>
       </c>
       <c r="D14" t="n">
-        <v>346.6203751846734</v>
+        <v>345.207955645442</v>
       </c>
       <c r="E14" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4190979003906</v>
       </c>
       <c r="F14" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>352.4550184254314</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C15" t="n">
-        <v>352.6108721017735</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D15" t="n">
-        <v>345.2079859687916</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E15" t="n">
-        <v>347.4191284179688</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F15" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406127602151</v>
       </c>
       <c r="C16" t="n">
-        <v>349.0945029745603</v>
+        <v>356.0882755673564</v>
       </c>
       <c r="D16" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373288971846</v>
       </c>
       <c r="E16" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265502929688</v>
       </c>
       <c r="F16" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>349.2406127602151</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C17" t="n">
-        <v>356.0882755673564</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D17" t="n">
-        <v>348.2373288971846</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E17" t="n">
-        <v>355.0265502929688</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F17" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C18" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D18" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E18" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F18" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>354.5200118501019</v>
+        <v>346.3573316043178</v>
       </c>
       <c r="C19" t="n">
-        <v>354.5589826989666</v>
+        <v>352.8835660308217</v>
       </c>
       <c r="D19" t="n">
-        <v>348.7146038632694</v>
+        <v>344.4676766060103</v>
       </c>
       <c r="E19" t="n">
-        <v>352.1140747070312</v>
+        <v>351.1010437011719</v>
       </c>
       <c r="F19" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>346.3573617095742</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C20" t="n">
-        <v>352.883596703336</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D20" t="n">
-        <v>344.4677065470185</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E20" t="n">
-        <v>351.10107421875</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F20" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>351.9972042484119</v>
+        <v>354.0719227699667</v>
       </c>
       <c r="C21" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7213754856504</v>
       </c>
       <c r="D21" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0263843961002</v>
       </c>
       <c r="E21" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876098632812</v>
       </c>
       <c r="F21" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063444379755</v>
       </c>
       <c r="C22" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180517731913</v>
       </c>
       <c r="D22" t="n">
-        <v>352.0264145317695</v>
+        <v>349.3282643556941</v>
       </c>
       <c r="E22" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2993774414062</v>
       </c>
       <c r="F22" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>370.8063128551364</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C23" t="n">
-        <v>371.118020163803</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D23" t="n">
-        <v>349.3282346022162</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E23" t="n">
-        <v>358.2993469238281</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F23" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064021770676</v>
       </c>
       <c r="C24" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443442519412</v>
       </c>
       <c r="D24" t="n">
-        <v>344.701472908826</v>
+        <v>334.6880914224008</v>
       </c>
       <c r="E24" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082580566406</v>
       </c>
       <c r="F24" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>338.5064329398476</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C25" t="n">
-        <v>345.3443756361395</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D25" t="n">
-        <v>334.6881218381804</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E25" t="n">
-        <v>335.8082885742188</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F25" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>335.4576347488759</v>
+        <v>330.3340003407686</v>
       </c>
       <c r="C26" t="n">
-        <v>337.298598712068</v>
+        <v>331.863286433141</v>
       </c>
       <c r="D26" t="n">
-        <v>328.3761763650699</v>
+        <v>318.128991755756</v>
       </c>
       <c r="E26" t="n">
-        <v>332.7010192871094</v>
+        <v>325.1325073242188</v>
       </c>
       <c r="F26" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>330.3340623523696</v>
+        <v>319.1323440808776</v>
       </c>
       <c r="C27" t="n">
-        <v>331.8633487318257</v>
+        <v>327.7722802636044</v>
       </c>
       <c r="D27" t="n">
-        <v>318.1290514761847</v>
+        <v>318.7135040219252</v>
       </c>
       <c r="E27" t="n">
-        <v>325.132568359375</v>
+        <v>322.2493286132812</v>
       </c>
       <c r="F27" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>319.1323138584834</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C28" t="n">
-        <v>327.7722492229931</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D28" t="n">
-        <v>318.7134738391959</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E28" t="n">
-        <v>322.2492980957031</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F28" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>317.8367876317881</v>
+        <v>320.3888776178953</v>
       </c>
       <c r="C29" t="n">
-        <v>321.6453780396488</v>
+        <v>323.7493777886428</v>
       </c>
       <c r="D29" t="n">
-        <v>315.8107493995538</v>
+        <v>313.1126243976539</v>
       </c>
       <c r="E29" t="n">
-        <v>319.2394409179688</v>
+        <v>313.2197570800781</v>
       </c>
       <c r="F29" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>320.3888464018165</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C30" t="n">
-        <v>323.7493462451443</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D30" t="n">
-        <v>313.1125938905139</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E30" t="n">
-        <v>313.2197265625</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F30" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>311.3690496699339</v>
+        <v>311.6904703912621</v>
       </c>
       <c r="C31" t="n">
-        <v>316.1322033153182</v>
+        <v>315.8399890894766</v>
       </c>
       <c r="D31" t="n">
-        <v>306.0117020081513</v>
+        <v>308.9436347895907</v>
       </c>
       <c r="E31" t="n">
-        <v>315.801025390625</v>
+        <v>313.2392272949219</v>
       </c>
       <c r="F31" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>311.6904400245728</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C32" t="n">
-        <v>315.8399583185172</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D32" t="n">
-        <v>308.9436046905141</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E32" t="n">
-        <v>313.2391967773438</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F32" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>314.9145846167937</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C33" t="n">
-        <v>319.3563099222018</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D33" t="n">
-        <v>311.5833055007609</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E33" t="n">
-        <v>318.9569702148438</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F33" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>319.9310727655453</v>
+        <v>329.5743133227241</v>
       </c>
       <c r="C34" t="n">
-        <v>334.2692843856479</v>
+        <v>330.2366692120174</v>
       </c>
       <c r="D34" t="n">
-        <v>318.5965811998377</v>
+        <v>322.6974290151713</v>
       </c>
       <c r="E34" t="n">
-        <v>330.265869140625</v>
+        <v>323.8955078125</v>
       </c>
       <c r="F34" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>329.5742512174487</v>
+        <v>318.4699706680781</v>
       </c>
       <c r="C35" t="n">
-        <v>330.2366069819271</v>
+        <v>319.6972700691676</v>
       </c>
       <c r="D35" t="n">
-        <v>322.6973682057821</v>
+        <v>312.1775010814912</v>
       </c>
       <c r="E35" t="n">
-        <v>323.8954467773438</v>
+        <v>313.511962890625</v>
       </c>
       <c r="F35" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>318.4699396678824</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C36" t="n">
-        <v>319.6972389495053</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D36" t="n">
-        <v>312.177470693811</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E36" t="n">
-        <v>313.5119323730469</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F36" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7877447280039</v>
       </c>
       <c r="C37" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650261221254</v>
       </c>
       <c r="D37" t="n">
-        <v>311.1450007536453</v>
+        <v>300.7614447812334</v>
       </c>
       <c r="E37" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4466857910156</v>
       </c>
       <c r="F37" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>308.7878064307793</v>
+        <v>305.7876123248052</v>
       </c>
       <c r="C38" t="n">
-        <v>309.2650879202724</v>
+        <v>306.8298669435948</v>
       </c>
       <c r="D38" t="n">
-        <v>300.7615048801725</v>
+        <v>296.6314254151897</v>
       </c>
       <c r="E38" t="n">
-        <v>305.4467468261719</v>
+        <v>301.0731506347656</v>
       </c>
       <c r="F38" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>305.7876433202538</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C39" t="n">
-        <v>306.829898044689</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D39" t="n">
-        <v>296.6314554825427</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E39" t="n">
-        <v>301.0731811523438</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F39" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>302.7486093748369</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C40" t="n">
-        <v>306.5864211229751</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D40" t="n">
-        <v>301.9596204864886</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E40" t="n">
-        <v>303.4596862792969</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F40" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C41" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D41" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E41" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F41" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>316.1127181611407</v>
+        <v>312.7911523817683</v>
       </c>
       <c r="C42" t="n">
-        <v>317.3984886748711</v>
+        <v>319.4927115758689</v>
       </c>
       <c r="D42" t="n">
-        <v>309.3819381150768</v>
+        <v>312.5768573008158</v>
       </c>
       <c r="E42" t="n">
-        <v>310.7748413085938</v>
+        <v>317.8173217773438</v>
       </c>
       <c r="F42" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>312.7911824167217</v>
+        <v>318.1193136428872</v>
       </c>
       <c r="C43" t="n">
-        <v>319.4927422543219</v>
+        <v>326.4962635484334</v>
       </c>
       <c r="D43" t="n">
-        <v>312.576887315192</v>
+        <v>317.4374872026767</v>
       </c>
       <c r="E43" t="n">
-        <v>317.8173522949219</v>
+        <v>321.1583862304688</v>
       </c>
       <c r="F43" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>318.1192834140923</v>
+        <v>323.0675713492342</v>
       </c>
       <c r="C44" t="n">
-        <v>326.4962325236318</v>
+        <v>323.4474405593548</v>
       </c>
       <c r="D44" t="n">
-        <v>317.4374570386713</v>
+        <v>320.3596767020838</v>
       </c>
       <c r="E44" t="n">
-        <v>321.1583557128906</v>
+        <v>321.2168273925781</v>
       </c>
       <c r="F44" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>323.067540655824</v>
+        <v>318.6745269453515</v>
       </c>
       <c r="C45" t="n">
-        <v>323.4474098298547</v>
+        <v>321.4993043410047</v>
       </c>
       <c r="D45" t="n">
-        <v>320.3596462659403</v>
+        <v>314.6516410865056</v>
       </c>
       <c r="E45" t="n">
-        <v>321.216796875</v>
+        <v>314.8269653320312</v>
       </c>
       <c r="F45" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>318.6744651642728</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C46" t="n">
-        <v>321.4992420122895</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D46" t="n">
-        <v>314.6515800853393</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E46" t="n">
-        <v>314.826904296875</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F46" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C47" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D47" t="n">
-        <v>314.4275769247672</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E47" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F47" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>317.5446185401456</v>
+        <v>330.5970491985518</v>
       </c>
       <c r="C48" t="n">
-        <v>332.5549367443995</v>
+        <v>332.4088222358486</v>
       </c>
       <c r="D48" t="n">
-        <v>316.5803054378969</v>
+        <v>320.1940611974609</v>
       </c>
       <c r="E48" t="n">
-        <v>330.8990173339844</v>
+        <v>324.84033203125</v>
       </c>
       <c r="F48" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>330.5970181401507</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C49" t="n">
-        <v>332.4087910072381</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D49" t="n">
-        <v>320.1940311163831</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E49" t="n">
-        <v>324.8403015136719</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F49" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>326.311185594663</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C50" t="n">
-        <v>327.0027621721813</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D50" t="n">
-        <v>319.9895246756281</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E50" t="n">
-        <v>322.3272705078125</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F50" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894639081939</v>
       </c>
       <c r="C51" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0325801360812</v>
       </c>
       <c r="D51" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278299745985</v>
       </c>
       <c r="E51" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261108398438</v>
       </c>
       <c r="F51" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>316.894669558022</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C52" t="n">
-        <v>320.0326109139432</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D52" t="n">
-        <v>316.2278603865539</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E52" t="n">
-        <v>317.3261413574219</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F52" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C53" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D53" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E53" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F53" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566703772105</v>
       </c>
       <c r="C54" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2916615784552</v>
       </c>
       <c r="D54" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291859826966</v>
       </c>
       <c r="E54" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2125244140625</v>
       </c>
       <c r="F54" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>330.9566101169558</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C55" t="n">
-        <v>338.2915999826528</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D55" t="n">
-        <v>330.8291257456542</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E55" t="n">
-        <v>335.2124633789062</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F55" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C56" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D56" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E56" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F56" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>333.8200206972608</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C57" t="n">
-        <v>334.3789469115978</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D57" t="n">
-        <v>324.6120577084619</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E57" t="n">
-        <v>327.7206115722656</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F57" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>327.1420632206801</v>
+        <v>322.552799383924</v>
       </c>
       <c r="C58" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785647692876</v>
       </c>
       <c r="D58" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773440842135</v>
       </c>
       <c r="E58" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781372070312</v>
       </c>
       <c r="F58" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>322.5527687928765</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C59" t="n">
-        <v>323.7785340619881</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D59" t="n">
-        <v>318.2773138986521</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E59" t="n">
-        <v>321.7781066894531</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F59" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>321.6996588106788</v>
+        <v>316.6397026430911</v>
       </c>
       <c r="C60" t="n">
-        <v>328.112871433911</v>
+        <v>323.4059214629105</v>
       </c>
       <c r="D60" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139372798661</v>
       </c>
       <c r="E60" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558959960938</v>
       </c>
       <c r="F60" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>316.639672337624</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C61" t="n">
-        <v>323.4058905098511</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D61" t="n">
-        <v>315.4139070917166</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E61" t="n">
-        <v>318.8558654785156</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F61" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C62" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D62" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E62" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F62" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C63" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D63" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E63" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F63" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C64" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D64" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E64" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F64" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C65" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D65" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E65" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F65" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C66" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D66" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E66" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F66" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C67" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D67" t="n">
-        <v>323.484378234348</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E67" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F67" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>324.4845627249562</v>
+        <v>328.9464075107404</v>
       </c>
       <c r="C68" t="n">
-        <v>333.6631082445032</v>
+        <v>340.2136332445062</v>
       </c>
       <c r="D68" t="n">
-        <v>321.1504873151108</v>
+        <v>327.377421847917</v>
       </c>
       <c r="E68" t="n">
-        <v>329.8779296875</v>
+        <v>335.3890075683594</v>
       </c>
       <c r="F68" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>328.9463775793847</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C69" t="n">
-        <v>340.2136022879278</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D69" t="n">
-        <v>327.3773920593259</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E69" t="n">
-        <v>335.3889770507812</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F69" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>341.5963098138764</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C70" t="n">
-        <v>345.7736979738297</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D70" t="n">
-        <v>338.4289212269501</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E70" t="n">
-        <v>342.2042846679688</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F70" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C71" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D71" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E71" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F71" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>334.3986242436816</v>
+        <v>340.5176266555306</v>
       </c>
       <c r="C72" t="n">
-        <v>341.1550277170099</v>
+        <v>342.2925325530242</v>
       </c>
       <c r="D72" t="n">
-        <v>334.1926741052517</v>
+        <v>335.840116682576</v>
       </c>
       <c r="E72" t="n">
-        <v>340.1253967285156</v>
+        <v>337.31103515625</v>
       </c>
       <c r="F72" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C73" t="n">
-        <v>342.2925015847546</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D73" t="n">
-        <v>335.8400862980764</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E73" t="n">
-        <v>337.3110046386719</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F73" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C74" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D74" t="n">
-        <v>327.465664861477</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E74" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F74" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>334.8791141795932</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C75" t="n">
-        <v>335.2125187841528</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D75" t="n">
-        <v>326.3968234220132</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E75" t="n">
-        <v>327.4558715820312</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F75" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C76" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D76" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E76" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F76" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C77" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D77" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E77" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F77" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C78" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D78" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E78" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F78" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C79" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D79" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E79" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F79" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489839349073</v>
       </c>
       <c r="C80" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683609450301</v>
       </c>
       <c r="D80" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0469292856779</v>
       </c>
       <c r="E80" t="n">
-        <v>341.0079040527344</v>
+        <v>347.59765625</v>
       </c>
       <c r="F80" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>340.4489540449518</v>
+        <v>347.4112823812074</v>
       </c>
       <c r="C81" t="n">
-        <v>348.0683303861261</v>
+        <v>350.9316765208364</v>
       </c>
       <c r="D81" t="n">
-        <v>340.0468994310211</v>
+        <v>346.1462842881223</v>
       </c>
       <c r="E81" t="n">
-        <v>347.5976257324219</v>
+        <v>349.3529052734375</v>
       </c>
       <c r="F81" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>347.4113430771444</v>
+        <v>347.0876909760341</v>
       </c>
       <c r="C82" t="n">
-        <v>350.9317378318185</v>
+        <v>347.9114016111286</v>
       </c>
       <c r="D82" t="n">
-        <v>346.1463447630524</v>
+        <v>340.5371789096768</v>
       </c>
       <c r="E82" t="n">
-        <v>349.3529663085938</v>
+        <v>344.8224792480469</v>
       </c>
       <c r="F82" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>347.0877216940886</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C83" t="n">
-        <v>347.9114324020834</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D83" t="n">
-        <v>340.537209047996</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E83" t="n">
-        <v>344.822509765625</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F83" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>288.2706063388866</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C84" t="n">
-        <v>293.6933912983777</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D84" t="n">
-        <v>274.96368990819</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E84" t="n">
-        <v>277.2191162109375</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F84" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>278.2193161239855</v>
+        <v>288.6235657000577</v>
       </c>
       <c r="C85" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689623036692</v>
       </c>
       <c r="D85" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126518953886</v>
       </c>
       <c r="E85" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231384277344</v>
       </c>
       <c r="F85" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>288.623596430627</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C86" t="n">
-        <v>289.8689931668393</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D86" t="n">
-        <v>283.6126820924317</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E86" t="n">
-        <v>286.6231689453125</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F86" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4747261855329</v>
       </c>
       <c r="C87" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7698129535399</v>
       </c>
       <c r="D87" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072456694325</v>
       </c>
       <c r="E87" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530700683594</v>
       </c>
       <c r="F87" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>280.4746956220067</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C88" t="n">
-        <v>284.7697819219751</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D88" t="n">
-        <v>276.8072155055542</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E88" t="n">
-        <v>280.0530395507812</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F88" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424507136568</v>
       </c>
       <c r="C89" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841654678224</v>
       </c>
       <c r="D89" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367562069888</v>
       </c>
       <c r="E89" t="n">
-        <v>278.6703796386719</v>
+        <v>270.5705261230469</v>
       </c>
       <c r="F89" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>276.5424819048067</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C90" t="n">
-        <v>278.9841969343727</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D90" t="n">
-        <v>268.7367865177365</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E90" t="n">
-        <v>270.570556640625</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F90" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>268.9721802809009</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C91" t="n">
-        <v>271.5217784748567</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D91" t="n">
-        <v>261.1272811769848</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E91" t="n">
-        <v>263.3434448242188</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F91" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348608333229</v>
       </c>
       <c r="C92" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479519102809</v>
       </c>
       <c r="D92" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209657772727</v>
       </c>
       <c r="E92" t="n">
-        <v>271.286376953125</v>
+        <v>270.3548278808594</v>
       </c>
       <c r="F92" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>268.8348304873182</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C93" t="n">
-        <v>274.7479208968081</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D93" t="n">
-        <v>268.0209355231403</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E93" t="n">
-        <v>270.3547973632812</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F93" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>272.139502815215</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C94" t="n">
-        <v>274.0713101587253</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D94" t="n">
-        <v>267.3639259113162</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E94" t="n">
-        <v>267.9228820800781</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F94" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7671258575986</v>
       </c>
       <c r="C95" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7591102609402</v>
       </c>
       <c r="D95" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626809260317</v>
       </c>
       <c r="E95" t="n">
-        <v>273.5025634765625</v>
+        <v>278.8567199707031</v>
       </c>
       <c r="F95" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>272.7670960064547</v>
+        <v>280.0922508710514</v>
       </c>
       <c r="C96" t="n">
-        <v>280.7590795351679</v>
+        <v>287.7704307745099</v>
       </c>
       <c r="D96" t="n">
-        <v>270.4626513270822</v>
+        <v>278.9939700602999</v>
       </c>
       <c r="E96" t="n">
-        <v>278.856689453125</v>
+        <v>287.5056762695312</v>
       </c>
       <c r="F96" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>280.0923103323967</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C97" t="n">
-        <v>287.7704918658715</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D97" t="n">
-        <v>278.994029288489</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E97" t="n">
-        <v>287.5057373046875</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F97" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>288.3000088357305</v>
+        <v>284.377578031072</v>
       </c>
       <c r="C98" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050624231632</v>
       </c>
       <c r="D98" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7395146362062</v>
       </c>
       <c r="E98" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124877929688</v>
       </c>
       <c r="F98" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>284.3775473228927</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C99" t="n">
-        <v>284.5050317012176</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D99" t="n">
-        <v>280.7394843208789</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E99" t="n">
-        <v>282.6124572753906</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F99" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>285.2503082207336</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C100" t="n">
-        <v>285.2503082207336</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D100" t="n">
-        <v>281.3278592694971</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E100" t="n">
-        <v>284.3088989257812</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F100" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C101" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D101" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E101" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F101" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7287838236561</v>
       </c>
       <c r="C102" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9248883144977</v>
       </c>
       <c r="D102" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5303926707583</v>
       </c>
       <c r="E102" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387329101562</v>
       </c>
       <c r="F102" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>276.7288152602706</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C103" t="n">
-        <v>276.9249197733898</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D103" t="n">
-        <v>266.5304229488273</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E103" t="n">
-        <v>268.6387634277344</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F103" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C104" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D104" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E104" t="n">
-        <v>278.6900024414062</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F104" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>281.4161285575944</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C105" t="n">
-        <v>289.5355972025459</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D105" t="n">
-        <v>279.7000570330196</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E105" t="n">
-        <v>281.1023254394531</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F105" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C106" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D106" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E106" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F106" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C107" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D107" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E107" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F107" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>283.3871388529354</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C108" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D108" t="n">
-        <v>278.8468991181569</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E108" t="n">
-        <v>283.6028747558594</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F108" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265691931125</v>
       </c>
       <c r="C109" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406159339096</v>
       </c>
       <c r="D109" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807450619272</v>
       </c>
       <c r="E109" t="n">
-        <v>286.2995300292969</v>
+        <v>283.17138671875</v>
       </c>
       <c r="F109" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>284.4265998459625</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C110" t="n">
-        <v>285.7406467283754</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D110" t="n">
-        <v>281.1807753649725</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E110" t="n">
-        <v>283.1714172363281</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F110" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,25 +3303,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C111" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D111" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E111" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F111" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C112" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D112" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E112" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F112" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G112" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C113" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D113" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E113" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F113" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>279.0580549356083</v>
+        <v>281.42981524537</v>
       </c>
       <c r="C114" t="n">
-        <v>282.8528771272727</v>
+        <v>284.1771098102745</v>
       </c>
       <c r="D114" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039702199029</v>
       </c>
       <c r="E114" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907409667969</v>
       </c>
       <c r="F114" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>281.4297838763166</v>
+        <v>274.7888644946905</v>
       </c>
       <c r="C115" t="n">
-        <v>284.177078134999</v>
+        <v>279.5521686416635</v>
       </c>
       <c r="D115" t="n">
-        <v>273.039671765164</v>
+        <v>274.5418055263856</v>
       </c>
       <c r="E115" t="n">
-        <v>273.7907104492188</v>
+        <v>278.7714538574219</v>
       </c>
       <c r="F115" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>274.7888344130931</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C116" t="n">
-        <v>279.5521380386192</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D116" t="n">
-        <v>274.5417754718342</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E116" t="n">
-        <v>278.7714233398438</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F116" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>280.6392236042361</v>
+        <v>284.4142561376558</v>
       </c>
       <c r="C117" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902591728541</v>
       </c>
       <c r="D117" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4890865630293</v>
       </c>
       <c r="E117" t="n">
-        <v>282.1314392089844</v>
+        <v>284.1869812011719</v>
       </c>
       <c r="F117" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>284.41428667964</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C118" t="n">
-        <v>285.5902898411239</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D118" t="n">
-        <v>281.4891167908925</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E118" t="n">
-        <v>284.18701171875</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F118" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589864168267</v>
       </c>
       <c r="C119" t="n">
-        <v>285.0072039222152</v>
+        <v>284.167211683611</v>
       </c>
       <c r="D119" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7752266949594</v>
       </c>
       <c r="E119" t="n">
-        <v>280.9850769042969</v>
+        <v>277.140869140625</v>
       </c>
       <c r="F119" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>280.6589555118485</v>
+        <v>275.7079269716043</v>
       </c>
       <c r="C120" t="n">
-        <v>284.1671803923218</v>
+        <v>279.769592245506</v>
       </c>
       <c r="D120" t="n">
-        <v>276.7751962176443</v>
+        <v>271.7648753401377</v>
       </c>
       <c r="E120" t="n">
-        <v>277.1408386230469</v>
+        <v>272.3479309082031</v>
       </c>
       <c r="F120" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>275.7078960775263</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C121" t="n">
-        <v>279.7695608963037</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D121" t="n">
-        <v>271.7648448878931</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E121" t="n">
-        <v>272.347900390625</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F121" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069555541203</v>
       </c>
       <c r="C122" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639086768414</v>
       </c>
       <c r="D122" t="n">
-        <v>265.9243614270812</v>
+        <v>264.4420149324948</v>
       </c>
       <c r="E122" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768432617188</v>
       </c>
       <c r="F122" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>265.7069856894997</v>
+        <v>271.7648489371355</v>
       </c>
       <c r="C123" t="n">
-        <v>270.1639393177099</v>
+        <v>272.8321303468297</v>
       </c>
       <c r="D123" t="n">
-        <v>264.44204492441</v>
+        <v>263.9676538860649</v>
       </c>
       <c r="E123" t="n">
-        <v>269.0768737792969</v>
+        <v>267.3671875</v>
       </c>
       <c r="F123" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>271.7648799566674</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C124" t="n">
-        <v>272.8321614881822</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D124" t="n">
-        <v>263.9676840156166</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E124" t="n">
-        <v>267.3672180175781</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F124" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C125" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D125" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E125" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F125" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>264.3530902318651</v>
+        <v>257.119221076063</v>
       </c>
       <c r="C126" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2439223272896</v>
       </c>
       <c r="D126" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505334149961</v>
       </c>
       <c r="E126" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102966308594</v>
       </c>
       <c r="F126" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>257.1191907461688</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C127" t="n">
-        <v>259.2438917467647</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D127" t="n">
-        <v>253.6505034942698</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E127" t="n">
-        <v>258.7102661132812</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F127" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C128" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D128" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E128" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F128" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867574628081</v>
       </c>
       <c r="C129" t="n">
-        <v>272.0613148441149</v>
+        <v>275.7573496838748</v>
       </c>
       <c r="D129" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356885397691</v>
       </c>
       <c r="E129" t="n">
-        <v>270.7568664550781</v>
+        <v>273.998291015625</v>
       </c>
       <c r="F129" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>269.0867274922702</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C130" t="n">
-        <v>275.757318970375</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D130" t="n">
-        <v>268.3356586528844</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E130" t="n">
-        <v>273.9982604980469</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F130" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C131" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D131" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E131" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F131" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3295702834321</v>
       </c>
       <c r="C132" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881602178994</v>
       </c>
       <c r="D132" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439063119584</v>
       </c>
       <c r="E132" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804016113281</v>
       </c>
       <c r="F132" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>308.3296014014268</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C133" t="n">
-        <v>309.2881914326393</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D133" t="n">
-        <v>301.2439367148364</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E133" t="n">
-        <v>302.3804321289062</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F133" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272252898824</v>
       </c>
       <c r="C134" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187390262146</v>
       </c>
       <c r="D134" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213410567302</v>
       </c>
       <c r="E134" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7497863769531</v>
       </c>
       <c r="F134" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>304.3272561704691</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C135" t="n">
-        <v>306.7187701494722</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D135" t="n">
-        <v>300.6213715612747</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E135" t="n">
-        <v>300.7498168945312</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F135" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C136" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D136" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E136" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F136" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C137" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D137" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E137" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F137" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2942713469933</v>
       </c>
       <c r="C138" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8617880440979</v>
       </c>
       <c r="D138" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4264912428012</v>
       </c>
       <c r="E138" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6777954101562</v>
       </c>
       <c r="F138" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>311.2943017295384</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C139" t="n">
-        <v>314.8618187748353</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D139" t="n">
-        <v>309.4265214430497</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E139" t="n">
-        <v>312.6778259277344</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F139" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>316.2848676157387</v>
+        <v>320.3761995931397</v>
       </c>
       <c r="C140" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719565905757</v>
       </c>
       <c r="D140" t="n">
-        <v>313.4091278691752</v>
+        <v>316.3540722325493</v>
       </c>
       <c r="E140" t="n">
-        <v>320.8110046386719</v>
+        <v>319.674560546875</v>
       </c>
       <c r="F140" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>320.37616900858</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C141" t="n">
-        <v>321.5719258918635</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D141" t="n">
-        <v>316.35404203196</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E141" t="n">
-        <v>319.6745300292969</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F141" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7522179221875</v>
       </c>
       <c r="C142" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418624071809</v>
       </c>
       <c r="D142" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931592239693</v>
       </c>
       <c r="E142" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611450195312</v>
       </c>
       <c r="F142" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>346.7521876325058</v>
+        <v>350.5074689695779</v>
       </c>
       <c r="C143" t="n">
-        <v>354.3418314545246</v>
+        <v>352.6519539416425</v>
       </c>
       <c r="D143" t="n">
-        <v>344.9931290879458</v>
+        <v>346.3766505322415</v>
       </c>
       <c r="E143" t="n">
-        <v>349.3611145019531</v>
+        <v>350.3888854980469</v>
       </c>
       <c r="F143" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>350.5074994974842</v>
+        <v>352.2961973442777</v>
       </c>
       <c r="C144" t="n">
-        <v>352.6519846563255</v>
+        <v>354.0651480045056</v>
       </c>
       <c r="D144" t="n">
-        <v>346.3766807003688</v>
+        <v>347.256218509828</v>
       </c>
       <c r="E144" t="n">
-        <v>350.388916015625</v>
+        <v>350.7446899414062</v>
       </c>
       <c r="F144" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>352.2961666917061</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C145" t="n">
-        <v>354.0651171980212</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D145" t="n">
-        <v>347.2561882957746</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E145" t="n">
-        <v>350.7446594238281</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F145" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C146" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D146" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E146" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F146" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C147" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D147" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E147" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F147" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C148" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D148" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E148" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F148" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C149" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D149" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E149" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F149" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C150" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D150" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E150" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F150" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216097846273</v>
       </c>
       <c r="C151" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260581192055</v>
       </c>
       <c r="D151" t="n">
-        <v>360.360183242299</v>
+        <v>357.553592134861</v>
       </c>
       <c r="E151" t="n">
-        <v>366.388427734375</v>
+        <v>359.58935546875</v>
       </c>
       <c r="F151" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>366.1216408565838</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C152" t="n">
-        <v>367.4260893018678</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D152" t="n">
-        <v>357.5536224796683</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E152" t="n">
-        <v>359.5893859863281</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F152" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C153" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D153" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E153" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F153" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="C154" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="D154" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="E154" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="F154" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>367.6138324799484</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C155" t="n">
-        <v>375.5098571777344</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D155" t="n">
-        <v>367.6138324799484</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E155" t="n">
-        <v>375.5098571777344</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F155" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3461148231528</v>
       </c>
       <c r="C156" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7447189140002</v>
       </c>
       <c r="D156" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5160002982997</v>
       </c>
       <c r="E156" t="n">
-        <v>379.9173889160156</v>
+        <v>391.7268371582031</v>
       </c>
       <c r="F156" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>378.3460853480032</v>
+        <v>391.8354914196509</v>
       </c>
       <c r="C157" t="n">
-        <v>392.7446883171237</v>
+        <v>399.3954891946478</v>
       </c>
       <c r="D157" t="n">
-        <v>377.5159708878205</v>
+        <v>388.3766661486073</v>
       </c>
       <c r="E157" t="n">
-        <v>391.726806640625</v>
+        <v>396.440673828125</v>
       </c>
       <c r="F157" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>391.835521582727</v>
+        <v>396.2825535174053</v>
       </c>
       <c r="C158" t="n">
-        <v>399.3955199396844</v>
+        <v>397.1719597005697</v>
       </c>
       <c r="D158" t="n">
-        <v>388.3766960454267</v>
+        <v>391.3413745458666</v>
       </c>
       <c r="E158" t="n">
-        <v>396.4407043457031</v>
+        <v>394.39501953125</v>
       </c>
       <c r="F158" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>396.2825841810375</v>
+        <v>389.661393370787</v>
       </c>
       <c r="C159" t="n">
-        <v>397.1719904330225</v>
+        <v>392.9522357226725</v>
       </c>
       <c r="D159" t="n">
-        <v>391.3414048271592</v>
+        <v>385.6590501412673</v>
       </c>
       <c r="E159" t="n">
-        <v>394.3950500488281</v>
+        <v>389.2167053222656</v>
       </c>
       <c r="F159" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>389.6613628183419</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C160" t="n">
-        <v>392.9522049122001</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D160" t="n">
-        <v>385.6590199026367</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E160" t="n">
-        <v>389.2166748046875</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F160" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119575218886</v>
       </c>
       <c r="C161" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432444558516</v>
       </c>
       <c r="D161" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512600592197</v>
       </c>
       <c r="E161" t="n">
-        <v>386.5286865234375</v>
+        <v>384.660888671875</v>
       </c>
       <c r="F161" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>385.4119880990537</v>
+        <v>384.9672762725209</v>
       </c>
       <c r="C162" t="n">
-        <v>390.3432754242469</v>
+        <v>388.7522365943216</v>
       </c>
       <c r="D162" t="n">
-        <v>382.9512904411622</v>
+        <v>376.2214128322495</v>
       </c>
       <c r="E162" t="n">
-        <v>384.6609191894531</v>
+        <v>378.7908020019531</v>
       </c>
       <c r="F162" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>384.9672452573303</v>
+        <v>376.6364218669779</v>
       </c>
       <c r="C163" t="n">
-        <v>388.7522052741927</v>
+        <v>381.5677088398597</v>
       </c>
       <c r="D163" t="n">
-        <v>376.2213825216763</v>
+        <v>376.0632583748818</v>
       </c>
       <c r="E163" t="n">
-        <v>378.790771484375</v>
+        <v>377.9804382324219</v>
       </c>
       <c r="F163" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>376.6364522760421</v>
+        <v>377.4270609393932</v>
       </c>
       <c r="C164" t="n">
-        <v>381.5677396470687</v>
+        <v>385.9456494081999</v>
       </c>
       <c r="D164" t="n">
-        <v>376.0632887376697</v>
+        <v>376.5277626686598</v>
       </c>
       <c r="E164" t="n">
-        <v>377.98046875</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F164" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>377.4270309363715</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C165" t="n">
-        <v>385.9456187280053</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D165" t="n">
-        <v>376.5277327371266</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E165" t="n">
-        <v>383.8999633789062</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F165" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C166" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D166" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E166" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F166" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312519906984</v>
       </c>
       <c r="C167" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6806841025421</v>
       </c>
       <c r="D167" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783087193446</v>
       </c>
       <c r="E167" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298461914062</v>
       </c>
       <c r="F167" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>380.4312827021371</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C168" t="n">
-        <v>384.6807151570288</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D168" t="n">
-        <v>376.4783391116702</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E168" t="n">
-        <v>378.0298767089844</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F168" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C169" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D169" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E169" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F169" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C170" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D170" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E170" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F170" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C171" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D171" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E171" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F171" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119903823484</v>
       </c>
       <c r="C172" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6581194399012</v>
       </c>
       <c r="D172" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2341151633045</v>
       </c>
       <c r="E172" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058776855469</v>
       </c>
       <c r="F172" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>385.4119603627872</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C173" t="n">
-        <v>396.6580885443842</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D173" t="n">
-        <v>385.2340851575979</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E173" t="n">
-        <v>391.8058471679688</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F173" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C174" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D174" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E174" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F174" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>392.4580996989546</v>
+        <v>405.1668188073661</v>
       </c>
       <c r="C175" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="D175" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6468293766872</v>
       </c>
       <c r="E175" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="F175" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>405.166788512205</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C176" t="n">
-        <v>408.1413879394531</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D176" t="n">
-        <v>402.6467992699509</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E176" t="n">
-        <v>408.1413879394531</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F176" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C177" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D177" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E177" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F177" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C178" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D178" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E178" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F178" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C179" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D179" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E179" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F179" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C180" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D180" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E180" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F180" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G180" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C181" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D181" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E181" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F181" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C182" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D182" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E182" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F182" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C183" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D183" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E183" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F183" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C184" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D184" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E184" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F184" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C185" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D185" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E185" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F185" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C186" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D186" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E186" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F186" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C187" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D187" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E187" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F187" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C188" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D188" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E188" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F188" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C189" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D189" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E189" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F189" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C190" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D190" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E190" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F190" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C191" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D191" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E191" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F191" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C192" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D192" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E192" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F192" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C193" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D193" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E193" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F193" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C194" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D194" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E194" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F194" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C195" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D195" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E195" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F195" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C196" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D196" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E196" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F196" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C197" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D197" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E197" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F197" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C198" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D198" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E198" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F198" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C199" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D199" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E199" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F199" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C200" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D200" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E200" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F200" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C201" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D201" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E201" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F201" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C202" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D202" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E202" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F202" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C203" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D203" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E203" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F203" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C204" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D204" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E204" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F204" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C205" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D205" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E205" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F205" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C206" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D206" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E206" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F206" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C207" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D207" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E207" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F207" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C208" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D208" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E208" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F208" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C209" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D209" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E209" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F209" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C210" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D210" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E210" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F210" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C211" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D211" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E211" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F211" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C212" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D212" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E212" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F212" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C213" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D213" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E213" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F213" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C214" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D214" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E214" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F214" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C215" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D215" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E215" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F215" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C216" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D216" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E216" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F216" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C217" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D217" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E217" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F217" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C218" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D218" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E218" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F218" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C219" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D219" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E219" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F219" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C220" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D220" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E220" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F220" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C221" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D221" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E221" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F221" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C222" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D222" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E222" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F222" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C223" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D223" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E223" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F223" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C224" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D224" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E224" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F224" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C225" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D225" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E225" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F225" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C226" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D226" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E226" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F226" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C227" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D227" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E227" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F227" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C228" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D228" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E228" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F228" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C229" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D229" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E229" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F229" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C230" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D230" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E230" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F230" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C231" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D231" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E231" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F231" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C232" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D232" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E232" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F232" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C233" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D233" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E233" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F233" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C234" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D234" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E234" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F234" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C235" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D235" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E235" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F235" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C236" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D236" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E236" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F236" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C237" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D237" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E237" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F237" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C238" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D238" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E238" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F238" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C239" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D239" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E239" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F239" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C240" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D240" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E240" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F240" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C241" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D241" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E241" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F241" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C242" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D242" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E242" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F242" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C243" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D243" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E243" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F243" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C244" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D244" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E244" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F244" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C245" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D245" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E245" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F245" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>375.2900085449219</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C246" t="n">
-        <v>378.489990234375</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D246" t="n">
-        <v>372.4200134277344</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E246" t="n">
-        <v>376.8999938964844</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F246" t="n">
-        <v>8606300</v>
+        <v>5712300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>377.8699951171875</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="C247" t="n">
-        <v>378.9500122070312</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="D247" t="n">
-        <v>373.8200073242188</v>
+        <v>372.4100036621094</v>
       </c>
       <c r="E247" t="n">
-        <v>377.5599975585938</v>
+        <v>372.9500122070312</v>
       </c>
       <c r="F247" t="n">
-        <v>5712300</v>
+        <v>4495000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>381.3900146484375</v>
+        <v>370.8900146484375</v>
       </c>
       <c r="C248" t="n">
-        <v>381.3900146484375</v>
+        <v>372.6099853515625</v>
       </c>
       <c r="D248" t="n">
-        <v>372.4100036621094</v>
+        <v>366</v>
       </c>
       <c r="E248" t="n">
-        <v>372.9500122070312</v>
+        <v>371.2900085449219</v>
       </c>
       <c r="F248" t="n">
-        <v>4495000</v>
+        <v>3859300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>370.8900146484375</v>
+        <v>371.9200134277344</v>
       </c>
       <c r="C249" t="n">
-        <v>372.6099853515625</v>
+        <v>375.2799987792969</v>
       </c>
       <c r="D249" t="n">
-        <v>366</v>
+        <v>368.5</v>
       </c>
       <c r="E249" t="n">
-        <v>371.2900085449219</v>
+        <v>375.010009765625</v>
       </c>
       <c r="F249" t="n">
-        <v>3859300</v>
+        <v>4651000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>371.9200134277344</v>
+        <v>375.9500122070312</v>
       </c>
       <c r="C250" t="n">
-        <v>375.2799987792969</v>
+        <v>379.1700134277344</v>
       </c>
       <c r="D250" t="n">
-        <v>368.5</v>
+        <v>371.1700134277344</v>
       </c>
       <c r="E250" t="n">
-        <v>375.010009765625</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="F250" t="n">
-        <v>4651000</v>
+        <v>4077400</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>375.9500122070312</v>
+        <v>376.3599853515625</v>
       </c>
       <c r="C251" t="n">
-        <v>379.1700134277344</v>
+        <v>380.9800109863281</v>
       </c>
       <c r="D251" t="n">
-        <v>371.1700134277344</v>
+        <v>374.5599975585938</v>
       </c>
       <c r="E251" t="n">
-        <v>376.5899963378906</v>
+        <v>377.8299865722656</v>
       </c>
       <c r="F251" t="n">
-        <v>4077400</v>
+        <v>4677100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>376.3599853515625</v>
+        <v>374.8800048828125</v>
       </c>
       <c r="C252" t="n">
-        <v>380.9800109863281</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="D252" t="n">
-        <v>374.5599975585938</v>
+        <v>371.3299865722656</v>
       </c>
       <c r="E252" t="n">
-        <v>377.8299865722656</v>
+        <v>374.9400024414062</v>
       </c>
       <c r="F252" t="n">
-        <v>4614700</v>
+        <v>3284700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>374.94</v>
+      </c>
+      <c r="D2" t="n">
         <v>377.83</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="F2" t="n">
         <v>376.59</v>
       </c>
-      <c r="E2" t="n">
-        <v>376.36</v>
-      </c>
-      <c r="F2" t="n">
-        <v>380.98</v>
-      </c>
       <c r="G2" t="n">
-        <v>374.56</v>
+        <v>371.33</v>
       </c>
       <c r="H2" t="n">
-        <v>4494798</v>
+        <v>3276363</v>
       </c>
       <c r="I2" t="n">
-        <v>4968876</v>
+        <v>4930261</v>
       </c>
       <c r="J2" t="n">
-        <v>339138248704</v>
+        <v>336544202752</v>
       </c>
       <c r="K2" t="n">
-        <v>24.21987</v>
+        <v>24.267962</v>
       </c>
       <c r="L2" t="n">
-        <v>16.710608</v>
+        <v>16.582788</v>
       </c>
       <c r="M2" t="n">
-        <v>15.6</v>
+        <v>15.45</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4733088</v>
+        <v>3.4467416</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>388500258816</v>
+        <v>385906212864</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24:52</t>
+          <t>2026-09-30 16:07:19</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>334.8342081470359</v>
+        <v>334.9803326465864</v>
       </c>
       <c r="C2" t="n">
-        <v>340.2597470322082</v>
+        <v>339.6558538996071</v>
       </c>
       <c r="D2" t="n">
-        <v>333.4510253931927</v>
+        <v>332.7692198568235</v>
       </c>
       <c r="E2" t="n">
-        <v>336.343994140625</v>
+        <v>339.2662048339844</v>
       </c>
       <c r="F2" t="n">
-        <v>7429700</v>
+        <v>8825500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>334.9803326465864</v>
+        <v>338.2824047650262</v>
       </c>
       <c r="C3" t="n">
-        <v>339.6558538996071</v>
+        <v>345.87033541468</v>
       </c>
       <c r="D3" t="n">
-        <v>332.7692198568235</v>
+        <v>335.7108637419195</v>
       </c>
       <c r="E3" t="n">
-        <v>339.2662048339844</v>
+        <v>344.5456237792969</v>
       </c>
       <c r="F3" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>338.2824047650262</v>
+        <v>347.984106417045</v>
       </c>
       <c r="C4" t="n">
-        <v>345.87033541468</v>
+        <v>358.4552866661233</v>
       </c>
       <c r="D4" t="n">
-        <v>335.7108637419195</v>
+        <v>347.3606916499901</v>
       </c>
       <c r="E4" t="n">
-        <v>344.5456237792969</v>
+        <v>350.8576049804688</v>
       </c>
       <c r="F4" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>347.9840761494036</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C5" t="n">
-        <v>358.4552554876992</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D5" t="n">
-        <v>347.3606614365734</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E5" t="n">
-        <v>350.8575744628906</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F5" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>351.6660530964717</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C6" t="n">
-        <v>353.1173978230779</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D6" t="n">
-        <v>347.8477120863685</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E6" t="n">
-        <v>349.4646606445312</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F6" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4130008055815</v>
       </c>
       <c r="C7" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132992932725</v>
       </c>
       <c r="D7" t="n">
-        <v>348.77305405812</v>
+        <v>356.3123046396842</v>
       </c>
       <c r="E7" t="n">
-        <v>354.2278137207031</v>
+        <v>360.3254699707031</v>
       </c>
       <c r="F7" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>357.4130008055815</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C8" t="n">
-        <v>364.9132992932725</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D8" t="n">
-        <v>356.3123046396842</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E8" t="n">
-        <v>360.3254699707031</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F8" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>362.8579709138762</v>
+        <v>359.8189563090651</v>
       </c>
       <c r="C9" t="n">
-        <v>366.4620162306247</v>
+        <v>359.8189563090651</v>
       </c>
       <c r="D9" t="n">
-        <v>356.585002247802</v>
+        <v>343.3670435790787</v>
       </c>
       <c r="E9" t="n">
-        <v>358.1532592773438</v>
+        <v>345.305419921875</v>
       </c>
       <c r="F9" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>359.8189245088024</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C10" t="n">
-        <v>359.8189245088024</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D10" t="n">
-        <v>343.3670132328114</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E10" t="n">
-        <v>345.3053894042969</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F10" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>345.5391725764172</v>
+        <v>345.743758076041</v>
       </c>
       <c r="C11" t="n">
-        <v>349.8445450312873</v>
+        <v>352.9323197996358</v>
       </c>
       <c r="D11" t="n">
-        <v>344.1560194689148</v>
+        <v>344.2339422221326</v>
       </c>
       <c r="E11" t="n">
-        <v>349.3575134277344</v>
+        <v>350.5945739746094</v>
       </c>
       <c r="F11" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685670322262</v>
       </c>
       <c r="C12" t="n">
-        <v>352.9322890785681</v>
+        <v>354.77327893078</v>
       </c>
       <c r="D12" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203751846734</v>
       </c>
       <c r="E12" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828979492188</v>
       </c>
       <c r="F12" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4549874654966</v>
       </c>
       <c r="C13" t="n">
-        <v>354.77327893078</v>
+        <v>352.6108411281484</v>
       </c>
       <c r="D13" t="n">
-        <v>346.6203751846734</v>
+        <v>345.207955645442</v>
       </c>
       <c r="E13" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4190979003906</v>
       </c>
       <c r="F13" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>352.4549874654966</v>
+        <v>341.8961320639185</v>
       </c>
       <c r="C14" t="n">
-        <v>352.6108411281484</v>
+        <v>349.0944723037945</v>
       </c>
       <c r="D14" t="n">
-        <v>345.207955645442</v>
+        <v>341.7305282652253</v>
       </c>
       <c r="E14" t="n">
-        <v>347.4190979003906</v>
+        <v>347.3508911132812</v>
       </c>
       <c r="F14" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>341.896162102252</v>
+        <v>349.2405827399879</v>
       </c>
       <c r="C15" t="n">
-        <v>349.0945029745603</v>
+        <v>356.0882449585139</v>
       </c>
       <c r="D15" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2372989631983</v>
       </c>
       <c r="E15" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265197753906</v>
       </c>
       <c r="F15" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>349.2406127602151</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C16" t="n">
-        <v>356.0882755673564</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D16" t="n">
-        <v>348.2373288971846</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E16" t="n">
-        <v>355.0265502929688</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F16" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5200425762015</v>
       </c>
       <c r="C17" t="n">
-        <v>361.426134922211</v>
+        <v>354.5590134284439</v>
       </c>
       <c r="D17" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7146340862168</v>
       </c>
       <c r="E17" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1141052246094</v>
       </c>
       <c r="F17" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>354.5200118501019</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C18" t="n">
-        <v>354.5589826989666</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D18" t="n">
-        <v>348.7146038632694</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E18" t="n">
-        <v>352.1140747070312</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F18" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>346.3573316043178</v>
+        <v>351.9971738259649</v>
       </c>
       <c r="C19" t="n">
-        <v>352.8835660308217</v>
+        <v>355.9421471732778</v>
       </c>
       <c r="D19" t="n">
-        <v>344.4676766060103</v>
+        <v>350.6919328534217</v>
       </c>
       <c r="E19" t="n">
-        <v>351.1010437011719</v>
+        <v>353.0978698730469</v>
       </c>
       <c r="F19" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>351.9972042484119</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C20" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D20" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E20" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F20" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>354.0719227699667</v>
+        <v>370.8063128551364</v>
       </c>
       <c r="C21" t="n">
-        <v>356.7213754856504</v>
+        <v>371.118020163803</v>
       </c>
       <c r="D21" t="n">
-        <v>352.0263843961002</v>
+        <v>349.3282346022162</v>
       </c>
       <c r="E21" t="n">
-        <v>356.4876098632812</v>
+        <v>358.2993469238281</v>
       </c>
       <c r="F21" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>370.8063444379755</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C22" t="n">
-        <v>371.1180517731913</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D22" t="n">
-        <v>349.3282643556941</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E22" t="n">
-        <v>358.2993774414062</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F22" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064021770676</v>
       </c>
       <c r="C23" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443442519412</v>
       </c>
       <c r="D23" t="n">
-        <v>344.701472908826</v>
+        <v>334.6880914224008</v>
       </c>
       <c r="E23" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082580566406</v>
       </c>
       <c r="F23" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>338.5064021770676</v>
+        <v>335.4576347488759</v>
       </c>
       <c r="C24" t="n">
-        <v>345.3443442519412</v>
+        <v>337.298598712068</v>
       </c>
       <c r="D24" t="n">
-        <v>334.6880914224008</v>
+        <v>328.3761763650699</v>
       </c>
       <c r="E24" t="n">
-        <v>335.8082580566406</v>
+        <v>332.7010192871094</v>
       </c>
       <c r="F24" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>335.4576039784424</v>
+        <v>330.3340313465691</v>
       </c>
       <c r="C25" t="n">
-        <v>337.298567772769</v>
+        <v>331.8633175824834</v>
       </c>
       <c r="D25" t="n">
-        <v>328.3761462441955</v>
+        <v>318.1290216159704</v>
       </c>
       <c r="E25" t="n">
-        <v>332.7009887695312</v>
+        <v>325.1325378417969</v>
       </c>
       <c r="F25" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>330.3340003407686</v>
+        <v>319.1323440808776</v>
       </c>
       <c r="C26" t="n">
-        <v>331.863286433141</v>
+        <v>327.7722802636044</v>
       </c>
       <c r="D26" t="n">
-        <v>318.128991755756</v>
+        <v>318.7135040219252</v>
       </c>
       <c r="E26" t="n">
-        <v>325.1325073242188</v>
+        <v>322.2493286132812</v>
       </c>
       <c r="F26" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>319.1323440808776</v>
+        <v>317.8368180152801</v>
       </c>
       <c r="C27" t="n">
-        <v>327.7722802636044</v>
+        <v>321.6454087872217</v>
       </c>
       <c r="D27" t="n">
-        <v>318.7135040219252</v>
+        <v>315.8107795893674</v>
       </c>
       <c r="E27" t="n">
-        <v>322.2493286132812</v>
+        <v>319.2394714355469</v>
       </c>
       <c r="F27" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>317.8367876317881</v>
+        <v>320.3888464018165</v>
       </c>
       <c r="C28" t="n">
-        <v>321.6453780396488</v>
+        <v>323.7493462451443</v>
       </c>
       <c r="D28" t="n">
-        <v>315.8107493995538</v>
+        <v>313.1125938905139</v>
       </c>
       <c r="E28" t="n">
-        <v>319.2394409179688</v>
+        <v>313.2197265625</v>
       </c>
       <c r="F28" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>320.3888776178953</v>
+        <v>311.3690496699339</v>
       </c>
       <c r="C29" t="n">
-        <v>323.7493777886428</v>
+        <v>316.1322033153182</v>
       </c>
       <c r="D29" t="n">
-        <v>313.1126243976539</v>
+        <v>306.0117020081513</v>
       </c>
       <c r="E29" t="n">
-        <v>313.2197570800781</v>
+        <v>315.801025390625</v>
       </c>
       <c r="F29" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>311.3690195806419</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C30" t="n">
-        <v>316.1321727657366</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D30" t="n">
-        <v>306.011672436569</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E30" t="n">
-        <v>315.8009948730469</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F30" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>311.6904703912621</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C31" t="n">
-        <v>315.8399890894766</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D31" t="n">
-        <v>308.9436347895907</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E31" t="n">
-        <v>313.2392272949219</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F31" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>314.9146147475993</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C32" t="n">
-        <v>319.3563404779885</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D32" t="n">
-        <v>311.583335312832</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E32" t="n">
-        <v>318.9570007324219</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F32" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>319.931043202934</v>
+        <v>329.5742822700864</v>
       </c>
       <c r="C33" t="n">
-        <v>334.2692534981419</v>
+        <v>330.2366380969722</v>
       </c>
       <c r="D33" t="n">
-        <v>318.5965517605375</v>
+        <v>322.6973986104767</v>
       </c>
       <c r="E33" t="n">
-        <v>330.2658386230469</v>
+        <v>323.8954772949219</v>
       </c>
       <c r="F33" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>329.5743133227241</v>
+        <v>318.4699706680781</v>
       </c>
       <c r="C34" t="n">
-        <v>330.2366692120174</v>
+        <v>319.6972700691676</v>
       </c>
       <c r="D34" t="n">
-        <v>322.6974290151713</v>
+        <v>312.1775010814912</v>
       </c>
       <c r="E34" t="n">
-        <v>323.8955078125</v>
+        <v>313.511962890625</v>
       </c>
       <c r="F34" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>318.4699706680781</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C35" t="n">
-        <v>319.6972700691676</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D35" t="n">
-        <v>312.1775010814912</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E35" t="n">
-        <v>313.511962890625</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F35" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7877447280039</v>
       </c>
       <c r="C36" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650261221254</v>
       </c>
       <c r="D36" t="n">
-        <v>311.1450007536453</v>
+        <v>300.7614447812334</v>
       </c>
       <c r="E36" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4466857910156</v>
       </c>
       <c r="F36" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>308.7877447280039</v>
+        <v>305.7876433202538</v>
       </c>
       <c r="C37" t="n">
-        <v>309.2650261221254</v>
+        <v>306.829898044689</v>
       </c>
       <c r="D37" t="n">
-        <v>300.7614447812334</v>
+        <v>296.6314554825427</v>
       </c>
       <c r="E37" t="n">
-        <v>305.4466857910156</v>
+        <v>301.0731811523438</v>
       </c>
       <c r="F37" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>305.7876123248052</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C38" t="n">
-        <v>306.8298669435948</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D38" t="n">
-        <v>296.6314254151897</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E38" t="n">
-        <v>301.0731506347656</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F38" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>302.7485789287686</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C39" t="n">
-        <v>306.5863902909554</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D39" t="n">
-        <v>301.9595901197654</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E39" t="n">
-        <v>303.4596557617188</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F39" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C40" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D40" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E40" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F40" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>316.1127492028895</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C41" t="n">
-        <v>317.3985198428805</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D41" t="n">
-        <v>309.3819684958741</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E41" t="n">
-        <v>310.7748718261719</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F41" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>312.7911523817683</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C42" t="n">
-        <v>319.4927115758689</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D42" t="n">
-        <v>312.5768573008158</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E42" t="n">
-        <v>317.8173217773438</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F42" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>318.1193136428872</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C43" t="n">
-        <v>326.4962635484334</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D43" t="n">
-        <v>317.4374872026767</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E43" t="n">
-        <v>321.1583862304688</v>
+        <v>321.216796875</v>
       </c>
       <c r="F43" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>323.0675713492342</v>
+        <v>318.6744960548122</v>
       </c>
       <c r="C44" t="n">
-        <v>323.4474405593548</v>
+        <v>321.4992731766471</v>
       </c>
       <c r="D44" t="n">
-        <v>320.3596767020838</v>
+        <v>314.6516105859225</v>
       </c>
       <c r="E44" t="n">
-        <v>321.2168273925781</v>
+        <v>314.8269348144531</v>
       </c>
       <c r="F44" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>318.6745269453515</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C45" t="n">
-        <v>321.4993043410047</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D45" t="n">
-        <v>314.6516410865056</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E45" t="n">
-        <v>314.8269653320312</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F45" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5446185401456</v>
       </c>
       <c r="C46" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549367443995</v>
       </c>
       <c r="D46" t="n">
-        <v>314.4275769247672</v>
+        <v>316.5803054378969</v>
       </c>
       <c r="E46" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8990173339844</v>
       </c>
       <c r="F46" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>317.5445892541937</v>
+        <v>330.5970491985518</v>
       </c>
       <c r="C47" t="n">
-        <v>332.5549060741021</v>
+        <v>332.4088222358486</v>
       </c>
       <c r="D47" t="n">
-        <v>316.58027624088</v>
+        <v>320.1940611974609</v>
       </c>
       <c r="E47" t="n">
-        <v>330.8989868164062</v>
+        <v>324.84033203125</v>
       </c>
       <c r="F47" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>330.5970491985518</v>
+        <v>326.3111238051217</v>
       </c>
       <c r="C48" t="n">
-        <v>332.4088222358486</v>
+        <v>327.0027002516846</v>
       </c>
       <c r="D48" t="n">
-        <v>320.1940611974609</v>
+        <v>319.9894640831421</v>
       </c>
       <c r="E48" t="n">
-        <v>324.84033203125</v>
+        <v>322.3272094726562</v>
       </c>
       <c r="F48" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,25 +1691,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>326.3111546998924</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C49" t="n">
-        <v>327.0027312119329</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D49" t="n">
-        <v>319.9894943793851</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E49" t="n">
-        <v>322.3272399902344</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F49" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C50" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D50" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E50" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F50" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>316.894639081939</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C51" t="n">
-        <v>320.0325801360812</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D51" t="n">
-        <v>316.2278299745985</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E51" t="n">
-        <v>317.3261108398438</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F51" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C52" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D52" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E52" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F52" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566101169558</v>
       </c>
       <c r="C53" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2915999826528</v>
       </c>
       <c r="D53" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291257456542</v>
       </c>
       <c r="E53" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2124633789062</v>
       </c>
       <c r="F53" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>330.9566703772105</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C54" t="n">
-        <v>338.2916615784552</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D54" t="n">
-        <v>330.8291859826966</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E54" t="n">
-        <v>335.2125244140625</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F54" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200206972608</v>
       </c>
       <c r="C55" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789469115978</v>
       </c>
       <c r="D55" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120577084619</v>
       </c>
       <c r="E55" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206115722656</v>
       </c>
       <c r="F55" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>333.8200517828203</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C56" t="n">
-        <v>334.3789780492049</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D56" t="n">
-        <v>324.6120879365693</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E56" t="n">
-        <v>327.7206420898438</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F56" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>327.1420632206801</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C57" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D57" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E57" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F57" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>322.552799383924</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C58" t="n">
-        <v>323.7785647692876</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D58" t="n">
-        <v>318.2773440842135</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E58" t="n">
-        <v>321.7781372070312</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F58" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>321.6996588106788</v>
+        <v>316.639672337624</v>
       </c>
       <c r="C59" t="n">
-        <v>328.112871433911</v>
+        <v>323.4058905098511</v>
       </c>
       <c r="D59" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139070917166</v>
       </c>
       <c r="E59" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558654785156</v>
       </c>
       <c r="F59" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>316.6397026430911</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C60" t="n">
-        <v>323.4059214629105</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D60" t="n">
-        <v>315.4139372798661</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E60" t="n">
-        <v>318.8558959960938</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F60" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C61" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D61" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E61" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F61" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C62" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D62" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E62" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F62" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C63" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D63" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E63" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F63" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C64" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D64" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E64" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F64" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C65" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D65" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E65" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F65" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845627249562</v>
       </c>
       <c r="C66" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631082445032</v>
       </c>
       <c r="D66" t="n">
-        <v>323.484378234348</v>
+        <v>321.1504873151108</v>
       </c>
       <c r="E66" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779296875</v>
       </c>
       <c r="F66" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>324.4845927435845</v>
+        <v>328.9463775793847</v>
       </c>
       <c r="C67" t="n">
-        <v>333.6631391122548</v>
+        <v>340.2136022879278</v>
       </c>
       <c r="D67" t="n">
-        <v>321.1505170252981</v>
+        <v>327.3773920593259</v>
       </c>
       <c r="E67" t="n">
-        <v>329.8779602050781</v>
+        <v>335.3889770507812</v>
       </c>
       <c r="F67" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>328.9464075107404</v>
+        <v>341.5963098138764</v>
       </c>
       <c r="C68" t="n">
-        <v>340.2136332445062</v>
+        <v>345.7736979738297</v>
       </c>
       <c r="D68" t="n">
-        <v>327.377421847917</v>
+        <v>338.4289212269501</v>
       </c>
       <c r="E68" t="n">
-        <v>335.3890075683594</v>
+        <v>342.2042846679688</v>
       </c>
       <c r="F68" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>341.5962793505171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C69" t="n">
-        <v>345.7736671379334</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D69" t="n">
-        <v>338.4288910460567</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E69" t="n">
-        <v>342.2042541503906</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F69" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3986242436816</v>
       </c>
       <c r="C70" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1550277170099</v>
       </c>
       <c r="D70" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926741052517</v>
       </c>
       <c r="E70" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253967285156</v>
       </c>
       <c r="F70" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>334.3985942399352</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C71" t="n">
-        <v>341.1549971070486</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D71" t="n">
-        <v>334.1926441199842</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E71" t="n">
-        <v>340.1253662109375</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F71" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>340.5176266555306</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C72" t="n">
-        <v>342.2925325530242</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D72" t="n">
-        <v>335.840116682576</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E72" t="n">
-        <v>337.31103515625</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F72" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8791141795932</v>
       </c>
       <c r="C73" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2125187841528</v>
       </c>
       <c r="D73" t="n">
-        <v>327.465664861477</v>
+        <v>326.3968234220132</v>
       </c>
       <c r="E73" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558715820312</v>
       </c>
       <c r="F73" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>334.8790829701986</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C74" t="n">
-        <v>335.2124875436862</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D74" t="n">
-        <v>326.3967930031341</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E74" t="n">
-        <v>327.4558410644531</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F74" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C75" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D75" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E75" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F75" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C76" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D76" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E76" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F76" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C77" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D77" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E77" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F77" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C78" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D78" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E78" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F78" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C79" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D79" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E79" t="n">
-        <v>341.0079040527344</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F79" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>340.4489839349073</v>
+        <v>347.4113430771444</v>
       </c>
       <c r="C80" t="n">
-        <v>348.0683609450301</v>
+        <v>350.9317378318185</v>
       </c>
       <c r="D80" t="n">
-        <v>340.0469292856779</v>
+        <v>346.1463447630524</v>
       </c>
       <c r="E80" t="n">
-        <v>347.59765625</v>
+        <v>349.3529663085938</v>
       </c>
       <c r="F80" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>347.4112823812074</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C81" t="n">
-        <v>350.9316765208364</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D81" t="n">
-        <v>346.1462842881223</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E81" t="n">
-        <v>349.3529052734375</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F81" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>347.0876909760341</v>
+        <v>288.2706063388866</v>
       </c>
       <c r="C82" t="n">
-        <v>347.9114016111286</v>
+        <v>293.6933912983777</v>
       </c>
       <c r="D82" t="n">
-        <v>340.5371789096768</v>
+        <v>274.96368990819</v>
       </c>
       <c r="E82" t="n">
-        <v>344.8224792480469</v>
+        <v>277.2191162109375</v>
       </c>
       <c r="F82" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>288.2705746047087</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C83" t="n">
-        <v>293.6933589672342</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D83" t="n">
-        <v>274.9636596388997</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E83" t="n">
-        <v>277.2190856933594</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F83" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>278.2193161239855</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C84" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D84" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E84" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F84" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>288.6235657000577</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C85" t="n">
-        <v>289.8689623036692</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D85" t="n">
-        <v>283.6126518953886</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E85" t="n">
-        <v>286.6231384277344</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F85" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4746956220067</v>
       </c>
       <c r="C86" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7697819219751</v>
       </c>
       <c r="D86" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072155055542</v>
       </c>
       <c r="E86" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530395507812</v>
       </c>
       <c r="F86" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>280.4747261855329</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C87" t="n">
-        <v>284.7698129535399</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D87" t="n">
-        <v>276.8072456694325</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E87" t="n">
-        <v>280.0530700683594</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F87" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C88" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D88" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E88" t="n">
-        <v>278.6703796386719</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F88" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>276.5424507136568</v>
+        <v>268.9721802809009</v>
       </c>
       <c r="C89" t="n">
-        <v>278.9841654678224</v>
+        <v>271.5217784748567</v>
       </c>
       <c r="D89" t="n">
-        <v>268.7367562069888</v>
+        <v>261.1272811769848</v>
       </c>
       <c r="E89" t="n">
-        <v>270.5705261230469</v>
+        <v>263.3434448242188</v>
       </c>
       <c r="F89" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>268.9721491110363</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C90" t="n">
-        <v>271.5217470095316</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D90" t="n">
-        <v>261.127250916227</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E90" t="n">
-        <v>263.3434143066406</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F90" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C91" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D91" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E91" t="n">
-        <v>271.286376953125</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F91" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>268.8348608333229</v>
+        <v>272.139502815215</v>
       </c>
       <c r="C92" t="n">
-        <v>274.7479519102809</v>
+        <v>274.0713101587253</v>
       </c>
       <c r="D92" t="n">
-        <v>268.0209657772727</v>
+        <v>267.3639259113162</v>
       </c>
       <c r="E92" t="n">
-        <v>270.3548278808594</v>
+        <v>267.9228820800781</v>
       </c>
       <c r="F92" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>272.1395338130845</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C93" t="n">
-        <v>274.0713413766361</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D93" t="n">
-        <v>267.3639563652268</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E93" t="n">
-        <v>267.9229125976562</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F93" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7670960064547</v>
       </c>
       <c r="C94" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7590795351679</v>
       </c>
       <c r="D94" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626513270822</v>
       </c>
       <c r="E94" t="n">
-        <v>273.5025634765625</v>
+        <v>278.856689453125</v>
       </c>
       <c r="F94" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>272.7671258575986</v>
+        <v>280.0923103323967</v>
       </c>
       <c r="C95" t="n">
-        <v>280.7591102609402</v>
+        <v>287.7704918658715</v>
       </c>
       <c r="D95" t="n">
-        <v>270.4626809260317</v>
+        <v>278.994029288489</v>
       </c>
       <c r="E95" t="n">
-        <v>278.8567199707031</v>
+        <v>287.5057373046875</v>
       </c>
       <c r="F95" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>280.0922508710514</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C96" t="n">
-        <v>287.7704307745099</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D96" t="n">
-        <v>278.9939700602999</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E96" t="n">
-        <v>287.5056762695312</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F96" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>288.3000088357305</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C97" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D97" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E97" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F97" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>284.377578031072</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C98" t="n">
-        <v>284.5050624231632</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D98" t="n">
-        <v>280.7395146362062</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E98" t="n">
-        <v>282.6124877929688</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F98" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>285.2503082207336</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C99" t="n">
-        <v>285.2503082207336</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D99" t="n">
-        <v>281.3278592694971</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E99" t="n">
-        <v>284.3088989257812</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F99" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C100" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D100" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E100" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F100" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C101" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D101" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E101" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F101" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>276.7287838236561</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C102" t="n">
-        <v>276.9248883144977</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D102" t="n">
-        <v>266.5303926707583</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E102" t="n">
-        <v>268.6387329101562</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F102" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4161285575944</v>
       </c>
       <c r="C103" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355972025459</v>
       </c>
       <c r="D103" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000570330196</v>
       </c>
       <c r="E103" t="n">
-        <v>278.6900024414062</v>
+        <v>281.1023254394531</v>
       </c>
       <c r="F103" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>281.4160980059485</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C104" t="n">
-        <v>289.5355657694184</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D104" t="n">
-        <v>279.7000266676773</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E104" t="n">
-        <v>281.102294921875</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F104" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C105" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D105" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E105" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F105" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C106" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D106" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E106" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F106" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>283.3871388529354</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C107" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D107" t="n">
-        <v>278.8468991181569</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E107" t="n">
-        <v>283.6028747558594</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F107" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C108" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D108" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E108" t="n">
-        <v>286.2995300292969</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F108" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>284.4265691931125</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C109" t="n">
-        <v>285.7406159339096</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D109" t="n">
-        <v>281.1807450619272</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E109" t="n">
-        <v>283.17138671875</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F109" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,25 +3277,25 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C110" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D110" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E110" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F110" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3303,25 +3303,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C111" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D111" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E111" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F111" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G111" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C112" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D112" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E112" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F112" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>279.0580549356083</v>
+        <v>281.4297838763166</v>
       </c>
       <c r="C113" t="n">
-        <v>282.8528771272727</v>
+        <v>284.177078134999</v>
       </c>
       <c r="D113" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039671765164</v>
       </c>
       <c r="E113" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907104492188</v>
       </c>
       <c r="F113" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>281.42981524537</v>
+        <v>274.7888344130931</v>
       </c>
       <c r="C114" t="n">
-        <v>284.1771098102745</v>
+        <v>279.5521380386192</v>
       </c>
       <c r="D114" t="n">
-        <v>273.039702199029</v>
+        <v>274.5417754718342</v>
       </c>
       <c r="E114" t="n">
-        <v>273.7907409667969</v>
+        <v>278.7714233398438</v>
       </c>
       <c r="F114" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>274.7888644946905</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C115" t="n">
-        <v>279.5521686416635</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D115" t="n">
-        <v>274.5418055263856</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E115" t="n">
-        <v>278.7714538574219</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F115" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>280.6392236042361</v>
+        <v>284.41428667964</v>
       </c>
       <c r="C116" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902898411239</v>
       </c>
       <c r="D116" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4891167908925</v>
       </c>
       <c r="E116" t="n">
-        <v>282.1314392089844</v>
+        <v>284.18701171875</v>
       </c>
       <c r="F116" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>284.4142561376558</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C117" t="n">
-        <v>285.5902591728541</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D117" t="n">
-        <v>281.4890865630293</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E117" t="n">
-        <v>284.1869812011719</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F117" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589555118485</v>
       </c>
       <c r="C118" t="n">
-        <v>285.0072039222152</v>
+        <v>284.1671803923218</v>
       </c>
       <c r="D118" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7751962176443</v>
       </c>
       <c r="E118" t="n">
-        <v>280.9850769042969</v>
+        <v>277.1408386230469</v>
       </c>
       <c r="F118" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>280.6589864168267</v>
+        <v>275.7078960775263</v>
       </c>
       <c r="C119" t="n">
-        <v>284.167211683611</v>
+        <v>279.7695608963037</v>
       </c>
       <c r="D119" t="n">
-        <v>276.7752266949594</v>
+        <v>271.7648448878931</v>
       </c>
       <c r="E119" t="n">
-        <v>277.140869140625</v>
+        <v>272.347900390625</v>
       </c>
       <c r="F119" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>275.7079269716043</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C120" t="n">
-        <v>279.769592245506</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D120" t="n">
-        <v>271.7648753401377</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E120" t="n">
-        <v>272.3479309082031</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F120" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069856894997</v>
       </c>
       <c r="C121" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639393177099</v>
       </c>
       <c r="D121" t="n">
-        <v>265.9243614270812</v>
+        <v>264.44204492441</v>
       </c>
       <c r="E121" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768737792969</v>
       </c>
       <c r="F121" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>265.7069555541203</v>
+        <v>271.7648799566674</v>
       </c>
       <c r="C122" t="n">
-        <v>270.1639086768414</v>
+        <v>272.8321614881822</v>
       </c>
       <c r="D122" t="n">
-        <v>264.4420149324948</v>
+        <v>263.9676840156166</v>
       </c>
       <c r="E122" t="n">
-        <v>269.0768432617188</v>
+        <v>267.3672180175781</v>
       </c>
       <c r="F122" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>271.7648489371355</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C123" t="n">
-        <v>272.8321303468297</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D123" t="n">
-        <v>263.9676538860649</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E123" t="n">
-        <v>267.3671875</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F123" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C124" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D124" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E124" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F124" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>264.3530902318651</v>
+        <v>257.1191907461688</v>
       </c>
       <c r="C125" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2438917467647</v>
       </c>
       <c r="D125" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505034942698</v>
       </c>
       <c r="E125" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102661132812</v>
       </c>
       <c r="F125" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>257.119221076063</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C126" t="n">
-        <v>259.2439223272896</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D126" t="n">
-        <v>253.6505334149961</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E126" t="n">
-        <v>258.7102966308594</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F126" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C127" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D127" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E127" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F127" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867274922702</v>
       </c>
       <c r="C128" t="n">
-        <v>272.0613148441149</v>
+        <v>275.757318970375</v>
       </c>
       <c r="D128" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356586528844</v>
       </c>
       <c r="E128" t="n">
-        <v>270.7568664550781</v>
+        <v>273.9982604980469</v>
       </c>
       <c r="F128" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>269.0867574628081</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C129" t="n">
-        <v>275.7573496838748</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D129" t="n">
-        <v>268.3356885397691</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E129" t="n">
-        <v>273.998291015625</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F129" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C130" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D130" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E130" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F130" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3296014014268</v>
       </c>
       <c r="C131" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881914326393</v>
       </c>
       <c r="D131" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439367148364</v>
       </c>
       <c r="E131" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804321289062</v>
       </c>
       <c r="F131" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>308.3295702834321</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C132" t="n">
-        <v>309.2881602178994</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D132" t="n">
-        <v>301.2439063119584</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E132" t="n">
-        <v>302.3804016113281</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F132" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272561704691</v>
       </c>
       <c r="C133" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187701494722</v>
       </c>
       <c r="D133" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213715612747</v>
       </c>
       <c r="E133" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7498168945312</v>
       </c>
       <c r="F133" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>304.3272252898824</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C134" t="n">
-        <v>306.7187390262146</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D134" t="n">
-        <v>300.6213410567302</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E134" t="n">
-        <v>300.7497863769531</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F134" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C135" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D135" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E135" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F135" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C136" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D136" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E136" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F136" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2943017295384</v>
       </c>
       <c r="C137" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8618187748353</v>
       </c>
       <c r="D137" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4265214430497</v>
       </c>
       <c r="E137" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6778259277344</v>
       </c>
       <c r="F137" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>311.2942713469933</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C138" t="n">
-        <v>314.8617880440979</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D138" t="n">
-        <v>309.4264912428012</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E138" t="n">
-        <v>312.6777954101562</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F138" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>316.2848676157387</v>
+        <v>320.37616900858</v>
       </c>
       <c r="C139" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719258918635</v>
       </c>
       <c r="D139" t="n">
-        <v>313.4091278691752</v>
+        <v>316.35404203196</v>
       </c>
       <c r="E139" t="n">
-        <v>320.8110046386719</v>
+        <v>319.6745300292969</v>
       </c>
       <c r="F139" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>320.3761995931397</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C140" t="n">
-        <v>321.5719565905757</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D140" t="n">
-        <v>316.3540722325493</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E140" t="n">
-        <v>319.674560546875</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F140" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7521876325058</v>
       </c>
       <c r="C141" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418314545246</v>
       </c>
       <c r="D141" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931290879458</v>
       </c>
       <c r="E141" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611145019531</v>
       </c>
       <c r="F141" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>346.7522179221875</v>
+        <v>350.5074994974842</v>
       </c>
       <c r="C142" t="n">
-        <v>354.3418624071809</v>
+        <v>352.6519846563255</v>
       </c>
       <c r="D142" t="n">
-        <v>344.9931592239693</v>
+        <v>346.3766807003688</v>
       </c>
       <c r="E142" t="n">
-        <v>349.3611450195312</v>
+        <v>350.388916015625</v>
       </c>
       <c r="F142" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>350.5074689695779</v>
+        <v>352.2961666917061</v>
       </c>
       <c r="C143" t="n">
-        <v>352.6519539416425</v>
+        <v>354.0651171980212</v>
       </c>
       <c r="D143" t="n">
-        <v>346.3766505322415</v>
+        <v>347.2561882957746</v>
       </c>
       <c r="E143" t="n">
-        <v>350.3888854980469</v>
+        <v>350.7446594238281</v>
       </c>
       <c r="F143" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>352.2961973442777</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C144" t="n">
-        <v>354.0651480045056</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D144" t="n">
-        <v>347.256218509828</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E144" t="n">
-        <v>350.7446899414062</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F144" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C145" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D145" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E145" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F145" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C146" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D146" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E146" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F146" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C147" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D147" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E147" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F147" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C148" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D148" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E148" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F148" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C149" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D149" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E149" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F149" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216408565838</v>
       </c>
       <c r="C150" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260893018678</v>
       </c>
       <c r="D150" t="n">
-        <v>360.360183242299</v>
+        <v>357.5536224796683</v>
       </c>
       <c r="E150" t="n">
-        <v>366.388427734375</v>
+        <v>359.5893859863281</v>
       </c>
       <c r="F150" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>366.1216097846273</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C151" t="n">
-        <v>367.4260581192055</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D151" t="n">
-        <v>357.553592134861</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E151" t="n">
-        <v>359.58935546875</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F151" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C152" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D152" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E152" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F152" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="C153" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="D153" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="E153" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="F153" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>367.6138623558188</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C154" t="n">
-        <v>375.5098876953125</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D154" t="n">
-        <v>367.6138623558188</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E154" t="n">
-        <v>375.5098876953125</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F154" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3460853480032</v>
       </c>
       <c r="C155" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7446883171237</v>
       </c>
       <c r="D155" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5159708878205</v>
       </c>
       <c r="E155" t="n">
-        <v>379.9173889160156</v>
+        <v>391.726806640625</v>
       </c>
       <c r="F155" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>378.3461148231528</v>
+        <v>391.835521582727</v>
       </c>
       <c r="C156" t="n">
-        <v>392.7447189140002</v>
+        <v>399.3955199396844</v>
       </c>
       <c r="D156" t="n">
-        <v>377.5160002982997</v>
+        <v>388.3766960454267</v>
       </c>
       <c r="E156" t="n">
-        <v>391.7268371582031</v>
+        <v>396.4407043457031</v>
       </c>
       <c r="F156" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>391.8354914196509</v>
+        <v>396.2825841810375</v>
       </c>
       <c r="C157" t="n">
-        <v>399.3954891946478</v>
+        <v>397.1719904330225</v>
       </c>
       <c r="D157" t="n">
-        <v>388.3766661486073</v>
+        <v>391.3414048271592</v>
       </c>
       <c r="E157" t="n">
-        <v>396.440673828125</v>
+        <v>394.3950500488281</v>
       </c>
       <c r="F157" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>396.2825535174053</v>
+        <v>389.6613628183419</v>
       </c>
       <c r="C158" t="n">
-        <v>397.1719597005697</v>
+        <v>392.9522049122001</v>
       </c>
       <c r="D158" t="n">
-        <v>391.3413745458666</v>
+        <v>385.6590199026367</v>
       </c>
       <c r="E158" t="n">
-        <v>394.39501953125</v>
+        <v>389.2166748046875</v>
       </c>
       <c r="F158" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>389.661393370787</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C159" t="n">
-        <v>392.9522357226725</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D159" t="n">
-        <v>385.6590501412673</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E159" t="n">
-        <v>389.2167053222656</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F159" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119880990537</v>
       </c>
       <c r="C160" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432754242469</v>
       </c>
       <c r="D160" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512904411622</v>
       </c>
       <c r="E160" t="n">
-        <v>386.5286865234375</v>
+        <v>384.6609191894531</v>
       </c>
       <c r="F160" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>385.4119575218886</v>
+        <v>384.9672452573303</v>
       </c>
       <c r="C161" t="n">
-        <v>390.3432444558516</v>
+        <v>388.7522052741927</v>
       </c>
       <c r="D161" t="n">
-        <v>382.9512600592197</v>
+        <v>376.2213825216763</v>
       </c>
       <c r="E161" t="n">
-        <v>384.660888671875</v>
+        <v>378.790771484375</v>
       </c>
       <c r="F161" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>384.9672762725209</v>
+        <v>376.6364522760421</v>
       </c>
       <c r="C162" t="n">
-        <v>388.7522365943216</v>
+        <v>381.5677396470687</v>
       </c>
       <c r="D162" t="n">
-        <v>376.2214128322495</v>
+        <v>376.0632887376697</v>
       </c>
       <c r="E162" t="n">
-        <v>378.7908020019531</v>
+        <v>377.98046875</v>
       </c>
       <c r="F162" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>376.6364218669779</v>
+        <v>377.4270309363715</v>
       </c>
       <c r="C163" t="n">
-        <v>381.5677088398597</v>
+        <v>385.9456187280053</v>
       </c>
       <c r="D163" t="n">
-        <v>376.0632583748818</v>
+        <v>376.5277327371266</v>
       </c>
       <c r="E163" t="n">
-        <v>377.9804382324219</v>
+        <v>383.8999633789062</v>
       </c>
       <c r="F163" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>377.4270609393932</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C164" t="n">
-        <v>385.9456494081999</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D164" t="n">
-        <v>376.5277626686598</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E164" t="n">
-        <v>383.8999938964844</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F164" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C165" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D165" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E165" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F165" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312827021371</v>
       </c>
       <c r="C166" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6807151570288</v>
       </c>
       <c r="D166" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783391116702</v>
       </c>
       <c r="E166" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298767089844</v>
       </c>
       <c r="F166" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>380.4312519906984</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C167" t="n">
-        <v>384.6806841025421</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D167" t="n">
-        <v>376.4783087193446</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E167" t="n">
-        <v>378.0298461914062</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F167" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C168" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D168" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E168" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F168" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C169" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D169" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E169" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F169" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C170" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D170" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E170" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F170" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119603627872</v>
       </c>
       <c r="C171" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6580885443842</v>
       </c>
       <c r="D171" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2340851575979</v>
       </c>
       <c r="E171" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058471679688</v>
       </c>
       <c r="F171" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>385.4119903823484</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C172" t="n">
-        <v>396.6581194399012</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D172" t="n">
-        <v>385.2341151633045</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E172" t="n">
-        <v>391.8058776855469</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F172" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C173" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D173" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E173" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F173" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>392.4580996989546</v>
+        <v>405.166788512205</v>
       </c>
       <c r="C174" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="D174" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6467992699509</v>
       </c>
       <c r="E174" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="F174" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>405.1668188073661</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C175" t="n">
-        <v>408.1414184570312</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D175" t="n">
-        <v>402.6468293766872</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E175" t="n">
-        <v>408.1414184570312</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F175" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C176" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D176" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E176" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F176" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C177" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D177" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E177" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F177" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C178" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D178" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E178" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F178" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C179" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D179" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E179" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F179" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G179" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C180" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D180" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E180" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F180" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C181" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D181" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E181" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F181" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C182" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D182" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E182" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F182" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C183" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D183" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E183" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F183" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C184" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D184" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E184" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F184" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C185" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D185" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E185" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F185" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C186" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D186" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E186" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F186" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C187" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D187" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E187" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F187" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C188" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D188" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E188" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F188" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C189" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D189" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E189" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F189" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C190" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D190" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E190" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F190" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C191" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D191" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E191" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F191" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C192" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D192" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E192" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F192" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C193" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D193" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E193" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F193" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C194" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D194" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E194" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F194" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C195" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D195" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E195" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F195" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C196" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D196" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E196" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F196" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C197" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D197" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E197" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F197" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C198" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D198" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E198" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F198" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C199" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D199" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E199" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F199" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C200" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D200" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E200" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F200" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C201" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D201" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E201" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F201" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C202" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D202" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E202" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F202" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C203" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D203" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E203" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F203" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C204" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D204" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E204" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F204" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C205" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D205" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E205" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F205" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C206" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D206" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E206" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F206" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C207" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D207" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E207" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F207" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C208" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D208" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E208" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F208" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C209" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D209" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E209" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F209" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C210" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D210" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E210" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F210" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C211" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D211" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E211" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F211" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C212" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D212" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E212" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F212" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C213" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D213" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E213" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F213" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C214" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D214" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E214" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F214" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C215" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D215" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E215" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F215" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C216" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D216" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E216" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F216" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C217" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D217" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E217" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F217" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C218" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D218" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E218" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F218" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C219" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D219" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E219" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F219" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C220" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D220" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E220" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F220" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C221" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D221" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E221" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F221" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C222" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D222" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E222" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F222" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C223" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D223" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E223" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F223" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C224" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D224" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E224" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F224" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C225" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D225" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E225" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F225" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C226" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D226" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E226" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F226" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C227" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D227" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E227" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F227" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C228" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D228" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E228" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F228" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C229" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D229" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E229" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F229" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C230" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D230" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E230" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F230" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C231" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D231" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E231" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F231" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C232" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D232" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E232" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F232" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C233" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D233" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E233" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F233" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C234" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D234" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E234" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F234" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C235" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D235" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E235" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F235" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C236" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D236" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E236" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F236" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C237" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D237" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E237" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F237" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C238" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D238" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E238" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F238" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C239" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D239" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E239" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F239" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C240" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D240" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E240" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F240" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,25 +6683,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C241" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D241" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E241" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F241" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C242" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D242" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E242" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F242" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C243" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D243" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E243" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F243" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C244" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D244" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E244" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F244" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>375.2900085449219</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C245" t="n">
-        <v>378.489990234375</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D245" t="n">
-        <v>372.4200134277344</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E245" t="n">
-        <v>376.8999938964844</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F245" t="n">
-        <v>8606300</v>
+        <v>5712300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>377.8699951171875</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="C246" t="n">
-        <v>378.9500122070312</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="D246" t="n">
-        <v>373.8200073242188</v>
+        <v>372.4100036621094</v>
       </c>
       <c r="E246" t="n">
-        <v>377.5599975585938</v>
+        <v>372.9500122070312</v>
       </c>
       <c r="F246" t="n">
-        <v>5712300</v>
+        <v>4495000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>381.3900146484375</v>
+        <v>370.8900146484375</v>
       </c>
       <c r="C247" t="n">
-        <v>381.3900146484375</v>
+        <v>372.6099853515625</v>
       </c>
       <c r="D247" t="n">
-        <v>372.4100036621094</v>
+        <v>366</v>
       </c>
       <c r="E247" t="n">
-        <v>372.9500122070312</v>
+        <v>371.2900085449219</v>
       </c>
       <c r="F247" t="n">
-        <v>4495000</v>
+        <v>3859300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>370.8900146484375</v>
+        <v>371.9200134277344</v>
       </c>
       <c r="C248" t="n">
-        <v>372.6099853515625</v>
+        <v>375.2799987792969</v>
       </c>
       <c r="D248" t="n">
-        <v>366</v>
+        <v>368.5</v>
       </c>
       <c r="E248" t="n">
-        <v>371.2900085449219</v>
+        <v>375.010009765625</v>
       </c>
       <c r="F248" t="n">
-        <v>3859300</v>
+        <v>4651000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>371.9200134277344</v>
+        <v>375.9500122070312</v>
       </c>
       <c r="C249" t="n">
-        <v>375.2799987792969</v>
+        <v>379.1700134277344</v>
       </c>
       <c r="D249" t="n">
-        <v>368.5</v>
+        <v>371.1700134277344</v>
       </c>
       <c r="E249" t="n">
-        <v>375.010009765625</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="F249" t="n">
-        <v>4651000</v>
+        <v>4077400</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>375.9500122070312</v>
+        <v>376.3599853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>379.1700134277344</v>
+        <v>380.9800109863281</v>
       </c>
       <c r="D250" t="n">
-        <v>371.1700134277344</v>
+        <v>374.5599975585938</v>
       </c>
       <c r="E250" t="n">
-        <v>376.5899963378906</v>
+        <v>377.8299865722656</v>
       </c>
       <c r="F250" t="n">
-        <v>4077400</v>
+        <v>4677100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>376.3599853515625</v>
+        <v>374.8800048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>380.9800109863281</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="D251" t="n">
-        <v>374.5599975585938</v>
+        <v>371.3299865722656</v>
       </c>
       <c r="E251" t="n">
-        <v>377.8299865722656</v>
+        <v>374.9400024414062</v>
       </c>
       <c r="F251" t="n">
-        <v>4677100</v>
+        <v>3284700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>374.8800048828125</v>
+        <v>374.9299926757812</v>
       </c>
       <c r="C252" t="n">
-        <v>376.5899963378906</v>
+        <v>374.9299926757812</v>
       </c>
       <c r="D252" t="n">
-        <v>371.3299865722656</v>
+        <v>365.7200012207031</v>
       </c>
       <c r="E252" t="n">
-        <v>374.9400024414062</v>
+        <v>367.0799865722656</v>
       </c>
       <c r="F252" t="n">
-        <v>3284700</v>
+        <v>4788300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,37 +10530,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>367.08</v>
+      </c>
+      <c r="D2" t="n">
         <v>374.94</v>
       </c>
-      <c r="D2" t="n">
-        <v>377.83</v>
-      </c>
       <c r="E2" t="n">
-        <v>374.88</v>
+        <v>374.93</v>
       </c>
       <c r="F2" t="n">
-        <v>376.59</v>
+        <v>374.05</v>
       </c>
       <c r="G2" t="n">
-        <v>371.33</v>
+        <v>365.76</v>
       </c>
       <c r="H2" t="n">
-        <v>3276363</v>
+        <v>4782910</v>
       </c>
       <c r="I2" t="n">
         <v>4930261</v>
       </c>
       <c r="J2" t="n">
-        <v>336544202752</v>
+        <v>329489088512</v>
       </c>
       <c r="K2" t="n">
-        <v>24.267962</v>
+        <v>23.591259</v>
       </c>
       <c r="L2" t="n">
-        <v>16.582788</v>
+        <v>16.235157</v>
       </c>
       <c r="M2" t="n">
-        <v>15.45</v>
+        <v>15.56</v>
       </c>
       <c r="N2" t="n">
         <v>461.62</v>
@@ -10572,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4467416</v>
+        <v>3.3744862</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>385906212864</v>
+        <v>378851131392</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:07:19</t>
+          <t>2026-10-01 17:02:59</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>334.9803326465864</v>
+        <v>338.2824047650262</v>
       </c>
       <c r="C2" t="n">
-        <v>339.6558538996071</v>
+        <v>345.87033541468</v>
       </c>
       <c r="D2" t="n">
-        <v>332.7692198568235</v>
+        <v>335.7108637419195</v>
       </c>
       <c r="E2" t="n">
-        <v>339.2662048339844</v>
+        <v>344.5456237792969</v>
       </c>
       <c r="F2" t="n">
-        <v>8825500</v>
+        <v>8564200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>338.2824047650262</v>
+        <v>347.9840458817623</v>
       </c>
       <c r="C3" t="n">
-        <v>345.87033541468</v>
+        <v>358.4552243092751</v>
       </c>
       <c r="D3" t="n">
-        <v>335.7108637419195</v>
+        <v>347.3606312231566</v>
       </c>
       <c r="E3" t="n">
-        <v>344.5456237792969</v>
+        <v>350.8575439453125</v>
       </c>
       <c r="F3" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>347.984106417045</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C4" t="n">
-        <v>358.4552866661233</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D4" t="n">
-        <v>347.3606916499901</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E4" t="n">
-        <v>350.8576049804688</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F4" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C5" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D5" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E5" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F5" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C6" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D6" t="n">
-        <v>348.77305405812</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E6" t="n">
-        <v>354.2278137207031</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F6" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>357.4130008055815</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C7" t="n">
-        <v>364.9132992932725</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D7" t="n">
-        <v>356.3123046396842</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E7" t="n">
-        <v>360.3254699707031</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F7" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>362.8580018323341</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="C8" t="n">
-        <v>366.4620474561767</v>
+        <v>359.8189245088024</v>
       </c>
       <c r="D8" t="n">
-        <v>356.5850326317519</v>
+        <v>343.3670132328114</v>
       </c>
       <c r="E8" t="n">
-        <v>358.1532897949219</v>
+        <v>345.3053894042969</v>
       </c>
       <c r="F8" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>359.8189563090651</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C9" t="n">
-        <v>359.8189563090651</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D9" t="n">
-        <v>343.3670435790787</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E9" t="n">
-        <v>345.305419921875</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F9" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>345.5391423923842</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C10" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D10" t="n">
-        <v>344.155989405705</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E10" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F10" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>345.743758076041</v>
+        <v>350.0685974010841</v>
       </c>
       <c r="C11" t="n">
-        <v>352.9323197996358</v>
+        <v>354.7733097077772</v>
       </c>
       <c r="D11" t="n">
-        <v>344.2339422221326</v>
+        <v>346.6204052543966</v>
       </c>
       <c r="E11" t="n">
-        <v>350.5945739746094</v>
+        <v>351.7829284667969</v>
       </c>
       <c r="F11" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>350.0685670322262</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C12" t="n">
-        <v>354.77327893078</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D12" t="n">
-        <v>346.6203751846734</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E12" t="n">
-        <v>351.7828979492188</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F12" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>352.4549874654966</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C13" t="n">
-        <v>352.6108411281484</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D13" t="n">
-        <v>345.207955645442</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E13" t="n">
-        <v>347.4190979003906</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F13" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>341.8961320639185</v>
+        <v>349.2406127602151</v>
       </c>
       <c r="C14" t="n">
-        <v>349.0944723037945</v>
+        <v>356.0882755673564</v>
       </c>
       <c r="D14" t="n">
-        <v>341.7305282652253</v>
+        <v>348.2373288971846</v>
       </c>
       <c r="E14" t="n">
-        <v>347.3508911132812</v>
+        <v>355.0265502929688</v>
       </c>
       <c r="F14" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>349.2405827399879</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C15" t="n">
-        <v>356.0882449585139</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D15" t="n">
-        <v>348.2372989631983</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E15" t="n">
-        <v>355.0265197753906</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F15" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5200118501019</v>
       </c>
       <c r="C16" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589826989666</v>
       </c>
       <c r="D16" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7146038632694</v>
       </c>
       <c r="E16" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140747070312</v>
       </c>
       <c r="F16" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>354.5200425762015</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C17" t="n">
-        <v>354.5590134284439</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D17" t="n">
-        <v>348.7146340862168</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E17" t="n">
-        <v>352.1141052246094</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F17" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>346.3573617095742</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C18" t="n">
-        <v>352.883596703336</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D18" t="n">
-        <v>344.4677065470185</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E18" t="n">
-        <v>351.10107421875</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F18" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>351.9971738259649</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C19" t="n">
-        <v>355.9421471732778</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D19" t="n">
-        <v>350.6919328534217</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E19" t="n">
-        <v>353.0978698730469</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F19" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063444379755</v>
       </c>
       <c r="C20" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180517731913</v>
       </c>
       <c r="D20" t="n">
-        <v>352.0264145317695</v>
+        <v>349.3282643556941</v>
       </c>
       <c r="E20" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2993774414062</v>
       </c>
       <c r="F20" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>370.8063128551364</v>
+        <v>354.8317550345645</v>
       </c>
       <c r="C21" t="n">
-        <v>371.118020163803</v>
+        <v>356.6532485328659</v>
       </c>
       <c r="D21" t="n">
-        <v>349.3282346022162</v>
+        <v>344.7015033078588</v>
       </c>
       <c r="E21" t="n">
-        <v>358.2993469238281</v>
+        <v>346.0457153320312</v>
       </c>
       <c r="F21" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C22" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D22" t="n">
-        <v>344.701472908826</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E22" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F22" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>338.5064021770676</v>
+        <v>335.4576347488759</v>
       </c>
       <c r="C23" t="n">
-        <v>345.3443442519412</v>
+        <v>337.298598712068</v>
       </c>
       <c r="D23" t="n">
-        <v>334.6880914224008</v>
+        <v>328.3761763650699</v>
       </c>
       <c r="E23" t="n">
-        <v>335.8082580566406</v>
+        <v>332.7010192871094</v>
       </c>
       <c r="F23" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>335.4576347488759</v>
+        <v>330.3340623523696</v>
       </c>
       <c r="C24" t="n">
-        <v>337.298598712068</v>
+        <v>331.8633487318257</v>
       </c>
       <c r="D24" t="n">
-        <v>328.3761763650699</v>
+        <v>318.1290514761847</v>
       </c>
       <c r="E24" t="n">
-        <v>332.7010192871094</v>
+        <v>325.132568359375</v>
       </c>
       <c r="F24" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>330.3340313465691</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C25" t="n">
-        <v>331.8633175824834</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D25" t="n">
-        <v>318.1290216159704</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E25" t="n">
-        <v>325.1325378417969</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F25" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>319.1323440808776</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C26" t="n">
-        <v>327.7722802636044</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D26" t="n">
-        <v>318.7135040219252</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E26" t="n">
-        <v>322.2493286132812</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F26" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>317.8368180152801</v>
+        <v>320.3888776178953</v>
       </c>
       <c r="C27" t="n">
-        <v>321.6454087872217</v>
+        <v>323.7493777886428</v>
       </c>
       <c r="D27" t="n">
-        <v>315.8107795893674</v>
+        <v>313.1126243976539</v>
       </c>
       <c r="E27" t="n">
-        <v>319.2394714355469</v>
+        <v>313.2197570800781</v>
       </c>
       <c r="F27" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>320.3888464018165</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C28" t="n">
-        <v>323.7493462451443</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D28" t="n">
-        <v>313.1125938905139</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E28" t="n">
-        <v>313.2197265625</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F28" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>311.3690496699339</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C29" t="n">
-        <v>316.1322033153182</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D29" t="n">
-        <v>306.0117020081513</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E29" t="n">
-        <v>315.801025390625</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F29" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>311.6904400245728</v>
+        <v>314.9146147475993</v>
       </c>
       <c r="C30" t="n">
-        <v>315.8399583185172</v>
+        <v>319.3563404779885</v>
       </c>
       <c r="D30" t="n">
-        <v>308.9436046905141</v>
+        <v>311.583335312832</v>
       </c>
       <c r="E30" t="n">
-        <v>313.2391967773438</v>
+        <v>318.9570007324219</v>
       </c>
       <c r="F30" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>314.9146147475993</v>
+        <v>319.9310727655453</v>
       </c>
       <c r="C31" t="n">
-        <v>319.3563404779885</v>
+        <v>334.2692843856479</v>
       </c>
       <c r="D31" t="n">
-        <v>311.583335312832</v>
+        <v>318.5965811998377</v>
       </c>
       <c r="E31" t="n">
-        <v>318.9570007324219</v>
+        <v>330.265869140625</v>
       </c>
       <c r="F31" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>319.931043202934</v>
+        <v>329.5742822700864</v>
       </c>
       <c r="C32" t="n">
-        <v>334.2692534981419</v>
+        <v>330.2366380969722</v>
       </c>
       <c r="D32" t="n">
-        <v>318.5965517605375</v>
+        <v>322.6973986104767</v>
       </c>
       <c r="E32" t="n">
-        <v>330.2658386230469</v>
+        <v>323.8954772949219</v>
       </c>
       <c r="F32" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>329.5742822700864</v>
+        <v>318.4699706680781</v>
       </c>
       <c r="C33" t="n">
-        <v>330.2366380969722</v>
+        <v>319.6972700691676</v>
       </c>
       <c r="D33" t="n">
-        <v>322.6973986104767</v>
+        <v>312.1775010814912</v>
       </c>
       <c r="E33" t="n">
-        <v>323.8954772949219</v>
+        <v>313.511962890625</v>
       </c>
       <c r="F33" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>318.4699706680781</v>
+        <v>312.2846677767845</v>
       </c>
       <c r="C34" t="n">
-        <v>319.6972700691676</v>
+        <v>319.3758466817346</v>
       </c>
       <c r="D34" t="n">
-        <v>312.1775010814912</v>
+        <v>311.1450007536453</v>
       </c>
       <c r="E34" t="n">
-        <v>313.511962890625</v>
+        <v>312.2067260742188</v>
       </c>
       <c r="F34" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7877755793916</v>
       </c>
       <c r="C35" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650570211989</v>
       </c>
       <c r="D35" t="n">
-        <v>311.1450007536453</v>
+        <v>300.761474830703</v>
       </c>
       <c r="E35" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4467163085938</v>
       </c>
       <c r="F35" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>308.7877447280039</v>
+        <v>305.7876433202538</v>
       </c>
       <c r="C36" t="n">
-        <v>309.2650261221254</v>
+        <v>306.829898044689</v>
       </c>
       <c r="D36" t="n">
-        <v>300.7614447812334</v>
+        <v>296.6314554825427</v>
       </c>
       <c r="E36" t="n">
-        <v>305.4466857910156</v>
+        <v>301.0731811523438</v>
       </c>
       <c r="F36" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>305.7876433202538</v>
+        <v>302.7485789287686</v>
       </c>
       <c r="C37" t="n">
-        <v>306.829898044689</v>
+        <v>306.5863902909554</v>
       </c>
       <c r="D37" t="n">
-        <v>296.6314554825427</v>
+        <v>301.9595901197654</v>
       </c>
       <c r="E37" t="n">
-        <v>301.0731811523438</v>
+        <v>303.4596557617188</v>
       </c>
       <c r="F37" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>302.7485789287686</v>
+        <v>303.8200433114142</v>
       </c>
       <c r="C38" t="n">
-        <v>306.5863902909554</v>
+        <v>315.4406096571707</v>
       </c>
       <c r="D38" t="n">
-        <v>301.9595901197654</v>
+        <v>303.3622324379126</v>
       </c>
       <c r="E38" t="n">
-        <v>303.4596557617188</v>
+        <v>311.6709899902344</v>
       </c>
       <c r="F38" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127181611407</v>
       </c>
       <c r="C39" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3984886748711</v>
       </c>
       <c r="D39" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819381150768</v>
       </c>
       <c r="E39" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748413085938</v>
       </c>
       <c r="F39" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>316.1127492028895</v>
+        <v>312.7911824167217</v>
       </c>
       <c r="C40" t="n">
-        <v>317.3985198428805</v>
+        <v>319.4927422543219</v>
       </c>
       <c r="D40" t="n">
-        <v>309.3819684958741</v>
+        <v>312.576887315192</v>
       </c>
       <c r="E40" t="n">
-        <v>310.7748718261719</v>
+        <v>317.8173522949219</v>
       </c>
       <c r="F40" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>312.7911824167217</v>
+        <v>318.1192531852973</v>
       </c>
       <c r="C41" t="n">
-        <v>319.4927422543219</v>
+        <v>326.4962014988301</v>
       </c>
       <c r="D41" t="n">
-        <v>312.576887315192</v>
+        <v>317.4374268746658</v>
       </c>
       <c r="E41" t="n">
-        <v>317.8173522949219</v>
+        <v>321.1583251953125</v>
       </c>
       <c r="F41" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>318.1192834140923</v>
+        <v>323.0675099624138</v>
       </c>
       <c r="C42" t="n">
-        <v>326.4962325236318</v>
+        <v>323.4473791003546</v>
       </c>
       <c r="D42" t="n">
-        <v>317.4374570386713</v>
+        <v>320.3596158297967</v>
       </c>
       <c r="E42" t="n">
-        <v>321.1583557128906</v>
+        <v>321.2167663574219</v>
       </c>
       <c r="F42" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>323.067540655824</v>
+        <v>318.6745269453515</v>
       </c>
       <c r="C43" t="n">
-        <v>323.4474098298547</v>
+        <v>321.4993043410047</v>
       </c>
       <c r="D43" t="n">
-        <v>320.3596462659403</v>
+        <v>314.6516410865056</v>
       </c>
       <c r="E43" t="n">
-        <v>321.216796875</v>
+        <v>314.8269653320312</v>
       </c>
       <c r="F43" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>318.6744960548122</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C44" t="n">
-        <v>321.4992731766471</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D44" t="n">
-        <v>314.6516105859225</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E44" t="n">
-        <v>314.8269348144531</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F44" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5446185401456</v>
       </c>
       <c r="C45" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549367443995</v>
       </c>
       <c r="D45" t="n">
-        <v>314.4275769247672</v>
+        <v>316.5803054378969</v>
       </c>
       <c r="E45" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8990173339844</v>
       </c>
       <c r="F45" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>317.5446185401456</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C46" t="n">
-        <v>332.5549367443995</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D46" t="n">
-        <v>316.5803054378969</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E46" t="n">
-        <v>330.8990173339844</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F46" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>330.5970491985518</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C47" t="n">
-        <v>332.4088222358486</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D47" t="n">
-        <v>320.1940611974609</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E47" t="n">
-        <v>324.84033203125</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F47" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,25 +1665,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>326.3111238051217</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C48" t="n">
-        <v>327.0027002516846</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D48" t="n">
-        <v>319.9894640831421</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E48" t="n">
-        <v>322.3272094726562</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F48" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1691,25 +1691,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894669558022</v>
       </c>
       <c r="C49" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0326109139432</v>
       </c>
       <c r="D49" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278603865539</v>
       </c>
       <c r="E49" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261413574219</v>
       </c>
       <c r="F49" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G49" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>316.894669558022</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C50" t="n">
-        <v>320.0326109139432</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D50" t="n">
-        <v>316.2278603865539</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E50" t="n">
-        <v>317.3261413574219</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F50" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C51" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D51" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E51" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F51" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566402470831</v>
       </c>
       <c r="C52" t="n">
-        <v>332.6727006619286</v>
+        <v>338.291630780554</v>
       </c>
       <c r="D52" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291558641754</v>
       </c>
       <c r="E52" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2124938964844</v>
       </c>
       <c r="F52" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>330.9566101169558</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C53" t="n">
-        <v>338.2915999826528</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D53" t="n">
-        <v>330.8291257456542</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E53" t="n">
-        <v>335.2124633789062</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F53" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C54" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D54" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E54" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F54" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>333.8200206972608</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C55" t="n">
-        <v>334.3789469115978</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D55" t="n">
-        <v>324.6120577084619</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E55" t="n">
-        <v>327.7206115722656</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F55" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>327.1420632206801</v>
+        <v>322.5527687928765</v>
       </c>
       <c r="C56" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785340619881</v>
       </c>
       <c r="D56" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773138986521</v>
       </c>
       <c r="E56" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781066894531</v>
       </c>
       <c r="F56" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>322.5527687928765</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C57" t="n">
-        <v>323.7785340619881</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D57" t="n">
-        <v>318.2773138986521</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E57" t="n">
-        <v>321.7781066894531</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F57" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>321.6996588106788</v>
+        <v>316.639672337624</v>
       </c>
       <c r="C58" t="n">
-        <v>328.112871433911</v>
+        <v>323.4058905098511</v>
       </c>
       <c r="D58" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139070917166</v>
       </c>
       <c r="E58" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558654785156</v>
       </c>
       <c r="F58" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>316.639672337624</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C59" t="n">
-        <v>323.4058905098511</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D59" t="n">
-        <v>315.4139070917166</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E59" t="n">
-        <v>318.8558654785156</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F59" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C60" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D60" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E60" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F60" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C61" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D61" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E61" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F61" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C62" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D62" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E62" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F62" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C63" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D63" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E63" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F63" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C64" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D64" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E64" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F64" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C65" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D65" t="n">
-        <v>323.484378234348</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E65" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F65" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>324.4845627249562</v>
+        <v>328.9463775793847</v>
       </c>
       <c r="C66" t="n">
-        <v>333.6631082445032</v>
+        <v>340.2136022879278</v>
       </c>
       <c r="D66" t="n">
-        <v>321.1504873151108</v>
+        <v>327.3773920593259</v>
       </c>
       <c r="E66" t="n">
-        <v>329.8779296875</v>
+        <v>335.3889770507812</v>
       </c>
       <c r="F66" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>328.9463775793847</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C67" t="n">
-        <v>340.2136022879278</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D67" t="n">
-        <v>327.3773920593259</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E67" t="n">
-        <v>335.3889770507812</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F67" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>341.5963098138764</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C68" t="n">
-        <v>345.7736979738297</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D68" t="n">
-        <v>338.4289212269501</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E68" t="n">
-        <v>342.2042846679688</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F68" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C69" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D69" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E69" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F69" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>334.3986242436816</v>
+        <v>340.5175958478422</v>
       </c>
       <c r="C70" t="n">
-        <v>341.1550277170099</v>
+        <v>342.2925015847546</v>
       </c>
       <c r="D70" t="n">
-        <v>334.1926741052517</v>
+        <v>335.8400862980764</v>
       </c>
       <c r="E70" t="n">
-        <v>340.1253967285156</v>
+        <v>337.3110046386719</v>
       </c>
       <c r="F70" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C71" t="n">
-        <v>342.2925015847546</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D71" t="n">
-        <v>335.8400862980764</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E71" t="n">
-        <v>337.3110046386719</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F71" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C72" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D72" t="n">
-        <v>327.465664861477</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E72" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F72" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>334.8791141795932</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C73" t="n">
-        <v>335.2125187841528</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D73" t="n">
-        <v>326.3968234220132</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E73" t="n">
-        <v>327.4558715820312</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F73" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C74" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D74" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E74" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F74" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C75" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D75" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E75" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F75" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524690830655</v>
       </c>
       <c r="C76" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003373667196</v>
       </c>
       <c r="D76" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1699239761241</v>
       </c>
       <c r="E76" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8686218261719</v>
       </c>
       <c r="F76" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C77" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D77" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E77" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F77" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489540449518</v>
       </c>
       <c r="C78" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683303861261</v>
       </c>
       <c r="D78" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0468994310211</v>
       </c>
       <c r="E78" t="n">
-        <v>341.0079040527344</v>
+        <v>347.5976257324219</v>
       </c>
       <c r="F78" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>340.4489540449518</v>
+        <v>347.4113127291759</v>
       </c>
       <c r="C79" t="n">
-        <v>348.0683303861261</v>
+        <v>350.9317071763275</v>
       </c>
       <c r="D79" t="n">
-        <v>340.0468994310211</v>
+        <v>346.1463145255873</v>
       </c>
       <c r="E79" t="n">
-        <v>347.5976257324219</v>
+        <v>349.3529357910156</v>
       </c>
       <c r="F79" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>347.4113430771444</v>
+        <v>347.0877216940886</v>
       </c>
       <c r="C80" t="n">
-        <v>350.9317378318185</v>
+        <v>347.9114324020834</v>
       </c>
       <c r="D80" t="n">
-        <v>346.1463447630524</v>
+        <v>340.537209047996</v>
       </c>
       <c r="E80" t="n">
-        <v>349.3529663085938</v>
+        <v>344.822509765625</v>
       </c>
       <c r="F80" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>347.0877216940886</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C81" t="n">
-        <v>347.9114324020834</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D81" t="n">
-        <v>340.537209047996</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E81" t="n">
-        <v>344.822509765625</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F81" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>288.2706063388866</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C82" t="n">
-        <v>293.6933912983777</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D82" t="n">
-        <v>274.96368990819</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E82" t="n">
-        <v>277.2191162109375</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F82" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>278.2193161239855</v>
+        <v>288.623596430627</v>
       </c>
       <c r="C83" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689931668393</v>
       </c>
       <c r="D83" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126820924317</v>
       </c>
       <c r="E83" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231689453125</v>
       </c>
       <c r="F83" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>288.623596430627</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C84" t="n">
-        <v>289.8689931668393</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D84" t="n">
-        <v>283.6126820924317</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E84" t="n">
-        <v>286.6231689453125</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F84" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4746956220067</v>
       </c>
       <c r="C85" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7697819219751</v>
       </c>
       <c r="D85" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072155055542</v>
       </c>
       <c r="E85" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530395507812</v>
       </c>
       <c r="F85" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>280.4746956220067</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C86" t="n">
-        <v>284.7697819219751</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D86" t="n">
-        <v>276.8072155055542</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E86" t="n">
-        <v>280.0530395507812</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F86" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424819048067</v>
       </c>
       <c r="C87" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841969343727</v>
       </c>
       <c r="D87" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367865177365</v>
       </c>
       <c r="E87" t="n">
-        <v>278.6703796386719</v>
+        <v>270.570556640625</v>
       </c>
       <c r="F87" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>276.5424819048067</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C88" t="n">
-        <v>278.9841969343727</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D88" t="n">
-        <v>268.7367865177365</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E88" t="n">
-        <v>270.570556640625</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F88" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>268.9721802809009</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C89" t="n">
-        <v>271.5217784748567</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D89" t="n">
-        <v>261.1272811769848</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E89" t="n">
-        <v>263.3434448242188</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F89" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348304873182</v>
       </c>
       <c r="C90" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479208968081</v>
       </c>
       <c r="D90" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209355231403</v>
       </c>
       <c r="E90" t="n">
-        <v>271.286376953125</v>
+        <v>270.3547973632812</v>
       </c>
       <c r="F90" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>268.8348304873182</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C91" t="n">
-        <v>274.7479208968081</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D91" t="n">
-        <v>268.0209355231403</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E91" t="n">
-        <v>270.3547973632812</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F91" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>272.139502815215</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C92" t="n">
-        <v>274.0713101587253</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D92" t="n">
-        <v>267.3639259113162</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E92" t="n">
-        <v>267.9228820800781</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F92" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7670960064547</v>
       </c>
       <c r="C93" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7590795351679</v>
       </c>
       <c r="D93" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626513270822</v>
       </c>
       <c r="E93" t="n">
-        <v>273.5025634765625</v>
+        <v>278.856689453125</v>
       </c>
       <c r="F93" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>272.7670960064547</v>
+        <v>280.092280601724</v>
       </c>
       <c r="C94" t="n">
-        <v>280.7590795351679</v>
+        <v>287.7704613201907</v>
       </c>
       <c r="D94" t="n">
-        <v>270.4626513270822</v>
+        <v>278.9939996743944</v>
       </c>
       <c r="E94" t="n">
-        <v>278.856689453125</v>
+        <v>287.5057067871094</v>
       </c>
       <c r="F94" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>280.0923103323967</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C95" t="n">
-        <v>287.7704918658715</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D95" t="n">
-        <v>278.994029288489</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E95" t="n">
-        <v>287.5057373046875</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F95" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>288.3000088357305</v>
+        <v>284.3775473228927</v>
       </c>
       <c r="C96" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050317012176</v>
       </c>
       <c r="D96" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7394843208789</v>
       </c>
       <c r="E96" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124572753906</v>
       </c>
       <c r="F96" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>284.3775473228927</v>
+        <v>285.2503388393621</v>
       </c>
       <c r="C97" t="n">
-        <v>284.5050317012176</v>
+        <v>285.2503388393621</v>
       </c>
       <c r="D97" t="n">
-        <v>280.7394843208789</v>
+        <v>281.3278894670919</v>
       </c>
       <c r="E97" t="n">
-        <v>282.6124572753906</v>
+        <v>284.3089294433594</v>
       </c>
       <c r="F97" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>285.2503082207336</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C98" t="n">
-        <v>285.2503082207336</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D98" t="n">
-        <v>281.3278592694971</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E98" t="n">
-        <v>284.3088989257812</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F98" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C99" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D99" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E99" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F99" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7288152602706</v>
       </c>
       <c r="C100" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9249197733898</v>
       </c>
       <c r="D100" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5304229488273</v>
       </c>
       <c r="E100" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387634277344</v>
       </c>
       <c r="F100" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>276.7288152602706</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C101" t="n">
-        <v>276.9249197733898</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D101" t="n">
-        <v>266.5304229488273</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E101" t="n">
-        <v>268.6387634277344</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F101" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C102" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D102" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E102" t="n">
-        <v>278.6900024414062</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F102" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>281.4161285575944</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C103" t="n">
-        <v>289.5355972025459</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D103" t="n">
-        <v>279.7000570330196</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E103" t="n">
-        <v>281.1023254394531</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F103" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C104" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D104" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E104" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F104" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C105" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D105" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E105" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F105" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>283.3871388529354</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C106" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D106" t="n">
-        <v>278.8468991181569</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E106" t="n">
-        <v>283.6028747558594</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F106" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265998459625</v>
       </c>
       <c r="C107" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406467283754</v>
       </c>
       <c r="D107" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807753649725</v>
       </c>
       <c r="E107" t="n">
-        <v>286.2995300292969</v>
+        <v>283.1714172363281</v>
       </c>
       <c r="F107" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>284.4265998459625</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C108" t="n">
-        <v>285.7406467283754</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D108" t="n">
-        <v>281.1807753649725</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E108" t="n">
-        <v>283.1714172363281</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F108" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,25 +3251,25 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C109" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D109" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E109" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F109" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3277,25 +3277,25 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C110" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D110" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E110" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F110" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G110" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C111" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D111" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E111" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F111" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>279.0580549356083</v>
+        <v>281.4297838763166</v>
       </c>
       <c r="C112" t="n">
-        <v>282.8528771272727</v>
+        <v>284.177078134999</v>
       </c>
       <c r="D112" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039671765164</v>
       </c>
       <c r="E112" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907104492188</v>
       </c>
       <c r="F112" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>281.4297838763166</v>
+        <v>274.7888344130931</v>
       </c>
       <c r="C113" t="n">
-        <v>284.177078134999</v>
+        <v>279.5521380386192</v>
       </c>
       <c r="D113" t="n">
-        <v>273.039671765164</v>
+        <v>274.5417754718342</v>
       </c>
       <c r="E113" t="n">
-        <v>273.7907104492188</v>
+        <v>278.7714233398438</v>
       </c>
       <c r="F113" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>274.7888344130931</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C114" t="n">
-        <v>279.5521380386192</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D114" t="n">
-        <v>274.5417754718342</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E114" t="n">
-        <v>278.7714233398438</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F114" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>280.6392236042361</v>
+        <v>284.41428667964</v>
       </c>
       <c r="C115" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902898411239</v>
       </c>
       <c r="D115" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4891167908925</v>
       </c>
       <c r="E115" t="n">
-        <v>282.1314392089844</v>
+        <v>284.18701171875</v>
       </c>
       <c r="F115" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>284.41428667964</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C116" t="n">
-        <v>285.5902898411239</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D116" t="n">
-        <v>281.4891167908925</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E116" t="n">
-        <v>284.18701171875</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F116" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589555118485</v>
       </c>
       <c r="C117" t="n">
-        <v>285.0072039222152</v>
+        <v>284.1671803923218</v>
       </c>
       <c r="D117" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7751962176443</v>
       </c>
       <c r="E117" t="n">
-        <v>280.9850769042969</v>
+        <v>277.1408386230469</v>
       </c>
       <c r="F117" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>280.6589555118485</v>
+        <v>275.7078960775263</v>
       </c>
       <c r="C118" t="n">
-        <v>284.1671803923218</v>
+        <v>279.7695608963037</v>
       </c>
       <c r="D118" t="n">
-        <v>276.7751962176443</v>
+        <v>271.7648448878931</v>
       </c>
       <c r="E118" t="n">
-        <v>277.1408386230469</v>
+        <v>272.347900390625</v>
       </c>
       <c r="F118" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>275.7078960775263</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C119" t="n">
-        <v>279.7695608963037</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D119" t="n">
-        <v>271.7648448878931</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E119" t="n">
-        <v>272.347900390625</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F119" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069856894997</v>
       </c>
       <c r="C120" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639393177099</v>
       </c>
       <c r="D120" t="n">
-        <v>265.9243614270812</v>
+        <v>264.44204492441</v>
       </c>
       <c r="E120" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768737792969</v>
       </c>
       <c r="F120" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>265.7069856894997</v>
+        <v>271.7648799566674</v>
       </c>
       <c r="C121" t="n">
-        <v>270.1639393177099</v>
+        <v>272.8321614881822</v>
       </c>
       <c r="D121" t="n">
-        <v>264.44204492441</v>
+        <v>263.9676840156166</v>
       </c>
       <c r="E121" t="n">
-        <v>269.0768737792969</v>
+        <v>267.3672180175781</v>
       </c>
       <c r="F121" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>271.7648799566674</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C122" t="n">
-        <v>272.8321614881822</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D122" t="n">
-        <v>263.9676840156166</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E122" t="n">
-        <v>267.3672180175781</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F122" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C123" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D123" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E123" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F123" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>264.3530902318651</v>
+        <v>257.1191907461688</v>
       </c>
       <c r="C124" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2438917467647</v>
       </c>
       <c r="D124" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505034942698</v>
       </c>
       <c r="E124" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102661132812</v>
       </c>
       <c r="F124" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>257.1191907461688</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C125" t="n">
-        <v>259.2438917467647</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D125" t="n">
-        <v>253.6505034942698</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E125" t="n">
-        <v>258.7102661132812</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F125" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C126" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D126" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E126" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F126" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867274922702</v>
       </c>
       <c r="C127" t="n">
-        <v>272.0613148441149</v>
+        <v>275.757318970375</v>
       </c>
       <c r="D127" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356586528844</v>
       </c>
       <c r="E127" t="n">
-        <v>270.7568664550781</v>
+        <v>273.9982604980469</v>
       </c>
       <c r="F127" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>269.0867274922702</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C128" t="n">
-        <v>275.757318970375</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D128" t="n">
-        <v>268.3356586528844</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E128" t="n">
-        <v>273.9982604980469</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F128" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C129" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D129" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E129" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F129" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3296014014268</v>
       </c>
       <c r="C130" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881914326393</v>
       </c>
       <c r="D130" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439367148364</v>
       </c>
       <c r="E130" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804321289062</v>
       </c>
       <c r="F130" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>308.3296014014268</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C131" t="n">
-        <v>309.2881914326393</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D131" t="n">
-        <v>301.2439367148364</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E131" t="n">
-        <v>302.3804321289062</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F131" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272561704691</v>
       </c>
       <c r="C132" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187701494722</v>
       </c>
       <c r="D132" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213715612747</v>
       </c>
       <c r="E132" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7498168945312</v>
       </c>
       <c r="F132" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>304.3272561704691</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C133" t="n">
-        <v>306.7187701494722</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D133" t="n">
-        <v>300.6213715612747</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E133" t="n">
-        <v>300.7498168945312</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F133" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C134" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D134" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E134" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F134" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C135" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D135" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E135" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F135" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2943017295384</v>
       </c>
       <c r="C136" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8618187748353</v>
       </c>
       <c r="D136" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4265214430497</v>
       </c>
       <c r="E136" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6778259277344</v>
       </c>
       <c r="F136" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>311.2943017295384</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C137" t="n">
-        <v>314.8618187748353</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D137" t="n">
-        <v>309.4265214430497</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E137" t="n">
-        <v>312.6778259277344</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F137" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>316.2848676157387</v>
+        <v>320.37616900858</v>
       </c>
       <c r="C138" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719258918635</v>
       </c>
       <c r="D138" t="n">
-        <v>313.4091278691752</v>
+        <v>316.35404203196</v>
       </c>
       <c r="E138" t="n">
-        <v>320.8110046386719</v>
+        <v>319.6745300292969</v>
       </c>
       <c r="F138" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>320.37616900858</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C139" t="n">
-        <v>321.5719258918635</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D139" t="n">
-        <v>316.35404203196</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E139" t="n">
-        <v>319.6745300292969</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F139" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7521876325058</v>
       </c>
       <c r="C140" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418314545246</v>
       </c>
       <c r="D140" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931290879458</v>
       </c>
       <c r="E140" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611145019531</v>
       </c>
       <c r="F140" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>346.7521876325058</v>
+        <v>350.5074994974842</v>
       </c>
       <c r="C141" t="n">
-        <v>354.3418314545246</v>
+        <v>352.6519846563255</v>
       </c>
       <c r="D141" t="n">
-        <v>344.9931290879458</v>
+        <v>346.3766807003688</v>
       </c>
       <c r="E141" t="n">
-        <v>349.3611145019531</v>
+        <v>350.388916015625</v>
       </c>
       <c r="F141" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>350.5074994974842</v>
+        <v>352.2961666917061</v>
       </c>
       <c r="C142" t="n">
-        <v>352.6519846563255</v>
+        <v>354.0651171980212</v>
       </c>
       <c r="D142" t="n">
-        <v>346.3766807003688</v>
+        <v>347.2561882957746</v>
       </c>
       <c r="E142" t="n">
-        <v>350.388916015625</v>
+        <v>350.7446594238281</v>
       </c>
       <c r="F142" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>352.2961666917061</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C143" t="n">
-        <v>354.0651171980212</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D143" t="n">
-        <v>347.2561882957746</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E143" t="n">
-        <v>350.7446594238281</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F143" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C144" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D144" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E144" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F144" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C145" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D145" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E145" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F145" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C146" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D146" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E146" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F146" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C147" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D147" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E147" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F147" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C148" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D148" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E148" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F148" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216408565838</v>
       </c>
       <c r="C149" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260893018678</v>
       </c>
       <c r="D149" t="n">
-        <v>360.360183242299</v>
+        <v>357.5536224796683</v>
       </c>
       <c r="E149" t="n">
-        <v>366.388427734375</v>
+        <v>359.5893859863281</v>
       </c>
       <c r="F149" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>366.1216408565838</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C150" t="n">
-        <v>367.4260893018678</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D150" t="n">
-        <v>357.5536224796683</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E150" t="n">
-        <v>359.5893859863281</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F150" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C151" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D151" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E151" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F151" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="C152" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="D152" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138324799484</v>
       </c>
       <c r="E152" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098571777344</v>
       </c>
       <c r="F152" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>367.6138324799484</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C153" t="n">
-        <v>375.5098571777344</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D153" t="n">
-        <v>367.6138324799484</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E153" t="n">
-        <v>375.5098571777344</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F153" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3460853480032</v>
       </c>
       <c r="C154" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7446883171237</v>
       </c>
       <c r="D154" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5159708878205</v>
       </c>
       <c r="E154" t="n">
-        <v>379.9173889160156</v>
+        <v>391.726806640625</v>
       </c>
       <c r="F154" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>378.3460853480032</v>
+        <v>391.835521582727</v>
       </c>
       <c r="C155" t="n">
-        <v>392.7446883171237</v>
+        <v>399.3955199396844</v>
       </c>
       <c r="D155" t="n">
-        <v>377.5159708878205</v>
+        <v>388.3766960454267</v>
       </c>
       <c r="E155" t="n">
-        <v>391.726806640625</v>
+        <v>396.4407043457031</v>
       </c>
       <c r="F155" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>391.835521582727</v>
+        <v>396.2825841810375</v>
       </c>
       <c r="C156" t="n">
-        <v>399.3955199396844</v>
+        <v>397.1719904330225</v>
       </c>
       <c r="D156" t="n">
-        <v>388.3766960454267</v>
+        <v>391.3414048271592</v>
       </c>
       <c r="E156" t="n">
-        <v>396.4407043457031</v>
+        <v>394.3950500488281</v>
       </c>
       <c r="F156" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>396.2825841810375</v>
+        <v>389.6613628183419</v>
       </c>
       <c r="C157" t="n">
-        <v>397.1719904330225</v>
+        <v>392.9522049122001</v>
       </c>
       <c r="D157" t="n">
-        <v>391.3414048271592</v>
+        <v>385.6590199026367</v>
       </c>
       <c r="E157" t="n">
-        <v>394.3950500488281</v>
+        <v>389.2166748046875</v>
       </c>
       <c r="F157" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>389.6613628183419</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C158" t="n">
-        <v>392.9522049122001</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D158" t="n">
-        <v>385.6590199026367</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E158" t="n">
-        <v>389.2166748046875</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F158" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119880990537</v>
       </c>
       <c r="C159" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432754242469</v>
       </c>
       <c r="D159" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512904411622</v>
       </c>
       <c r="E159" t="n">
-        <v>386.5286865234375</v>
+        <v>384.6609191894531</v>
       </c>
       <c r="F159" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>385.4119880990537</v>
+        <v>384.9672452573303</v>
       </c>
       <c r="C160" t="n">
-        <v>390.3432754242469</v>
+        <v>388.7522052741927</v>
       </c>
       <c r="D160" t="n">
-        <v>382.9512904411622</v>
+        <v>376.2213825216763</v>
       </c>
       <c r="E160" t="n">
-        <v>384.6609191894531</v>
+        <v>378.790771484375</v>
       </c>
       <c r="F160" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>384.9672452573303</v>
+        <v>376.6364522760421</v>
       </c>
       <c r="C161" t="n">
-        <v>388.7522052741927</v>
+        <v>381.5677396470687</v>
       </c>
       <c r="D161" t="n">
-        <v>376.2213825216763</v>
+        <v>376.0632887376697</v>
       </c>
       <c r="E161" t="n">
-        <v>378.790771484375</v>
+        <v>377.98046875</v>
       </c>
       <c r="F161" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>376.6364522760421</v>
+        <v>377.4270309363715</v>
       </c>
       <c r="C162" t="n">
-        <v>381.5677396470687</v>
+        <v>385.9456187280053</v>
       </c>
       <c r="D162" t="n">
-        <v>376.0632887376697</v>
+        <v>376.5277327371266</v>
       </c>
       <c r="E162" t="n">
-        <v>377.98046875</v>
+        <v>383.8999633789062</v>
       </c>
       <c r="F162" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>377.4270309363715</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C163" t="n">
-        <v>385.9456187280053</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D163" t="n">
-        <v>376.5277327371266</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E163" t="n">
-        <v>383.8999633789062</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F163" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C164" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D164" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E164" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F164" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312827021371</v>
       </c>
       <c r="C165" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6807151570288</v>
       </c>
       <c r="D165" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783391116702</v>
       </c>
       <c r="E165" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298767089844</v>
       </c>
       <c r="F165" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>380.4312827021371</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C166" t="n">
-        <v>384.6807151570288</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D166" t="n">
-        <v>376.4783391116702</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E166" t="n">
-        <v>378.0298767089844</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F166" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C167" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D167" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E167" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F167" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C168" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D168" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E168" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F168" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C169" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D169" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E169" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F169" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119603627872</v>
       </c>
       <c r="C170" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6580885443842</v>
       </c>
       <c r="D170" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2340851575979</v>
       </c>
       <c r="E170" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058471679688</v>
       </c>
       <c r="F170" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>385.4119603627872</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C171" t="n">
-        <v>396.6580885443842</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D171" t="n">
-        <v>385.2340851575979</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E171" t="n">
-        <v>391.8058471679688</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F171" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C172" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D172" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E172" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F172" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>392.4580996989546</v>
+        <v>405.166788512205</v>
       </c>
       <c r="C173" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="D173" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6467992699509</v>
       </c>
       <c r="E173" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1413879394531</v>
       </c>
       <c r="F173" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>405.166788512205</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C174" t="n">
-        <v>408.1413879394531</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D174" t="n">
-        <v>402.6467992699509</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E174" t="n">
-        <v>408.1413879394531</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F174" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C175" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D175" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E175" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F175" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C176" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D176" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E176" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F176" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C177" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D177" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E177" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F177" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C178" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D178" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E178" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F178" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G178" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C179" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D179" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E179" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F179" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C180" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D180" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E180" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F180" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C181" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D181" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E181" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F181" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C182" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D182" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E182" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F182" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C183" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D183" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E183" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F183" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C184" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D184" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E184" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F184" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C185" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D185" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E185" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F185" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C186" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D186" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E186" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F186" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C187" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D187" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E187" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F187" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C188" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D188" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E188" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F188" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C189" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D189" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E189" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F189" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C190" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D190" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E190" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F190" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C191" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D191" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E191" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F191" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C192" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D192" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E192" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F192" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C193" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D193" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E193" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F193" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C194" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D194" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E194" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F194" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C195" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D195" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E195" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F195" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C196" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D196" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E196" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F196" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C197" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D197" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E197" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F197" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C198" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D198" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E198" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F198" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C199" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D199" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E199" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F199" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C200" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D200" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E200" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F200" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C201" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D201" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E201" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F201" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C202" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D202" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E202" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F202" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C203" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D203" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E203" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F203" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C204" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D204" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E204" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F204" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C205" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D205" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E205" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F205" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C206" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D206" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E206" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F206" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C207" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D207" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E207" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F207" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C208" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D208" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E208" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F208" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C209" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D209" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E209" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F209" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C210" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D210" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E210" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F210" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C211" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D211" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E211" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F211" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C212" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D212" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E212" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F212" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C213" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D213" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E213" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F213" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C214" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D214" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E214" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F214" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C215" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D215" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E215" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F215" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C216" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D216" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E216" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F216" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C217" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D217" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E217" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F217" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C218" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D218" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E218" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F218" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C219" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D219" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E219" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F219" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C220" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D220" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E220" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F220" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C221" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D221" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E221" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F221" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C222" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D222" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E222" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F222" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C223" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D223" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E223" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F223" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C224" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D224" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E224" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F224" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C225" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D225" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E225" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F225" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C226" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D226" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E226" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F226" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C227" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D227" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E227" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F227" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C228" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D228" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E228" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F228" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C229" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D229" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E229" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F229" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C230" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D230" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E230" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F230" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C231" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D231" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E231" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F231" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C232" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D232" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E232" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F232" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C233" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D233" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E233" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F233" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C234" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D234" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E234" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F234" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C235" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D235" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E235" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F235" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C236" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D236" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E236" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F236" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C237" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D237" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E237" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F237" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C238" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D238" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E238" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F238" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C239" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D239" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E239" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F239" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C240" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E240" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F240" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G240" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C241" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D241" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E241" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F241" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C242" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D242" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E242" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F242" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C243" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D243" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E243" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F243" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>375.2900085449219</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C244" t="n">
-        <v>378.489990234375</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D244" t="n">
-        <v>372.4200134277344</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E244" t="n">
-        <v>376.8999938964844</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F244" t="n">
-        <v>8606300</v>
+        <v>5712300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>377.8699951171875</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>378.9500122070312</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="D245" t="n">
-        <v>373.8200073242188</v>
+        <v>372.4100036621094</v>
       </c>
       <c r="E245" t="n">
-        <v>377.5599975585938</v>
+        <v>372.9500122070312</v>
       </c>
       <c r="F245" t="n">
-        <v>5712300</v>
+        <v>4495000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>381.3900146484375</v>
+        <v>370.8900146484375</v>
       </c>
       <c r="C246" t="n">
-        <v>381.3900146484375</v>
+        <v>372.6099853515625</v>
       </c>
       <c r="D246" t="n">
-        <v>372.4100036621094</v>
+        <v>366</v>
       </c>
       <c r="E246" t="n">
-        <v>372.9500122070312</v>
+        <v>371.2900085449219</v>
       </c>
       <c r="F246" t="n">
-        <v>4495000</v>
+        <v>3859300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>370.8900146484375</v>
+        <v>371.9200134277344</v>
       </c>
       <c r="C247" t="n">
-        <v>372.6099853515625</v>
+        <v>375.2799987792969</v>
       </c>
       <c r="D247" t="n">
-        <v>366</v>
+        <v>368.5</v>
       </c>
       <c r="E247" t="n">
-        <v>371.2900085449219</v>
+        <v>375.010009765625</v>
       </c>
       <c r="F247" t="n">
-        <v>3859300</v>
+        <v>4651000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>371.9200134277344</v>
+        <v>375.9500122070312</v>
       </c>
       <c r="C248" t="n">
-        <v>375.2799987792969</v>
+        <v>379.1700134277344</v>
       </c>
       <c r="D248" t="n">
-        <v>368.5</v>
+        <v>371.1700134277344</v>
       </c>
       <c r="E248" t="n">
-        <v>375.010009765625</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="F248" t="n">
-        <v>4651000</v>
+        <v>4077400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>375.9500122070312</v>
+        <v>376.3599853515625</v>
       </c>
       <c r="C249" t="n">
-        <v>379.1700134277344</v>
+        <v>380.9800109863281</v>
       </c>
       <c r="D249" t="n">
-        <v>371.1700134277344</v>
+        <v>374.5599975585938</v>
       </c>
       <c r="E249" t="n">
-        <v>376.5899963378906</v>
+        <v>377.8299865722656</v>
       </c>
       <c r="F249" t="n">
-        <v>4077400</v>
+        <v>4677100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>376.3599853515625</v>
+        <v>374.8800048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>380.9800109863281</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>374.5599975585938</v>
+        <v>371.3299865722656</v>
       </c>
       <c r="E250" t="n">
-        <v>377.8299865722656</v>
+        <v>374.9400024414062</v>
       </c>
       <c r="F250" t="n">
-        <v>4677100</v>
+        <v>3284700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>374.8800048828125</v>
+        <v>374.9299926757812</v>
       </c>
       <c r="C251" t="n">
-        <v>376.5899963378906</v>
+        <v>374.9299926757812</v>
       </c>
       <c r="D251" t="n">
-        <v>371.3299865722656</v>
+        <v>365.7200012207031</v>
       </c>
       <c r="E251" t="n">
-        <v>374.9400024414062</v>
+        <v>367.0799865722656</v>
       </c>
       <c r="F251" t="n">
-        <v>3284700</v>
+        <v>4788300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>374.9299926757812</v>
+        <v>367.989990234375</v>
       </c>
       <c r="C252" t="n">
-        <v>374.9299926757812</v>
+        <v>371.8599853515625</v>
       </c>
       <c r="D252" t="n">
-        <v>365.7200012207031</v>
+        <v>362.6000061035156</v>
       </c>
       <c r="E252" t="n">
-        <v>367.0799865722656</v>
+        <v>365.2000122070312</v>
       </c>
       <c r="F252" t="n">
-        <v>4788300</v>
+        <v>3940700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,34 +10530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="D2" t="n">
         <v>367.08</v>
       </c>
-      <c r="D2" t="n">
-        <v>374.94</v>
-      </c>
       <c r="E2" t="n">
-        <v>374.93</v>
+        <v>367.99</v>
       </c>
       <c r="F2" t="n">
-        <v>374.05</v>
+        <v>371.8599</v>
       </c>
       <c r="G2" t="n">
-        <v>365.76</v>
+        <v>362.6</v>
       </c>
       <c r="H2" t="n">
-        <v>4782910</v>
+        <v>3933201</v>
       </c>
       <c r="I2" t="n">
-        <v>4930261</v>
+        <v>4927314</v>
       </c>
       <c r="J2" t="n">
-        <v>329489088512</v>
+        <v>327801634816</v>
       </c>
       <c r="K2" t="n">
-        <v>23.591259</v>
+        <v>23.470438</v>
       </c>
       <c r="L2" t="n">
-        <v>16.235157</v>
+        <v>16.15201</v>
       </c>
       <c r="M2" t="n">
         <v>15.56</v>
@@ -10572,7 +10572,7 @@
         <v>0.622</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>0.03135</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.3744862</v>
+        <v>3.3572042</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10608,7 +10608,7 @@
         <v>450525986816</v>
       </c>
       <c r="AC2" t="n">
-        <v>378851131392</v>
+        <v>377163644928</v>
       </c>
       <c r="AD2" t="n">
         <v>26680999936</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:02:59</t>
+          <t>2026-10-02 19:38:41</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>338.2824047650262</v>
+        <v>347.9840761494036</v>
       </c>
       <c r="C2" t="n">
-        <v>345.87033541468</v>
+        <v>358.4552554876992</v>
       </c>
       <c r="D2" t="n">
-        <v>335.7108637419195</v>
+        <v>347.3606614365734</v>
       </c>
       <c r="E2" t="n">
-        <v>344.5456237792969</v>
+        <v>350.8575744628906</v>
       </c>
       <c r="F2" t="n">
-        <v>8564200</v>
+        <v>13494800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>347.9840458817623</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C3" t="n">
-        <v>358.4552243092751</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D3" t="n">
-        <v>347.3606312231566</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E3" t="n">
-        <v>350.8575439453125</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F3" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C4" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D4" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E4" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F4" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C5" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D5" t="n">
-        <v>348.77305405812</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E5" t="n">
-        <v>354.2278137207031</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F5" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>357.4129705346734</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C6" t="n">
-        <v>364.9132683871306</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D6" t="n">
-        <v>356.3122744619989</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E6" t="n">
-        <v>360.325439453125</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F6" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>362.8580018323341</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="C7" t="n">
-        <v>366.4620474561767</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="D7" t="n">
-        <v>356.5850326317519</v>
+        <v>343.3669828865441</v>
       </c>
       <c r="E7" t="n">
-        <v>358.1532897949219</v>
+        <v>345.3053588867188</v>
       </c>
       <c r="F7" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>359.8189245088024</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C8" t="n">
-        <v>359.8189245088024</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D8" t="n">
-        <v>343.3670132328114</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E8" t="n">
-        <v>345.3053894042969</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F8" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>345.5391423923842</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C9" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D9" t="n">
-        <v>344.155989405705</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E9" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F9" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685366633683</v>
       </c>
       <c r="C10" t="n">
-        <v>352.9322890785681</v>
+        <v>354.7732481537828</v>
       </c>
       <c r="D10" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203451149501</v>
       </c>
       <c r="E10" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828674316406</v>
       </c>
       <c r="F10" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>350.0685974010841</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C11" t="n">
-        <v>354.7733097077772</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D11" t="n">
-        <v>346.6204052543966</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E11" t="n">
-        <v>351.7829284667969</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F11" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>352.4550184254314</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C12" t="n">
-        <v>352.6108721017735</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D12" t="n">
-        <v>345.2079859687916</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E12" t="n">
-        <v>347.4191284179688</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F12" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406427804422</v>
       </c>
       <c r="C13" t="n">
-        <v>349.0945029745603</v>
+        <v>356.088306176199</v>
       </c>
       <c r="D13" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373588311709</v>
       </c>
       <c r="E13" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265808105469</v>
       </c>
       <c r="F13" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>349.2406127602151</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C14" t="n">
-        <v>356.0882755673564</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D14" t="n">
-        <v>348.2373288971846</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E14" t="n">
-        <v>355.0265502929688</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F14" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5199811240022</v>
       </c>
       <c r="C15" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589519694893</v>
       </c>
       <c r="D15" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7145736403219</v>
       </c>
       <c r="E15" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140441894531</v>
       </c>
       <c r="F15" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>354.5200118501019</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C16" t="n">
-        <v>354.5589826989666</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D16" t="n">
-        <v>348.7146038632694</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E16" t="n">
-        <v>352.1140747070312</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F16" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>346.3573617095742</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C17" t="n">
-        <v>352.883596703336</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D17" t="n">
-        <v>344.4677065470185</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E17" t="n">
-        <v>351.10107421875</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F17" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>351.9972042484119</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C18" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D18" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E18" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F18" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063444379755</v>
       </c>
       <c r="C19" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180517731913</v>
       </c>
       <c r="D19" t="n">
-        <v>352.0264145317695</v>
+        <v>349.3282643556941</v>
       </c>
       <c r="E19" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2993774414062</v>
       </c>
       <c r="F19" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>370.8063444379755</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C20" t="n">
-        <v>371.1180517731913</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D20" t="n">
-        <v>349.3282643556941</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E20" t="n">
-        <v>358.2993774414062</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F20" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>354.8317550345645</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C21" t="n">
-        <v>356.6532485328659</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D21" t="n">
-        <v>344.7015033078588</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E21" t="n">
-        <v>346.0457153320312</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F21" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>338.5064329398476</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C22" t="n">
-        <v>345.3443756361395</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D22" t="n">
-        <v>334.6881218381804</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E22" t="n">
-        <v>335.8082885742188</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F22" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>335.4576347488759</v>
+        <v>330.3340313465691</v>
       </c>
       <c r="C23" t="n">
-        <v>337.298598712068</v>
+        <v>331.8633175824834</v>
       </c>
       <c r="D23" t="n">
-        <v>328.3761763650699</v>
+        <v>318.1290216159704</v>
       </c>
       <c r="E23" t="n">
-        <v>332.7010192871094</v>
+        <v>325.1325378417969</v>
       </c>
       <c r="F23" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>330.3340623523696</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C24" t="n">
-        <v>331.8633487318257</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D24" t="n">
-        <v>318.1290514761847</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E24" t="n">
-        <v>325.132568359375</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F24" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>319.1323138584834</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C25" t="n">
-        <v>327.7722492229931</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D25" t="n">
-        <v>318.7134738391959</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E25" t="n">
-        <v>322.2492980957031</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F25" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>317.8367876317881</v>
+        <v>320.3888464018165</v>
       </c>
       <c r="C26" t="n">
-        <v>321.6453780396488</v>
+        <v>323.7493462451443</v>
       </c>
       <c r="D26" t="n">
-        <v>315.8107493995538</v>
+        <v>313.1125938905139</v>
       </c>
       <c r="E26" t="n">
-        <v>319.2394409179688</v>
+        <v>313.2197265625</v>
       </c>
       <c r="F26" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>320.3888776178953</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C27" t="n">
-        <v>323.7493777886428</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D27" t="n">
-        <v>313.1126243976539</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E27" t="n">
-        <v>313.2197570800781</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F27" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>311.3690195806419</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C28" t="n">
-        <v>316.1321727657366</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D28" t="n">
-        <v>306.011672436569</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E28" t="n">
-        <v>315.8009948730469</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F28" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>311.6904400245728</v>
+        <v>314.9145846167937</v>
       </c>
       <c r="C29" t="n">
-        <v>315.8399583185172</v>
+        <v>319.3563099222018</v>
       </c>
       <c r="D29" t="n">
-        <v>308.9436046905141</v>
+        <v>311.5833055007609</v>
       </c>
       <c r="E29" t="n">
-        <v>313.2391967773438</v>
+        <v>318.9569702148438</v>
       </c>
       <c r="F29" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>314.9146147475993</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C30" t="n">
-        <v>319.3563404779885</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D30" t="n">
-        <v>311.583335312832</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E30" t="n">
-        <v>318.9570007324219</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F30" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>319.9310727655453</v>
+        <v>329.5742822700864</v>
       </c>
       <c r="C31" t="n">
-        <v>334.2692843856479</v>
+        <v>330.2366380969722</v>
       </c>
       <c r="D31" t="n">
-        <v>318.5965811998377</v>
+        <v>322.6973986104767</v>
       </c>
       <c r="E31" t="n">
-        <v>330.265869140625</v>
+        <v>323.8954772949219</v>
       </c>
       <c r="F31" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>329.5742822700864</v>
+        <v>318.4699396678824</v>
       </c>
       <c r="C32" t="n">
-        <v>330.2366380969722</v>
+        <v>319.6972389495053</v>
       </c>
       <c r="D32" t="n">
-        <v>322.6973986104767</v>
+        <v>312.177470693811</v>
       </c>
       <c r="E32" t="n">
-        <v>323.8954772949219</v>
+        <v>313.5119323730469</v>
       </c>
       <c r="F32" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>318.4699706680781</v>
+        <v>312.2846372515878</v>
       </c>
       <c r="C33" t="n">
-        <v>319.6972700691676</v>
+        <v>319.3758154633895</v>
       </c>
       <c r="D33" t="n">
-        <v>312.1775010814912</v>
+        <v>311.1449703398488</v>
       </c>
       <c r="E33" t="n">
-        <v>313.511962890625</v>
+        <v>312.2066955566406</v>
       </c>
       <c r="F33" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>312.2846677767845</v>
+        <v>308.7877447280039</v>
       </c>
       <c r="C34" t="n">
-        <v>319.3758466817346</v>
+        <v>309.2650261221254</v>
       </c>
       <c r="D34" t="n">
-        <v>311.1450007536453</v>
+        <v>300.7614447812334</v>
       </c>
       <c r="E34" t="n">
-        <v>312.2067260742188</v>
+        <v>305.4466857910156</v>
       </c>
       <c r="F34" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>308.7877755793916</v>
+        <v>305.7876123248052</v>
       </c>
       <c r="C35" t="n">
-        <v>309.2650570211989</v>
+        <v>306.8298669435948</v>
       </c>
       <c r="D35" t="n">
-        <v>300.761474830703</v>
+        <v>296.6314254151897</v>
       </c>
       <c r="E35" t="n">
-        <v>305.4467163085938</v>
+        <v>301.0731506347656</v>
       </c>
       <c r="F35" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>305.7876433202538</v>
+        <v>302.7485484827002</v>
       </c>
       <c r="C36" t="n">
-        <v>306.829898044689</v>
+        <v>306.5863594589355</v>
       </c>
       <c r="D36" t="n">
-        <v>296.6314554825427</v>
+        <v>301.9595597530421</v>
       </c>
       <c r="E36" t="n">
-        <v>301.0731811523438</v>
+        <v>303.4596252441406</v>
       </c>
       <c r="F36" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>302.7485789287686</v>
+        <v>303.8200730602589</v>
       </c>
       <c r="C37" t="n">
-        <v>306.5863902909554</v>
+        <v>315.4406405438549</v>
       </c>
       <c r="D37" t="n">
-        <v>301.9595901197654</v>
+        <v>303.3622621419303</v>
       </c>
       <c r="E37" t="n">
-        <v>303.4596557617188</v>
+        <v>311.6710205078125</v>
       </c>
       <c r="F37" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>303.8200433114142</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C38" t="n">
-        <v>315.4406096571707</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D38" t="n">
-        <v>303.3622324379126</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E38" t="n">
-        <v>311.6709899902344</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F38" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>316.1127181611407</v>
+        <v>312.791122346815</v>
       </c>
       <c r="C39" t="n">
-        <v>317.3984886748711</v>
+        <v>319.4926808974158</v>
       </c>
       <c r="D39" t="n">
-        <v>309.3819381150768</v>
+        <v>312.5768272864395</v>
       </c>
       <c r="E39" t="n">
-        <v>310.7748413085938</v>
+        <v>317.8172912597656</v>
       </c>
       <c r="F39" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>312.7911824167217</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C40" t="n">
-        <v>319.4927422543219</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D40" t="n">
-        <v>312.576887315192</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E40" t="n">
-        <v>317.8173522949219</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F40" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>318.1192531852973</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C41" t="n">
-        <v>326.4962014988301</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D41" t="n">
-        <v>317.4374268746658</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E41" t="n">
-        <v>321.1583251953125</v>
+        <v>321.216796875</v>
       </c>
       <c r="F41" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>323.0675099624138</v>
+        <v>318.6744960548122</v>
       </c>
       <c r="C42" t="n">
-        <v>323.4473791003546</v>
+        <v>321.4992731766471</v>
       </c>
       <c r="D42" t="n">
-        <v>320.3596158297967</v>
+        <v>314.6516105859225</v>
       </c>
       <c r="E42" t="n">
-        <v>321.2167663574219</v>
+        <v>314.8269348144531</v>
       </c>
       <c r="F42" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>318.6745269453515</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C43" t="n">
-        <v>321.4993043410047</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D43" t="n">
-        <v>314.6516410865056</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E43" t="n">
-        <v>314.8269653320312</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F43" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C44" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D44" t="n">
-        <v>314.4275769247672</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E44" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F44" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>317.5446185401456</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C45" t="n">
-        <v>332.5549367443995</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D45" t="n">
-        <v>316.5803054378969</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E45" t="n">
-        <v>330.8990173339844</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F45" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>330.5970181401507</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C46" t="n">
-        <v>332.4087910072381</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D46" t="n">
-        <v>320.1940311163831</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E46" t="n">
-        <v>324.8403015136719</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F46" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>326.3111546998924</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C47" t="n">
-        <v>327.0027312119329</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D47" t="n">
-        <v>319.9894943793851</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E47" t="n">
-        <v>322.3272399902344</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F47" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1665,25 +1665,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894639081939</v>
       </c>
       <c r="C48" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0325801360812</v>
       </c>
       <c r="D48" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278299745985</v>
       </c>
       <c r="E48" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261108398438</v>
       </c>
       <c r="F48" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>316.894669558022</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C49" t="n">
-        <v>320.0326109139432</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D49" t="n">
-        <v>316.2278603865539</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E49" t="n">
-        <v>317.3261413574219</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F49" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C50" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D50" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E50" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F50" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566703772105</v>
       </c>
       <c r="C51" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2916615784552</v>
       </c>
       <c r="D51" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291859826966</v>
       </c>
       <c r="E51" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2125244140625</v>
       </c>
       <c r="F51" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>330.9566402470831</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C52" t="n">
-        <v>338.291630780554</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D52" t="n">
-        <v>330.8291558641754</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E52" t="n">
-        <v>335.2124938964844</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F52" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C53" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D53" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E53" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F53" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>333.8200517828203</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C54" t="n">
-        <v>334.3789780492049</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D54" t="n">
-        <v>324.6120879365693</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E54" t="n">
-        <v>327.7206420898438</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F54" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>327.1420632206801</v>
+        <v>322.552799383924</v>
       </c>
       <c r="C55" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785647692876</v>
       </c>
       <c r="D55" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773440842135</v>
       </c>
       <c r="E55" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781372070312</v>
       </c>
       <c r="F55" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>322.5527687928765</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C56" t="n">
-        <v>323.7785340619881</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D56" t="n">
-        <v>318.2773138986521</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E56" t="n">
-        <v>321.7781066894531</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F56" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>321.6996588106788</v>
+        <v>316.6397026430911</v>
       </c>
       <c r="C57" t="n">
-        <v>328.112871433911</v>
+        <v>323.4059214629105</v>
       </c>
       <c r="D57" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139372798661</v>
       </c>
       <c r="E57" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558959960938</v>
       </c>
       <c r="F57" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>316.639672337624</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C58" t="n">
-        <v>323.4058905098511</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D58" t="n">
-        <v>315.4139070917166</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E58" t="n">
-        <v>318.8558654785156</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F58" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C59" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D59" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E59" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F59" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C60" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D60" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E60" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F60" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C61" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D61" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E61" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F61" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C62" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D62" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E62" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F62" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C63" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D63" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E63" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F63" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C64" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D64" t="n">
-        <v>323.484378234348</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E64" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F64" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>324.4845927435845</v>
+        <v>328.9464075107404</v>
       </c>
       <c r="C65" t="n">
-        <v>333.6631391122548</v>
+        <v>340.2136332445062</v>
       </c>
       <c r="D65" t="n">
-        <v>321.1505170252981</v>
+        <v>327.377421847917</v>
       </c>
       <c r="E65" t="n">
-        <v>329.8779602050781</v>
+        <v>335.3890075683594</v>
       </c>
       <c r="F65" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>328.9463775793847</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C66" t="n">
-        <v>340.2136022879278</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D66" t="n">
-        <v>327.3773920593259</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E66" t="n">
-        <v>335.3889770507812</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F66" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>341.5962793505171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C67" t="n">
-        <v>345.7736671379334</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D67" t="n">
-        <v>338.4288910460567</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E67" t="n">
-        <v>342.2042541503906</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F67" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C68" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D68" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E68" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F68" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>334.3985942399352</v>
+        <v>340.5176266555306</v>
       </c>
       <c r="C69" t="n">
-        <v>341.1549971070486</v>
+        <v>342.2925325530242</v>
       </c>
       <c r="D69" t="n">
-        <v>334.1926441199842</v>
+        <v>335.840116682576</v>
       </c>
       <c r="E69" t="n">
-        <v>340.1253662109375</v>
+        <v>337.31103515625</v>
       </c>
       <c r="F69" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>340.5175958478422</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C70" t="n">
-        <v>342.2925015847546</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D70" t="n">
-        <v>335.8400862980764</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E70" t="n">
-        <v>337.3110046386719</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F70" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C71" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D71" t="n">
-        <v>327.465664861477</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E71" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F71" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>334.8790829701986</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C72" t="n">
-        <v>335.2124875436862</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D72" t="n">
-        <v>326.3967930031341</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E72" t="n">
-        <v>327.4558410644531</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F72" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C73" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D73" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E73" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F73" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C74" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D74" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E74" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F74" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C75" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D75" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E75" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F75" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>321.0524690830655</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C76" t="n">
-        <v>333.3003373667196</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D76" t="n">
-        <v>320.1699239761241</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E76" t="n">
-        <v>331.8686218261719</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F76" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489839349073</v>
       </c>
       <c r="C77" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683609450301</v>
       </c>
       <c r="D77" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0469292856779</v>
       </c>
       <c r="E77" t="n">
-        <v>341.0079040527344</v>
+        <v>347.59765625</v>
       </c>
       <c r="F77" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>340.4489540449518</v>
+        <v>347.4112823812074</v>
       </c>
       <c r="C78" t="n">
-        <v>348.0683303861261</v>
+        <v>350.9316765208364</v>
       </c>
       <c r="D78" t="n">
-        <v>340.0468994310211</v>
+        <v>346.1462842881223</v>
       </c>
       <c r="E78" t="n">
-        <v>347.5976257324219</v>
+        <v>349.3529052734375</v>
       </c>
       <c r="F78" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>347.4113127291759</v>
+        <v>347.0876909760341</v>
       </c>
       <c r="C79" t="n">
-        <v>350.9317071763275</v>
+        <v>347.9114016111286</v>
       </c>
       <c r="D79" t="n">
-        <v>346.1463145255873</v>
+        <v>340.5371789096768</v>
       </c>
       <c r="E79" t="n">
-        <v>349.3529357910156</v>
+        <v>344.8224792480469</v>
       </c>
       <c r="F79" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>347.0877216940886</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C80" t="n">
-        <v>347.9114324020834</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D80" t="n">
-        <v>340.537209047996</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E80" t="n">
-        <v>344.822509765625</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F80" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>288.2705746047087</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C81" t="n">
-        <v>293.6933589672342</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D81" t="n">
-        <v>274.9636596388997</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E81" t="n">
-        <v>277.2190856933594</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F81" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>278.2193161239855</v>
+        <v>288.6235657000577</v>
       </c>
       <c r="C82" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689623036692</v>
       </c>
       <c r="D82" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126518953886</v>
       </c>
       <c r="E82" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231384277344</v>
       </c>
       <c r="F82" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>288.623596430627</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C83" t="n">
-        <v>289.8689931668393</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D83" t="n">
-        <v>283.6126820924317</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E83" t="n">
-        <v>286.6231689453125</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F83" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4747261855329</v>
       </c>
       <c r="C84" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7698129535399</v>
       </c>
       <c r="D84" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072456694325</v>
       </c>
       <c r="E84" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530700683594</v>
       </c>
       <c r="F84" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>280.4746956220067</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C85" t="n">
-        <v>284.7697819219751</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D85" t="n">
-        <v>276.8072155055542</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E85" t="n">
-        <v>280.0530395507812</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F85" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424507136568</v>
       </c>
       <c r="C86" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841654678224</v>
       </c>
       <c r="D86" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367562069888</v>
       </c>
       <c r="E86" t="n">
-        <v>278.6703796386719</v>
+        <v>270.5705261230469</v>
       </c>
       <c r="F86" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>276.5424819048067</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C87" t="n">
-        <v>278.9841969343727</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D87" t="n">
-        <v>268.7367865177365</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E87" t="n">
-        <v>270.570556640625</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F87" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>268.9721491110363</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C88" t="n">
-        <v>271.5217470095316</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D88" t="n">
-        <v>261.127250916227</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E88" t="n">
-        <v>263.3434143066406</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F88" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348608333229</v>
       </c>
       <c r="C89" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479519102809</v>
       </c>
       <c r="D89" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209657772727</v>
       </c>
       <c r="E89" t="n">
-        <v>271.286376953125</v>
+        <v>270.3548278808594</v>
       </c>
       <c r="F89" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>268.8348304873182</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C90" t="n">
-        <v>274.7479208968081</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D90" t="n">
-        <v>268.0209355231403</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E90" t="n">
-        <v>270.3547973632812</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F90" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>272.1395338130845</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C91" t="n">
-        <v>274.0713413766361</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D91" t="n">
-        <v>267.3639563652268</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E91" t="n">
-        <v>267.9229125976562</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F91" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7671258575986</v>
       </c>
       <c r="C92" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7591102609402</v>
       </c>
       <c r="D92" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626809260317</v>
       </c>
       <c r="E92" t="n">
-        <v>273.5025634765625</v>
+        <v>278.8567199707031</v>
       </c>
       <c r="F92" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>272.7670960064547</v>
+        <v>280.0922508710514</v>
       </c>
       <c r="C93" t="n">
-        <v>280.7590795351679</v>
+        <v>287.7704307745099</v>
       </c>
       <c r="D93" t="n">
-        <v>270.4626513270822</v>
+        <v>278.9939700602999</v>
       </c>
       <c r="E93" t="n">
-        <v>278.856689453125</v>
+        <v>287.5056762695312</v>
       </c>
       <c r="F93" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>280.092280601724</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C94" t="n">
-        <v>287.7704613201907</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D94" t="n">
-        <v>278.9939996743944</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E94" t="n">
-        <v>287.5057067871094</v>
+        <v>283.4851989746094</v>
       </c>
       <c r="F94" t="n">
-        <v>10281900</v>
+        <v>6091700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>288.3000088357305</v>
+        <v>284.377578031072</v>
       </c>
       <c r="C95" t="n">
-        <v>288.5255604322975</v>
+        <v>284.5050624231632</v>
       </c>
       <c r="D95" t="n">
-        <v>282.7497397683958</v>
+        <v>280.7395146362062</v>
       </c>
       <c r="E95" t="n">
-        <v>283.4851989746094</v>
+        <v>282.6124877929688</v>
       </c>
       <c r="F95" t="n">
-        <v>6091700</v>
+        <v>6632000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>284.3775473228927</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="C96" t="n">
-        <v>284.5050317012176</v>
+        <v>285.2503082207336</v>
       </c>
       <c r="D96" t="n">
-        <v>280.7394843208789</v>
+        <v>281.3278592694971</v>
       </c>
       <c r="E96" t="n">
-        <v>282.6124572753906</v>
+        <v>284.3088989257812</v>
       </c>
       <c r="F96" t="n">
-        <v>6632000</v>
+        <v>4931800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>285.2503388393621</v>
+        <v>283.2988839747449</v>
       </c>
       <c r="C97" t="n">
-        <v>285.2503388393621</v>
+        <v>285.1620413364778</v>
       </c>
       <c r="D97" t="n">
-        <v>281.3278894670919</v>
+        <v>280.0138268252642</v>
       </c>
       <c r="E97" t="n">
-        <v>284.3089294433594</v>
+        <v>284.3775634765625</v>
       </c>
       <c r="F97" t="n">
-        <v>4931800</v>
+        <v>6974100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>283.2988839747449</v>
+        <v>282.9556520269239</v>
       </c>
       <c r="C98" t="n">
-        <v>285.1620413364778</v>
+        <v>286.1132246607002</v>
       </c>
       <c r="D98" t="n">
-        <v>280.0138268252642</v>
+        <v>276.2090649023382</v>
       </c>
       <c r="E98" t="n">
-        <v>284.3775634765625</v>
+        <v>276.8660583496094</v>
       </c>
       <c r="F98" t="n">
-        <v>6974100</v>
+        <v>7247500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>282.9556520269239</v>
+        <v>276.7287838236561</v>
       </c>
       <c r="C99" t="n">
-        <v>286.1132246607002</v>
+        <v>276.9248883144977</v>
       </c>
       <c r="D99" t="n">
-        <v>276.2090649023382</v>
+        <v>266.5303926707583</v>
       </c>
       <c r="E99" t="n">
-        <v>276.8660583496094</v>
+        <v>268.6387329101562</v>
       </c>
       <c r="F99" t="n">
-        <v>7247500</v>
+        <v>9684500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>276.7288152602706</v>
+        <v>271.9139684697379</v>
       </c>
       <c r="C100" t="n">
-        <v>276.9249197733898</v>
+        <v>279.2195114888904</v>
       </c>
       <c r="D100" t="n">
-        <v>266.5304229488273</v>
+        <v>271.5020981735627</v>
       </c>
       <c r="E100" t="n">
-        <v>268.6387634277344</v>
+        <v>278.6900024414062</v>
       </c>
       <c r="F100" t="n">
-        <v>9684500</v>
+        <v>11380600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>271.9139684697379</v>
+        <v>281.4160980059485</v>
       </c>
       <c r="C101" t="n">
-        <v>279.2195114888904</v>
+        <v>289.5355657694184</v>
       </c>
       <c r="D101" t="n">
-        <v>271.5020981735627</v>
+        <v>279.7000266676773</v>
       </c>
       <c r="E101" t="n">
-        <v>278.6900024414062</v>
+        <v>281.102294921875</v>
       </c>
       <c r="F101" t="n">
-        <v>11380600</v>
+        <v>10210000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>281.4160980059485</v>
+        <v>279.1803129234154</v>
       </c>
       <c r="C102" t="n">
-        <v>289.5355657694184</v>
+        <v>288.4274790393609</v>
       </c>
       <c r="D102" t="n">
-        <v>279.7000266676773</v>
+        <v>278.3467865455038</v>
       </c>
       <c r="E102" t="n">
-        <v>281.102294921875</v>
+        <v>287.5841369628906</v>
       </c>
       <c r="F102" t="n">
-        <v>10210000</v>
+        <v>9723300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>279.1803129234154</v>
+        <v>282.573240677092</v>
       </c>
       <c r="C103" t="n">
-        <v>288.4274790393609</v>
+        <v>289.5846125554742</v>
       </c>
       <c r="D103" t="n">
-        <v>278.3467865455038</v>
+        <v>281.9260329754997</v>
       </c>
       <c r="E103" t="n">
-        <v>287.5841369628906</v>
+        <v>289.2119750976562</v>
       </c>
       <c r="F103" t="n">
-        <v>9723300</v>
+        <v>8141400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>282.573240677092</v>
+        <v>283.3871388529354</v>
       </c>
       <c r="C104" t="n">
-        <v>289.5846125554742</v>
+        <v>288.0450472755065</v>
       </c>
       <c r="D104" t="n">
-        <v>281.9260329754997</v>
+        <v>278.8468991181569</v>
       </c>
       <c r="E104" t="n">
-        <v>289.2119750976562</v>
+        <v>283.6028747558594</v>
       </c>
       <c r="F104" t="n">
-        <v>8141400</v>
+        <v>7051100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>283.3871388529354</v>
+        <v>283.4067419898253</v>
       </c>
       <c r="C105" t="n">
-        <v>288.0450472755065</v>
+        <v>288.6333918574902</v>
       </c>
       <c r="D105" t="n">
-        <v>278.8468991181569</v>
+        <v>282.102511003054</v>
       </c>
       <c r="E105" t="n">
-        <v>283.6028747558594</v>
+        <v>286.2995300292969</v>
       </c>
       <c r="F105" t="n">
-        <v>7051100</v>
+        <v>7796000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>283.4067419898253</v>
+        <v>284.4265691931125</v>
       </c>
       <c r="C106" t="n">
-        <v>288.6333918574902</v>
+        <v>285.7406159339096</v>
       </c>
       <c r="D106" t="n">
-        <v>282.102511003054</v>
+        <v>281.1807450619272</v>
       </c>
       <c r="E106" t="n">
-        <v>286.2995300292969</v>
+        <v>283.17138671875</v>
       </c>
       <c r="F106" t="n">
-        <v>7796000</v>
+        <v>5397900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>284.4265998459625</v>
+        <v>281.7691239489905</v>
       </c>
       <c r="C107" t="n">
-        <v>285.7406467283754</v>
+        <v>285.681757300537</v>
       </c>
       <c r="D107" t="n">
-        <v>281.1807753649725</v>
+        <v>277.5622889631125</v>
       </c>
       <c r="E107" t="n">
-        <v>283.1714172363281</v>
+        <v>280.9258117675781</v>
       </c>
       <c r="F107" t="n">
-        <v>5397900</v>
+        <v>6816900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,25 +3225,25 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>281.7691239489905</v>
+        <v>278.6825254902615</v>
       </c>
       <c r="C108" t="n">
-        <v>285.681757300537</v>
+        <v>281.8448924528684</v>
       </c>
       <c r="D108" t="n">
-        <v>277.5622889631125</v>
+        <v>275.3818211832701</v>
       </c>
       <c r="E108" t="n">
-        <v>280.9258117675781</v>
+        <v>281.8152465820312</v>
       </c>
       <c r="F108" t="n">
-        <v>6816900</v>
+        <v>10348800</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3251,25 +3251,25 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>278.6825254902615</v>
+        <v>283.9992105555065</v>
       </c>
       <c r="C109" t="n">
-        <v>281.8448924528684</v>
+        <v>284.1968396214306</v>
       </c>
       <c r="D109" t="n">
-        <v>275.3818211832701</v>
+        <v>275.6189600693905</v>
       </c>
       <c r="E109" t="n">
-        <v>281.8152465820312</v>
+        <v>279.0184936523438</v>
       </c>
       <c r="F109" t="n">
-        <v>10348800</v>
+        <v>6075600</v>
       </c>
       <c r="G109" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>283.9992105555065</v>
+        <v>279.0580549356083</v>
       </c>
       <c r="C110" t="n">
-        <v>284.1968396214306</v>
+        <v>282.8528771272727</v>
       </c>
       <c r="D110" t="n">
-        <v>275.6189600693905</v>
+        <v>277.2989962609529</v>
       </c>
       <c r="E110" t="n">
-        <v>279.0184936523438</v>
+        <v>281.894287109375</v>
       </c>
       <c r="F110" t="n">
-        <v>6075600</v>
+        <v>6878800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>279.0580549356083</v>
+        <v>281.42981524537</v>
       </c>
       <c r="C111" t="n">
-        <v>282.8528771272727</v>
+        <v>284.1771098102745</v>
       </c>
       <c r="D111" t="n">
-        <v>277.2989962609529</v>
+        <v>273.039702199029</v>
       </c>
       <c r="E111" t="n">
-        <v>281.894287109375</v>
+        <v>273.7907409667969</v>
       </c>
       <c r="F111" t="n">
-        <v>6878800</v>
+        <v>10512300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>281.4297838763166</v>
+        <v>274.7888644946905</v>
       </c>
       <c r="C112" t="n">
-        <v>284.177078134999</v>
+        <v>279.5521686416635</v>
       </c>
       <c r="D112" t="n">
-        <v>273.039671765164</v>
+        <v>274.5418055263856</v>
       </c>
       <c r="E112" t="n">
-        <v>273.7907104492188</v>
+        <v>278.7714538574219</v>
       </c>
       <c r="F112" t="n">
-        <v>10512300</v>
+        <v>4737600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>274.7888344130931</v>
+        <v>280.6392236042361</v>
       </c>
       <c r="C113" t="n">
-        <v>279.5521380386192</v>
+        <v>284.0189732750403</v>
       </c>
       <c r="D113" t="n">
-        <v>274.5417754718342</v>
+        <v>277.7338078332982</v>
       </c>
       <c r="E113" t="n">
-        <v>278.7714233398438</v>
+        <v>282.1314392089844</v>
       </c>
       <c r="F113" t="n">
-        <v>4737600</v>
+        <v>4854000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>280.6392236042361</v>
+        <v>284.4142561376558</v>
       </c>
       <c r="C114" t="n">
-        <v>284.0189732750403</v>
+        <v>285.5902591728541</v>
       </c>
       <c r="D114" t="n">
-        <v>277.7338078332982</v>
+        <v>281.4890865630293</v>
       </c>
       <c r="E114" t="n">
-        <v>282.1314392089844</v>
+        <v>284.1869812011719</v>
       </c>
       <c r="F114" t="n">
-        <v>4854000</v>
+        <v>5752000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>284.41428667964</v>
+        <v>281.8448673992793</v>
       </c>
       <c r="C115" t="n">
-        <v>285.5902898411239</v>
+        <v>285.0072039222152</v>
       </c>
       <c r="D115" t="n">
-        <v>281.4891167908925</v>
+        <v>279.7399202812535</v>
       </c>
       <c r="E115" t="n">
-        <v>284.18701171875</v>
+        <v>280.9850769042969</v>
       </c>
       <c r="F115" t="n">
-        <v>5752000</v>
+        <v>4544100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>281.8448673992793</v>
+        <v>280.6589864168267</v>
       </c>
       <c r="C116" t="n">
-        <v>285.0072039222152</v>
+        <v>284.167211683611</v>
       </c>
       <c r="D116" t="n">
-        <v>279.7399202812535</v>
+        <v>276.7752266949594</v>
       </c>
       <c r="E116" t="n">
-        <v>280.9850769042969</v>
+        <v>277.140869140625</v>
       </c>
       <c r="F116" t="n">
-        <v>4544100</v>
+        <v>5542100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>280.6589555118485</v>
+        <v>275.7079269716043</v>
       </c>
       <c r="C117" t="n">
-        <v>284.1671803923218</v>
+        <v>279.769592245506</v>
       </c>
       <c r="D117" t="n">
-        <v>276.7751962176443</v>
+        <v>271.7648753401377</v>
       </c>
       <c r="E117" t="n">
-        <v>277.1408386230469</v>
+        <v>272.3479309082031</v>
       </c>
       <c r="F117" t="n">
-        <v>5542100</v>
+        <v>38893000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>275.7078960775263</v>
+        <v>275.8561490740913</v>
       </c>
       <c r="C118" t="n">
-        <v>279.7695608963037</v>
+        <v>277.4471941978335</v>
       </c>
       <c r="D118" t="n">
-        <v>271.7648448878931</v>
+        <v>265.9243614270812</v>
       </c>
       <c r="E118" t="n">
-        <v>272.347900390625</v>
+        <v>266.3690795898438</v>
       </c>
       <c r="F118" t="n">
-        <v>38893000</v>
+        <v>10424200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>275.8561490740913</v>
+        <v>265.7069555541203</v>
       </c>
       <c r="C119" t="n">
-        <v>277.4471941978335</v>
+        <v>270.1639086768414</v>
       </c>
       <c r="D119" t="n">
-        <v>265.9243614270812</v>
+        <v>264.4420149324948</v>
       </c>
       <c r="E119" t="n">
-        <v>266.3690795898438</v>
+        <v>269.0768432617188</v>
       </c>
       <c r="F119" t="n">
-        <v>10424200</v>
+        <v>5911700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>265.7069856894997</v>
+        <v>271.7648489371355</v>
       </c>
       <c r="C120" t="n">
-        <v>270.1639393177099</v>
+        <v>272.8321303468297</v>
       </c>
       <c r="D120" t="n">
-        <v>264.44204492441</v>
+        <v>263.9676538860649</v>
       </c>
       <c r="E120" t="n">
-        <v>269.0768737792969</v>
+        <v>267.3671875</v>
       </c>
       <c r="F120" t="n">
-        <v>5911700</v>
+        <v>8121200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>271.7648799566674</v>
+        <v>266.813786399154</v>
       </c>
       <c r="C121" t="n">
-        <v>272.8321614881822</v>
+        <v>271.4091072097051</v>
       </c>
       <c r="D121" t="n">
-        <v>263.9676840156166</v>
+        <v>264.0368460847004</v>
       </c>
       <c r="E121" t="n">
-        <v>267.3672180175781</v>
+        <v>264.8966064453125</v>
       </c>
       <c r="F121" t="n">
-        <v>8121200</v>
+        <v>6218800</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>266.813786399154</v>
+        <v>264.3530902318651</v>
       </c>
       <c r="C122" t="n">
-        <v>271.4091072097051</v>
+        <v>264.5211035963603</v>
       </c>
       <c r="D122" t="n">
-        <v>264.0368460847004</v>
+        <v>252.9587320723257</v>
       </c>
       <c r="E122" t="n">
-        <v>264.8966064453125</v>
+        <v>255.9728393554688</v>
       </c>
       <c r="F122" t="n">
-        <v>6218800</v>
+        <v>10735300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>264.3530902318651</v>
+        <v>257.119221076063</v>
       </c>
       <c r="C123" t="n">
-        <v>264.5211035963603</v>
+        <v>259.2439223272896</v>
       </c>
       <c r="D123" t="n">
-        <v>252.9587320723257</v>
+        <v>253.6505334149961</v>
       </c>
       <c r="E123" t="n">
-        <v>255.9728393554688</v>
+        <v>258.7102966308594</v>
       </c>
       <c r="F123" t="n">
-        <v>10735300</v>
+        <v>7774700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>257.1191907461688</v>
+        <v>259.9060317076502</v>
       </c>
       <c r="C124" t="n">
-        <v>259.2438917467647</v>
+        <v>268.6815709876363</v>
       </c>
       <c r="D124" t="n">
-        <v>253.6505034942698</v>
+        <v>259.5206052453565</v>
       </c>
       <c r="E124" t="n">
-        <v>258.7102661132812</v>
+        <v>267.40673828125</v>
       </c>
       <c r="F124" t="n">
-        <v>7774700</v>
+        <v>9170800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>259.9060317076502</v>
+        <v>270.9841413969268</v>
       </c>
       <c r="C125" t="n">
-        <v>268.6815709876363</v>
+        <v>272.0613148441149</v>
       </c>
       <c r="D125" t="n">
-        <v>259.5206052453565</v>
+        <v>267.5747458421163</v>
       </c>
       <c r="E125" t="n">
-        <v>267.40673828125</v>
+        <v>270.7568664550781</v>
       </c>
       <c r="F125" t="n">
-        <v>9170800</v>
+        <v>5473400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>270.9841413969268</v>
+        <v>269.0867574628081</v>
       </c>
       <c r="C126" t="n">
-        <v>272.0613148441149</v>
+        <v>275.7573496838748</v>
       </c>
       <c r="D126" t="n">
-        <v>267.5747458421163</v>
+        <v>268.3356885397691</v>
       </c>
       <c r="E126" t="n">
-        <v>270.7568664550781</v>
+        <v>273.998291015625</v>
       </c>
       <c r="F126" t="n">
-        <v>5473400</v>
+        <v>6407000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>269.0867274922702</v>
+        <v>274.6109769278597</v>
       </c>
       <c r="C127" t="n">
-        <v>275.757318970375</v>
+        <v>279.9671982310729</v>
       </c>
       <c r="D127" t="n">
-        <v>268.3356586528844</v>
+        <v>273.9883835303555</v>
       </c>
       <c r="E127" t="n">
-        <v>273.9982604980469</v>
+        <v>278.0500183105469</v>
       </c>
       <c r="F127" t="n">
-        <v>6407000</v>
+        <v>7097000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>274.6109769278597</v>
+        <v>305.2166521040811</v>
       </c>
       <c r="C128" t="n">
-        <v>279.9671982310729</v>
+        <v>308.7545232213582</v>
       </c>
       <c r="D128" t="n">
-        <v>273.9883835303555</v>
+        <v>297.2119355877115</v>
       </c>
       <c r="E128" t="n">
-        <v>278.0500183105469</v>
+        <v>304.1098327636719</v>
       </c>
       <c r="F128" t="n">
-        <v>7097000</v>
+        <v>22099800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>305.2166521040811</v>
+        <v>308.3295702834321</v>
       </c>
       <c r="C129" t="n">
-        <v>308.7545232213582</v>
+        <v>309.2881602178994</v>
       </c>
       <c r="D129" t="n">
-        <v>297.2119355877115</v>
+        <v>301.2439063119584</v>
       </c>
       <c r="E129" t="n">
-        <v>304.1098327636719</v>
+        <v>302.3804016113281</v>
       </c>
       <c r="F129" t="n">
-        <v>22099800</v>
+        <v>9645000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>308.3296014014268</v>
+        <v>302.2222955343541</v>
       </c>
       <c r="C130" t="n">
-        <v>309.2881914326393</v>
+        <v>304.2679509863046</v>
       </c>
       <c r="D130" t="n">
-        <v>301.2439367148364</v>
+        <v>300.5620665408429</v>
       </c>
       <c r="E130" t="n">
-        <v>302.3804321289062</v>
+        <v>303.2994689941406</v>
       </c>
       <c r="F130" t="n">
-        <v>9645000</v>
+        <v>5742000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>302.2222955343541</v>
+        <v>304.3272252898824</v>
       </c>
       <c r="C131" t="n">
-        <v>304.2679509863046</v>
+        <v>306.7187390262146</v>
       </c>
       <c r="D131" t="n">
-        <v>300.5620665408429</v>
+        <v>300.6213410567302</v>
       </c>
       <c r="E131" t="n">
-        <v>303.2994689941406</v>
+        <v>300.7497863769531</v>
       </c>
       <c r="F131" t="n">
-        <v>5742000</v>
+        <v>5212900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>304.3272561704691</v>
+        <v>299.6825108634778</v>
       </c>
       <c r="C132" t="n">
-        <v>306.7187701494722</v>
+        <v>309.6340527574118</v>
       </c>
       <c r="D132" t="n">
-        <v>300.6213715612747</v>
+        <v>299.3564063143342</v>
       </c>
       <c r="E132" t="n">
-        <v>300.7498168945312</v>
+        <v>309.3178100585938</v>
       </c>
       <c r="F132" t="n">
-        <v>5212900</v>
+        <v>7972200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>299.6825108634778</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="C133" t="n">
-        <v>309.6340527574118</v>
+        <v>315.8599180273897</v>
       </c>
       <c r="D133" t="n">
-        <v>299.3564063143342</v>
+        <v>308.8335760443198</v>
       </c>
       <c r="E133" t="n">
-        <v>309.3178100585938</v>
+        <v>310.4938049316406</v>
       </c>
       <c r="F133" t="n">
-        <v>7972200</v>
+        <v>5864500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>308.8335760443198</v>
+        <v>312.2825100891185</v>
       </c>
       <c r="C134" t="n">
-        <v>315.8599180273897</v>
+        <v>314.0218147327601</v>
       </c>
       <c r="D134" t="n">
-        <v>308.8335760443198</v>
+        <v>307.4895604690128</v>
       </c>
       <c r="E134" t="n">
-        <v>310.4938049316406</v>
+        <v>310.3554382324219</v>
       </c>
       <c r="F134" t="n">
-        <v>5864500</v>
+        <v>5041200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>312.2825100891185</v>
+        <v>311.2942713469933</v>
       </c>
       <c r="C135" t="n">
-        <v>314.0218147327601</v>
+        <v>314.8617880440979</v>
       </c>
       <c r="D135" t="n">
-        <v>307.4895604690128</v>
+        <v>309.4264912428012</v>
       </c>
       <c r="E135" t="n">
-        <v>310.3554382324219</v>
+        <v>312.6777954101562</v>
       </c>
       <c r="F135" t="n">
-        <v>5041200</v>
+        <v>5205600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>311.2943017295384</v>
+        <v>316.2848676157387</v>
       </c>
       <c r="C136" t="n">
-        <v>314.8618187748353</v>
+        <v>321.443459891993</v>
       </c>
       <c r="D136" t="n">
-        <v>309.4265214430497</v>
+        <v>313.4091278691752</v>
       </c>
       <c r="E136" t="n">
-        <v>312.6778259277344</v>
+        <v>320.8110046386719</v>
       </c>
       <c r="F136" t="n">
-        <v>5205600</v>
+        <v>9414700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>316.2848676157387</v>
+        <v>320.3761995931397</v>
       </c>
       <c r="C137" t="n">
-        <v>321.443459891993</v>
+        <v>321.5719565905757</v>
       </c>
       <c r="D137" t="n">
-        <v>313.4091278691752</v>
+        <v>316.3540722325493</v>
       </c>
       <c r="E137" t="n">
-        <v>320.8110046386719</v>
+        <v>319.674560546875</v>
       </c>
       <c r="F137" t="n">
-        <v>9414700</v>
+        <v>9050600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>320.37616900858</v>
+        <v>348.8571343403697</v>
       </c>
       <c r="C138" t="n">
-        <v>321.5719258918635</v>
+        <v>353.472178702815</v>
       </c>
       <c r="D138" t="n">
-        <v>316.35404203196</v>
+        <v>341.1686609140239</v>
       </c>
       <c r="E138" t="n">
-        <v>319.6745300292969</v>
+        <v>341.9394836425781</v>
       </c>
       <c r="F138" t="n">
-        <v>9050600</v>
+        <v>26097300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>348.8571343403697</v>
+        <v>346.7522179221875</v>
       </c>
       <c r="C139" t="n">
-        <v>353.472178702815</v>
+        <v>354.3418624071809</v>
       </c>
       <c r="D139" t="n">
-        <v>341.1686609140239</v>
+        <v>344.9931592239693</v>
       </c>
       <c r="E139" t="n">
-        <v>341.9394836425781</v>
+        <v>349.3611450195312</v>
       </c>
       <c r="F139" t="n">
-        <v>26097300</v>
+        <v>11807300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>346.7521876325058</v>
+        <v>350.5074689695779</v>
       </c>
       <c r="C140" t="n">
-        <v>354.3418314545246</v>
+        <v>352.6519539416425</v>
       </c>
       <c r="D140" t="n">
-        <v>344.9931290879458</v>
+        <v>346.3766505322415</v>
       </c>
       <c r="E140" t="n">
-        <v>349.3611145019531</v>
+        <v>350.3888854980469</v>
       </c>
       <c r="F140" t="n">
-        <v>11807300</v>
+        <v>7255800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>350.5074994974842</v>
+        <v>352.2961973442777</v>
       </c>
       <c r="C141" t="n">
-        <v>352.6519846563255</v>
+        <v>354.0651480045056</v>
       </c>
       <c r="D141" t="n">
-        <v>346.3766807003688</v>
+        <v>347.256218509828</v>
       </c>
       <c r="E141" t="n">
-        <v>350.388916015625</v>
+        <v>350.7446899414062</v>
       </c>
       <c r="F141" t="n">
-        <v>7255800</v>
+        <v>8554600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>352.2961666917061</v>
+        <v>349.7465417706892</v>
       </c>
       <c r="C142" t="n">
-        <v>354.0651171980212</v>
+        <v>352.2961769099271</v>
       </c>
       <c r="D142" t="n">
-        <v>347.2561882957746</v>
+        <v>344.844900560564</v>
       </c>
       <c r="E142" t="n">
-        <v>350.7446594238281</v>
+        <v>350.5173645019531</v>
       </c>
       <c r="F142" t="n">
-        <v>8554600</v>
+        <v>7256100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>349.7465417706892</v>
+        <v>352.6420862239859</v>
       </c>
       <c r="C143" t="n">
-        <v>352.2961769099271</v>
+        <v>365.28163151709</v>
       </c>
       <c r="D143" t="n">
-        <v>344.844900560564</v>
+        <v>351.5352668687036</v>
       </c>
       <c r="E143" t="n">
-        <v>350.5173645019531</v>
+        <v>362.4552612304688</v>
       </c>
       <c r="F143" t="n">
-        <v>7256100</v>
+        <v>10604100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>352.6420862239859</v>
+        <v>361.6943118802069</v>
       </c>
       <c r="C144" t="n">
-        <v>365.28163151709</v>
+        <v>366.4773696532562</v>
       </c>
       <c r="D144" t="n">
-        <v>351.5352668687036</v>
+        <v>360.7159680643861</v>
       </c>
       <c r="E144" t="n">
-        <v>362.4552612304688</v>
+        <v>366.3785400390625</v>
       </c>
       <c r="F144" t="n">
-        <v>10604100</v>
+        <v>9046600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>361.6943118802069</v>
+        <v>364.1747868031508</v>
       </c>
       <c r="C145" t="n">
-        <v>366.4773696532562</v>
+        <v>367.613828109226</v>
       </c>
       <c r="D145" t="n">
-        <v>360.7159680643861</v>
+        <v>358.7295978571138</v>
       </c>
       <c r="E145" t="n">
-        <v>366.3785400390625</v>
+        <v>366.1216125488281</v>
       </c>
       <c r="F145" t="n">
-        <v>9046600</v>
+        <v>6879900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>364.1747868031508</v>
+        <v>367.5842026752116</v>
       </c>
       <c r="C146" t="n">
-        <v>367.613828109226</v>
+        <v>368.513146797899</v>
       </c>
       <c r="D146" t="n">
-        <v>358.7295978571138</v>
+        <v>362.7023151057061</v>
       </c>
       <c r="E146" t="n">
-        <v>366.1216125488281</v>
+        <v>364.4416198730469</v>
       </c>
       <c r="F146" t="n">
-        <v>6879900</v>
+        <v>4945400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>367.5842026752116</v>
+        <v>364.214296881966</v>
       </c>
       <c r="C147" t="n">
-        <v>368.513146797899</v>
+        <v>366.4674733296609</v>
       </c>
       <c r="D147" t="n">
-        <v>362.7023151057061</v>
+        <v>360.360183242299</v>
       </c>
       <c r="E147" t="n">
-        <v>364.4416198730469</v>
+        <v>366.388427734375</v>
       </c>
       <c r="F147" t="n">
-        <v>4945400</v>
+        <v>4916900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>364.214296881966</v>
+        <v>366.1216097846273</v>
       </c>
       <c r="C148" t="n">
-        <v>366.4674733296609</v>
+        <v>367.4260581192055</v>
       </c>
       <c r="D148" t="n">
-        <v>360.360183242299</v>
+        <v>357.553592134861</v>
       </c>
       <c r="E148" t="n">
-        <v>366.388427734375</v>
+        <v>359.58935546875</v>
       </c>
       <c r="F148" t="n">
-        <v>4916900</v>
+        <v>6489000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>366.1216408565838</v>
+        <v>358.8284404495387</v>
       </c>
       <c r="C149" t="n">
-        <v>367.4260893018678</v>
+        <v>364.2143076961161</v>
       </c>
       <c r="D149" t="n">
-        <v>357.5536224796683</v>
+        <v>354.0354905816196</v>
       </c>
       <c r="E149" t="n">
-        <v>359.5893859863281</v>
+        <v>362.9592590332031</v>
       </c>
       <c r="F149" t="n">
-        <v>6489000</v>
+        <v>6695500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>358.8284404495387</v>
+        <v>362.3267825015715</v>
       </c>
       <c r="C150" t="n">
-        <v>364.2143076961161</v>
+        <v>365.45947304961</v>
       </c>
       <c r="D150" t="n">
-        <v>354.0354905816196</v>
+        <v>360.4293565255828</v>
       </c>
       <c r="E150" t="n">
-        <v>362.9592590332031</v>
+        <v>365.3902893066406</v>
       </c>
       <c r="F150" t="n">
-        <v>6695500</v>
+        <v>5235400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>362.3267825015715</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="C151" t="n">
-        <v>365.45947304961</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="D151" t="n">
-        <v>360.4293565255828</v>
+        <v>367.6138623558188</v>
       </c>
       <c r="E151" t="n">
-        <v>365.3902893066406</v>
+        <v>375.5098876953125</v>
       </c>
       <c r="F151" t="n">
-        <v>5235400</v>
+        <v>6455100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>367.6138324799484</v>
+        <v>375.9743375633532</v>
       </c>
       <c r="C152" t="n">
-        <v>375.5098571777344</v>
+        <v>380.2830313516125</v>
       </c>
       <c r="D152" t="n">
-        <v>367.6138324799484</v>
+        <v>371.6458597568035</v>
       </c>
       <c r="E152" t="n">
-        <v>375.5098571777344</v>
+        <v>379.9173889160156</v>
       </c>
       <c r="F152" t="n">
-        <v>6455100</v>
+        <v>6949600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>375.9743375633532</v>
+        <v>378.3461148231528</v>
       </c>
       <c r="C153" t="n">
-        <v>380.2830313516125</v>
+        <v>392.7447189140002</v>
       </c>
       <c r="D153" t="n">
-        <v>371.6458597568035</v>
+        <v>377.5160002982997</v>
       </c>
       <c r="E153" t="n">
-        <v>379.9173889160156</v>
+        <v>391.7268371582031</v>
       </c>
       <c r="F153" t="n">
-        <v>6949600</v>
+        <v>9236300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>378.3460853480032</v>
+        <v>391.8354914196509</v>
       </c>
       <c r="C154" t="n">
-        <v>392.7446883171237</v>
+        <v>399.3954891946478</v>
       </c>
       <c r="D154" t="n">
-        <v>377.5159708878205</v>
+        <v>388.3766661486073</v>
       </c>
       <c r="E154" t="n">
-        <v>391.726806640625</v>
+        <v>396.440673828125</v>
       </c>
       <c r="F154" t="n">
-        <v>9236300</v>
+        <v>8454100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>391.835521582727</v>
+        <v>396.2825535174053</v>
       </c>
       <c r="C155" t="n">
-        <v>399.3955199396844</v>
+        <v>397.1719597005697</v>
       </c>
       <c r="D155" t="n">
-        <v>388.3766960454267</v>
+        <v>391.3413745458666</v>
       </c>
       <c r="E155" t="n">
-        <v>396.4407043457031</v>
+        <v>394.39501953125</v>
       </c>
       <c r="F155" t="n">
-        <v>8454100</v>
+        <v>5342500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>396.2825841810375</v>
+        <v>389.661393370787</v>
       </c>
       <c r="C156" t="n">
-        <v>397.1719904330225</v>
+        <v>392.9522357226725</v>
       </c>
       <c r="D156" t="n">
-        <v>391.3414048271592</v>
+        <v>385.6590501412673</v>
       </c>
       <c r="E156" t="n">
-        <v>394.3950500488281</v>
+        <v>389.2167053222656</v>
       </c>
       <c r="F156" t="n">
-        <v>5342500</v>
+        <v>9811200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>389.6613628183419</v>
+        <v>385.4119752058043</v>
       </c>
       <c r="C157" t="n">
-        <v>392.9522049122001</v>
+        <v>387.5268143663777</v>
       </c>
       <c r="D157" t="n">
-        <v>385.6590199026367</v>
+        <v>378.9884422857075</v>
       </c>
       <c r="E157" t="n">
-        <v>389.2166748046875</v>
+        <v>386.5286865234375</v>
       </c>
       <c r="F157" t="n">
-        <v>9811200</v>
+        <v>8400700</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>385.4119752058043</v>
+        <v>385.4119575218886</v>
       </c>
       <c r="C158" t="n">
-        <v>387.5268143663777</v>
+        <v>390.3432444558516</v>
       </c>
       <c r="D158" t="n">
-        <v>378.9884422857075</v>
+        <v>382.9512600592197</v>
       </c>
       <c r="E158" t="n">
-        <v>386.5286865234375</v>
+        <v>384.660888671875</v>
       </c>
       <c r="F158" t="n">
-        <v>8400700</v>
+        <v>5016800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>385.4119880990537</v>
+        <v>384.9672762725209</v>
       </c>
       <c r="C159" t="n">
-        <v>390.3432754242469</v>
+        <v>388.7522365943216</v>
       </c>
       <c r="D159" t="n">
-        <v>382.9512904411622</v>
+        <v>376.2214128322495</v>
       </c>
       <c r="E159" t="n">
-        <v>384.6609191894531</v>
+        <v>378.7908020019531</v>
       </c>
       <c r="F159" t="n">
-        <v>5016800</v>
+        <v>7783900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>384.9672452573303</v>
+        <v>376.6364218669779</v>
       </c>
       <c r="C160" t="n">
-        <v>388.7522052741927</v>
+        <v>381.5677088398597</v>
       </c>
       <c r="D160" t="n">
-        <v>376.2213825216763</v>
+        <v>376.0632583748818</v>
       </c>
       <c r="E160" t="n">
-        <v>378.790771484375</v>
+        <v>377.9804382324219</v>
       </c>
       <c r="F160" t="n">
-        <v>7783900</v>
+        <v>4732500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>376.6364522760421</v>
+        <v>377.4270609393932</v>
       </c>
       <c r="C161" t="n">
-        <v>381.5677396470687</v>
+        <v>385.9456494081999</v>
       </c>
       <c r="D161" t="n">
-        <v>376.0632887376697</v>
+        <v>376.5277626686598</v>
       </c>
       <c r="E161" t="n">
-        <v>377.98046875</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F161" t="n">
-        <v>4732500</v>
+        <v>5598600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>377.4270309363715</v>
+        <v>381.4590342432408</v>
       </c>
       <c r="C162" t="n">
-        <v>385.9456187280053</v>
+        <v>381.9729060229619</v>
       </c>
       <c r="D162" t="n">
-        <v>376.5277327371266</v>
+        <v>371.981856156588</v>
       </c>
       <c r="E162" t="n">
-        <v>383.8999633789062</v>
+        <v>372.4265441894531</v>
       </c>
       <c r="F162" t="n">
-        <v>5598600</v>
+        <v>6498100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>381.4590342432408</v>
+        <v>373.978089171931</v>
       </c>
       <c r="C163" t="n">
-        <v>381.9729060229619</v>
+        <v>380.0063339481963</v>
       </c>
       <c r="D163" t="n">
-        <v>371.981856156588</v>
+        <v>372.6538567388769</v>
       </c>
       <c r="E163" t="n">
-        <v>372.4265441894531</v>
+        <v>379.4924621582031</v>
       </c>
       <c r="F163" t="n">
-        <v>6498100</v>
+        <v>4544000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>373.978089171931</v>
+        <v>380.4312519906984</v>
       </c>
       <c r="C164" t="n">
-        <v>380.0063339481963</v>
+        <v>384.6806841025421</v>
       </c>
       <c r="D164" t="n">
-        <v>372.6538567388769</v>
+        <v>376.4783087193446</v>
       </c>
       <c r="E164" t="n">
-        <v>379.4924621582031</v>
+        <v>378.0298461914062</v>
       </c>
       <c r="F164" t="n">
-        <v>4544000</v>
+        <v>4330800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>380.4312827021371</v>
+        <v>379.265147571566</v>
       </c>
       <c r="C165" t="n">
-        <v>384.6807151570288</v>
+        <v>380.5893799715138</v>
       </c>
       <c r="D165" t="n">
-        <v>376.4783391116702</v>
+        <v>371.0331563353153</v>
       </c>
       <c r="E165" t="n">
-        <v>378.0298767089844</v>
+        <v>375.8359680175781</v>
       </c>
       <c r="F165" t="n">
-        <v>4330800</v>
+        <v>10257900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>379.265147571566</v>
+        <v>371.6853813293241</v>
       </c>
       <c r="C166" t="n">
-        <v>380.5893799715138</v>
+        <v>378.8402295886877</v>
       </c>
       <c r="D166" t="n">
-        <v>371.0331563353153</v>
+        <v>371.4976442585204</v>
       </c>
       <c r="E166" t="n">
-        <v>375.8359680175781</v>
+        <v>375.3912658691406</v>
       </c>
       <c r="F166" t="n">
-        <v>10257900</v>
+        <v>6623700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>371.6853813293241</v>
+        <v>373.5333823120854</v>
       </c>
       <c r="C167" t="n">
-        <v>378.8402295886877</v>
+        <v>375.6086533861857</v>
       </c>
       <c r="D167" t="n">
-        <v>371.4976442585204</v>
+        <v>370.311723920821</v>
       </c>
       <c r="E167" t="n">
-        <v>375.3912658691406</v>
+        <v>373.4740905761719</v>
       </c>
       <c r="F167" t="n">
-        <v>6623700</v>
+        <v>3874400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>373.5333823120854</v>
+        <v>375.5296184023749</v>
       </c>
       <c r="C168" t="n">
-        <v>375.6086533861857</v>
+        <v>382.9018493087182</v>
       </c>
       <c r="D168" t="n">
-        <v>370.311723920821</v>
+        <v>372.3771436667856</v>
       </c>
       <c r="E168" t="n">
-        <v>373.4740905761719</v>
+        <v>372.5649108886719</v>
       </c>
       <c r="F168" t="n">
-        <v>3874400</v>
+        <v>6808400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>375.5296184023749</v>
+        <v>385.4119903823484</v>
       </c>
       <c r="C169" t="n">
-        <v>382.9018493087182</v>
+        <v>396.6581194399012</v>
       </c>
       <c r="D169" t="n">
-        <v>372.3771436667856</v>
+        <v>385.2341151633045</v>
       </c>
       <c r="E169" t="n">
-        <v>372.5649108886719</v>
+        <v>391.8058776855469</v>
       </c>
       <c r="F169" t="n">
-        <v>6808400</v>
+        <v>12666100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>385.4119603627872</v>
+        <v>394.8397525939222</v>
       </c>
       <c r="C170" t="n">
-        <v>396.6580885443842</v>
+        <v>399.2868138360328</v>
       </c>
       <c r="D170" t="n">
-        <v>385.2340851575979</v>
+        <v>392.5272843670525</v>
       </c>
       <c r="E170" t="n">
-        <v>391.8058471679688</v>
+        <v>394.7705688476562</v>
       </c>
       <c r="F170" t="n">
-        <v>12666100</v>
+        <v>10897300</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>394.8397525939222</v>
+        <v>392.4580996989546</v>
       </c>
       <c r="C171" t="n">
-        <v>399.2868138360328</v>
+        <v>403.9018573320044</v>
       </c>
       <c r="D171" t="n">
-        <v>392.5272843670525</v>
+        <v>390.3432605482298</v>
       </c>
       <c r="E171" t="n">
-        <v>394.7705688476562</v>
+        <v>401.7870483398438</v>
       </c>
       <c r="F171" t="n">
-        <v>10897300</v>
+        <v>6963200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>392.4580996989546</v>
+        <v>405.1668188073661</v>
       </c>
       <c r="C172" t="n">
-        <v>403.9018573320044</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="D172" t="n">
-        <v>390.3432605482298</v>
+        <v>402.6468293766872</v>
       </c>
       <c r="E172" t="n">
-        <v>401.7870483398438</v>
+        <v>408.1414184570312</v>
       </c>
       <c r="F172" t="n">
-        <v>6963200</v>
+        <v>8590400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>405.166788512205</v>
+        <v>408.6355178300448</v>
       </c>
       <c r="C173" t="n">
-        <v>408.1413879394531</v>
+        <v>411.0863535582731</v>
       </c>
       <c r="D173" t="n">
-        <v>402.6467992699509</v>
+        <v>399.7907950421236</v>
       </c>
       <c r="E173" t="n">
-        <v>408.1413879394531</v>
+        <v>402.6665649414062</v>
       </c>
       <c r="F173" t="n">
-        <v>8590400</v>
+        <v>6512900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>408.6355178300448</v>
+        <v>403.9018510073829</v>
       </c>
       <c r="C174" t="n">
-        <v>411.0863535582731</v>
+        <v>405.1569297923697</v>
       </c>
       <c r="D174" t="n">
-        <v>399.7907950421236</v>
+        <v>398.3677244184781</v>
       </c>
       <c r="E174" t="n">
-        <v>402.6665649414062</v>
+        <v>400.7790222167969</v>
       </c>
       <c r="F174" t="n">
-        <v>6512900</v>
+        <v>4938100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>403.9018510073829</v>
+        <v>404.1983674177345</v>
       </c>
       <c r="C175" t="n">
-        <v>405.1569297923697</v>
+        <v>405.0680198185554</v>
       </c>
       <c r="D175" t="n">
-        <v>398.3677244184781</v>
+        <v>400.0477646532951</v>
       </c>
       <c r="E175" t="n">
-        <v>400.7790222167969</v>
+        <v>403.714111328125</v>
       </c>
       <c r="F175" t="n">
-        <v>4938100</v>
+        <v>7269600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>404.1983674177345</v>
+        <v>404.2110392057612</v>
       </c>
       <c r="C176" t="n">
-        <v>405.0680198185554</v>
+        <v>411.6253760831061</v>
       </c>
       <c r="D176" t="n">
-        <v>400.0477646532951</v>
+        <v>397.2041664686265</v>
       </c>
       <c r="E176" t="n">
-        <v>403.714111328125</v>
+        <v>408.5244750976562</v>
       </c>
       <c r="F176" t="n">
-        <v>7269600</v>
+        <v>6777900</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>404.2110392057612</v>
+        <v>408.166667860176</v>
       </c>
       <c r="C177" t="n">
-        <v>411.6253760831061</v>
+        <v>409.2301268352938</v>
       </c>
       <c r="D177" t="n">
-        <v>397.2041664686265</v>
+        <v>404.0520200618331</v>
       </c>
       <c r="E177" t="n">
-        <v>408.5244750976562</v>
+        <v>405.1552124023438</v>
       </c>
       <c r="F177" t="n">
-        <v>6777900</v>
+        <v>4815100</v>
       </c>
       <c r="G177" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>408.166667860176</v>
+        <v>406.6162060558993</v>
       </c>
       <c r="C178" t="n">
-        <v>409.2301268352938</v>
+        <v>408.6437298747245</v>
       </c>
       <c r="D178" t="n">
-        <v>404.0520200618331</v>
+        <v>396.1506502177288</v>
       </c>
       <c r="E178" t="n">
-        <v>405.1552124023438</v>
+        <v>397.0848999023438</v>
       </c>
       <c r="F178" t="n">
-        <v>4815100</v>
+        <v>5838800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>406.6162060558993</v>
+        <v>400.3050851420949</v>
       </c>
       <c r="C179" t="n">
-        <v>408.6437298747245</v>
+        <v>403.7141170062105</v>
       </c>
       <c r="D179" t="n">
-        <v>396.1506502177288</v>
+        <v>396.7072439594676</v>
       </c>
       <c r="E179" t="n">
-        <v>397.0848999023438</v>
+        <v>398.5061645507812</v>
       </c>
       <c r="F179" t="n">
-        <v>5838800</v>
+        <v>11896900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>400.3050851420949</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="C180" t="n">
-        <v>403.7141170062105</v>
+        <v>406.9541476446936</v>
       </c>
       <c r="D180" t="n">
-        <v>396.7072439594676</v>
+        <v>399.6789681783447</v>
       </c>
       <c r="E180" t="n">
-        <v>398.5061645507812</v>
+        <v>404.191162109375</v>
       </c>
       <c r="F180" t="n">
-        <v>11896900</v>
+        <v>5818600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>399.6789681783447</v>
+        <v>407.0137590655401</v>
       </c>
       <c r="C181" t="n">
-        <v>406.9541476446936</v>
+        <v>407.3914383485204</v>
       </c>
       <c r="D181" t="n">
-        <v>399.6789681783447</v>
+        <v>400.3746474166842</v>
       </c>
       <c r="E181" t="n">
-        <v>404.191162109375</v>
+        <v>406.7454223632812</v>
       </c>
       <c r="F181" t="n">
-        <v>5818600</v>
+        <v>6675900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>407.0137590655401</v>
+        <v>408.0275405710553</v>
       </c>
       <c r="C182" t="n">
-        <v>407.3914383485204</v>
+        <v>410.8998382586385</v>
       </c>
       <c r="D182" t="n">
-        <v>400.3746474166842</v>
+        <v>397.5520359316292</v>
       </c>
       <c r="E182" t="n">
-        <v>406.7454223632812</v>
+        <v>403.3165283203125</v>
       </c>
       <c r="F182" t="n">
-        <v>6675900</v>
+        <v>6858800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>408.0275405710553</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="C183" t="n">
-        <v>410.8998382586385</v>
+        <v>415.0244415980686</v>
       </c>
       <c r="D183" t="n">
-        <v>397.5520359316292</v>
+        <v>404.1613393115512</v>
       </c>
       <c r="E183" t="n">
-        <v>403.3165283203125</v>
+        <v>412.9869995117188</v>
       </c>
       <c r="F183" t="n">
-        <v>6858800</v>
+        <v>6014400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="C184" t="n">
-        <v>415.0244415980686</v>
+        <v>425.3110956697316</v>
       </c>
       <c r="D184" t="n">
-        <v>404.1613393115512</v>
+        <v>413.6131380385679</v>
       </c>
       <c r="E184" t="n">
-        <v>412.9869995117188</v>
+        <v>425.2713623046875</v>
       </c>
       <c r="F184" t="n">
-        <v>6014400</v>
+        <v>10588200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>413.6131380385679</v>
+        <v>423.9196901108692</v>
       </c>
       <c r="C185" t="n">
-        <v>425.3110956697316</v>
+        <v>424.0886630783183</v>
       </c>
       <c r="D185" t="n">
-        <v>413.6131380385679</v>
+        <v>413.2652939172264</v>
       </c>
       <c r="E185" t="n">
-        <v>425.2713623046875</v>
+        <v>417.2507629394531</v>
       </c>
       <c r="F185" t="n">
-        <v>10588200</v>
+        <v>5167400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>423.9196901108692</v>
+        <v>420.1330016088457</v>
       </c>
       <c r="C186" t="n">
-        <v>424.0886630783183</v>
+        <v>420.1528682919667</v>
       </c>
       <c r="D186" t="n">
-        <v>413.2652939172264</v>
+        <v>410.7209557472728</v>
       </c>
       <c r="E186" t="n">
-        <v>417.2507629394531</v>
+        <v>413.0863952636719</v>
       </c>
       <c r="F186" t="n">
-        <v>5167400</v>
+        <v>5779800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>420.1330016088457</v>
+        <v>414.5573140678119</v>
       </c>
       <c r="C187" t="n">
-        <v>420.1528682919667</v>
+        <v>425.4005496015332</v>
       </c>
       <c r="D187" t="n">
-        <v>410.7209557472728</v>
+        <v>411.1980248067586</v>
       </c>
       <c r="E187" t="n">
-        <v>413.0863952636719</v>
+        <v>423.9296264648438</v>
       </c>
       <c r="F187" t="n">
-        <v>5779800</v>
+        <v>4985900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>414.5573140678119</v>
+        <v>425.5099032988985</v>
       </c>
       <c r="C188" t="n">
-        <v>425.4005496015332</v>
+        <v>427.5672424396051</v>
       </c>
       <c r="D188" t="n">
-        <v>411.1980248067586</v>
+        <v>417.9663567804552</v>
       </c>
       <c r="E188" t="n">
-        <v>423.9296264648438</v>
+        <v>422.7568359375</v>
       </c>
       <c r="F188" t="n">
-        <v>4985900</v>
+        <v>3928800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>425.5099032988985</v>
+        <v>420.8982555962246</v>
       </c>
       <c r="C189" t="n">
-        <v>427.5672424396051</v>
+        <v>421.8424537826169</v>
       </c>
       <c r="D189" t="n">
-        <v>417.9663567804552</v>
+        <v>412.5099054894139</v>
       </c>
       <c r="E189" t="n">
-        <v>422.7568359375</v>
+        <v>415.4319152832031</v>
       </c>
       <c r="F189" t="n">
-        <v>3928800</v>
+        <v>6379000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>420.8982555962246</v>
+        <v>421.3554771585211</v>
       </c>
       <c r="C190" t="n">
-        <v>421.8424537826169</v>
+        <v>425.9770135204084</v>
       </c>
       <c r="D190" t="n">
-        <v>412.5099054894139</v>
+        <v>419.546608111588</v>
       </c>
       <c r="E190" t="n">
-        <v>415.4319152832031</v>
+        <v>425.5695190429688</v>
       </c>
       <c r="F190" t="n">
-        <v>6379000</v>
+        <v>5800500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>421.3554771585211</v>
+        <v>424.5358632950858</v>
       </c>
       <c r="C191" t="n">
-        <v>425.9770135204084</v>
+        <v>428.1337042740362</v>
       </c>
       <c r="D191" t="n">
-        <v>419.546608111588</v>
+        <v>421.236174203027</v>
       </c>
       <c r="E191" t="n">
-        <v>425.5695190429688</v>
+        <v>422.995361328125</v>
       </c>
       <c r="F191" t="n">
-        <v>5800500</v>
+        <v>3859200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>424.5358632950858</v>
+        <v>424.4961077137118</v>
       </c>
       <c r="C192" t="n">
-        <v>428.1337042740362</v>
+        <v>431.6421079373234</v>
       </c>
       <c r="D192" t="n">
-        <v>421.236174203027</v>
+        <v>420.9280818552513</v>
       </c>
       <c r="E192" t="n">
-        <v>422.995361328125</v>
+        <v>429.0381469726562</v>
       </c>
       <c r="F192" t="n">
-        <v>3859200</v>
+        <v>5566000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>424.4961077137118</v>
+        <v>429.0282351931601</v>
       </c>
       <c r="C193" t="n">
-        <v>431.6421079373234</v>
+        <v>430.2109246052771</v>
       </c>
       <c r="D193" t="n">
-        <v>420.9280818552513</v>
+        <v>421.0572973965209</v>
       </c>
       <c r="E193" t="n">
-        <v>429.0381469726562</v>
+        <v>422.0213623046875</v>
       </c>
       <c r="F193" t="n">
-        <v>5566000</v>
+        <v>3798600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>429.0282351931601</v>
+        <v>423.8600586972866</v>
       </c>
       <c r="C194" t="n">
-        <v>430.2109246052771</v>
+        <v>428.9089563935811</v>
       </c>
       <c r="D194" t="n">
-        <v>421.0572973965209</v>
+        <v>422.9258089520534</v>
       </c>
       <c r="E194" t="n">
-        <v>422.0213623046875</v>
+        <v>426.4640197753906</v>
       </c>
       <c r="F194" t="n">
-        <v>3798600</v>
+        <v>3863800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>423.8600586972866</v>
+        <v>428.3623316954033</v>
       </c>
       <c r="C195" t="n">
-        <v>428.9089563935811</v>
+        <v>429.5052877671748</v>
       </c>
       <c r="D195" t="n">
-        <v>422.9258089520534</v>
+        <v>419.2087042833569</v>
       </c>
       <c r="E195" t="n">
-        <v>426.4640197753906</v>
+        <v>422.587890625</v>
       </c>
       <c r="F195" t="n">
-        <v>3863800</v>
+        <v>5135900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>428.3623316954033</v>
+        <v>416.9227440878186</v>
       </c>
       <c r="C196" t="n">
-        <v>429.5052877671748</v>
+        <v>421.5144651938549</v>
       </c>
       <c r="D196" t="n">
-        <v>419.2087042833569</v>
+        <v>411.8340829429332</v>
       </c>
       <c r="E196" t="n">
-        <v>422.587890625</v>
+        <v>415.9586791992188</v>
       </c>
       <c r="F196" t="n">
-        <v>5135900</v>
+        <v>6764800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>416.9227440878186</v>
+        <v>446.6398026289249</v>
       </c>
       <c r="C197" t="n">
-        <v>421.5144651938549</v>
+        <v>458.7949371104763</v>
       </c>
       <c r="D197" t="n">
-        <v>411.8340829429332</v>
+        <v>417.7973820738866</v>
       </c>
       <c r="E197" t="n">
-        <v>415.9586791992188</v>
+        <v>420.7889709472656</v>
       </c>
       <c r="F197" t="n">
-        <v>6764800</v>
+        <v>13281900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>446.6398026289249</v>
+        <v>424.1085101449368</v>
       </c>
       <c r="C198" t="n">
-        <v>458.7949371104763</v>
+        <v>434.7927210350189</v>
       </c>
       <c r="D198" t="n">
-        <v>417.7973820738866</v>
+        <v>422.4984292637336</v>
       </c>
       <c r="E198" t="n">
-        <v>420.7889709472656</v>
+        <v>423.4823608398438</v>
       </c>
       <c r="F198" t="n">
-        <v>13281900</v>
+        <v>10718100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>424.1085101449368</v>
+        <v>424.6352826432401</v>
       </c>
       <c r="C199" t="n">
-        <v>434.7927210350189</v>
+        <v>428.3821997886642</v>
       </c>
       <c r="D199" t="n">
-        <v>422.4984292637336</v>
+        <v>414.8256906800468</v>
       </c>
       <c r="E199" t="n">
-        <v>423.4823608398438</v>
+        <v>418.9701538085938</v>
       </c>
       <c r="F199" t="n">
-        <v>10718100</v>
+        <v>4818800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>424.6352826432401</v>
+        <v>419.8944835510819</v>
       </c>
       <c r="C200" t="n">
-        <v>428.3821997886642</v>
+        <v>434.3256119583864</v>
       </c>
       <c r="D200" t="n">
-        <v>414.8256906800468</v>
+        <v>417.926589996571</v>
       </c>
       <c r="E200" t="n">
-        <v>418.9701538085938</v>
+        <v>433.6795959472656</v>
       </c>
       <c r="F200" t="n">
-        <v>4818800</v>
+        <v>6833600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>419.8944835510819</v>
+        <v>432.2881481663885</v>
       </c>
       <c r="C201" t="n">
-        <v>434.3256119583864</v>
+        <v>433.6497590080594</v>
       </c>
       <c r="D201" t="n">
-        <v>417.926589996571</v>
+        <v>427.0702778038668</v>
       </c>
       <c r="E201" t="n">
-        <v>433.6795959472656</v>
+        <v>428.67041015625</v>
       </c>
       <c r="F201" t="n">
-        <v>6833600</v>
+        <v>4234100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>432.2881481663885</v>
+        <v>425.6490319049457</v>
       </c>
       <c r="C202" t="n">
-        <v>433.6497590080594</v>
+        <v>427.8554470044401</v>
       </c>
       <c r="D202" t="n">
-        <v>427.0702778038668</v>
+        <v>417.8272001430648</v>
       </c>
       <c r="E202" t="n">
-        <v>428.67041015625</v>
+        <v>420.9678649902344</v>
       </c>
       <c r="F202" t="n">
-        <v>4234100</v>
+        <v>4868700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>425.6490319049457</v>
+        <v>422.6375605105379</v>
       </c>
       <c r="C203" t="n">
-        <v>427.8554470044401</v>
+        <v>426.3745593613837</v>
       </c>
       <c r="D203" t="n">
-        <v>417.8272001430648</v>
+        <v>416.3562613820867</v>
       </c>
       <c r="E203" t="n">
-        <v>420.9678649902344</v>
+        <v>418.1651000976562</v>
       </c>
       <c r="F203" t="n">
-        <v>4868700</v>
+        <v>3752500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>422.6375605105379</v>
+        <v>419.9242977601041</v>
       </c>
       <c r="C204" t="n">
-        <v>426.3745593613837</v>
+        <v>420.2920285503067</v>
       </c>
       <c r="D204" t="n">
-        <v>416.3562613820867</v>
+        <v>410.0153117846154</v>
       </c>
       <c r="E204" t="n">
-        <v>418.1651000976562</v>
+        <v>415.0841064453125</v>
       </c>
       <c r="F204" t="n">
-        <v>3752500</v>
+        <v>4615700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>419.9242977601041</v>
+        <v>417.3600694454911</v>
       </c>
       <c r="C205" t="n">
-        <v>420.2920285503067</v>
+        <v>427.8256258440344</v>
       </c>
       <c r="D205" t="n">
-        <v>410.0153117846154</v>
+        <v>412.5695600114177</v>
       </c>
       <c r="E205" t="n">
-        <v>415.0841064453125</v>
+        <v>426.1658630371094</v>
       </c>
       <c r="F205" t="n">
-        <v>4615700</v>
+        <v>5917300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>417.3600694454911</v>
+        <v>425.6390950681477</v>
       </c>
       <c r="C206" t="n">
-        <v>427.8256258440344</v>
+        <v>429.0381479748715</v>
       </c>
       <c r="D206" t="n">
-        <v>412.5695600114177</v>
+        <v>417.7774999531414</v>
       </c>
       <c r="E206" t="n">
-        <v>426.1658630371094</v>
+        <v>417.9961547851562</v>
       </c>
       <c r="F206" t="n">
-        <v>5917300</v>
+        <v>5257900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>425.6390950681477</v>
+        <v>412.6490895753043</v>
       </c>
       <c r="C207" t="n">
-        <v>429.0381479748715</v>
+        <v>424.7247269708298</v>
       </c>
       <c r="D207" t="n">
-        <v>417.7774999531414</v>
+        <v>408.7729631722832</v>
       </c>
       <c r="E207" t="n">
-        <v>417.9961547851562</v>
+        <v>418.8906555175781</v>
       </c>
       <c r="F207" t="n">
-        <v>5257900</v>
+        <v>3647500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>412.6490895753043</v>
+        <v>419.4173861384651</v>
       </c>
       <c r="C208" t="n">
-        <v>424.7247269708298</v>
+        <v>420.2224265621711</v>
       </c>
       <c r="D208" t="n">
-        <v>408.7729631722832</v>
+        <v>411.5259760202005</v>
       </c>
       <c r="E208" t="n">
-        <v>418.8906555175781</v>
+        <v>411.8638916015625</v>
       </c>
       <c r="F208" t="n">
-        <v>3647500</v>
+        <v>3920900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>419.4173861384651</v>
+        <v>414.8753627675596</v>
       </c>
       <c r="C209" t="n">
-        <v>420.2224265621711</v>
+        <v>416.7736773978178</v>
       </c>
       <c r="D209" t="n">
-        <v>411.5259760202005</v>
+        <v>410.7905301162958</v>
       </c>
       <c r="E209" t="n">
-        <v>411.8638916015625</v>
+        <v>412.8180236816406</v>
       </c>
       <c r="F209" t="n">
-        <v>3920900</v>
+        <v>3209600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>414.8753627675596</v>
+        <v>413.0168058398714</v>
       </c>
       <c r="C210" t="n">
-        <v>416.7736773978178</v>
+        <v>413.4541155038886</v>
       </c>
       <c r="D210" t="n">
-        <v>410.7905301162958</v>
+        <v>404.1812276531693</v>
       </c>
       <c r="E210" t="n">
-        <v>412.8180236816406</v>
+        <v>405.0558166503906</v>
       </c>
       <c r="F210" t="n">
-        <v>3209600</v>
+        <v>5266300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>413.0168058398714</v>
+        <v>400.7225079776698</v>
       </c>
       <c r="C211" t="n">
-        <v>413.4541155038886</v>
+        <v>413.8118915184926</v>
       </c>
       <c r="D211" t="n">
-        <v>404.1812276531693</v>
+        <v>395.3654798398698</v>
       </c>
       <c r="E211" t="n">
-        <v>405.0558166503906</v>
+        <v>410.2239990234375</v>
       </c>
       <c r="F211" t="n">
-        <v>5266300</v>
+        <v>5399000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>400.7225079776698</v>
+        <v>412.728574598682</v>
       </c>
       <c r="C212" t="n">
-        <v>413.8118915184926</v>
+        <v>414.4181828862322</v>
       </c>
       <c r="D212" t="n">
-        <v>395.3654798398698</v>
+        <v>399.9373426764689</v>
       </c>
       <c r="E212" t="n">
-        <v>410.2239990234375</v>
+        <v>401.4977416992188</v>
       </c>
       <c r="F212" t="n">
-        <v>5399000</v>
+        <v>4712400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>412.728574598682</v>
+        <v>399.1322922233893</v>
       </c>
       <c r="C213" t="n">
-        <v>414.4181828862322</v>
+        <v>408.1269250227407</v>
       </c>
       <c r="D213" t="n">
-        <v>399.9373426764689</v>
+        <v>398.2079910410381</v>
       </c>
       <c r="E213" t="n">
-        <v>401.4977416992188</v>
+        <v>404.5886840820312</v>
       </c>
       <c r="F213" t="n">
-        <v>4712400</v>
+        <v>4095900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>399.1322922233893</v>
+        <v>406.0993979544625</v>
       </c>
       <c r="C214" t="n">
-        <v>408.1269250227407</v>
+        <v>410.5420430290281</v>
       </c>
       <c r="D214" t="n">
-        <v>398.2079910410381</v>
+        <v>405.4931153467772</v>
       </c>
       <c r="E214" t="n">
-        <v>404.5886840820312</v>
+        <v>406.238525390625</v>
       </c>
       <c r="F214" t="n">
-        <v>4095900</v>
+        <v>3182200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>406.0993979544625</v>
+        <v>406.4969587134404</v>
       </c>
       <c r="C215" t="n">
-        <v>410.5420430290281</v>
+        <v>408.3853248271201</v>
       </c>
       <c r="D215" t="n">
-        <v>405.4931153467772</v>
+        <v>398.8639668658938</v>
       </c>
       <c r="E215" t="n">
-        <v>406.238525390625</v>
+        <v>399.7286376953125</v>
       </c>
       <c r="F215" t="n">
-        <v>3182200</v>
+        <v>3398900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>406.4969587134404</v>
+        <v>398.5260459867315</v>
       </c>
       <c r="C216" t="n">
-        <v>408.3853248271201</v>
+        <v>404.7079813067043</v>
       </c>
       <c r="D216" t="n">
-        <v>398.8639668658938</v>
+        <v>398.0489726285335</v>
       </c>
       <c r="E216" t="n">
-        <v>399.7286376953125</v>
+        <v>403.1078186035156</v>
       </c>
       <c r="F216" t="n">
-        <v>3398900</v>
+        <v>3317200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>398.5260459867315</v>
+        <v>403.1078338152345</v>
       </c>
       <c r="C217" t="n">
-        <v>404.7079813067043</v>
+        <v>404.8272573401537</v>
       </c>
       <c r="D217" t="n">
-        <v>398.0489726285335</v>
+        <v>396.1506729824118</v>
       </c>
       <c r="E217" t="n">
-        <v>403.1078186035156</v>
+        <v>396.6177978515625</v>
       </c>
       <c r="F217" t="n">
-        <v>3317200</v>
+        <v>4170200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>403.1078338152345</v>
+        <v>395.5642702547857</v>
       </c>
       <c r="C218" t="n">
-        <v>404.8272573401537</v>
+        <v>400.7125617691589</v>
       </c>
       <c r="D218" t="n">
-        <v>396.1506729824118</v>
+        <v>394.1330805188561</v>
       </c>
       <c r="E218" t="n">
-        <v>396.6177978515625</v>
+        <v>399.2714538574219</v>
       </c>
       <c r="F218" t="n">
-        <v>4170200</v>
+        <v>3476400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>395.5642702547857</v>
+        <v>396.1308110575831</v>
       </c>
       <c r="C219" t="n">
-        <v>400.7125617691589</v>
+        <v>396.4587781552261</v>
       </c>
       <c r="D219" t="n">
-        <v>394.1330805188561</v>
+        <v>389.0344923640698</v>
       </c>
       <c r="E219" t="n">
-        <v>399.2714538574219</v>
+        <v>393.1988525390625</v>
       </c>
       <c r="F219" t="n">
-        <v>3476400</v>
+        <v>5295100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>396.1308110575831</v>
+        <v>394.9977452515739</v>
       </c>
       <c r="C220" t="n">
-        <v>396.4587781552261</v>
+        <v>396.3494379061722</v>
       </c>
       <c r="D220" t="n">
-        <v>389.0344923640698</v>
+        <v>391.1017523988161</v>
       </c>
       <c r="E220" t="n">
-        <v>393.1988525390625</v>
+        <v>391.5191650390625</v>
       </c>
       <c r="F220" t="n">
-        <v>5295100</v>
+        <v>3605100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>394.9977452515739</v>
+        <v>392.1552670341675</v>
       </c>
       <c r="C221" t="n">
-        <v>396.3494379061722</v>
+        <v>394.3716001815704</v>
       </c>
       <c r="D221" t="n">
-        <v>391.1017523988161</v>
+        <v>383.9656746212449</v>
       </c>
       <c r="E221" t="n">
-        <v>391.5191650390625</v>
+        <v>386.2317199707031</v>
       </c>
       <c r="F221" t="n">
-        <v>3605100</v>
+        <v>5268500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>392.1552670341675</v>
+        <v>385.8739371481429</v>
       </c>
       <c r="C222" t="n">
-        <v>394.3716001815704</v>
+        <v>390.3066337673781</v>
       </c>
       <c r="D222" t="n">
-        <v>383.9656746212449</v>
+        <v>381.4809738935195</v>
       </c>
       <c r="E222" t="n">
-        <v>386.2317199707031</v>
+        <v>382.4947509765625</v>
       </c>
       <c r="F222" t="n">
-        <v>5268500</v>
+        <v>4497200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>385.8739371481429</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="C223" t="n">
-        <v>390.3066337673781</v>
+        <v>391.250826577815</v>
       </c>
       <c r="D223" t="n">
-        <v>381.4809738935195</v>
+        <v>383.6377017073448</v>
       </c>
       <c r="E223" t="n">
-        <v>382.4947509765625</v>
+        <v>387.7225341796875</v>
       </c>
       <c r="F223" t="n">
-        <v>4497200</v>
+        <v>4879600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>383.6377017073448</v>
+        <v>388.6468854751683</v>
       </c>
       <c r="C224" t="n">
-        <v>391.250826577815</v>
+        <v>397.1345997494796</v>
       </c>
       <c r="D224" t="n">
-        <v>383.6377017073448</v>
+        <v>388.4679640045169</v>
       </c>
       <c r="E224" t="n">
-        <v>387.7225341796875</v>
+        <v>396.3196411132812</v>
       </c>
       <c r="F224" t="n">
-        <v>4879600</v>
+        <v>4683900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>388.6468854751683</v>
+        <v>395.3654892531199</v>
       </c>
       <c r="C225" t="n">
-        <v>397.1345997494796</v>
+        <v>396.5879726878088</v>
       </c>
       <c r="D225" t="n">
-        <v>388.4679640045169</v>
+        <v>393.1988379276376</v>
       </c>
       <c r="E225" t="n">
-        <v>396.3196411132812</v>
+        <v>394.1629028320312</v>
       </c>
       <c r="F225" t="n">
-        <v>4683900</v>
+        <v>2655000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>395.3654892531199</v>
+        <v>393.9044956601749</v>
       </c>
       <c r="C226" t="n">
-        <v>396.5879726878088</v>
+        <v>403.7637998223176</v>
       </c>
       <c r="D226" t="n">
-        <v>393.1988379276376</v>
+        <v>393.5864770723492</v>
       </c>
       <c r="E226" t="n">
-        <v>394.1629028320312</v>
+        <v>398.5558776855469</v>
       </c>
       <c r="F226" t="n">
-        <v>2655000</v>
+        <v>3557000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>393.9044956601749</v>
+        <v>394.4411932932572</v>
       </c>
       <c r="C227" t="n">
-        <v>403.7637998223176</v>
+        <v>397.4327821218027</v>
       </c>
       <c r="D227" t="n">
-        <v>393.5864770723492</v>
+        <v>391.360158894761</v>
       </c>
       <c r="E227" t="n">
-        <v>398.5558776855469</v>
+        <v>392.63232421875</v>
       </c>
       <c r="F227" t="n">
-        <v>3557000</v>
+        <v>3668200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>394.4411932932572</v>
+        <v>393.99396168554</v>
       </c>
       <c r="C228" t="n">
-        <v>397.4327821218027</v>
+        <v>394.3119802653936</v>
       </c>
       <c r="D228" t="n">
-        <v>391.360158894761</v>
+        <v>390.2569628122352</v>
       </c>
       <c r="E228" t="n">
-        <v>392.63232421875</v>
+        <v>390.5451965332031</v>
       </c>
       <c r="F228" t="n">
-        <v>3668200</v>
+        <v>2455500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
-        <v>393.99396168554</v>
+        <v>391.1116881429976</v>
       </c>
       <c r="C229" t="n">
-        <v>394.3119802653936</v>
+        <v>392.0757530584314</v>
       </c>
       <c r="D229" t="n">
-        <v>390.2569628122352</v>
+        <v>385.3372471573089</v>
       </c>
       <c r="E229" t="n">
-        <v>390.5451965332031</v>
+        <v>387.02685546875</v>
       </c>
       <c r="F229" t="n">
-        <v>2455500</v>
+        <v>5748000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>391.1116881429976</v>
+        <v>389.6804891479818</v>
       </c>
       <c r="C230" t="n">
-        <v>392.0757530584314</v>
+        <v>397.1544867752485</v>
       </c>
       <c r="D230" t="n">
-        <v>385.3372471573089</v>
+        <v>389.3823372557507</v>
       </c>
       <c r="E230" t="n">
-        <v>387.02685546875</v>
+        <v>393.8746643066406</v>
       </c>
       <c r="F230" t="n">
-        <v>5748000</v>
+        <v>3716200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>389.6804891479818</v>
+        <v>396.8264835430965</v>
       </c>
       <c r="C231" t="n">
-        <v>397.1544867752485</v>
+        <v>398.6850647467894</v>
       </c>
       <c r="D231" t="n">
-        <v>389.3823372557507</v>
+        <v>394.083395182361</v>
       </c>
       <c r="E231" t="n">
-        <v>393.8746643066406</v>
+        <v>397.214111328125</v>
       </c>
       <c r="F231" t="n">
-        <v>3716200</v>
+        <v>3265300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>396.8264835430965</v>
+        <v>397.5719145517662</v>
       </c>
       <c r="C232" t="n">
-        <v>398.6850647467894</v>
+        <v>402.6804729256668</v>
       </c>
       <c r="D232" t="n">
-        <v>394.083395182361</v>
+        <v>392.8807991736857</v>
       </c>
       <c r="E232" t="n">
-        <v>397.214111328125</v>
+        <v>398.4862976074219</v>
       </c>
       <c r="F232" t="n">
-        <v>3265300</v>
+        <v>5488900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>397.5719145517662</v>
+        <v>394.6200883073414</v>
       </c>
       <c r="C233" t="n">
-        <v>402.6804729256668</v>
+        <v>399.7684103646221</v>
       </c>
       <c r="D233" t="n">
-        <v>392.8807991736857</v>
+        <v>392.7814343556134</v>
       </c>
       <c r="E233" t="n">
-        <v>398.4862976074219</v>
+        <v>394.7095642089844</v>
       </c>
       <c r="F233" t="n">
-        <v>5488900</v>
+        <v>5565400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>394.6200883073414</v>
+        <v>389.9985512542227</v>
       </c>
       <c r="C234" t="n">
-        <v>399.7684103646221</v>
+        <v>401.4182544062181</v>
       </c>
       <c r="D234" t="n">
-        <v>392.7814343556134</v>
+        <v>388.0505547204797</v>
       </c>
       <c r="E234" t="n">
-        <v>394.7095642089844</v>
+        <v>398.3869018554688</v>
       </c>
       <c r="F234" t="n">
-        <v>5565400</v>
+        <v>7049400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>389.9985512542227</v>
+        <v>402.6904143062879</v>
       </c>
       <c r="C235" t="n">
-        <v>401.4182544062181</v>
+        <v>404.0420766863295</v>
       </c>
       <c r="D235" t="n">
-        <v>388.0505547204797</v>
+        <v>375.7661756497595</v>
       </c>
       <c r="E235" t="n">
-        <v>398.3869018554688</v>
+        <v>390.6545104980469</v>
       </c>
       <c r="F235" t="n">
-        <v>7049400</v>
+        <v>7735200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>402.6904143062879</v>
+        <v>393.5765028166354</v>
       </c>
       <c r="C236" t="n">
-        <v>404.0420766863295</v>
+        <v>396.826479685953</v>
       </c>
       <c r="D236" t="n">
-        <v>375.7661756497595</v>
+        <v>385.2279163988086</v>
       </c>
       <c r="E236" t="n">
-        <v>390.6545104980469</v>
+        <v>385.9037475585938</v>
       </c>
       <c r="F236" t="n">
-        <v>7735200</v>
+        <v>4339900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>393.5765028166354</v>
+        <v>388.0306670998862</v>
       </c>
       <c r="C237" t="n">
-        <v>396.826479685953</v>
+        <v>389.3326475544677</v>
       </c>
       <c r="D237" t="n">
-        <v>385.2279163988086</v>
+        <v>373.5995091898494</v>
       </c>
       <c r="E237" t="n">
-        <v>385.9037475585938</v>
+        <v>376.7699890136719</v>
       </c>
       <c r="F237" t="n">
-        <v>4339900</v>
+        <v>7478400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,25 +6605,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>388.0306670998862</v>
+        <v>381.4400024414062</v>
       </c>
       <c r="C238" t="n">
-        <v>389.3326475544677</v>
+        <v>386.4599914550781</v>
       </c>
       <c r="D238" t="n">
-        <v>373.5995091898494</v>
+        <v>379.2799987792969</v>
       </c>
       <c r="E238" t="n">
-        <v>376.7699890136719</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="F238" t="n">
-        <v>7478400</v>
+        <v>4474000</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>381.4400024414062</v>
+        <v>383.5499877929688</v>
       </c>
       <c r="C239" t="n">
-        <v>386.4599914550781</v>
+        <v>383.7999877929688</v>
       </c>
       <c r="D239" t="n">
-        <v>379.2799987792969</v>
+        <v>375.5</v>
       </c>
       <c r="E239" t="n">
-        <v>383.5499877929688</v>
+        <v>375.9299926757812</v>
       </c>
       <c r="F239" t="n">
-        <v>4474000</v>
+        <v>4391400</v>
       </c>
       <c r="G239" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>383.5499877929688</v>
+        <v>375.8999938964844</v>
       </c>
       <c r="C240" t="n">
-        <v>383.7999877929688</v>
+        <v>380.2200012207031</v>
       </c>
       <c r="D240" t="n">
-        <v>375.5</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="E240" t="n">
-        <v>375.9299926757812</v>
+        <v>375.260009765625</v>
       </c>
       <c r="F240" t="n">
-        <v>4391400</v>
+        <v>4414900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>375.8999938964844</v>
+        <v>376.4500122070312</v>
       </c>
       <c r="C241" t="n">
-        <v>380.2200012207031</v>
+        <v>380.5</v>
       </c>
       <c r="D241" t="n">
-        <v>373.6300048828125</v>
+        <v>374.2000122070312</v>
       </c>
       <c r="E241" t="n">
-        <v>375.260009765625</v>
+        <v>375.2099914550781</v>
       </c>
       <c r="F241" t="n">
-        <v>4414900</v>
+        <v>4833700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>376.4500122070312</v>
+        <v>375.2900085449219</v>
       </c>
       <c r="C242" t="n">
-        <v>380.5</v>
+        <v>378.489990234375</v>
       </c>
       <c r="D242" t="n">
-        <v>374.2000122070312</v>
+        <v>372.4200134277344</v>
       </c>
       <c r="E242" t="n">
-        <v>375.2099914550781</v>
+        <v>376.8999938964844</v>
       </c>
       <c r="F242" t="n">
-        <v>4833700</v>
+        <v>8606300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>375.2900085449219</v>
+        <v>377.8699951171875</v>
       </c>
       <c r="C243" t="n">
-        <v>378.489990234375</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="D243" t="n">
-        <v>372.4200134277344</v>
+        <v>373.8200073242188</v>
       </c>
       <c r="E243" t="n">
-        <v>376.8999938964844</v>
+        <v>377.5599975585938</v>
       </c>
       <c r="F243" t="n">
-        <v>8606300</v>
+        <v>5712300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>377.8699951171875</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>378.9500122070312</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="D244" t="n">
-        <v>373.8200073242188</v>
+        <v>372.4100036621094</v>
       </c>
       <c r="E244" t="n">
-        <v>377.5599975585938</v>
+        <v>372.9500122070312</v>
       </c>
       <c r="F244" t="n">
-        <v>5712300</v>
+        <v>4495000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>381.3900146484375</v>
+        <v>370.8900146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>381.3900146484375</v>
+        <v>372.6099853515625</v>
       </c>
       <c r="D245" t="n">
-        <v>372.4100036621094</v>
+        <v>366</v>
       </c>
       <c r="E245" t="n">
-        <v>372.9500122070312</v>
+        <v>371.2900085449219</v>
       </c>
       <c r="F245" t="n">
-        <v>4495000</v>
+        <v>3859300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>370.8900146484375</v>
+        <v>371.9200134277344</v>
       </c>
       <c r="C246" t="n">
-        <v>372.6099853515625</v>
+        <v>375.2799987792969</v>
       </c>
       <c r="D246" t="n">
-        <v>366</v>
+        <v>368.5</v>
       </c>
       <c r="E246" t="n">
-        <v>371.2900085449219</v>
+        <v>375.010009765625</v>
       </c>
       <c r="F246" t="n">
-        <v>3859300</v>
+        <v>4651000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>371.9200134277344</v>
+        <v>375.9500122070312</v>
       </c>
       <c r="C247" t="n">
-        <v>375.2799987792969</v>
+        <v>379.1700134277344</v>
       </c>
       <c r="D247" t="n">
-        <v>368.5</v>
+        <v>371.1700134277344</v>
       </c>
       <c r="E247" t="n">
-        <v>375.010009765625</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="F247" t="n">
-        <v>4651000</v>
+        <v>4077400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>375.9500122070312</v>
+        <v>376.3599853515625</v>
       </c>
       <c r="C248" t="n">
-        <v>379.1700134277344</v>
+        <v>380.9800109863281</v>
       </c>
       <c r="D248" t="n">
-        <v>371.1700134277344</v>
+        <v>374.5599975585938</v>
       </c>
       <c r="E248" t="n">
-        <v>376.5899963378906</v>
+        <v>377.8299865722656</v>
       </c>
       <c r="F248" t="n">
-        <v>4077400</v>
+        <v>4677100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>376.3599853515625</v>
+        <v>374.8800048828125</v>
       </c>
       <c r="C249" t="n">
-        <v>380.9800109863281</v>
+        <v>376.5899963378906</v>
       </c>
       <c r="D249" t="n">
-        <v>374.5599975585938</v>
+        <v>371.3299865722656</v>
       </c>
       <c r="E249" t="n">
-        <v>377.8299865722656</v>
+        <v>374.9400024414062</v>
       </c>
       <c r="F249" t="n">
-        <v>4677100</v>
+        <v>3284700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>374.8800048828125</v>
+        <v>374.9299926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>376.5899963378906</v>
+        <v>374.9299926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>371.3299865722656</v>
+        <v>365.7200012207031</v>
       </c>
       <c r="E250" t="n">
-        <v>374.9400024414062</v>
+        <v>367.0799865722656</v>
       </c>
       <c r="F250" t="n">
-        <v>3284700</v>
+        <v>4788300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>374.9299926757812</v>
+        <v>367.989990234375</v>
       </c>
       <c r="C251" t="n">
-        <v>374.9299926757812</v>
+        <v>371.8599853515625</v>
       </c>
       <c r="D251" t="n">
-        <v>365.7200012207031</v>
+        <v>362.6000061035156</v>
       </c>
       <c r="E251" t="n">
-        <v>367.0799865722656</v>
+        <v>365.2000122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>4788300</v>
+        <v>3940700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>367.989990234375</v>
+        <v>365.1400146484375</v>
       </c>
       <c r="C252" t="n">
-        <v>371.8599853515625</v>
+        <v>372.6749877929688</v>
       </c>
       <c r="D252" t="n">
-        <v>362.6000061035156</v>
+        <v>364.4700012207031</v>
       </c>
       <c r="E252" t="n">
-        <v>365.2000122070312</v>
+        <v>371.8999938964844</v>
       </c>
       <c r="F252" t="n">
-        <v>3940700</v>
+        <v>3292808</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10530,34 +10530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="D2" t="n">
         <v>365.2</v>
       </c>
-      <c r="D2" t="n">
-        <v>367.08</v>
-      </c>
       <c r="E2" t="n">
-        <v>367.99</v>
+        <v>365.14</v>
       </c>
       <c r="F2" t="n">
-        <v>371.8599</v>
+        <v>372.675</v>
       </c>
       <c r="G2" t="n">
-        <v>362.6</v>
+        <v>364.47</v>
       </c>
       <c r="H2" t="n">
-        <v>3933201</v>
+        <v>3292808</v>
       </c>
       <c r="I2" t="n">
         <v>4927314</v>
       </c>
       <c r="J2" t="n">
-        <v>327801634816</v>
+        <v>333815513088</v>
       </c>
       <c r="K2" t="n">
-        <v>23.470438</v>
+        <v>23.901028</v>
       </c>
       <c r="L2" t="n">
-        <v>16.15201</v>
+        <v>16.448336</v>
       </c>
       <c r="M2" t="n">
         <v>15.56</v>
@@ -10596,7 +10596,7 @@
         <v>108.781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.3572042</v>
+        <v>3.4187956</v>
       </c>
       <c r="Z2" t="n">
         <v>0.615</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:41</t>
+          <t>2026-10-03 05:34:44</t>
         </is>
       </c>
     </row>

--- a/data/UNH_data.xlsx
+++ b/data/UNH_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>347.9840761494036</v>
+        <v>351.6660223866534</v>
       </c>
       <c r="C2" t="n">
-        <v>358.4552554876992</v>
+        <v>353.1173669865184</v>
       </c>
       <c r="D2" t="n">
-        <v>347.3606614365734</v>
+        <v>347.8476817099931</v>
       </c>
       <c r="E2" t="n">
-        <v>350.8575744628906</v>
+        <v>349.4646301269531</v>
       </c>
       <c r="F2" t="n">
-        <v>13494800</v>
+        <v>7181700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>351.6660223866534</v>
+        <v>350.0880452744822</v>
       </c>
       <c r="C3" t="n">
-        <v>353.1173669865184</v>
+        <v>355.2603182962649</v>
       </c>
       <c r="D3" t="n">
-        <v>347.8476817099931</v>
+        <v>348.77305405812</v>
       </c>
       <c r="E3" t="n">
-        <v>349.4646301269531</v>
+        <v>354.2278137207031</v>
       </c>
       <c r="F3" t="n">
-        <v>7181700</v>
+        <v>7236200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>350.0880452744822</v>
+        <v>357.4129705346734</v>
       </c>
       <c r="C4" t="n">
-        <v>355.2603182962649</v>
+        <v>364.9132683871306</v>
       </c>
       <c r="D4" t="n">
-        <v>348.77305405812</v>
+        <v>356.3122744619989</v>
       </c>
       <c r="E4" t="n">
-        <v>354.2278137207031</v>
+        <v>360.325439453125</v>
       </c>
       <c r="F4" t="n">
-        <v>7236200</v>
+        <v>9438300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>357.4129705346734</v>
+        <v>362.8580018323341</v>
       </c>
       <c r="C5" t="n">
-        <v>364.9132683871306</v>
+        <v>366.4620474561767</v>
       </c>
       <c r="D5" t="n">
-        <v>356.3122744619989</v>
+        <v>356.5850326317519</v>
       </c>
       <c r="E5" t="n">
-        <v>360.325439453125</v>
+        <v>358.1532897949219</v>
       </c>
       <c r="F5" t="n">
-        <v>9438300</v>
+        <v>8759800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>362.8580018323341</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="C6" t="n">
-        <v>366.4620474561767</v>
+        <v>359.8188927085395</v>
       </c>
       <c r="D6" t="n">
-        <v>356.5850326317519</v>
+        <v>343.3669828865441</v>
       </c>
       <c r="E6" t="n">
-        <v>358.1532897949219</v>
+        <v>345.3053588867188</v>
       </c>
       <c r="F6" t="n">
-        <v>8759800</v>
+        <v>13141900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>359.8188927085395</v>
+        <v>345.5391423923842</v>
       </c>
       <c r="C7" t="n">
-        <v>359.8188927085395</v>
+        <v>349.8445144711653</v>
       </c>
       <c r="D7" t="n">
-        <v>343.3669828865441</v>
+        <v>344.155989405705</v>
       </c>
       <c r="E7" t="n">
-        <v>345.3053588867188</v>
+        <v>349.3574829101562</v>
       </c>
       <c r="F7" t="n">
-        <v>13141900</v>
+        <v>5659400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>345.5391423923842</v>
+        <v>345.7437279807031</v>
       </c>
       <c r="C8" t="n">
-        <v>349.8445144711653</v>
+        <v>352.9322890785681</v>
       </c>
       <c r="D8" t="n">
-        <v>344.155989405705</v>
+        <v>344.233912258217</v>
       </c>
       <c r="E8" t="n">
-        <v>349.3574829101562</v>
+        <v>350.5945434570312</v>
       </c>
       <c r="F8" t="n">
-        <v>5659400</v>
+        <v>5974800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>345.7437279807031</v>
+        <v>350.0685366633683</v>
       </c>
       <c r="C9" t="n">
-        <v>352.9322890785681</v>
+        <v>354.7732481537828</v>
       </c>
       <c r="D9" t="n">
-        <v>344.233912258217</v>
+        <v>346.6203451149501</v>
       </c>
       <c r="E9" t="n">
-        <v>350.5945434570312</v>
+        <v>351.7828674316406</v>
       </c>
       <c r="F9" t="n">
-        <v>5974800</v>
+        <v>6579600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B10" t="n">
-        <v>350.0685366633683</v>
+        <v>352.4550184254314</v>
       </c>
       <c r="C10" t="n">
-        <v>354.7732481537828</v>
+        <v>352.6108721017735</v>
       </c>
       <c r="D10" t="n">
-        <v>346.6203451149501</v>
+        <v>345.2079859687916</v>
       </c>
       <c r="E10" t="n">
-        <v>351.7828674316406</v>
+        <v>347.4191284179688</v>
       </c>
       <c r="F10" t="n">
-        <v>6579600</v>
+        <v>5872100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="n">
-        <v>352.4550184254314</v>
+        <v>341.896162102252</v>
       </c>
       <c r="C11" t="n">
-        <v>352.6108721017735</v>
+        <v>349.0945029745603</v>
       </c>
       <c r="D11" t="n">
-        <v>345.2079859687916</v>
+        <v>341.7305582890092</v>
       </c>
       <c r="E11" t="n">
-        <v>347.4191284179688</v>
+        <v>347.3509216308594</v>
       </c>
       <c r="F11" t="n">
-        <v>5872100</v>
+        <v>8608400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B12" t="n">
-        <v>341.896162102252</v>
+        <v>349.2406427804422</v>
       </c>
       <c r="C12" t="n">
-        <v>349.0945029745603</v>
+        <v>356.088306176199</v>
       </c>
       <c r="D12" t="n">
-        <v>341.7305582890092</v>
+        <v>348.2373588311709</v>
       </c>
       <c r="E12" t="n">
-        <v>347.3509216308594</v>
+        <v>355.0265808105469</v>
       </c>
       <c r="F12" t="n">
-        <v>8608400</v>
+        <v>5996500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B13" t="n">
-        <v>349.2406427804422</v>
+        <v>355.6694476256362</v>
       </c>
       <c r="C13" t="n">
-        <v>356.088306176199</v>
+        <v>361.426134922211</v>
       </c>
       <c r="D13" t="n">
-        <v>348.2373588311709</v>
+        <v>352.1238433439322</v>
       </c>
       <c r="E13" t="n">
-        <v>355.0265808105469</v>
+        <v>355.8934631347656</v>
       </c>
       <c r="F13" t="n">
-        <v>5996500</v>
+        <v>6885300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B14" t="n">
-        <v>355.6694476256362</v>
+        <v>354.5199811240022</v>
       </c>
       <c r="C14" t="n">
-        <v>361.426134922211</v>
+        <v>354.5589519694893</v>
       </c>
       <c r="D14" t="n">
-        <v>352.1238433439322</v>
+        <v>348.7145736403219</v>
       </c>
       <c r="E14" t="n">
-        <v>355.8934631347656</v>
+        <v>352.1140441894531</v>
       </c>
       <c r="F14" t="n">
-        <v>6885300</v>
+        <v>7833000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B15" t="n">
-        <v>354.5199811240022</v>
+        <v>346.3573617095742</v>
       </c>
       <c r="C15" t="n">
-        <v>354.5589519694893</v>
+        <v>352.883596703336</v>
       </c>
       <c r="D15" t="n">
-        <v>348.7145736403219</v>
+        <v>344.4677065470185</v>
       </c>
       <c r="E15" t="n">
-        <v>352.1140441894531</v>
+        <v>351.10107421875</v>
       </c>
       <c r="F15" t="n">
-        <v>7833000</v>
+        <v>5756700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B16" t="n">
-        <v>346.3573617095742</v>
+        <v>351.9972042484119</v>
       </c>
       <c r="C16" t="n">
-        <v>352.883596703336</v>
+        <v>355.9421779366814</v>
       </c>
       <c r="D16" t="n">
-        <v>344.4677065470185</v>
+        <v>350.6919631630593</v>
       </c>
       <c r="E16" t="n">
-        <v>351.10107421875</v>
+        <v>353.097900390625</v>
       </c>
       <c r="F16" t="n">
-        <v>5756700</v>
+        <v>5462100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B17" t="n">
-        <v>351.9972042484119</v>
+        <v>354.0719530807468</v>
       </c>
       <c r="C17" t="n">
-        <v>355.9421779366814</v>
+        <v>356.7214060232403</v>
       </c>
       <c r="D17" t="n">
-        <v>350.6919631630593</v>
+        <v>352.0264145317695</v>
       </c>
       <c r="E17" t="n">
-        <v>353.097900390625</v>
+        <v>356.4876403808594</v>
       </c>
       <c r="F17" t="n">
-        <v>5462100</v>
+        <v>7766400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B18" t="n">
-        <v>354.0719530807468</v>
+        <v>370.8063444379755</v>
       </c>
       <c r="C18" t="n">
-        <v>356.7214060232403</v>
+        <v>371.1180517731913</v>
       </c>
       <c r="D18" t="n">
-        <v>352.0264145317695</v>
+        <v>349.3282643556941</v>
       </c>
       <c r="E18" t="n">
-        <v>356.4876403808594</v>
+        <v>358.2993774414062</v>
       </c>
       <c r="F18" t="n">
-        <v>7766400</v>
+        <v>18858700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B19" t="n">
-        <v>370.8063444379755</v>
+        <v>354.8317237421505</v>
       </c>
       <c r="C19" t="n">
-        <v>371.1180517731913</v>
+        <v>356.6532170798153</v>
       </c>
       <c r="D19" t="n">
-        <v>349.3282643556941</v>
+        <v>344.701472908826</v>
       </c>
       <c r="E19" t="n">
-        <v>358.2993774414062</v>
+        <v>346.0456848144531</v>
       </c>
       <c r="F19" t="n">
-        <v>18858700</v>
+        <v>11874900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B20" t="n">
-        <v>354.8317237421505</v>
+        <v>338.5064329398476</v>
       </c>
       <c r="C20" t="n">
-        <v>356.6532170798153</v>
+        <v>345.3443756361395</v>
       </c>
       <c r="D20" t="n">
-        <v>344.701472908826</v>
+        <v>334.6881218381804</v>
       </c>
       <c r="E20" t="n">
-        <v>346.0456848144531</v>
+        <v>335.8082885742188</v>
       </c>
       <c r="F20" t="n">
-        <v>11874900</v>
+        <v>11441900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B21" t="n">
-        <v>338.5064329398476</v>
+        <v>335.4576039784424</v>
       </c>
       <c r="C21" t="n">
-        <v>345.3443756361395</v>
+        <v>337.298567772769</v>
       </c>
       <c r="D21" t="n">
-        <v>334.6881218381804</v>
+        <v>328.3761462441955</v>
       </c>
       <c r="E21" t="n">
-        <v>335.8082885742188</v>
+        <v>332.7009887695312</v>
       </c>
       <c r="F21" t="n">
-        <v>11441900</v>
+        <v>8390800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B22" t="n">
-        <v>335.4576039784424</v>
+        <v>330.3340313465691</v>
       </c>
       <c r="C22" t="n">
-        <v>337.298567772769</v>
+        <v>331.8633175824834</v>
       </c>
       <c r="D22" t="n">
-        <v>328.3761462441955</v>
+        <v>318.1290216159704</v>
       </c>
       <c r="E22" t="n">
-        <v>332.7009887695312</v>
+        <v>325.1325378417969</v>
       </c>
       <c r="F22" t="n">
-        <v>8390800</v>
+        <v>11181400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B23" t="n">
-        <v>330.3340313465691</v>
+        <v>319.1323138584834</v>
       </c>
       <c r="C23" t="n">
-        <v>331.8633175824834</v>
+        <v>327.7722492229931</v>
       </c>
       <c r="D23" t="n">
-        <v>318.1290216159704</v>
+        <v>318.7134738391959</v>
       </c>
       <c r="E23" t="n">
-        <v>325.1325378417969</v>
+        <v>322.2492980957031</v>
       </c>
       <c r="F23" t="n">
-        <v>11181400</v>
+        <v>9646600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B24" t="n">
-        <v>319.1323138584834</v>
+        <v>317.8367876317881</v>
       </c>
       <c r="C24" t="n">
-        <v>327.7722492229931</v>
+        <v>321.6453780396488</v>
       </c>
       <c r="D24" t="n">
-        <v>318.7134738391959</v>
+        <v>315.8107493995538</v>
       </c>
       <c r="E24" t="n">
-        <v>322.2492980957031</v>
+        <v>319.2394409179688</v>
       </c>
       <c r="F24" t="n">
-        <v>9646600</v>
+        <v>9697100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B25" t="n">
-        <v>317.8367876317881</v>
+        <v>320.3888464018165</v>
       </c>
       <c r="C25" t="n">
-        <v>321.6453780396488</v>
+        <v>323.7493462451443</v>
       </c>
       <c r="D25" t="n">
-        <v>315.8107493995538</v>
+        <v>313.1125938905139</v>
       </c>
       <c r="E25" t="n">
-        <v>319.2394409179688</v>
+        <v>313.2197265625</v>
       </c>
       <c r="F25" t="n">
-        <v>9697100</v>
+        <v>7922100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="n">
-        <v>320.3888464018165</v>
+        <v>311.3690195806419</v>
       </c>
       <c r="C26" t="n">
-        <v>323.7493462451443</v>
+        <v>316.1321727657366</v>
       </c>
       <c r="D26" t="n">
-        <v>313.1125938905139</v>
+        <v>306.011672436569</v>
       </c>
       <c r="E26" t="n">
-        <v>313.2197265625</v>
+        <v>315.8009948730469</v>
       </c>
       <c r="F26" t="n">
-        <v>7922100</v>
+        <v>9402900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="n">
-        <v>311.3690195806419</v>
+        <v>311.6904400245728</v>
       </c>
       <c r="C27" t="n">
-        <v>316.1321727657366</v>
+        <v>315.8399583185172</v>
       </c>
       <c r="D27" t="n">
-        <v>306.011672436569</v>
+        <v>308.9436046905141</v>
       </c>
       <c r="E27" t="n">
-        <v>315.8009948730469</v>
+        <v>313.2391967773438</v>
       </c>
       <c r="F27" t="n">
-        <v>9402900</v>
+        <v>9283800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B28" t="n">
-        <v>311.6904400245728</v>
+        <v>314.9145846167937</v>
       </c>
       <c r="C28" t="n">
-        <v>315.8399583185172</v>
+        <v>319.3563099222018</v>
       </c>
       <c r="D28" t="n">
-        <v>308.9436046905141</v>
+        <v>311.5833055007609</v>
       </c>
       <c r="E28" t="n">
-        <v>313.2391967773438</v>
+        <v>318.9569702148438</v>
       </c>
       <c r="F28" t="n">
-        <v>9283800</v>
+        <v>7157800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B29" t="n">
-        <v>314.9145846167937</v>
+        <v>319.931043202934</v>
       </c>
       <c r="C29" t="n">
-        <v>319.3563099222018</v>
+        <v>334.2692534981419</v>
       </c>
       <c r="D29" t="n">
-        <v>311.5833055007609</v>
+        <v>318.5965517605375</v>
       </c>
       <c r="E29" t="n">
-        <v>318.9569702148438</v>
+        <v>330.2658386230469</v>
       </c>
       <c r="F29" t="n">
-        <v>7157800</v>
+        <v>10403300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B30" t="n">
-        <v>319.931043202934</v>
+        <v>329.5742822700864</v>
       </c>
       <c r="C30" t="n">
-        <v>334.2692534981419</v>
+        <v>330.2366380969722</v>
       </c>
       <c r="D30" t="n">
-        <v>318.5965517605375</v>
+        <v>322.6973986104767</v>
       </c>
       <c r="E30" t="n">
-        <v>330.2658386230469</v>
+        <v>323.8954772949219</v>
       </c>
       <c r="F30" t="n">
-        <v>10403300</v>
+        <v>7788700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B31" t="n">
-        <v>329.5742822700864</v>
+        <v>318.4699396678824</v>
       </c>
       <c r="C31" t="n">
-        <v>330.2366380969722</v>
+        <v>319.6972389495053</v>
       </c>
       <c r="D31" t="n">
-        <v>322.6973986104767</v>
+        <v>312.177470693811</v>
       </c>
       <c r="E31" t="n">
-        <v>323.8954772949219</v>
+        <v>313.5119323730469</v>
       </c>
       <c r="F31" t="n">
-        <v>7788700</v>
+        <v>8676500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B32" t="n">
-        <v>318.4699396678824</v>
+        <v>312.2846372515878</v>
       </c>
       <c r="C32" t="n">
-        <v>319.6972389495053</v>
+        <v>319.3758154633895</v>
       </c>
       <c r="D32" t="n">
-        <v>312.177470693811</v>
+        <v>311.1449703398488</v>
       </c>
       <c r="E32" t="n">
-        <v>313.5119323730469</v>
+        <v>312.2066955566406</v>
       </c>
       <c r="F32" t="n">
-        <v>8676500</v>
+        <v>6485400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B33" t="n">
-        <v>312.2846372515878</v>
+        <v>308.7877447280039</v>
       </c>
       <c r="C33" t="n">
-        <v>319.3758154633895</v>
+        <v>309.2650261221254</v>
       </c>
       <c r="D33" t="n">
-        <v>311.1449703398488</v>
+        <v>300.7614447812334</v>
       </c>
       <c r="E33" t="n">
-        <v>312.2066955566406</v>
+        <v>305.4466857910156</v>
       </c>
       <c r="F33" t="n">
-        <v>6485400</v>
+        <v>9182100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B34" t="n">
-        <v>308.7877447280039</v>
+        <v>305.7876123248052</v>
       </c>
       <c r="C34" t="n">
-        <v>309.2650261221254</v>
+        <v>306.8298669435948</v>
       </c>
       <c r="D34" t="n">
-        <v>300.7614447812334</v>
+        <v>296.6314254151897</v>
       </c>
       <c r="E34" t="n">
-        <v>305.4466857910156</v>
+        <v>301.0731506347656</v>
       </c>
       <c r="F34" t="n">
-        <v>9182100</v>
+        <v>8181100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B35" t="n">
-        <v>305.7876123248052</v>
+        <v>302.7485484827002</v>
       </c>
       <c r="C35" t="n">
-        <v>306.8298669435948</v>
+        <v>306.5863594589355</v>
       </c>
       <c r="D35" t="n">
-        <v>296.6314254151897</v>
+        <v>301.9595597530421</v>
       </c>
       <c r="E35" t="n">
-        <v>301.0731506347656</v>
+        <v>303.4596252441406</v>
       </c>
       <c r="F35" t="n">
-        <v>8181100</v>
+        <v>7337600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B36" t="n">
-        <v>302.7485484827002</v>
+        <v>303.8200730602589</v>
       </c>
       <c r="C36" t="n">
-        <v>306.5863594589355</v>
+        <v>315.4406405438549</v>
       </c>
       <c r="D36" t="n">
-        <v>301.9595597530421</v>
+        <v>303.3622621419303</v>
       </c>
       <c r="E36" t="n">
-        <v>303.4596252441406</v>
+        <v>311.6710205078125</v>
       </c>
       <c r="F36" t="n">
-        <v>7337600</v>
+        <v>8406300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B37" t="n">
-        <v>303.8200730602589</v>
+        <v>316.1127492028895</v>
       </c>
       <c r="C37" t="n">
-        <v>315.4406405438549</v>
+        <v>317.3985198428805</v>
       </c>
       <c r="D37" t="n">
-        <v>303.3622621419303</v>
+        <v>309.3819684958741</v>
       </c>
       <c r="E37" t="n">
-        <v>311.6710205078125</v>
+        <v>310.7748718261719</v>
       </c>
       <c r="F37" t="n">
-        <v>8406300</v>
+        <v>10773800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B38" t="n">
-        <v>316.1127492028895</v>
+        <v>312.791122346815</v>
       </c>
       <c r="C38" t="n">
-        <v>317.3985198428805</v>
+        <v>319.4926808974158</v>
       </c>
       <c r="D38" t="n">
-        <v>309.3819684958741</v>
+        <v>312.5768272864395</v>
       </c>
       <c r="E38" t="n">
-        <v>310.7748718261719</v>
+        <v>317.8172912597656</v>
       </c>
       <c r="F38" t="n">
-        <v>10773800</v>
+        <v>6149100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B39" t="n">
-        <v>312.791122346815</v>
+        <v>318.1192834140923</v>
       </c>
       <c r="C39" t="n">
-        <v>319.4926808974158</v>
+        <v>326.4962325236318</v>
       </c>
       <c r="D39" t="n">
-        <v>312.5768272864395</v>
+        <v>317.4374570386713</v>
       </c>
       <c r="E39" t="n">
-        <v>317.8172912597656</v>
+        <v>321.1583557128906</v>
       </c>
       <c r="F39" t="n">
-        <v>6149100</v>
+        <v>5504200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B40" t="n">
-        <v>318.1192834140923</v>
+        <v>323.067540655824</v>
       </c>
       <c r="C40" t="n">
-        <v>326.4962325236318</v>
+        <v>323.4474098298547</v>
       </c>
       <c r="D40" t="n">
-        <v>317.4374570386713</v>
+        <v>320.3596462659403</v>
       </c>
       <c r="E40" t="n">
-        <v>321.1583557128906</v>
+        <v>321.216796875</v>
       </c>
       <c r="F40" t="n">
-        <v>5504200</v>
+        <v>2464500</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B41" t="n">
-        <v>323.067540655824</v>
+        <v>318.6744960548122</v>
       </c>
       <c r="C41" t="n">
-        <v>323.4474098298547</v>
+        <v>321.4992731766471</v>
       </c>
       <c r="D41" t="n">
-        <v>320.3596462659403</v>
+        <v>314.6516105859225</v>
       </c>
       <c r="E41" t="n">
-        <v>321.216796875</v>
+        <v>314.8269348144531</v>
       </c>
       <c r="F41" t="n">
-        <v>2464500</v>
+        <v>6154600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B42" t="n">
-        <v>318.6744960548122</v>
+        <v>314.9828000615735</v>
       </c>
       <c r="C42" t="n">
-        <v>321.4992731766471</v>
+        <v>320.1745733636284</v>
       </c>
       <c r="D42" t="n">
-        <v>314.6516105859225</v>
+        <v>314.4275769247672</v>
       </c>
       <c r="E42" t="n">
-        <v>314.8269348144531</v>
+        <v>316.1224670410156</v>
       </c>
       <c r="F42" t="n">
-        <v>6154600</v>
+        <v>7978100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B43" t="n">
-        <v>314.9828000615735</v>
+        <v>317.5445892541937</v>
       </c>
       <c r="C43" t="n">
-        <v>320.1745733636284</v>
+        <v>332.5549060741021</v>
       </c>
       <c r="D43" t="n">
-        <v>314.4275769247672</v>
+        <v>316.58027624088</v>
       </c>
       <c r="E43" t="n">
-        <v>316.1224670410156</v>
+        <v>330.8989868164062</v>
       </c>
       <c r="F43" t="n">
-        <v>7978100</v>
+        <v>9770000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B44" t="n">
-        <v>317.5445892541937</v>
+        <v>330.5970181401507</v>
       </c>
       <c r="C44" t="n">
-        <v>332.5549060741021</v>
+        <v>332.4087910072381</v>
       </c>
       <c r="D44" t="n">
-        <v>316.58027624088</v>
+        <v>320.1940311163831</v>
       </c>
       <c r="E44" t="n">
-        <v>330.8989868164062</v>
+        <v>324.8403015136719</v>
       </c>
       <c r="F44" t="n">
-        <v>9770000</v>
+        <v>8061600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B45" t="n">
-        <v>330.5970181401507</v>
+        <v>326.3111546998924</v>
       </c>
       <c r="C45" t="n">
-        <v>332.4087910072381</v>
+        <v>327.0027312119329</v>
       </c>
       <c r="D45" t="n">
-        <v>320.1940311163831</v>
+        <v>319.9894943793851</v>
       </c>
       <c r="E45" t="n">
-        <v>324.8403015136719</v>
+        <v>322.3272399902344</v>
       </c>
       <c r="F45" t="n">
-        <v>8061600</v>
+        <v>5906000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B46" t="n">
-        <v>326.3111546998924</v>
+        <v>322.3272606638288</v>
       </c>
       <c r="C46" t="n">
-        <v>327.0027312119329</v>
+        <v>322.7194995812246</v>
       </c>
       <c r="D46" t="n">
-        <v>319.9894943793851</v>
+        <v>316.5710415807314</v>
       </c>
       <c r="E46" t="n">
-        <v>322.3272399902344</v>
+        <v>317.3457336425781</v>
       </c>
       <c r="F46" t="n">
-        <v>5906000</v>
+        <v>4782800</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B47" t="n">
-        <v>322.3272606638288</v>
+        <v>316.894639081939</v>
       </c>
       <c r="C47" t="n">
-        <v>322.7194995812246</v>
+        <v>320.0325801360812</v>
       </c>
       <c r="D47" t="n">
-        <v>316.5710415807314</v>
+        <v>316.2278299745985</v>
       </c>
       <c r="E47" t="n">
-        <v>317.3457336425781</v>
+        <v>317.3261108398438</v>
       </c>
       <c r="F47" t="n">
-        <v>4782800</v>
+        <v>4628400</v>
       </c>
       <c r="G47" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B48" t="n">
-        <v>316.894639081939</v>
+        <v>316.4926256697473</v>
       </c>
       <c r="C48" t="n">
-        <v>320.0325801360812</v>
+        <v>322.3566981053691</v>
       </c>
       <c r="D48" t="n">
-        <v>316.2278299745985</v>
+        <v>313.4037028528859</v>
       </c>
       <c r="E48" t="n">
-        <v>317.3261108398438</v>
+        <v>322.003662109375</v>
       </c>
       <c r="F48" t="n">
-        <v>4628400</v>
+        <v>5910500</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B49" t="n">
-        <v>316.4926256697473</v>
+        <v>323.9648592286011</v>
       </c>
       <c r="C49" t="n">
-        <v>322.3566981053691</v>
+        <v>332.6727006619286</v>
       </c>
       <c r="D49" t="n">
-        <v>313.4037028528859</v>
+        <v>322.3860878949816</v>
       </c>
       <c r="E49" t="n">
-        <v>322.003662109375</v>
+        <v>330.2015686035156</v>
       </c>
       <c r="F49" t="n">
-        <v>5910500</v>
+        <v>7513200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B50" t="n">
-        <v>323.9648592286011</v>
+        <v>330.9566703772105</v>
       </c>
       <c r="C50" t="n">
-        <v>332.6727006619286</v>
+        <v>338.2916615784552</v>
       </c>
       <c r="D50" t="n">
-        <v>322.3860878949816</v>
+        <v>330.8291859826966</v>
       </c>
       <c r="E50" t="n">
-        <v>330.2015686035156</v>
+        <v>335.2125244140625</v>
       </c>
       <c r="F50" t="n">
-        <v>7513200</v>
+        <v>7979000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B51" t="n">
-        <v>330.9566703772105</v>
+        <v>334.3789640140598</v>
       </c>
       <c r="C51" t="n">
-        <v>338.2916615784552</v>
+        <v>338.2719958722702</v>
       </c>
       <c r="D51" t="n">
-        <v>330.8291859826966</v>
+        <v>330.466330684033</v>
       </c>
       <c r="E51" t="n">
-        <v>335.2125244140625</v>
+        <v>334.4868469238281</v>
       </c>
       <c r="F51" t="n">
-        <v>7979000</v>
+        <v>6447200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B52" t="n">
-        <v>334.3789640140598</v>
+        <v>333.8200517828203</v>
       </c>
       <c r="C52" t="n">
-        <v>338.2719958722702</v>
+        <v>334.3789780492049</v>
       </c>
       <c r="D52" t="n">
-        <v>330.466330684033</v>
+        <v>324.6120879365693</v>
       </c>
       <c r="E52" t="n">
-        <v>334.4868469238281</v>
+        <v>327.7206420898438</v>
       </c>
       <c r="F52" t="n">
-        <v>6447200</v>
+        <v>6334000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B53" t="n">
-        <v>333.8200517828203</v>
+        <v>327.1420632206801</v>
       </c>
       <c r="C53" t="n">
-        <v>334.3789780492049</v>
+        <v>329.0150363516344</v>
       </c>
       <c r="D53" t="n">
-        <v>324.6120879365693</v>
+        <v>324.0727717826809</v>
       </c>
       <c r="E53" t="n">
-        <v>327.7206420898438</v>
+        <v>325.2004699707031</v>
       </c>
       <c r="F53" t="n">
-        <v>6334000</v>
+        <v>4685600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B54" t="n">
-        <v>327.1420632206801</v>
+        <v>322.552799383924</v>
       </c>
       <c r="C54" t="n">
-        <v>329.0150363516344</v>
+        <v>323.7785647692876</v>
       </c>
       <c r="D54" t="n">
-        <v>324.0727717826809</v>
+        <v>318.2773440842135</v>
       </c>
       <c r="E54" t="n">
-        <v>325.2004699707031</v>
+        <v>321.7781372070312</v>
       </c>
       <c r="F54" t="n">
-        <v>4685600</v>
+        <v>6354900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B55" t="n">
-        <v>322.552799383924</v>
+        <v>321.6996588106788</v>
       </c>
       <c r="C55" t="n">
-        <v>323.7785647692876</v>
+        <v>328.112871433911</v>
       </c>
       <c r="D55" t="n">
-        <v>318.2773440842135</v>
+        <v>319.7482499702252</v>
       </c>
       <c r="E55" t="n">
-        <v>321.7781372070312</v>
+        <v>321.0720825195312</v>
       </c>
       <c r="F55" t="n">
-        <v>6354900</v>
+        <v>10553000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B56" t="n">
-        <v>321.6996588106788</v>
+        <v>316.6397026430911</v>
       </c>
       <c r="C56" t="n">
-        <v>328.112871433911</v>
+        <v>323.4059214629105</v>
       </c>
       <c r="D56" t="n">
-        <v>319.7482499702252</v>
+        <v>315.4139372798661</v>
       </c>
       <c r="E56" t="n">
-        <v>321.0720825195312</v>
+        <v>318.8558959960938</v>
       </c>
       <c r="F56" t="n">
-        <v>10553000</v>
+        <v>7872400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B57" t="n">
-        <v>316.6397026430911</v>
+        <v>317.7183603265456</v>
       </c>
       <c r="C57" t="n">
-        <v>323.4059214629105</v>
+        <v>321.4446748044559</v>
       </c>
       <c r="D57" t="n">
-        <v>315.4139372798661</v>
+        <v>317.4830229692616</v>
       </c>
       <c r="E57" t="n">
-        <v>318.8558959960938</v>
+        <v>318.5028381347656</v>
       </c>
       <c r="F57" t="n">
-        <v>7872400</v>
+        <v>4463300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B58" t="n">
-        <v>317.7183603265456</v>
+        <v>318.8951108888525</v>
       </c>
       <c r="C58" t="n">
-        <v>321.4446748044559</v>
+        <v>322.6116097139714</v>
       </c>
       <c r="D58" t="n">
-        <v>317.4830229692616</v>
+        <v>317.8458486148664</v>
       </c>
       <c r="E58" t="n">
-        <v>318.5028381347656</v>
+        <v>321.2289428710938</v>
       </c>
       <c r="F58" t="n">
-        <v>4463300</v>
+        <v>2842700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B59" t="n">
-        <v>318.8951108888525</v>
+        <v>320.856335890976</v>
       </c>
       <c r="C59" t="n">
-        <v>322.6116097139714</v>
+        <v>325.4554096762092</v>
       </c>
       <c r="D59" t="n">
-        <v>317.8458486148664</v>
+        <v>319.9345579941973</v>
       </c>
       <c r="E59" t="n">
-        <v>321.2289428710938</v>
+        <v>325.3965454101562</v>
       </c>
       <c r="F59" t="n">
-        <v>2842700</v>
+        <v>4359300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>320.856335890976</v>
+        <v>324.4747973847736</v>
       </c>
       <c r="C60" t="n">
-        <v>325.4554096762092</v>
+        <v>327.7696401358382</v>
       </c>
       <c r="D60" t="n">
-        <v>319.9345579941973</v>
+        <v>321.9153838853659</v>
       </c>
       <c r="E60" t="n">
-        <v>325.3965454101562</v>
+        <v>322.5625915527344</v>
       </c>
       <c r="F60" t="n">
-        <v>4359300</v>
+        <v>4346800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B61" t="n">
-        <v>324.4747973847736</v>
+        <v>323.3373036254844</v>
       </c>
       <c r="C61" t="n">
-        <v>327.7696401358382</v>
+        <v>329.6328178168744</v>
       </c>
       <c r="D61" t="n">
-        <v>321.9153838853659</v>
+        <v>323.1215677229996</v>
       </c>
       <c r="E61" t="n">
-        <v>322.5625915527344</v>
+        <v>325.7201843261719</v>
       </c>
       <c r="F61" t="n">
-        <v>4346800</v>
+        <v>4432500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>323.3373036254844</v>
+        <v>325.8770745510859</v>
       </c>
       <c r="C62" t="n">
-        <v>329.6328178168744</v>
+        <v>326.8674725874873</v>
       </c>
       <c r="D62" t="n">
-        <v>323.1215677229996</v>
+        <v>323.484378234348</v>
       </c>
       <c r="E62" t="n">
-        <v>325.7201843261719</v>
+        <v>323.7098999023438</v>
       </c>
       <c r="F62" t="n">
-        <v>4432500</v>
+        <v>4285200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B63" t="n">
-        <v>325.8770745510859</v>
+        <v>324.4845927435845</v>
       </c>
       <c r="C63" t="n">
-        <v>326.8674725874873</v>
+        <v>333.6631391122548</v>
       </c>
       <c r="D63" t="n">
-        <v>323.484378234348</v>
+        <v>321.1505170252981</v>
       </c>
       <c r="E63" t="n">
-        <v>323.7098999023438</v>
+        <v>329.8779602050781</v>
       </c>
       <c r="F63" t="n">
-        <v>4285200</v>
+        <v>6863600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B64" t="n">
-        <v>324.4845927435845</v>
+        <v>328.9464075107404</v>
       </c>
       <c r="C64" t="n">
-        <v>333.6631391122548</v>
+        <v>340.2136332445062</v>
       </c>
       <c r="D64" t="n">
-        <v>321.1505170252981</v>
+        <v>327.377421847917</v>
       </c>
       <c r="E64" t="n">
-        <v>329.8779602050781</v>
+        <v>335.3890075683594</v>
       </c>
       <c r="F64" t="n">
-        <v>6863600</v>
+        <v>7956600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B65" t="n">
-        <v>328.9464075107404</v>
+        <v>341.5962793505171</v>
       </c>
       <c r="C65" t="n">
-        <v>340.2136332445062</v>
+        <v>345.7736671379334</v>
       </c>
       <c r="D65" t="n">
-        <v>327.377421847917</v>
+        <v>338.4288910460567</v>
       </c>
       <c r="E65" t="n">
-        <v>335.3890075683594</v>
+        <v>342.2042541503906</v>
       </c>
       <c r="F65" t="n">
-        <v>7956600</v>
+        <v>9441900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B66" t="n">
-        <v>341.5962793505171</v>
+        <v>342.2140819842231</v>
       </c>
       <c r="C66" t="n">
-        <v>345.7736671379334</v>
+        <v>343.3221487155281</v>
       </c>
       <c r="D66" t="n">
-        <v>338.4288910460567</v>
+        <v>331.4861813179077</v>
       </c>
       <c r="E66" t="n">
-        <v>342.2042541503906</v>
+        <v>335.0752258300781</v>
       </c>
       <c r="F66" t="n">
-        <v>9441900</v>
+        <v>7461400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B67" t="n">
-        <v>342.2140819842231</v>
+        <v>334.3985942399352</v>
       </c>
       <c r="C67" t="n">
-        <v>343.3221487155281</v>
+        <v>341.1549971070486</v>
       </c>
       <c r="D67" t="n">
-        <v>331.4861813179077</v>
+        <v>334.1926441199842</v>
       </c>
       <c r="E67" t="n">
-        <v>335.0752258300781</v>
+        <v>340.1253662109375</v>
       </c>
       <c r="F67" t="n">
-        <v>7461400</v>
+        <v>5059300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B68" t="n">
-        <v>334.3985942399352</v>
+        <v>340.5176266555306</v>
       </c>
       <c r="C68" t="n">
-        <v>341.1549971070486</v>
+        <v>342.2925325530242</v>
       </c>
       <c r="D68" t="n">
-        <v>334.1926441199842</v>
+        <v>335.840116682576</v>
       </c>
       <c r="E68" t="n">
-        <v>340.1253662109375</v>
+        <v>337.31103515625</v>
       </c>
       <c r="F68" t="n">
-        <v>5059300</v>
+        <v>4129100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B69" t="n">
-        <v>340.5176266555306</v>
+        <v>334.8006554373331</v>
       </c>
       <c r="C69" t="n">
-        <v>342.2925325530242</v>
+        <v>336.0067893806199</v>
       </c>
       <c r="D69" t="n">
-        <v>335.840116682576</v>
+        <v>327.465664861477</v>
       </c>
       <c r="E69" t="n">
-        <v>337.31103515625</v>
+        <v>333.9082946777344</v>
       </c>
       <c r="F69" t="n">
-        <v>4129100</v>
+        <v>7146400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B70" t="n">
-        <v>334.8006554373331</v>
+        <v>334.8790829701986</v>
       </c>
       <c r="C70" t="n">
-        <v>336.0067893806199</v>
+        <v>335.2124875436862</v>
       </c>
       <c r="D70" t="n">
-        <v>327.465664861477</v>
+        <v>326.3967930031341</v>
       </c>
       <c r="E70" t="n">
-        <v>333.9082946777344</v>
+        <v>327.4558410644531</v>
       </c>
       <c r="F70" t="n">
-        <v>7146400</v>
+        <v>5605900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B71" t="n">
-        <v>334.8790829701986</v>
+        <v>328.8679359740775</v>
       </c>
       <c r="C71" t="n">
-        <v>335.2124875436862</v>
+        <v>333.5160286109023</v>
       </c>
       <c r="D71" t="n">
-        <v>326.3967930031341</v>
+        <v>327.6225691502204</v>
       </c>
       <c r="E71" t="n">
-        <v>327.4558410644531</v>
+        <v>328.4658813476562</v>
       </c>
       <c r="F71" t="n">
-        <v>5605900</v>
+        <v>5740900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B72" t="n">
-        <v>328.8679359740775</v>
+        <v>328.7012542904392</v>
       </c>
       <c r="C72" t="n">
-        <v>333.5160286109023</v>
+        <v>332.8688565573256</v>
       </c>
       <c r="D72" t="n">
-        <v>327.6225691502204</v>
+        <v>321.6996681176321</v>
       </c>
       <c r="E72" t="n">
-        <v>328.4658813476562</v>
+        <v>332.3883361816406</v>
       </c>
       <c r="F72" t="n">
-        <v>5740900</v>
+        <v>6943500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B73" t="n">
-        <v>328.7012542904392</v>
+        <v>328.3678119481101</v>
       </c>
       <c r="C73" t="n">
-        <v>332.8688565573256</v>
+        <v>329.6818587310364</v>
       </c>
       <c r="D73" t="n">
-        <v>321.6996681176321</v>
+        <v>324.0237067533218</v>
       </c>
       <c r="E73" t="n">
-        <v>332.3883361816406</v>
+        <v>324.6022644042969</v>
       </c>
       <c r="F73" t="n">
-        <v>6943500</v>
+        <v>8039100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B74" t="n">
-        <v>328.3678119481101</v>
+        <v>321.0524395601062</v>
       </c>
       <c r="C74" t="n">
-        <v>329.6818587310364</v>
+        <v>333.3003067174855</v>
       </c>
       <c r="D74" t="n">
-        <v>324.0237067533218</v>
+        <v>320.1698945343209</v>
       </c>
       <c r="E74" t="n">
-        <v>324.6022644042969</v>
+        <v>331.8685913085938</v>
       </c>
       <c r="F74" t="n">
-        <v>8039100</v>
+        <v>7596500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B75" t="n">
-        <v>321.0524395601062</v>
+        <v>332.8492030913102</v>
       </c>
       <c r="C75" t="n">
-        <v>333.3003067174855</v>
+        <v>341.3314929222494</v>
       </c>
       <c r="D75" t="n">
-        <v>320.1698945343209</v>
+        <v>332.1235596151242</v>
       </c>
       <c r="E75" t="n">
-        <v>331.8685913085938</v>
+        <v>341.0079040527344</v>
       </c>
       <c r="F75" t="n">
-        <v>7596500</v>
+        <v>8933300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B76" t="n">
-        <v>332.8492030913102</v>
+        <v>340.4489839349073</v>
       </c>
       <c r="C76" t="n">
-        <v>341.3314929222494</v>
+        <v>348.0683609450301</v>
       </c>
       <c r="D76" t="n">
-        <v>332.1235596151242</v>
+        <v>340.0469292856779</v>
       </c>
       <c r="E76" t="n">
-        <v>341.0079040527344</v>
+        <v>347.59765625</v>
       </c>
       <c r="F76" t="n">
-        <v>8933300</v>
+        <v>7491400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B77" t="n">
-        <v>340.4489839349073</v>
+        <v>347.4112823812074</v>
       </c>
       <c r="C77" t="n">
-        <v>348.0683609450301</v>
+        <v>350.9316765208364</v>
       </c>
       <c r="D77" t="n">
-        <v>340.0469292856779</v>
+        <v>346.1462842881223</v>
       </c>
       <c r="E77" t="n">
-        <v>347.59765625</v>
+        <v>349.3529052734375</v>
       </c>
       <c r="F77" t="n">
-        <v>7491400</v>
+        <v>9082200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B78" t="n">
-        <v>347.4112823812074</v>
+        <v>347.0876909760341</v>
       </c>
       <c r="C78" t="n">
-        <v>350.9316765208364</v>
+        <v>347.9114016111286</v>
       </c>
       <c r="D78" t="n">
-        <v>346.1462842881223</v>
+        <v>340.5371789096768</v>
       </c>
       <c r="E78" t="n">
-        <v>349.3529052734375</v>
+        <v>344.8224792480469</v>
       </c>
       <c r="F78" t="n">
-        <v>9082200</v>
+        <v>10399500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B79" t="n">
-        <v>347.0876909760341</v>
+        <v>288.2705746047087</v>
       </c>
       <c r="C79" t="n">
-        <v>347.9114016111286</v>
+        <v>293.6933589672342</v>
       </c>
       <c r="D79" t="n">
-        <v>340.5371789096768</v>
+        <v>274.9636596388997</v>
       </c>
       <c r="E79" t="n">
-        <v>344.8224792480469</v>
+        <v>277.2190856933594</v>
       </c>
       <c r="F79" t="n">
-        <v>10399500</v>
+        <v>65836900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B80" t="n">
-        <v>288.2705746047087</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="C80" t="n">
-        <v>293.6933589672342</v>
+        <v>289.2217870569602</v>
       </c>
       <c r="D80" t="n">
-        <v>274.9636596388997</v>
+        <v>278.2193161239855</v>
       </c>
       <c r="E80" t="n">
-        <v>277.2190856933594</v>
+        <v>288.3196105957031</v>
       </c>
       <c r="F80" t="n">
-        <v>65836900</v>
+        <v>23396900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B81" t="n">
-        <v>278.2193161239855</v>
+        <v>288.6235657000577</v>
       </c>
       <c r="C81" t="n">
-        <v>289.2217870569602</v>
+        <v>289.8689623036692</v>
       </c>
       <c r="D81" t="n">
-        <v>278.2193161239855</v>
+        <v>283.6126518953886</v>
       </c>
       <c r="E81" t="n">
-        <v>288.3196105957031</v>
+        <v>286.6231384277344</v>
       </c>
       <c r="F81" t="n">
-        <v>23396900</v>
+        <v>13456400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B82" t="n">
-        <v>288.6235657000577</v>
+        <v>286.4368439245325</v>
       </c>
       <c r="C82" t="n">
-        <v>289.8689623036692</v>
+        <v>287.2703703213834</v>
       </c>
       <c r="D82" t="n">
-        <v>283.6126518953886</v>
+        <v>279.1803192669512</v>
       </c>
       <c r="E82" t="n">
-        <v>286.6231384277344</v>
+        <v>281.3670654296875</v>
       </c>
       <c r="F82" t="n">
-        <v>13456400</v>
+        <v>12022200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B83" t="n">
-        <v>286.4368439245325</v>
+        <v>280.4747261855329</v>
       </c>
       <c r="C83" t="n">
-        <v>287.2703703213834</v>
+        <v>284.7698129535399</v>
       </c>
       <c r="D83" t="n">
-        <v>279.1803192669512</v>
+        <v>276.8072456694325</v>
       </c>
       <c r="E83" t="n">
-        <v>281.3670654296875</v>
+        <v>280.0530700683594</v>
       </c>
       <c r="F83" t="n">
-        <v>12022200</v>
+        <v>8664200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B84" t="n">
-        <v>280.4747261855329</v>
+        <v>279.1803171568922</v>
       </c>
       <c r="C84" t="n">
-        <v>284.7698129535399</v>
+        <v>282.5045770944785</v>
       </c>
       <c r="D84" t="n">
-        <v>276.8072456694325</v>
+        <v>273.1985764978856</v>
       </c>
       <c r="E84" t="n">
-        <v>280.0530700683594</v>
+        <v>278.6703796386719</v>
       </c>
       <c r="F84" t="n">
-        <v>8664200</v>
+        <v>10809100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B85" t="n">
-        <v>279.1803171568922</v>
+        <v>276.5424507136568</v>
       </c>
       <c r="C85" t="n">
-        <v>282.5045770944785</v>
+        <v>278.9841654678224</v>
       </c>
       <c r="D85" t="n">
-        <v>273.1985764978856</v>
+        <v>268.7367562069888</v>
       </c>
       <c r="E85" t="n">
-        <v>278.6703796386719</v>
+        <v>270.5705261230469</v>
       </c>
       <c r="F85" t="n">
-        <v>10809100</v>
+        <v>12944100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B86" t="n">
-        <v>276.5424507136568</v>
+        <v>268.9721491110363</v>
       </c>
       <c r="C86" t="n">
-        <v>278.9841654678224</v>
+        <v>271.5217470095316</v>
       </c>
       <c r="D86" t="n">
-        <v>268.7367562069888</v>
+        <v>261.127250916227</v>
       </c>
       <c r="E86" t="n">
-        <v>270.5705261230469</v>
+        <v>263.3434143066406</v>
       </c>
       <c r="F86" t="n">
-        <v>12944100</v>
+        <v>13035300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B87" t="n">
-        <v>268.9721491110363</v>
+        <v>261.882308928914</v>
       </c>
       <c r="C87" t="n">
-        <v>271.5217470095316</v>
+        <v>272.423890770905</v>
       </c>
       <c r="D87" t="n">
-        <v>261.127250916227</v>
+        <v>261.244916942255</v>
       </c>
       <c r="E87" t="n">
-        <v>263.3434143066406</v>
+        <v>271.286376953125</v>
       </c>
       <c r="F87" t="n">
-        <v>13035300</v>
+        <v>9572800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B88" t="n">
-        <v>261.882308928914</v>
+        <v>268.8348608333229</v>
       </c>
       <c r="C88" t="n">
-        <v>272.423890770905</v>
+        <v>274.7479519102809</v>
       </c>
       <c r="D88" t="n">
-        <v>261.244916942255</v>
+        <v>268.0209657772727</v>
       </c>
       <c r="E88" t="n">
-        <v>271.286376953125</v>
+        <v>270.3548278808594</v>
       </c>
       <c r="F88" t="n">
-        <v>9572800</v>
+        <v>10371600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B89" t="n">
-        <v>268.8348608333229</v>
+        <v>272.1395338130845</v>
       </c>
       <c r="C89" t="n">
-        <v>274.7479519102809</v>
+        <v>274.0713413766361</v>
       </c>
       <c r="D89" t="n">
-        <v>268.0209657772727</v>
+        <v>267.3639563652268</v>
       </c>
       <c r="E89" t="n">
-        <v>270.3548278808594</v>
+        <v>267.9229125976562</v>
       </c>
       <c r="F89" t="n">
-        <v>10371600</v>
+        <v>7284700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B90" t="n">
-        <v>272.1395338130845</v>
+        <v>267.1580010860985</v>
       </c>
       <c r="C90" t="n">
-        <v>274.0713413766361</v>
+        <v>274.2674398268017</v>
       </c>
       <c r="D90" t="n">
-        <v>267.3639563652268</v>
+        <v>264.5691704078053</v>
       </c>
       <c r="E90" t="n">
-        <v>267.9229125976562</v>
+        <v>273.5025634765625</v>
       </c>
       <c r="F90" t="n">
-        <v>7284700</v>
+        <v>6333100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B91" t="n">
-        <v>267.1580010860985</v>
+        <v>272.7671258575986</v>
       </c>
       <c r="C91" t="n">
-        <v>274.2674398268017</v>
+        <v>280.7591102609402</v>
       </c>
       <c r="D91" t="n">
-        <v>264.5691704078053</v>
+        <v>270.4626809260317</v>
       </c>
       <c r="E91" t="n">
-        <v>273.5025634765625</v>
+        <v>278.8567199707031</v>
       </c>
       <c r="F91" t="n">
-        <v>6333100</v>
+        <v>12336900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B92" t="n">
-        <v>272.7671258575986</v>
+        <v>280.0922508710514</v>
       </c>
       <c r="C92" t="n">
-        <v>280.7591102609402</v>
+        <v>287.7704307745099</v>
       </c>
       <c r="D92" t="n">
-        <v>270.4626809260317</v>
+        <v>278.9939700602999</v>
       </c>
       <c r="E92" t="n">
-        <v>278.8567199707031</v>
+        <v>287.5056762695312</v>
       </c>
       <c r="F92" t="n">
-        <v>12336900</v>
+        <v>10281900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B93" t="n">
-        <v>280.0922508710514</v>
+        <v>288.3000088357305</v>
       </c>
       <c r="C93" t="n">
-        <v>287.7704307745099</v>
+        <v>288.5255604322975</v>
       </c>
       <c r="D93" t="n">
-        <v>278.9939700602999</v>
+        <v>282.7497397683958</v>
       </c>
       <c r="E93" t="n">
-        <v>287.5056762695312</v>
+        <v>283.48519897460